--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1805,30 +1805,127 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>김해시</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>경남 김해시</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>2027. 1. ~ 2027. 12.</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
+김해시 제2026-4325호
+장유도서관 2027년 평생학습강좌 교육강사 채용 공고묶음 개체입니다.
+장유도서관 2027년 평생학습강좌 교육강사 채용 공고
+장유도서관 2027년 평생학습강좌 운영을 위하여 다음과 같이 강사를 채용하오니 전문 강사분들의 많은 관심과 지원을 바랍니다.2026년 9월 30일장 유 도 서 관 장
+장유도서관 2027년 평생학습강좌 운영을 위하여 다음과 같이 강사를 채용하오니 전문 강사분들의 많은 관심과 지원을 바랍니다.
+2026년 9월 30일
+장 유 도 서 관 장
+1. 모집 개요
+○ (모집대상) 2027년 장유도서관 평생학습강좌 교육강사
+○ (모집인원) 31강좌 30명(성인강좌 20, 초등강좌 8, 유아강좌 3)
+분야별모집강좌강의요일 및 시간모집인원비 고계31강좌30명성 인생활체육(4)화 10:00~11:501명수 10:00~11:501명목 10:00~11:501명목 19:00~20:501명야간미 술(5)화 10:00~11:501명화 14:00~15:501명목 10:00~11:501명금 19:00~20:501명야간수 19:00~20:501명비대면어 학(3)화 10:00~11:501명수 10:00~11:501명목 10:00~11:501명음 악(4)화 10:00~11:501명금 10:00~11:501명화 19:00~20:501명야간수 19:00~20:501명야간분야별
+모집강좌
+강의요일 및 시간
+모집인원비 고계
+31강좌30명성 인
+생활체육(4)
+화 10:00~11:501명
+수 10:00~11:501명
+목 10:00~11:501명
+목 19:00~20:501명야간
+미 술(5)
+화 10:00~11:501명
+화 14:00~15:501명
+목 10:00~11:501명
+금 19:00~20:501명야간
+수 19:00~20:501명비대면
+어 학(3)
+화 10:00~11:501명
+수 10:00~11:501명
+목 10:00~11:501명
+음 악(4)
+화 10:00~11:501명
+금 10:00~11:501명
+화 19:00~20:501명야간
+수 19:00~20:501명야간
+성 인인문교양(4)목 10:00~11:501명금 10:00~11:501명화, 수 19:00~20:50中 택11명야간목 19:00~20:501명비대면초 등음 악(2)토 10:00~10:501명토 11:00~11:50미 술(1)금 17:00~17:501명체험·놀이(2)목 16:00~16:501명금 16:00~16:501명학 습(3)토 10:00~10:501명토 10:00~10:501명비대면토 11:00~11:501명비대면유 아체험·놀이(2)목 17:00~17:501명금 17:00~17:501명학 습(1)토 11:00~11:501명성 인
+인문교양(4)
+목 10:00~11:501명
+금 10:00~11:501명
+화, 수 19:00~20:50
+中 택11명야간
+목 19:00~20:501명비대면초 등
+음 악(2)
+토 10:00~10:501명
+토 11:00~11:50
+미 술(1)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>모집 분야 수업 내용</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>8046</v>
+      </c>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -1883,15 +1980,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -1901,40 +1998,40 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>금빛초등학교 계약제교원(전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>금빛초등학교</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>경남 진주시</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>2026. 금빛초등학교 계약제교원(전일제강사) 채용 공고
 1. 전형 방법
@@ -1952,51 +2049,51 @@
 ◦ 최종합격자 발표 : 2026. 10. 3.(금) 13:00 이후(합격자에게 개별 통보)</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814445</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>한일여고 방과후학교(금융) 외부강사 모집공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>한일여자고등학교</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>2026년 한일여고 방과후학교(금융) 외부강사 모집공고
 1. 모집분야: 금융전문가 과정반(펀드투자권유대행인 시험대비) 1명
@@ -2006,53 +2103,53 @@
 기타 사항은 붙임의 공고문은 참고하세요.</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814450</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>충무공초 돌봄교실 특기적성 프로그램 개인위탁 외부강사 모집</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>충무공초등학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>충무공초등학교 돌봄교실 특기적성 프로그램을 운영할 역량 있는 외부 강사를 모집하오니 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집분야
@@ -2066,51 +2163,51 @@
 ※기타 세부사항은 첨부파일을 확인하여 주십시오.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814604</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>가람초 계약제교원(학교폭력 수업경감 시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>가람초등학교</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>가람초등학교에서는 계약제교원(학교폭력 수업경감 시간강사)을 아래와 같이 채용하고자 합니다.
 1. 모집 분야 및 인원: 과학(1명)
@@ -2121,53 +2218,53 @@
 ※ 자세한 사항은 첨부 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n">
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814491</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>경운초등학교 돌봄교실 특기적성 외부강사 공고</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>경운초등학교</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>2026학년도 경운초등학교에 근무할 외부강사를 다음과 같이 채용 공고합니다.
 1. 채용과목 : 돌봄교실 특기적성 프로그램 : 공예놀이
@@ -2178,51 +2275,51 @@
 6. 최종 합격자 발표일 : 2026. 10. 8.(목) 11:00이후 개별통보* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814577</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>방과후학교 리코더 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>수양초등학교</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>수양초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 개인 위탁 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원
@@ -2240,53 +2337,53 @@
 ※ 자세한 내용은 첨부파일을 참고해 주시기 바랍다.</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n">
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814600</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 재공고(수학)</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>꽃내중학교</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집 재공고
 꽃내중학교에서는 방과후학교 운영과 관련하여 아래와 같이 2026학년도 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
@@ -2306,51 +2403,51 @@
 ※. 자세한 사항은 첨부물을 참고하십시요.</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814587</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="O29" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>화정초등학교</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
@@ -2359,72 +2456,13 @@
 * 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>내곡초등학교</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>아래와 같이 결원대체강사 채용을 공고합니다.
-1. 대상: 초등교사 1명(전일제 또는 시간제)
-2. 기간: 2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>초등교사 1명(전일제 또는 시간제)</t>
-        </is>
-      </c>
+      <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
         </is>
       </c>
       <c r="L30" s="5" t="n"/>
@@ -2436,33 +2474,92 @@
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>내곡초등학교</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명(전일제 또는 시간제)
+2. 기간: 2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명(전일제 또는 시간제)</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -2473,51 +2570,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -2569,47 +2666,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -2621,51 +2718,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -2682,23 +2779,23 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>초등 특수 전일제강사 채용 공고</t>
+          <t>대청중학교 결원대체강사 (특수) 2차 채용 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>외간초등학교</t>
+          <t>대청중학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -640,221 +640,15 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026. 10. 7.(수)~2026. 10. 14.(수)(5일간)</t>
+          <t>2026.10.16.(금)~2026.10.19.(월) (2일)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>전일제강사(초등특수)
-채용 기간: 2026. 10. 7.(수)~2026. 10. 14.(수)(5일간)
-공고 및 접수: 2026.9.23.(수)~9.30.(수)14:00까지
-1차 (서류 심사)  2026.9.30.(수) 15:00
-2차 (면접 심사)2026.10.1.(목) 14:30
-최종 합격자 발표2026.10.2.(금) 10:00 이후 예정</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814487</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>거창중학교 시간강사(체육) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>거창중학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.6.∼2027.1.6. (주 5시간, 14주, 총 40시간 예상)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 거창중학교에 근무할 학교폭력 업무담당자 수업경감 시간강사를 다음과 같이 채용 공고합니다.
-1. 구분:  시간강사
-2. 과목: 체육
-3. 기간: 2026.10.6.∼2027.1.6. (주 5시간, 14주, 총 40시간 예상)
-4. 비고: 학교폭력 업무담당자 수업경감
-5. 수당: 1시간당 25000원
-6. 서류접수 및 전형일정
-가. 원서접수
-◦ 접수기간: 2026. 9. 23.(수) ~ 2026. 9. 30.(수) 15:00
-◦ 접수방법
-- 전자우편(주소: [이메일], 마감시간 15:00 전 도착분(스캔 자료), 면접시 원본 제출)
-- 거창중학교 교무실 직접 방문 제출
-※ 면접 장소 및 대상자 개별 안내
-나. 서류 심사: 2026. 10. 1.(목) 15:00(예정) 합격자에게 개별 통보
-다. 면접 심사: 2026. 10. 2.(금) 10:00(예정)
-라. 합격 대상자 결정 및 통지: 2026. 10. 2.(금) 11:00(예정)
-*자세한 사항은 첨부파일을 참조하여 주시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814525</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>금송중학교 시간강사(특수) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>금송중학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남 양산시</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.21.~2026.11.11.(16일간, 총34시간)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>금송중학교 시간 강사 채용 공고
-2026학년도 금송중학교에 근무할 시간강사 채용을 다음과 같이 공고합니다.
-1. 채용내용 및 응모자격
-가. 채용과목: 특수
-나. 채용기간: 2026.10.21.~2026.11.11.(16일간, 총34시간)
-다. 채용인원: 1명
-라. 응모자격
-1)1순위: 동일 학교급 및 과목 자격증 소지자
-2)2순위: 다른 학교급 또는 유사과목 자격증 소지자
-2. 전형방법:
-가. 1차시험: 서류전형
-나. 2차시험: 심층면접전형
-3. 제출서류
-가. 응시자 제출 서류
-◦ 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
-◦ 자기소개서 1부.(붙임서식)
-◦ 개인정보 수집 및 활용 동의서 1부.(붙임서식)
-나. 최종합격자 제출 서류
-◦ 교사 자격증 사본 또는 자격 인정 조서 1부.
-◦ 졸업증명서 사본 1부.(원본지참)
-◦ 범죄경력 조회 동의서 (장애인학대관련범죄 등 경력조회 포함) 1부.
-◦ 개인정보 수집 및 활용 동의서 1부.
-◦ 행정정보 공동이용 사전동의서 1부.
-◦ 공무원채용신체검사서(유효기간 1년) 또는 일반 건강검진 결과서 1부.
-◦ 잠복결핵감염검진 확인서 1부.
-◦ 마약류 투약 또는 중독 여부 판별 결과 통보서(또는 의사 진단서) 1부.
-◦ 가족 채용 제한 여부 확인서 1부.
-◦ 병적증명서 또는 주민등록 초본 1부.
-4. 서류접수 및 전형일정
-가. 원서접수
-◦ 접수기간: 2026.9.24.(목) ~ 2026.9.30.(수)
-◦ 접수장소: 금송중학교 전자우편
-◦ 접수방법: 전자우편(주소: [이메일], 스캔본 1부로 병합하여 제출,
-면접 시 원본 제출, 2026.9.30.(수) 발송분까지 유효)
-나. 1차: 서류전형 합격자 발표(개별 통보) 예정일: 2026.10.1.(목) 12:00 이후
-다. 2차: 면접(서류심사 합격자에 한함) 예정일: 2026.10.6.(화) 11:40
-◦ 일시 및 장소는 학교 내부사정에 의해 변경 가능
-5. 합격자 발표
-◦ 최종합격자 발표: 2026.10.8.(목) 12:00 이후 개별연락
-6. 유의사항
-◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 우선 임용될 수 있습니다.
-◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 최종합격 후 확인이 불가능한 서류만 제출
-◦ 상기 일정은 진행 상황에 따라 변경될 수 있으며, 변경 시 별도 통보합니다.
-◦ 기재사항이 사실과 다르거나 허위로 작성된 경우는 합격을 취소합니다.
-◦ 제출서류의 기재 착오, 누락, 서류 미제출, 연락불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.
-◦ 제출한 서류(전자우편 등 온라인으로 제출된 경우 제외)는 「채용 절차의 공정화에 관한 법률」제11조에 따라 합격자 발표가 끝난 후 불합격자의 채용서류 반환 청구 시(채용서류 반환청구서 작성 필수) 반환합니다.
-◦ 청구 기간 내 채용서류 반환 청구가 없을 시 ｢개인정보 보호법｣제21조에 따라 폐기합니다.
-◦ 최종합격자로 발표된 이후에도 결격사유가 있는 자는 합격을 취소합니다.
-◦ 기타 자세한 사항은 금송중학교(☎781-0352)로 문의하시길 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814476</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>대청중학교 결원대체강사 (특수) 2차 채용 공고</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>대청중학교</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.16.(금)~2026.10.19.(월) (2일)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목 : 특수 (시간제)
 2. 채용기간 : 2026.10.16.(금)~2026.10.19.(월) (2일)
@@ -868,47 +662,47 @@
 감사합니다.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814570</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>학교보건시간강사 채용 재공고(호암초)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>호암초등학교</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026.10.6. ~ 2026.12.30.(시간제, 주 15시간 미만 월 59시간 이하, 예산소진시까지)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>2026. 호암초등학교 학교보건시간강사를 다음과 같이 채용 모집을 재공고합니다.
 가. 채용 분야: 시간강사
@@ -921,49 +715,49 @@
 호암초등학교장</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814578</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>학교폭력 업무담당자 수업경감 시간강사 채용</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>신문초등학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>주당 4시간(시간 배분에 따라 요일 협의 가능)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>신문초등학교에서 학교폭력 업무담당자 수업경감 시간강사를 다음과 같이 채용하고자 하오니 관심 있는 분들의 많은 지원 바랍니다.
 1. 채용 과목 및 인원
@@ -980,49 +774,49 @@
 기타 자세한 사항은 첨부 파일을 참고해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814590</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>무지개초등학교 돌봄교실 특기·적성 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>무지개초등학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 16일 ~ 2027년 2월 26일</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026학년도 무지개초등학교 돌봄교실  특기·적성 프로그램 개인위탁 외부강사 모집 공고
 1. 모집강좌: 클레이(1명),영어(1명),책놀이(1명)
@@ -1039,49 +833,49 @@
 ※세부사항은 첨부파일을 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814532</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>가좌초등학교 시간제 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>가좌초등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~2027.2.(예산소진시까지)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. 채용분야 및 응모자격
 가. 채용구분: 시간제 강사 1명
@@ -1099,52 +893,52 @@
 ※ 기타 자세한 사항은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>교원 자격증 소지자
 교원 임용에 결격 사유가 없는 자</t>
         </is>
       </c>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814622</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>교원 수업대체강사(기계) 채용 공고[3차]</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>창원공업고등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 18일 ~ 2026년 12월 24일</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>창원공업고등학교에서 교원 수업대체강사(시간제) 채용을 다음과 같이 공고[3차]합니다.
 1. 채용분야 및 모집 인원
@@ -1158,49 +952,49 @@
 궁금하신 점은 창원공업고등학교 행정실([전화번호])로 문의 바랍니다</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814571</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교 결원대체강사(진로진학상담 시간강사) 채용 공고(국어도 가능)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 11.(수)~2026. 11. 18.(수), 총 11시간</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2026학년도 삼정자중학교 결원대체강사(진로진학상담)를 다음과 같이 채용하고자 합니다.
 1. 채용과목 및 채용 내용
@@ -1224,49 +1018,49 @@
 **자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814615</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>성호초등학교 전일제강사 채용 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>성호초등학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026.10.7.~ 2026.10.21.(15일)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 공고 합니다.
 1. 채용과목 및 인원: 특수교사 1명
@@ -1277,49 +1071,49 @@
 *자세한 사항은 붙임 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2026.10.30.(총16시간)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모자격
@@ -1347,49 +1141,49 @@
 5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>교방초등학교 방과후학교 개인위탁 외부강사[티볼] 모집 공고</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>교방초등학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026.11.1. ~2027.2.16.</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>[ 2026학년도 교방초 방과후학교 개인위탁외부강사 모집 공고 ]
 교방초등학교에서는
@@ -1403,49 +1197,49 @@
 6. 모집 세부 사항: 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814603</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 수학 시간강사 채용 공고</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2026.10. 12. ~ 2026.11.18. (주당18시간)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 시간강사 채용 공고
 1. 채용내용 : 수학 1명
@@ -1459,51 +1253,51 @@
 ※ 기타 자세한 사항은 공고문을 참고 하시기 바랍니다. ※ 관심 있는 분들의 많은 지원 바랍니다</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부, 기타 구비서류(채용합격자에 한해 별도안내)</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814606</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>남양초등학교 돌봄교실 특기적성프로그램 개인 위탁 외부강사 채용 공고</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>남양초등학교</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2027. 2. 24.(수) / 금요일(13:50~14:30, 14:40~15:20, 15:30~16:10)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>2026학년도 남양초등학교 돌봄교실 특기적성 프로그램 외부강사를 아래와 같이 모집하오니
 관심있는 분들의 많은 지원 바랍니다.
@@ -1519,49 +1313,49 @@
 5. 기타 자세한 내용은 첨부파일을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814493</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>김해내동초 돌봄 프로그램(종이접기 1명) 외부강사 모집 공고문</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>김해내동초등학교</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2027.2.28.</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>2026. 김해내동초 돌봄 프로그램(종이 접기 1명)외부 강사 모집 공고를  아래와 같이 실시합니다.
 1. 모집 인원: 1명
@@ -1571,49 +1365,49 @@
 5. 기타 자세한 사항은 첨부 문서를 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814620</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>증산중학교 계약제교원(시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1627,49 +1421,49 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814584</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -1722,49 +1516,142 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단 채용정보</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>시민생활체육관 공고 제2026-18호
+시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
+시민생활체육관 프로그램 운영을 위한 우수 강사진을 공개 모집하오니
+많은 참여 바랍니다.
+2026년 9월 30일
+창원시설공단 시민생활체육관팀장Ⅰ
+모집인원 : 1명
+프로그램 : 탁구종 목모집인원
+강 습 일
+운 영 시 간배분율
+(공단:강사)
+자 격 요 건탁 구1명월~일
+09:00~22:00
+20 : 80
+‣ 전문·생활스포츠(탁구 2급)이상 소지자 또는 전국대회이상 3위 이상 입상자(해당 종목 지도 경력 6개월 이상인 자
+※ 탁구: 보조강사 1명 이상 필수 / 보조강사 자격증 필수
+※ 탁구 강습반: 월·수·금 11개반, 화·목 11개반, 토(월 4회) 2개반Ⅱ
+기본(공통)자격
+만 18세 이상인 자로서 응시자격을 충족하는 자
+해당 종목 관련 자격증 소지자 중 해당 경력 6개월 이상인 자
+아동·청소년의 성 보호에 관한 법률에 의거 성범죄의 해당자는 선발할 수 없음
+도급강사 운영계약 지침 제12조 결격사유에 해당하지 않는 자
+제12조(결격사유) 다음 각 호의 어느 하나에 해당하는 자는 도급강사로 계약할 수 없다.
+1. 피성년후견인
+2. 파산선고를 받은 자로서 복권되지 아니한 자
+3. 금고 이상의 형을 선고받고 그 집행이 끝나거나 집행을 받지 아니하기로 확정된 후 5년이 지나지
+아니한 자
+4. 금고 이상의 형을 선고받고 그 집행유예기간이 끝난 날부터 2년이 지나지 아니한 자
+5. 금고 이상의 형의 선고유예를 선고받고 그 선고유예기간 중에 있는 자
+6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 자
+7. 징계로 파면처분을 받은 날부터 5년이 지나지 아니한 자
+8. 징계로 해임처분을 받은 날부터 3년이 지나지 아니한 자
+9. 부패방지 및 국민권익위원회의 설치와 운영에 관한 법률 제82조에 따른 비위면직자 등의
+취업제한 적용을 받는 자
+10. 재직기간 중 직무와 관련하여 「형법」 제355조 및 제356조에 규정된 죄를 범한 사람
+으로서 300만원 이상의 벌금형을 선고받고 그 형이 확정된 후 2년이 지나지 아니한 사람
+11. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 규정된 죄를 범한 사람으로서 100만
+원 이상의 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람
+12. 미성년자에 대한 다음 각 목의 어느 하나에 해당하는 죄를 저질러 파면ㆍ해임되거나 형 또는 치료감
+호를 선고받아 그 형 또는 치료감호가 확정된 사람(집행유예를 선고받은 후 그 집행유예기간이 경과한
+사람을 포함한다)
+가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄
+나. 「아동ㆍ청소년의 성보호에 관한 법률」 제2조제2호에 따른 아동ㆍ청소년대상 성범죄Ⅲ
+전형일정 및 방법
+계약기간: 2026. 11. 1. ~ 12. 31.(2개월)
+※ 1. 공사 및 휴장 등으로 인해 프로그램 운영이 어려울 시 계약기간이 변경될 수 있음
+2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -1788,47 +1675,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -1879,53 +1766,53 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H19" s="5" t="n">
         <v>8046</v>
       </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -1980,15 +1867,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H20" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -1998,102 +1885,40 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>금빛초등학교 계약제교원(전일제강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>금빛초등학교</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>경남 진주시</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>2026. 금빛초등학교 계약제교원(전일제강사) 채용 공고
-1. 전형 방법
-가. 1차 전형: 서류 심사
-나. 2차 전형: 면접 심사
-2. 서류 접수 및 전형 일정
-가. 원서 접수
-◦ 접수 기간: 2026. 9. 21.(월) ~ 9. 30.(수) 13:00까지 도착분에 한함
-◦ 접수 방법 : 전자우편(주소: [이메일] 스캔파일 또는 한글 제출)
-(스캔파일 제출 후 면접시험 시 원본 제출)
-나. 1차 : 서류전형 합격자 발표(개별 문자 통지) 예정일 : 2026. 10. 1.(목) 17:00 이후
-다. 2차 : 면접(서류 심사 합격자에 한함) 예정일 : 2026. 10. 3.(금) 13:00
-◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
-3. 합격자 발표
-◦ 최종합격자 발표 : 2026. 10. 3.(금) 13:00 이후(합격자에게 개별 통보)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814445</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>한일여고 방과후학교(금융) 외부강사 모집공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>한일여자고등학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>2026년 한일여고 방과후학교(금융) 외부강사 모집공고
 1. 모집분야: 금융전문가 과정반(펀드투자권유대행인 시험대비) 1명
@@ -2103,53 +1928,53 @@
 기타 사항은 붙임의 공고문은 참고하세요.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814450</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>충무공초 돌봄교실 특기적성 프로그램 개인위탁 외부강사 모집</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>충무공초등학교</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>충무공초등학교 돌봄교실 특기적성 프로그램을 운영할 역량 있는 외부 강사를 모집하오니 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집분야
@@ -2163,51 +1988,51 @@
 ※기타 세부사항은 첨부파일을 확인하여 주십시오.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814604</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>가람초 계약제교원(학교폭력 수업경감 시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>가람초등학교</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>가람초등학교에서는 계약제교원(학교폭력 수업경감 시간강사)을 아래와 같이 채용하고자 합니다.
 1. 모집 분야 및 인원: 과학(1명)
@@ -2218,53 +2043,53 @@
 ※ 자세한 사항은 첨부 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814491</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>경운초등학교 돌봄교실 특기적성 외부강사 공고</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>경운초등학교</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>2026학년도 경운초등학교에 근무할 외부강사를 다음과 같이 채용 공고합니다.
 1. 채용과목 : 돌봄교실 특기적성 프로그램 : 공예놀이
@@ -2275,51 +2100,51 @@
 6. 최종 합격자 발표일 : 2026. 10. 8.(목) 11:00이후 개별통보* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814577</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>방과후학교 리코더 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>수양초등학교</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>수양초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 개인 위탁 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원
@@ -2337,53 +2162,53 @@
 ※ 자세한 내용은 첨부파일을 참고해 주시기 바랍다.</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n">
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814600</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 재공고(수학)</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>꽃내중학교</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집 재공고
 꽃내중학교에서는 방과후학교 운영과 관련하여 아래와 같이 2026학년도 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
@@ -2403,51 +2228,51 @@
 ※. 자세한 사항은 첨부물을 참고하십시요.</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814587</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>화정초등학교</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
@@ -2456,13 +2281,187 @@
 * 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>주동초등학교</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2026년 주동초등학교에서는 초등 1~2학년 맞춤형프로그램과 관련하여 아래와 같이 외부강사(문화, 예술, 음악, 놀이영어 등 다양한 분야 지원 가능)를 모집하오니, 유능한 강사님들의 많은 지원 바랍니다.
+1.  서류접수:  2026.  10. 1.(목) ~ 2026. 10.  7.(수) 16시까지 도착분
+2. 서류심사 결과:  2026. 10. 8.(목) 10:00~ 합격자에 한하여 개별 통보(문자)
+3. 2차 면접심사(운영능력):  2026. 10. 13.(화) 10:00~  면접일정은 합격자에게 별도 안내(문자)
+4. 최종합격자발표:  2026. 10. 14.(수) 10:00~ 최종합격자 개별 통보(문자)
+※ 학교 사정에 따라 추후 일정은 변경될 수 있습니다.
+※ 자세한 사항은 첨부파일을 확인하시기 바랍니다.
+※ 접수시간을 반드시 준수해 주시길 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814652</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>어방초등학교</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
+1. 모집 분야 및 인원: 컴퓨터 1명
+2.모집 세부 사항
+가. 공고 기간: 2026.9.30.(수)∼2026.10.8.(목) 12:00까지
+나. 접수 장소: 어방초등학교 교무실로 직접 제출(우편접수 불가)
+※ 서류 제출 시 교무실에 강사 접수 대장을 작성하시고 봉투 겉면에 프로그램명, 강사명, 연락처를 정확히 기재하여 제출
+(서류는 스템플러가 아닌 집게나 클립 사용)
+※ 공휴일, 토, 일 서류 접수 불가, 평일 16시 30분 이후 접수 불가
+※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>내곡초등학교</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명(전일제 또는 시간제)
+2. 기간: 2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명(전일제 또는 시간제)</t>
+        </is>
+      </c>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
       <c r="L30" s="5" t="n"/>
@@ -2474,19 +2473,19 @@
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
+          <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>내곡초등학교</t>
+          <t>율하중학교</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -2496,70 +2495,11 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>아래와 같이 결원대체강사 채용을 공고합니다.
-1. 대상: 초등교사 1명(전일제 또는 시간제)
-2. 기간: 2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>초등교사 1명(전일제 또는 시간제)</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>계약제 교원(시간 강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>율하중학교</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -2570,51 +2510,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr">
+      <c r="O31" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -2666,47 +2606,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -2718,51 +2658,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -2779,13 +2719,59 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
       <c r="G35" s="5" t="n"/>
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="n"/>
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
       <c r="L35" s="5" t="n"/>
@@ -2797,7 +2783,7 @@
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>대청중학교 결원대체강사 (특수) 2차 채용 공고</t>
+          <t>학교보건시간강사 채용 재공고(호암초)</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>대청중학교</t>
+          <t>호암초등학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -645,64 +645,10 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026.10.16.(금)~2026.10.19.(월) (2일)</t>
+          <t>2026.10.6. ~ 2026.12.30.(시간제, 주 15시간 미만 월 59시간 이하, 예산소진시까지)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>1. 채용과목 : 특수 (시간제)
-2. 채용기간 : 2026.10.16.(금)~2026.10.19.(월) (2일)
-3. 접수기간 : 2026.09.28.(월)~2026.10.01.(목) 09:00 도착분까지
-4. 서류전형 : 2026.10.01.(목) 11:00 이후 (합격자에게 개별 통보)
-5. 최종면접 : 2026.10.01.(목) 15:30~
-- 1인 지원시, 1차 심사 결과 적격자라고 판단 될 경우 2차 면접 심사 생략 할 수 있음
-6. 최종합격자 발표 : 2026.10.02.(금) 11:00 이후
-7. 접수방법 : [이메일]
-상세한 내용은 첨부파일 참고 바랍니다.
-감사합니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814570</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>학교보건시간강사 채용 재공고(호암초)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>호암초등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.6. ~ 2026.12.30.(시간제, 주 15시간 미만 월 59시간 이하, 예산소진시까지)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>2026. 호암초등학교 학교보건시간강사를 다음과 같이 채용 모집을 재공고합니다.
 가. 채용 분야: 시간강사
@@ -715,49 +661,49 @@
 호암초등학교장</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814578</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>학교폭력 업무담당자 수업경감 시간강사 채용</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>신문초등학교</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>주당 4시간(시간 배분에 따라 요일 협의 가능)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>신문초등학교에서 학교폭력 업무담당자 수업경감 시간강사를 다음과 같이 채용하고자 하오니 관심 있는 분들의 많은 지원 바랍니다.
 1. 채용 과목 및 인원
@@ -774,49 +720,49 @@
 기타 자세한 사항은 첨부 파일을 참고해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814590</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>무지개초등학교 돌봄교실 특기·적성 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>무지개초등학교</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 16일 ~ 2027년 2월 26일</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026학년도 무지개초등학교 돌봄교실  특기·적성 프로그램 개인위탁 외부강사 모집 공고
 1. 모집강좌: 클레이(1명),영어(1명),책놀이(1명)
@@ -833,49 +779,49 @@
 ※세부사항은 첨부파일을 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814532</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>가좌초등학교 시간제 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>가좌초등학교</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~2027.2.(예산소진시까지)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. 채용분야 및 응모자격
 가. 채용구분: 시간제 강사 1명
@@ -893,52 +839,52 @@
 ※ 기타 자세한 사항은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>교원 자격증 소지자
 교원 임용에 결격 사유가 없는 자</t>
         </is>
       </c>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814622</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>교원 수업대체강사(기계) 채용 공고[3차]</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>창원공업고등학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 18일 ~ 2026년 12월 24일</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>창원공업고등학교에서 교원 수업대체강사(시간제) 채용을 다음과 같이 공고[3차]합니다.
 1. 채용분야 및 모집 인원
@@ -952,49 +898,49 @@
 궁금하신 점은 창원공업고등학교 행정실([전화번호])로 문의 바랍니다</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814571</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교 결원대체강사(진로진학상담 시간강사) 채용 공고(국어도 가능)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 11.(수)~2026. 11. 18.(수), 총 11시간</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026학년도 삼정자중학교 결원대체강사(진로진학상담)를 다음과 같이 채용하고자 합니다.
 1. 채용과목 및 채용 내용
@@ -1018,49 +964,49 @@
 **자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814615</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>성호초등학교 전일제강사 채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>성호초등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026.10.7.~ 2026.10.21.(15일)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 공고 합니다.
 1. 채용과목 및 인원: 특수교사 1명
@@ -1071,49 +1017,49 @@
 *자세한 사항은 붙임 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2026.10.30.(총16시간)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모자격
@@ -1141,49 +1087,49 @@
 5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>교방초등학교 방과후학교 개인위탁 외부강사[티볼] 모집 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>교방초등학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026.11.1. ~2027.2.16.</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>[ 2026학년도 교방초 방과후학교 개인위탁외부강사 모집 공고 ]
 교방초등학교에서는
@@ -1197,49 +1143,49 @@
 6. 모집 세부 사항: 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814603</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 수학 시간강사 채용 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026.10. 12. ~ 2026.11.18. (주당18시간)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 시간강사 채용 공고
 1. 채용내용 : 수학 1명
@@ -1253,51 +1199,51 @@
 ※ 기타 자세한 사항은 공고문을 참고 하시기 바랍니다. ※ 관심 있는 분들의 많은 지원 바랍니다</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부, 기타 구비서류(채용합격자에 한해 별도안내)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814606</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>남양초등학교 돌봄교실 특기적성프로그램 개인 위탁 외부강사 채용 공고</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>남양초등학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2027. 2. 24.(수) / 금요일(13:50~14:30, 14:40~15:20, 15:30~16:10)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>2026학년도 남양초등학교 돌봄교실 특기적성 프로그램 외부강사를 아래와 같이 모집하오니
 관심있는 분들의 많은 지원 바랍니다.
@@ -1313,49 +1259,49 @@
 5. 기타 자세한 내용은 첨부파일을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814493</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>김해내동초 돌봄 프로그램(종이접기 1명) 외부강사 모집 공고문</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>김해내동초등학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2027.2.28.</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>2026. 김해내동초 돌봄 프로그램(종이 접기 1명)외부 강사 모집 공고를  아래와 같이 실시합니다.
 1. 모집 인원: 1명
@@ -1365,49 +1311,49 @@
 5. 기타 자세한 사항은 첨부 문서를 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814620</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>증산중학교 계약제교원(시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1421,49 +1367,49 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814584</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -1516,49 +1462,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -1609,49 +1555,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -1675,47 +1621,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -1766,53 +1712,53 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H18" s="5" t="n">
         <v>8046</v>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -1867,15 +1813,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -1885,40 +1831,40 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>한일여고 방과후학교(금융) 외부강사 모집공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>한일여자고등학교</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>2026년 한일여고 방과후학교(금융) 외부강사 모집공고
 1. 모집분야: 금융전문가 과정반(펀드투자권유대행인 시험대비) 1명
@@ -1928,53 +1874,53 @@
 기타 사항은 붙임의 공고문은 참고하세요.</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814450</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>충무공초 돌봄교실 특기적성 프로그램 개인위탁 외부강사 모집</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>충무공초등학교</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>충무공초등학교 돌봄교실 특기적성 프로그램을 운영할 역량 있는 외부 강사를 모집하오니 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집분야
@@ -1988,51 +1934,51 @@
 ※기타 세부사항은 첨부파일을 확인하여 주십시오.</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814604</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>가람초 계약제교원(학교폭력 수업경감 시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>가람초등학교</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>가람초등학교에서는 계약제교원(학교폭력 수업경감 시간강사)을 아래와 같이 채용하고자 합니다.
 1. 모집 분야 및 인원: 과학(1명)
@@ -2043,53 +1989,53 @@
 ※ 자세한 사항은 첨부 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814491</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>경운초등학교 돌봄교실 특기적성 외부강사 공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>경운초등학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>2026학년도 경운초등학교에 근무할 외부강사를 다음과 같이 채용 공고합니다.
 1. 채용과목 : 돌봄교실 특기적성 프로그램 : 공예놀이
@@ -2100,51 +2046,51 @@
 6. 최종 합격자 발표일 : 2026. 10. 8.(목) 11:00이후 개별통보* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814577</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>방과후학교 리코더 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>수양초등학교</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>수양초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 개인 위탁 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원
@@ -2162,53 +2108,53 @@
 ※ 자세한 내용은 첨부파일을 참고해 주시기 바랍다.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814600</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 재공고(수학)</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>꽃내중학교</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집 재공고
 꽃내중학교에서는 방과후학교 운영과 관련하여 아래와 같이 2026학년도 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
@@ -2228,13 +2174,66 @@
 ※. 자세한 사항은 첨부물을 참고하십시요.</t>
         </is>
       </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814587</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>화정초등학교</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
+1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
+2. 서류전형 합격자 개별 통보일 : 2026. 10. 8.(목) 14:00이후
+3. 접수방법 : 직접 방문 접수
+* 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814587</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
         </is>
       </c>
       <c r="L26" s="5" t="n"/>
@@ -2246,19 +2245,19 @@
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
+          <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>화정초등학교</t>
+          <t>주동초등학교</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -2273,59 +2272,6 @@
       </c>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
-1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
-2. 서류전형 합격자 개별 통보일 : 2026. 10. 8.(목) 14:00이후
-3. 접수방법 : 직접 방문 접수
-* 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>주동초등학교</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>2026년 주동초등학교에서는 초등 1~2학년 맞춤형프로그램과 관련하여 아래와 같이 외부강사(문화, 예술, 음악, 놀이영어 등 다양한 분야 지원 가능)를 모집하오니, 유능한 강사님들의 많은 지원 바랍니다.
 1.  서류접수:  2026.  10. 1.(목) ~ 2026. 10.  7.(수) 16시까지 도착분
@@ -2337,51 +2283,51 @@
 ※ 접수시간을 반드시 준수해 주시길 바랍니다.</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814652</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -2394,15 +2340,74 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n">
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>내곡초등학교</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명(전일제 또는 시간제)
+2. 기간: 2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명(전일제 또는 시간제)</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
       <c r="L29" s="5" t="n"/>
@@ -2414,19 +2419,19 @@
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
+          <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>내곡초등학교</t>
+          <t>율하중학교</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2436,70 +2441,11 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>아래와 같이 결원대체강사 채용을 공고합니다.
-1. 대상: 초등교사 1명(전일제 또는 시간제)
-2. 기간: 2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>초등교사 1명(전일제 또는 시간제)</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>계약제 교원(시간 강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>율하중학교</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -2510,51 +2456,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="O30" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -2606,47 +2552,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr">
+      <c r="O31" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -2658,51 +2604,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -2719,13 +2665,59 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
       <c r="L34" s="5" t="n"/>
@@ -2736,52 +2728,6 @@
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>학교보건시간강사 채용 재공고(호암초)</t>
+          <t>무지개초등학교 돌봄교실 특기·적성 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>호암초등학교</t>
+          <t>무지개초등학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -640,129 +640,15 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026.10.6. ~ 2026.12.30.(시간제, 주 15시간 미만 월 59시간 이하, 예산소진시까지)</t>
+          <t>2026년 10월 16일 ~ 2027년 2월 26일</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>2026. 호암초등학교 학교보건시간강사를 다음과 같이 채용 모집을 재공고합니다.
-가. 채용 분야: 시간강사
-나. 채용기간: 2026.10.6. ~ 2026.12.30.(시간제, 주 15시간 미만 월 59시간 이하, 예산소진시까지)
-다. 채용인원: 1명
-라. 서류접수 및 전형일정
-- 접수기간: 2026.9.28.(월)~2026.10.1.(목) 12:00까지
-- 접수방법: 전자우편 접수( [이메일] )
-*기타 자세한 사항은 첨부파일을 참고하시기 바랍니다.
-호암초등학교장</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814578</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>학교폭력 업무담당자 수업경감 시간강사 채용</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>신문초등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>주당 4시간(시간 배분에 따라 요일 협의 가능)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>신문초등학교에서 학교폭력 업무담당자 수업경감 시간강사를 다음과 같이 채용하고자 하오니 관심 있는 분들의 많은 지원 바랍니다.
-1. 채용 과목 및 인원
-가. 과목: 과학
-나. 인원: 1명
-2. 근무조건
-가. 근무시간: 주당 4시간(시간 배분에 따라 요일 협의 가능)
-나. 보수: 시간당 25,000원
-3. 서류 접수 기간 및 방법
-가. 접수 기간: 2026. 9. 29.(화)~10. 1.(수) 13:00까지
-나. 접수 장소: 전자우편 접수
-다. 전자우편: [이메일]
-라. 제출 방법: 스캔본 제출(면접 시 원본 제출)
-기타 자세한 사항은 첨부 파일을 참고해 주시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814590</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>무지개초등학교 돌봄교실 특기·적성 프로그램 개인위탁 외부강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>무지개초등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 16일 ~ 2027년 2월 26일</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026학년도 무지개초등학교 돌봄교실  특기·적성 프로그램 개인위탁 외부강사 모집 공고
 1. 모집강좌: 클레이(1명),영어(1명),책놀이(1명)
@@ -779,49 +665,49 @@
 ※세부사항은 첨부파일을 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814532</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>가좌초등학교 시간제 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>가좌초등학교</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~2027.2.(예산소진시까지)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. 채용분야 및 응모자격
 가. 채용구분: 시간제 강사 1명
@@ -839,52 +725,52 @@
 ※ 기타 자세한 사항은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>교원 자격증 소지자
 교원 임용에 결격 사유가 없는 자</t>
         </is>
       </c>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814622</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>교원 수업대체강사(기계) 채용 공고[3차]</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>창원공업고등학교</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 18일 ~ 2026년 12월 24일</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>창원공업고등학교에서 교원 수업대체강사(시간제) 채용을 다음과 같이 공고[3차]합니다.
 1. 채용분야 및 모집 인원
@@ -898,49 +784,49 @@
 궁금하신 점은 창원공업고등학교 행정실([전화번호])로 문의 바랍니다</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814571</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교 결원대체강사(진로진학상담 시간강사) 채용 공고(국어도 가능)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 11.(수)~2026. 11. 18.(수), 총 11시간</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026학년도 삼정자중학교 결원대체강사(진로진학상담)를 다음과 같이 채용하고자 합니다.
 1. 채용과목 및 채용 내용
@@ -964,49 +850,49 @@
 **자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814615</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>성호초등학교 전일제강사 채용 공고</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>성호초등학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026.10.7.~ 2026.10.21.(15일)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 공고 합니다.
 1. 채용과목 및 인원: 특수교사 1명
@@ -1017,49 +903,49 @@
 *자세한 사항은 붙임 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2026.10.30.(총16시간)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모자격
@@ -1087,49 +973,49 @@
 5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>교방초등학교 방과후학교 개인위탁 외부강사[티볼] 모집 공고</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>교방초등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026.11.1. ~2027.2.16.</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>[ 2026학년도 교방초 방과후학교 개인위탁외부강사 모집 공고 ]
 교방초등학교에서는
@@ -1143,49 +1029,49 @@
 6. 모집 세부 사항: 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814603</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 수학 시간강사 채용 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026.10. 12. ~ 2026.11.18. (주당18시간)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 시간강사 채용 공고
 1. 채용내용 : 수학 1명
@@ -1199,51 +1085,51 @@
 ※ 기타 자세한 사항은 공고문을 참고 하시기 바랍니다. ※ 관심 있는 분들의 많은 지원 바랍니다</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부, 기타 구비서류(채용합격자에 한해 별도안내)</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814606</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>남양초등학교 돌봄교실 특기적성프로그램 개인 위탁 외부강사 채용 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>남양초등학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2027. 2. 24.(수) / 금요일(13:50~14:30, 14:40~15:20, 15:30~16:10)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>2026학년도 남양초등학교 돌봄교실 특기적성 프로그램 외부강사를 아래와 같이 모집하오니
 관심있는 분들의 많은 지원 바랍니다.
@@ -1259,6 +1145,133 @@
 5. 기타 자세한 내용은 첨부파일을 참고바랍니다.</t>
         </is>
       </c>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814493</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>태봉고등학교 결원대체시간강사(수학) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>태봉고등학교</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고입니다.
+1. 채용과목 및 인원, 채용기간
+가. 채용과목: 수학
+나. 채용인원: 1명
+다. 채용기간: 2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)
+라. 수업시수 및 수당: 총 9시간(주당 6시간)/시간당 26,000원
+2. 서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간 : 2026.10.02.(금)~2026.10.08.(목) 14:00까지(시간내 도착분에 한함)
+◦ 접수장소 : 태봉고등학교 전자우편(주소: [이메일], 스캔본 제출, 면접 시 반드시 원본 제출)
+나. 1차 : 서류전형 합격자 발표(개별 전화 통지) 예정일 : 2026. 10. 12.(월) 14:00 이후
+다. 2차 : 면접전형(서류심사 합격자에 한함) 예정일 : 2026. 10. 13.(화) 11:00 예정
+◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
+라. 최종합격자 발표 : 2026. 10. 14.(수) 10:00 이후(합격자 개별 통보)
+바. 비고: 오전수업만 있음
+※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814688</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>삼정자중학교 결원대체강사(과학 전일제강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>삼정자중학교</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 삼정자중학교 결원대체강사(과학)를 다음과 같이 채용하고자 합니다.
+1. 채용과목 및 채용 내용
+가. 채용과목: 과학 1명
+나. 근무기간: 2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]
+2. 원서접수
+가. 원서접수
+1) 접수기간 : 2026. 10. 1.(목)~2026. 10. 8.(목) 15:00
+2) 접수방법 : 온라인 접수
+(주소: [이메일], 응시원서 및 자기소개서 스캔본 제출)
+나. 1차 서류전형 합격자 발표(개별 전화 통지)예정 : 2026. 10. 8.(목) 16:00
+다. 2차 면접 (서류심사 합격자(3배수)에 한함) : 2026. 10. 12.(월) 10:00~
+-일시 및 장소는 서류전형 합격자에게만 개별 통보하며 학사일정에 따라 면접 시간이 변경될 수 있음
+라. 최종합격자 발표: 2026. 10. 12.(월) 오후 예정. 합격자에게 개별 통보
+-최종합격자를 채용 못 할 경우 차순위를 채용함.
+3. 제출서류
+가. 응시원서 1부(붙임서식, 사진첨부, 연락가능한 전화번호 반드시 기재)
+나. 자기소개서 1부(붙임서식)
+다. 개인정보 동의서 1부(붙임서식)
+**자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n">
         <v>1</v>
@@ -1267,7 +1280,7 @@
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814493</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814686</t>
         </is>
       </c>
       <c r="L12" s="5" t="n"/>
@@ -2733,6 +2746,59 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고등학교</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
+1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
+2. 과목: 특수
+3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
+-자세한 내용은 공고문 참조 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>무지개초등학교 돌봄교실 특기·적성 프로그램 개인위탁 외부강사 모집 공고</t>
+          <t>성호초등학교 전일제강사 채용 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>무지개초등학교</t>
+          <t>성호초등학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -640,259 +640,15 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026년 10월 16일 ~ 2027년 2월 26일</t>
+          <t>2026.10.7.~ 2026.10.21.(15일)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 무지개초등학교 돌봄교실  특기·적성 프로그램 개인위탁 외부강사 모집 공고
-1. 모집강좌: 클레이(1명),영어(1명),책놀이(1명)
-2.계약기간: 2026년 10월 16일 ~ 2027년 2월 26일
-(학사일정에 따라 변동될 수 있음, 예산 소진 시 미 운영함)
-3. 모집 세부 사항
-가. 공고 기간：2026. 9. 28.(월) ∼ 2026. 10. 2.(금)
-나. 서류 접수：2026. 9. 28.(월) ∼ 2026. 10. 2.(금) 12:00까지
-다. 접수 장소：전자 메일 접수([이메일])
-라. 1차 : 서류전형(1차 합격자: 모집정원 2배수) 2026. 10. 6.(화) 16:00 (개별통보)
-마. 2차 : 면접전형(서류전형 합격자에 한함) 2026. 10. 7.(수) 10:30~(학교 사정에 따라 변동 가능)
-바. 최종 결과: 2026. 10. 8.(목) 16:00 이후 계약 예정자에 한하여 개별 통보
-사. 문의: 무지개초 돌봄4교실 전화 [전화번호](10:30~18:30)
-※세부사항은 첨부파일을 참고 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814532</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>가좌초등학교 시간제 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>가좌초등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.12.~2027.2.(예산소진시까지)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>1. 채용분야 및 응모자격
-가. 채용구분: 시간제 강사 1명
-나. 채용기간: 2026.10.12.~2027.2.(예산소진시까지)
-다. 응모자격
-- 교원 자격증 소지자
-- 교원 임용에 결격 사유가 없는 자
-2. 서류접수 및 전형일정
-가. 공고 및 접수기간: 2026.9.29(화) ~ 2026. 10.2.(금) 12:00까지
-나. 원서접수 방법: 온라인 접수만 가능(*면접시 원본제출)
-E-mail: [이메일]  2026. 10. 2.(금) 12:00 발송분까지  *우편, 방문 접수 불가
-다. 1차: 서류전형 합격자 발표(개별 전화 통지) 예정일 : 2026. 10. 2.(금) 13:00 이후
-라. 2차: 면접(서류심사 합격자) 예정일 : 2026. 10. 6.(화) 10:00, 협의회실
-3. 합격자발표: 2026. 10. 6.(화) 16:00 이후 개별통보
-※ 기타 자세한 사항은 첨부파일 확인 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>교원 자격증 소지자
-교원 임용에 결격 사유가 없는 자</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814622</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>교원 수업대체강사(기계) 채용 공고[3차]</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>창원공업고등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 18일 ~ 2026년 12월 24일</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>창원공업고등학교에서 교원 수업대체강사(시간제) 채용을 다음과 같이 공고[3차]합니다.
-1. 채용분야 및 모집 인원
-가. 채용분야 : 시간강사
-나. 채용과목 : 기계
-다. 모집인원 : 1명
-라. 근무기간 : 2026년 10월 18일 ~ 2026년 12월 24일
-2. 원서접수기간
-- 2026. 9. 28.(월) ~ 10. 2.(금) 15:00까지
-※ 기타 자세한 사항은 첨부파일 참조하시고,
-궁금하신 점은 창원공업고등학교 행정실([전화번호])로 문의 바랍니다</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814571</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>삼정자중학교 결원대체강사(진로진학상담 시간강사) 채용 공고(국어도 가능)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>삼정자중학교</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2026. 11. 11.(수)~2026. 11. 18.(수), 총 11시간</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 삼정자중학교 결원대체강사(진로진학상담)를 다음과 같이 채용하고자 합니다.
-1. 채용과목 및 채용 내용
-가. 채용과목: 진로진학상담 1명
-- 1순위 지원자(진로진학상담)가 없을 경우, 2순위 지원자(유사과목 자격 소지자: 국어)를 채용할 수 있음.
-나. 근무기간: 2026. 11. 11.(수)~2026. 11. 18.(수), 총 11시간
-2. 원서접수
-가. 원서접수
-1) 접수기간 : 2026. 9. 29.(화)~2026. 10. 2.(금) 15:00
-2) 접수방법 : 온라인 접수
-(주소: [이메일], 응시원서 및 자기소개서 스캔본 제출)
-나. 1차 서류전형 합격자 발표(개별 전화 통지)예정 : 2026. 10. 2.(금) 16:00
-다. 2차 면접 (서류심사 합격자(3배수)에 한함) : 2026. 10. 6.(화) 10:00~
--일시 및 장소는 서류전형 합격자에게만 개별 통보하며 학사일정에 따라 면접 시간이 변경될 수 있음
-라. 최종합격자 발표: 2026. 10. 6.(화) 오후 예정. 합격자에게 개별 통보
--최종합격자를 채용 못 할 경우 차순위를 채용함.
-3. 제출서류
-가. 응시원서 1부(붙임서식, 사진첨부, 연락가능한 전화번호 반드시 기재)
-나. 자기소개서 1부(붙임서식)
-다. 개인정보 동의서 1부(붙임서식)
-**자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814615</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>성호초등학교 전일제강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>성호초등학교</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.7.~ 2026.10.21.(15일)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 공고 합니다.
 1. 채용과목 및 인원: 특수교사 1명
@@ -903,49 +659,49 @@
 *자세한 사항은 붙임 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2026.10.30.(총16시간)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모자격
@@ -973,49 +729,49 @@
 5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>교방초등학교 방과후학교 개인위탁 외부강사[티볼] 모집 공고</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>교방초등학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026.11.1. ~2027.2.16.</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>[ 2026학년도 교방초 방과후학교 개인위탁외부강사 모집 공고 ]
 교방초등학교에서는
@@ -1029,49 +785,49 @@
 6. 모집 세부 사항: 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814603</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 수학 시간강사 채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026.10. 12. ~ 2026.11.18. (주당18시간)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 시간강사 채용 공고
 1. 채용내용 : 수학 1명
@@ -1085,51 +841,51 @@
 ※ 기타 자세한 사항은 공고문을 참고 하시기 바랍니다. ※ 관심 있는 분들의 많은 지원 바랍니다</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부, 기타 구비서류(채용합격자에 한해 별도안내)</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814606</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>남양초등학교 돌봄교실 특기적성프로그램 개인 위탁 외부강사 채용 공고</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>남양초등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2027. 2. 24.(수) / 금요일(13:50~14:30, 14:40~15:20, 15:30~16:10)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>2026학년도 남양초등학교 돌봄교실 특기적성 프로그램 외부강사를 아래와 같이 모집하오니
 관심있는 분들의 많은 지원 바랍니다.
@@ -1145,49 +901,49 @@
 5. 기타 자세한 내용은 첨부파일을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814493</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교 결원대체시간강사(수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고입니다.
 1. 채용과목 및 인원, 채용기간
@@ -1207,49 +963,49 @@
 ※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814688</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교 결원대체강사(과학 전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2026학년도 삼정자중학교 결원대체강사(과학)를 다음과 같이 채용하고자 합니다.
 1. 채용과목 및 채용 내용
@@ -1272,49 +1028,100 @@
 **자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814686</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>창원중앙고등학교 결원대체 시간강사(1순위:윤리, 2순위:일반사회) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>창원중앙고등학교</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 26.(월)~2026. 10. 30.(금) (총 17시간)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 창원중앙고등학교 결원대체 시간강사 채용을 다음과 같이 공고합니다.
+1. 채용과목 : 윤리(1순위:윤리, 2순위:일반사회)
+2. 채용기간 : 2026. 10. 26.(월)~2026. 10. 30.(금) (총 17시간)
+3. 서류 접수
+- 공고 및 서류 접수 기간: 2026. 10. 2.(금)~2026. 10. 8.(목) 15:00까지
+- 방법: 이메일 접수(([이메일])
+* 자세한 사항은 첨부파일 참조 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814730</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>김해내동초 돌봄 프로그램(종이접기 1명) 외부강사 모집 공고문</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>김해내동초등학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2027.2.28.</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>2026. 김해내동초 돌봄 프로그램(종이 접기 1명)외부 강사 모집 공고를  아래와 같이 실시합니다.
 1. 모집 인원: 1명
@@ -1324,49 +1131,49 @@
 5. 기타 자세한 사항은 첨부 문서를 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814620</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>증산중학교 계약제교원(시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1380,49 +1187,49 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814584</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -1475,49 +1282,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -1568,49 +1375,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -1634,47 +1441,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -1725,53 +1532,53 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>8046</v>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -1826,15 +1633,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -1844,211 +1651,40 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>한일여고 방과후학교(금융) 외부강사 모집공고</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>한일여자고등학교</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>경남 창원시</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>2026년 한일여고 방과후학교(금융) 외부강사 모집공고
-1. 모집분야: 금융전문가 과정반(펀드투자권유대행인 시험대비) 1명
-2. 계약방법: 시수계약(시금 50,000원)
-3. 전형일자: 1차-2026년 10월 1일(목) 16:00 2차-2026년 10월 2일(금) 12:30
-4. 합격발표: 2026년 10월 2일(금) 16시 이후 개별 통지
-기타 사항은 붙임의 공고문은 참고하세요.</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814450</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>충무공초 돌봄교실 특기적성 프로그램 개인위탁 외부강사 모집</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>충무공초등학교</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>경운초등학교 돌봄교실 특기적성 외부강사 공고</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>경운초등학교</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>충무공초등학교 돌봄교실 특기적성 프로그램을 운영할 역량 있는 외부 강사를 모집하오니 관심 있는 분들의 많은 지원 바랍니다.
-1. 모집분야
-돌봄교실 특기적성프로그램(바둑&amp;체스 1명)
-2. 모집일정
-가. 서류접수: 2026. 9. 29.(화) ~ 2026. 10. 2.(금) 14:00까지
-나. 접수방법: 메일접수(방문 및 우편접수 없음)
-다. 1차 제안서 심사 및 2차 대상자 통보: 2026. 10. 2.(금) 16:00 이후 개별통보
-라. 2차 운영능력심사: 2026. 10. 7.(수) 9:40 예정
-마. 최종 선정 개인위탁 외부강사 공지: 2026. 10. 7.(수) 개별통보
-※기타 세부사항은 첨부파일을 확인하여 주십시오.</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814604</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>가람초 계약제교원(학교폭력 수업경감 시간강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>가람초등학교</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>가람초등학교에서는 계약제교원(학교폭력 수업경감 시간강사)을 아래와 같이 채용하고자 합니다.
-1. 모집 분야 및 인원: 과학(1명)
-2. 서류 접수 기간: 2026. 9. 28.(월) ∼ 2026. 10. 2.(금) 16:00 까지
-3. 접수 방법: 학교 메일 접수(방문, 팩스, 우편 제출 불가)
-* 메일 주소: [이메일]
-* 제목 입력 예시: 학교폭력 수업경감 시간강사 지원 서류(응시자명).pdf
-※ 자세한 사항은 첨부 파일을 참고하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814491</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>경운초등학교 돌봄교실 특기적성 외부강사 공고</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>경운초등학교</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>2026학년도 경운초등학교에 근무할 외부강사를 다음과 같이 채용 공고합니다.
 1. 채용과목 : 돌봄교실 특기적성 프로그램 : 공예놀이
@@ -2059,51 +1695,51 @@
 6. 최종 합격자 발표일 : 2026. 10. 8.(목) 11:00이후 개별통보* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814577</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>방과후학교 리코더 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>수양초등학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>수양초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 개인 위탁 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원
@@ -2121,53 +1757,53 @@
 ※ 자세한 내용은 첨부파일을 참고해 주시기 바랍다.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n">
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814600</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 재공고(수학)</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>꽃내중학교</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집 재공고
 꽃내중학교에서는 방과후학교 운영과 관련하여 아래와 같이 2026학년도 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
@@ -2187,51 +1823,51 @@
 ※. 자세한 사항은 첨부물을 참고하십시요.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814587</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>화정초등학교</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
@@ -2240,51 +1876,51 @@
 * 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>주동초등학교</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>2026년 주동초등학교에서는 초등 1~2학년 맞춤형프로그램과 관련하여 아래와 같이 외부강사(문화, 예술, 음악, 놀이영어 등 다양한 분야 지원 가능)를 모집하오니, 유능한 강사님들의 많은 지원 바랍니다.
 1.  서류접수:  2026.  10. 1.(목) ~ 2026. 10.  7.(수) 16시까지 도착분
@@ -2296,51 +1932,51 @@
 ※ 접수시간을 반드시 준수해 주시길 바랍니다.</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814652</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -2353,112 +1989,170 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>동원고등학교 결원대체강사 채용공고(수학)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>동원고등학교</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
+1. 원서접수
+가. 접수기간: 2026.10.6.(화)~2026.10.16.(금) 09:00~16:30
+나. 접수장소: 동원고등학교 교무실/교무행정원
+다. 접수방법: 우편 또는 이메일 접수 ([이메일])
+※원서 접수 마감시간까지 도착분 유효
+2. 서류전형 합격자 발표 예정: 2026.10.20.(화) (개별통지)
+3. 면접(서류심사 합격자에 한함) 예정: 2026.10.21.(수)
+※일시 및 장소는 서류전형 합격자에게만 개별통보
+***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -2469,51 +2163,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O30" s="5" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -2565,47 +2259,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -2617,51 +2311,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr">
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -2678,97 +2372,97 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O29" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>함양제일고등학교</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>10.26.(월)-11.11.(수)/ 총58시간</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
 1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
@@ -2777,25 +2471,70 @@
 -자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="O30" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,30 +625,128 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>한일여고 전일제 시간강사(기계) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>한일여자고등학교</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>2026년 10월 22일~10월 30일</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 한일여고 전일제시간강사(기계) 채용공고
+1. 채용분야: 전일제시간강사
+2. 접수기간: 2026년 9월 30일~10월 5일 10:00
+3. 채용기간: 2026년 10월 22일~10월 30일
+자세한 사항은 붙임의 공고문을 참고해주세요.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814634</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>한일여고 시간강사(청소년비즈쿨 사업운영 보결강사) 채용</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>한일여자고등학교</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>2026년 10월 19일~11월 6일</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 한일여고 시간강사(청소년비즈쿨 사업운영 보결강사) 채용공고
+1. 채용분야: 시간강사(영어)
+2. 접수기간: 2026년 9월 30일~10월 5일 10:00
+3. 채용기간: 2026년 10월 19일~11월 6일
+자세한 사항은 붙임의 공고문을 참고해주세요.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814635</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>성호초등학교 전일제강사 채용 공고</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>성호초등학교</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026.10.7.~ 2026.10.21.(15일)</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 공고 합니다.
 1. 채용과목 및 인원: 특수교사 1명
@@ -659,49 +757,105 @@
 *자세한 사항은 붙임 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
         </is>
       </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>합포고등학교 계약제교원(전일제 강사) 채용 재공고(국어)(3차)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>합포고등학교</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.14.(수)~2026.10.23.(금) (총 8일)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 합포고등학교에서 근무할 계약제교원(전일제강사) 채용을 다음과 같이 공고합니다.
+1. 채용 과목 및 인원: 국어(1)
+2. 채용 기간: 2026.10.14.(수)~2026.10.23.(금) (총 8일)
+3. 접수기간: 2026.9.30.(수) ~ 10.05.(월) 17:00까지
+4. 접수방법: 학교전자우편 접수([이메일], 면접 시 원본 제출 요망)
+5. 서류전형 합격자 발표(개별통지): 2026.10.06.(화) 15:00 이후
+6. 면접일시: 2026.10.07.(수) 09:40
+(일시 및 장소는 서류전형 합격자에게만 개별 통보)
+7. 최종 합격자 발표: 2026.10.07.(수) 15:00 이후
+(최종 합격자에 한하여 전화 또는 문자로 개별 통지)
+8. 문의 : 합포고 교무실([전화번호])
+기타 자세한 사항은 첨부파일을 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814629</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2026.10.30.(총16시간)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모자격
@@ -729,49 +883,162 @@
 5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>시간강사(과학과) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>구산고등학교</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 26.~ 2026. 10. 30. (총17시수)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>구산고등학교 공고 제2026-48호
+본교 교사의 결원을 대체할 시간강사 채용을 아래와 같이 채용 공고하고자 합니다.
+1. 채용 과목 및 인원: 과학과(지구과학, 물리, 화학, 생명과학, 공통과학) 1명
+2. 채용기간: 2026. 10. 26.~ 2026. 10. 30. (총17시수)
+3. 채용 시험 일정
+가. 응시원서접수
+1) 접수기간: 2026. 10. 1.(목)~2026. 10. 5.(월)
+2) 접수방법: 전자메일 접수
+나. 시험일정
+1) 1차서류심사: 2026. 10. 6.(화) 개별통보
+2) 2차면접심사: 2026. 10. 7.(수) 개별통보
+3) 합격자 발표: 2026. 10. 7.(수) 최종확정자 개별통보
+자세한 내용은 붙임파일 참조바랍니다.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814670</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>대청중학교 결원대체강사 (특수) 2차 채용 공고</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>대청중학교</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.16.(금)~2026.10.19.(월) (2일)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. 채용과목 : 특수 (시간제)
+2. 채용기간 : 2026.10.16.(금)~2026.10.19.(월) (2일)
+3. 접수기간 : 2026.10.02.(금)~2026.10.06.(화) 09:00 도착분까지
+4. 서류전형 : 2026.10.06.(화) 11:00 이후 (합격자에게 개별 통보)
+5. 최종면접 : 2026.10.06.(화) 15:30~
+- 1인 지원시, 1차 심사 결과 적격자라고 판단 될 경우 2차 면접 심사 생략 할 수 있음
+6. 최종합격자 발표 : 2026.10.07.(수) 11:00 이후
+7. 접수방법 : [이메일]
+상세한 내용은 첨부파일 참고 바랍니다.
+감사합니다.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814570</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>교방초등학교 방과후학교 개인위탁 외부강사[티볼] 모집 공고</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>교방초등학교</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026.11.1. ~2027.2.16.</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>[ 2026학년도 교방초 방과후학교 개인위탁외부강사 모집 공고 ]
 교방초등학교에서는
@@ -785,49 +1052,49 @@
 6. 모집 세부 사항: 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814603</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 수학 시간강사 채용 공고</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026.10. 12. ~ 2026.11.18. (주당18시간)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 시간강사 채용 공고
 1. 채용내용 : 수학 1명
@@ -841,51 +1108,320 @@
 ※ 기타 자세한 사항은 공고문을 참고 하시기 바랍니다. ※ 관심 있는 분들의 많은 지원 바랍니다</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부, 기타 구비서류(채용합격자에 한해 별도안내)</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814606</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>양산제일고등학교 전일제 강사(수학) 채용 3차 공고</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>양산제일고등학교</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 07. ~ 2026. 10. 30.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1. 채용과목: 수학(1명)
+2. 채용기간: 2026. 10. 07. ~ 2026. 10. 30.
+3. 서류 접수기간: 2026. 10. 01.(목) ~ 2026. 10. 06.(화) 10:00까지
+4. 접수방법: 전자우편 제출(주소: [이메일])
+5. 서류 심사결과 발표: 2026. 10. 06.(화) 11시 이후 합격자 개별 통보
+6. 면접전형(서류심사 합격자): 2026. 10. 06.(화) 오후 14시
+7. 최종합격자발표: 2026. 10. 06.(화) 15시 이후 (합격자 유선 통보)
+8. 기타 자세한 사항은 첨부 문서(공고문)를 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814677</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 방송댄스 개인위탁 외부강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>합성초등학교</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 29 ~ 2027. 2. 26.(학교사정에 따라 변동 될 수 있음)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>합성초등학교에서는 2026. 방과후학교 방송댄스 개인위탁 외부강사를 모집합니다.
+관심 있는 분들의 많은 지원 바랍니다.
+1. 모집 세부 사항
+가. 모집강좌 : 방송댄스 1명
+나. 계약기간 : 2026. 10. 29 ~ 2027. 2. 26.(학교사정에 따라 변동 될 수 있음)
+다. 접수기간 : 2026. 10. 1. ~ 2026. 10.6 . 12:00 도착에 한함.
+라. 접수장소 : 합성초등학교 1층 교무실로 직접 제출
+마. 기타사항 : 자세한 사항은 첨부파일 참고
+바. 문의사항 : 교무실 256-2696</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814636</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>마산여자고등학교 계약제교원(전일제강사-윤리) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>마산여자고등학교</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.12.(월)~2026.10.19.(월) 총 6일 / 일당 110,000원</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 마산여자고등학교에 근무할 계약제교원 전일제강사를 다음과 같이 채용 공고합니다.
+1. 채용과목: 도덕·윤리(1명)
+2. 채용기간: 2026.10.12.(월)~2026.10.19.(월) 총 6일 / 일당 110,000원
+3. 접수기간: 2026. 10. 1.(목) ~ 2026. 10. 6.(화) 16:00 도착에 한함
+4. 응시자격: 동일 과목 중등교사 자격증 소지자 지원 가능
+5. 전형방법
+가. 1차 전형: 서류심사(1차 합격자 발표 2026. 10. 7.(수) 10:00이후 (합격자 개별 통보))
+(※면접 대상자에 한하여 전화 혹은 문자로 통지)
+나. 2차 전형: 면접(1차 합격자 기준 2026. 10. 7.(수) 14:00~)
+(※면접 대상자에 한하여 전화 혹은 문자로 통지)
+6. 접수방법 : 전자우편 [이메일](우편, 방문 접수 불가)
+7. 최종 합격자 발표: 2026. 10. 7.(수) 16:00이후 (최종합격자에 한하여 전화 또는 문자로 개별 통지)
+8. 제출서류
+가. 응시원서 1부(붙임 서식, 사진 첨부, 연락 가능한 전화번호 반드시 기재)
+나. 자기소개서 1부(붙임 서식)
+다. 개인정보 수집·이용 동의서 1부(붙임 서식)
+※ 파일명을 '과목명-본인 이름'으로 수정 후 제출(파일 하나로 보내시면 됩니다.)
+9. 최종합격시 제출서류
+가. 교사 자격증 사본 또는 자격인정조서 1부.
+나. 졸업증명서 사본 1부(전문대학 이상, 2개 이상이면 모두 제출).
+다. 공무원채용신체검사서 1부. (유효기간 1년 내)
+라. 잠복결핵검사 확인서 1부
+마. 마약류 투약 또는 중독 여부 판별 결과 통보서 또는 의사 진단서 (유효기간 1년 내)
+바. 개인정보 수집 및 활용 동의서 1부
+사. 결격사유, 범죄경력조회동의서, 행정정보공동이용 동의서 각 1부.
+아. 가족 채용 제한 여부 확인서
+자. 병적증명서 또는 주민등록표 초본
+차. 경력증명서(사립학교: 경력확인서)
+(바~아 항목은 학교에서 작성합니다.)
+자세한 사항은 첨부파일 확인바랍니다.</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>동일 과목 중등교사 자격증 소지자 지원 가능</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814705</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>봉명초 돌봄교실 특기적성 프로그램 강사 추가 모집</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>봉명초등학교</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>2026년 10월 12일∼2027년 2월 26일 / 학기 중 : 14:00~15:30  ,   방학 중 : 13:00~ 14:30</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 초등돌봄교실 특기적성 개인위탁 외부강사를 다음과 같이 추가 공고 모집하고자 합니다.
+1. 모집 분야 및 인원순
+채용분야
+모집영역(강좌명)
+채용인원
+프로그램 운영 방법강사료1
+특기적성 프로그램
+동화구연(월), 전래놀이(화),
+종이접기(수),보드게임(목)
+강좌별 1명
+주1회 40분 2차시
+차시당 40,000원2
+운영 시간
+학기 중 : 14:00~15:30  ,   방학 중 : 13:00~ 14:30
+* 프로그램 운영에 필요한 재료비는 별도로 지원하지 않음.(단, 운영 상황에 따라 조정될 수 있음)
+※ 프로그램 운영 요일 및 시간은 강사와 협의하여 조정될 수 있음
+2. 모집 세부 사항
+가. 공고 기간: 2026년 10월 01일(목) ∼ 2026년 10월 06일(화)
+나. 서류 접수: 2026년 10월 01일(목) ∼ 2026년 10월 06일(화) 16:00까지
+다. 접수 장소: 봉명초등학교 교무실로 본인 직접 접수
+라.선정 및 계약방법: 1차 제안서 평가 합격자에 한해 2차 프로그램 운영 능력평가를 실시하여 계약 예정자를 선정
+마. 합격자 통보1차
+제안서(서류) 심사
+2026. 10. 06.(화)
+• 17:00시 까지 개별통보 예정
+• 1차 제안서 평가 통과자에 한하여 개별 통보2차
+운영능력(면접) 심사
+2026. 10. 07.(수)
+• 운영능력(면접)
+※ 면접 인원에 따라 일정 및 시간이 조정될 수 있음.
+※ 학교 사정에 의해 운영능력(면접) 심사 일정이 조정될 수 있음
+최종 심사 결과 발표
+2026. 10.08(목). 17:00까지 개별 통보 예정
+바. 계약 기간: 2026년 10월 12일∼2027년 2월 26일
+※ 학사 일정 등 불가피한 사유로 인해 계약 기간이 조정될 수 있음,
+※ 자세한 사항은 첨부파일을 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814672</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>남양초등학교 돌봄교실 특기적성프로그램 개인 위탁 외부강사 채용 공고</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>남양초등학교</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2027. 2. 24.(수) / 금요일(13:50~14:30, 14:40~15:20, 15:30~16:10)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>2026학년도 남양초등학교 돌봄교실 특기적성 프로그램 외부강사를 아래와 같이 모집하오니
 관심있는 분들의 많은 지원 바랍니다.
@@ -901,49 +1437,335 @@
 5. 기타 자세한 내용은 첨부파일을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814493</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>통영여자중학교 시간강사(수학) 채용</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>통영여자중학교</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 15~2026. 10. 23</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>통영여자중학교에서 근무할 시간강사를 다음과 같이 채용 공고합니다.
+- 채용기간 : 2026. 10. 15~2026. 10. 23
+- 접수기간 : 2026. 10. 2～2026. 10. 7. 12:00시까지
+- 접수장소 : 통영여자중학교 전자우편
+- 접수방법 : 전자우편(주소: [이메일], 스캔본 제출, 면접 시 원본 제출, 2026. 10. 7. 12:00시 발송분까지)
+자세한 내용은 첨부파일을 참고해주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814706</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>악양초등학교. 결원 대체 강사 채용 공고(전일제강사)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>악양초등학교</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.26 ~ 2026.10.30.(총5일)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 악양초등학교에 근무할 결원 대체 강사를 다음과 같이 채용 공고 안내
+1. 채용과목 : 초등(전일제강사 1명)
+2. 채용기간 : 2026.10.26 ~ 2026.10.30.(총5일)
+3. 응시자격
+1순위: 만 62세 미만 동일 자격 소지자
+2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
+*  1순위 지원자 없을 시  2순위자 채용 가능
+4. 서류 접수 : 2026.9.30.(수)~10.7.(수)15:00까지
+악양초등학교 전자우편 ([이메일])
+스캔본 제출, 면접 시 원본 제출,
+5. 제출서류
+◦ 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
+◦ 자기소개서 1부.(붙임서식)
+◦ 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)
+* 자세한 사항은 붙임 공고문을 참조바랍니다.</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>1순위: 만 62세 미만 동일 자격 소지자
+2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
+1순위 지원자 없을 시  2순위자 채용 가능</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재), 자기소개서 1부.(붙임서식), 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814642</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>대방중학교 전일제강사(기술·가정과) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>대방중학교</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>2026년 11월 9일 ~ 2026년 11월 13일(5일)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 대방중학교 기술·가정과 전일제강사를 다음과 같이 채용 공고합니다.
+1. 접수기간: 2026년 10월 2일(금) ~ 2026년 10월 7일(수), 09:00까지 도착분에 한함
+2. 접수방법: 이메일 접수([이메일])
+3. 서류심사결과 발표: 2026년 10월 7일(수), 13:30 이후(개별 알림)
+4. 면접심사: 2026년 10월 8일(목), 12:30 (장소 개별 알림)
+5. 최종합격자 발표: 2026년 10월 8일(목), 14:30 이후(합격자 개별 알림)
+※채용기간: 2026년 11월 9일 ~ 2026년 11월 13일(5일)
+기타 자세한 사항은 붙임 문서를 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814661</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>계동초 방과후학교 프로그램 개인위탁 외부강사(한자속독) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>계동초등학교</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>2026년 11월 1일 ∼ 2027년 2월 28일</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>2026. 계동초 방과후학교 프로그램(한자속독) 개인위탁 외부강사를 다음과 같이 모집합니다.
+1. 계약 기간: 2026년 11월 1일 ∼ 2027년 2월 28일
+*불가항력 사유 등으로 인해 정상적인 학사운영이 이루어지지 않을 경우 계약기간이 변동될 수 있음
+2. 모집 분야: 한자속독(1명)
+3. 모집 세부 사항
+가. 공고 및 접수기간: 2026년 10월 2일(금) ~ 10월 8일(목) 12:00까지
+나. 접수장소: 전자우편 접수 ([이메일])
+다. 문의전화: [전화번호] 또는 [전화번호]
+라. 합격자 통보: 1차 서류 전형 합격자에 한하여 개별 통보 후 2차 전형 실시
+-자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814720</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>분성초등학교 방과후학교 외부강사 모집 공고(바이올린)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>분성초등학교</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 3. ~ 2027. 2. 25.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>2026. 분성초 방과후학교 바이올린 개인위탁 외부강사를 다음과 같이 모집합니다.
+1. 계약 기간: 2026. 11. 3. ~ 2027. 2. 25.
+※ 학생 개인 악기 및 학교 보유 악기 우선 활용, 수량 부족 시 악기 무료 대여(지원)가 가능한 강사
+※ 실제 프로그램 운영 기간과 계약 기간은 일치하며, 공사 등 불가피한 사유 등으로 학사 일정이 변경 될     경우 운영 기간·계약 기간·운영 요일·운영 시간은 변경될 수 있음.
+※ 요일 변경 불가
+2. 모집 분야: 바이올린(주 2회(화, 목요일), 회당 2차시(차시당 40분) 운영 [주당 총 4차시])
+3. 모집 절차 및 내용(일정은 학교 사정에 의해 변경될 수 있음)
+가. 공고 및 접수기간: 2026.10.3.(토)~10.8.(목) 12:00까지 도착분에 한함
+나. 제출방법:인편/우편/공직자통합메일(메일주소:[이메일])
+(인편제출장소: 본교 교무실 본인이 직접제출)
+다. 문의전화: [전화번호]
+라. 합격자 통보: 1차 서류 전형 합격자에 한하여 개별 통보 후 2차 전형 실시
+-자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814693</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교 결원대체시간강사(수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고입니다.
 1. 채용과목 및 인원, 채용기간
@@ -963,49 +1785,49 @@
 ※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814688</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교 결원대체강사(과학 전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>2026학년도 삼정자중학교 결원대체강사(과학)를 다음과 같이 채용하고자 합니다.
 1. 채용과목 및 채용 내용
@@ -1028,49 +1850,49 @@
 **자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814686</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교 결원대체 시간강사(1순위:윤리, 2순위:일반사회) 채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.(월)~2026. 10. 30.(금) (총 17시간)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원중앙고등학교 결원대체 시간강사 채용을 다음과 같이 공고합니다.
 1. 채용과목 : 윤리(1순위:윤리, 2순위:일반사회)
@@ -1081,47 +1903,47 @@
 * 자세한 사항은 첨부파일 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814730</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>김해내동초 돌봄 프로그램(종이접기 1명) 외부강사 모집 공고문</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>김해내동초등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2027.2.28.</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>2026. 김해내동초 돌봄 프로그램(종이 접기 1명)외부 강사 모집 공고를  아래와 같이 실시합니다.
 1. 모집 인원: 1명
@@ -1131,49 +1953,49 @@
 5. 기타 자세한 사항은 첨부 문서를 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814620</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>증산중학교 계약제교원(시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1187,49 +2009,103 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n">
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814584</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>동진초등학교 2026.10.12.자 계약제교원(결원대체강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>동진초등학교</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 12. ~ 2026. 10. 17.(5일)</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>가. 채용 분야: 초등교사
+나. 채용 기간: 2026. 10. 12. ~ 2026. 10. 17.(5일)
+다. 채용 인원: 1명
+라. 응모 자격
+1) 1순위: 결원교원과 동일 학교급 자격증 소지자(만62세 미만)
+2) 2순위: 결원교원과 다른 학교급 또는 유사과목 자격소지자(만62세 미만),
+정년퇴직 혹은 명예퇴직자(만65세 미만)
+※ 국가공무원법 제33조의 규정에 의한 공무원임용 결격사유가 없는 자</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814468</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -1282,49 +2158,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -1375,49 +2251,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n">
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -1441,47 +2317,114 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>지세포중학교 시간강사(기술 가정) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>지세포중학교</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고
+합니다.
+1. 채용과목: 기술.가정(1명)
+2. 채용기간: 2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)
+3. 전형방법
+가. 1차 시험 : 서류전형
+나. 2차 시험 : 면접(서류전형 합격한 자에 한하여 개별 통보)
+4. 서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간 : 2026.9.30.(수)~2026.10.14.(수) 12:00까지
+◦ 접수장소 : 지세포중학교 교무실, 전자우편
+◦ 접수방법 : 전자우편([이메일])접수
+※ 전자우편 발송 후 지세포중학교 도착 여부를 본인이 반드시 확인할 것
+※ 제출 서류를 전자우편으로 제출 시 사본으로 제출하고, 2차 시험 시 원본 제출
+※ 전자우편 접수 시, 모든 서류는(필요시) 서명한 후 스캔하여 PDF, JPEG 등의 파일 형식으로
+※ 첨부 파일명 : 교과명_본인 이름
+나. 1차 : 서류전형 합격자 발표(개별 전화 통지) 예정일 : 2026.10.14.(수) 16:00 이후
+다. 2차 : 면접(서류심사 합격자에 한함) 2026.10.16.(금) 13:00~
+(시간과 장소는 서류전형 합격자에게 개별 통보)
+5. 합격자 발표
+◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -1532,53 +2475,359 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H31" s="5" t="n">
         <v>8046</v>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>유목초 특수학급 결원대체강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>내곡초등학교</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.1.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명
+2. 기간: 2026.10.1.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>유영초등학교</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.12.~2026.10.30.(19일간)</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>1. 채용과목: 초등 결원대체 강사(전일제)
+2. 채용 인원: 1명
+3. 채용기간: 2026.10.12.~2026.10.30.(19일간)
+4. 자세한 사항은 첨부파일 참조</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>남지초등학교</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>가. 채용 분야: 초등기간제교원
+나. 채용 기간: 2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)
+다. 채용 인원: 1명
+라. 응모 자격
+1) 1순위:초등교원자격(만 62세 미만)
+2) 2순위: 중등교원자격(만 62세 미만),
+정년퇴직 혹은 명예퇴직자(만65세 미만)
+※ 국가공무원법 제33조의 규정에 의한 공무원임용 결격사유가 없는 자
+※자세한 사항은 공고문 참고</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>칠원고등학교</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
+1. 채용과목: 영어(1명)
+2. 채용기간: 2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)
+상세내용은 첨부파일 확인 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -1633,15 +2882,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H38" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -1651,40 +2900,490 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>진영장등중학교 학교스포츠클럽 외부강사(대체) 채용공고</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>진영장등중학교</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>학교스포츠클럽 강사를 다음과 같이 채용하고자 합니다.
+1. 채용 분야 및 채용 인원: 학교스포츠클럽(축구) 강사 1명
+2. 접수기간: 2026. 9. 28.~2026. 10. 4.
+3. 접수방법: 학교 전자메일([이메일])
+※ 2026년 10월 4일 10:00 도착분에 한함.
+**채용(계약)기간 수정
+*자세한 내용은 첨부파일 참고하세요.</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814581</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>웅상고 계약제교원(학교폭력담당자 수업경감 시간강사) 2차 채용 공고</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>웅상고등학교</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 웅상고등학교에 근무할 기간제교사를 다음과 같이 채용 공고 합니다.
+1. 채용과목 및 응모 자격
+물리(과학), 1명, 시간강사
+2026.10. 1. ~ 2026.12.31.
+주당 5시간, 시간당 25,000원.
+물리교사자격증 소지자
+- 공통과학, 지구과학, 생물, 화학 교사자격증 지원가능
+- 정년퇴직자 및 명예퇴직자
+- 만 62세까지 지원가능
+❈ 채용의 1순위: 결원 교원과
+동일한 급별‧과목별
+교원자격증소지자, 만 62세 미만
+동일 자격소지자를 우선 임용.
+2순위: 명예퇴직자, 정년퇴직자,
+다른 학교급·유사과목 자격증 소지자 등, 만 62세 미만.
+2. 전형방법
+가. 1차 시험 : 서류전형
+나. 2차 시험 : 면접
+3. 제출서류
+가. 응시자 제출서류
+◦ 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
+◦ 자기소개서 1부.(붙임서식)
+◦ 개인정보동의서(붙임서식)
+나. 최종합격자 제출서류
+◦ 교사 자격증 사본 또는 자격 인정 조서 1부.
+◦ 졸업증명서 사본 1부.(원본지참)
+◦ 기본증명서 및 병적증명서 또는 주민등록 초본 1부.
+◦ 범죄경력조회동의서 1부.
+◦ 공무원채용신체검사서 1부.
+4. 서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간 : 2026. 9. 29.(화) 9:00 ~ 2026. 10. 5.(월) 16:00까지
+◦ 접수장소 : 웅상고등학교 3층 1교무실
+◦ 접수방법 : 이메일접수 ([이메일](영타), 2026. 10. 5.(월) 16:00까지)
+나. 1차 : 서류전형 합격자 발표(개별 전화 통지) 예정일 : 2026. 10. 6.(화) 15:00 이후
+다. 2차 : 면접예정일 : 2026. 10. 7.(수), 10:00 예정
+* 일시 및 장소는 서류전형 합격자에게만 개별 통보
+5. 합격자 발표
+◦ 최종합격자 발표 : 2026. 10. 7.(수) 17:00 이후 개별통보
+6. 유의사항
+◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 우선 임용될 수 있음
+◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 최종합격 후 확인이 불가능한 서류만 제출
+◦ 상기 일정은 진행상황에 따라 변경될 수 있으며 별도 통보함
+◦ 기재사항이 사실과 다르거나 허위로 작성된 경우는 합격을 취소합니다.
+◦ 제출서류의 기재착오, 누락, 서류 미제출, 연락불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.
+◦ 최종합격자로 발표된 이후에도 결격사유가 있는 자는 합격을 취소합니다.
+◦ 기타 자세한 사항은 웅상고등학교(☎[전화번호])로 문의하시기 바랍니다.
+2026년 9월 29일
+웅상고등학교장</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814610</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>김해한일여고 2026학년도 시간강사(수학) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>김해한일여자고등학교</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 김해한일여자고등학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
+1. 채용과목 : 수학(1명)
+2. 채용예정기간: 2026. 10.26.~2026.10.30.
+3 접수기간 : 2026. 9. 29.(화)~2026. 10. 5.(월) 16:00까지
+4. 접수방법 : 온라인접수, 방문접수, 우편접수
+5. 1차 합격자 발표일 : 2026. 10. 6.(화) 13:00이후 개별통보
+6. 2차 면접일 : 2026. 10. 7.(수)
+*면접시간 및 장소는 1차서류전형 합격자에게만 개별통보
+7. 최종 합격자 발표일 : 2026. 10. 7.(수) 13:00이후 개별통보
+* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814611</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>김해한일여고 2026학년도 결원대체 시간강사(진로진학) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>김해한일여자고등학교</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 김해한일여자고등학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
+1. 채용과목 : 진로진학(1명)
+2. 채용예정기간: 2026. 10.12.~2026.10.16.
+3 접수기간 : 2026. 9. 28.(월)~2026. 10. 5.(월) 16:00까지
+4. 접수방법 : 온라인접수, 방문접수, 우편접수
+5. 1차 합격자 발표일 : 2026. 10. 6.(화) 13:00이후 개별통보
+6. 2차 면접일 : 2026. 10. 7.(수)
+*면접시간 및 장소는 1차서류전형 합격자에게만 개별통보
+7. 최종 합격자 발표일 : 2026. 10. 7.(수) 13:00이후 개별통보
+* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814557</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>호암중학교 창체동아리(연극) 강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>호암중학교</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 호암중학교 창체동아리(연극) 강사 채용 공고
+1) 종목 및 선발인원: 창체동아리 연극 (1명)
+2) 접수기간: 2026.10.1.(목) ~2026.10.5.(월) 16:00까지
+3) 접수방법: 호암중학교 교무실(방문접수) 또는
+전자우편([이메일])
+4) 서류심사 발표 : 2026.10.6.(화) 16:00 이후(합격자만 개별통지)
+5) 면접심사 : 2026.10.7.(수) 10:00 본교 2층 소통실
+6) 합격자 발표 : 2026.10.7.(수) 14:00 이후 개별 통지
+*자세한 내용은 첨부 파일을 확인하세요</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814664</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>율하중 계약제교원(체육,영어 시간강사) 채용 계획</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>율하중학교</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>1. 채용과목: 체육(1), 영어(1)
+2. 서류접수 및 전형방법
+-1차: 서류전형 합격자 발표(개별 통지) 예정일: 2026.10.6. 15:30이후
+*접수기간: 2026.9.28.~2026.10.5. 23:00
+-2차: 면접심사
+*면접일시: 2026.10.7.(12:30 또는 12:40)
+*강사비: 시간당 22,000원
+*자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814563</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>[양산고] 결원대체강사(전일제-영어,정보,화학,수학,생물) 채용공고</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>양산고등학교</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경남 양산시</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>양산고등학교 공고 제2026-65호
+2026학년도 양산고등학교 결원대체강사(시간강사)를 채용 공고합니다.
+1. 서류접수 및 전형방법
+가. 원서접수
+◦ 접수기간 : 2026.09.29.(화) ~ 2026.10.05.(월)
+◦ 접수장소 : 양산고등학교 전자우편
+◦ 접수방법 : 전자우편(주소: [이메일])
+나. 1차 : 서류전형 합격자 발표(개별 통지) 예정일 : 2026.10.06.(화)
+다. 2차 : 면접심사(개별통지)
+◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보(예정일 : 2026.10.07.(수)
+◦ 응시자 1인 시 서류심사 적합 여부에 따라 면접 생략할 수 있음
+2. 합격자 발표
+◦ 최종합격자 발표 : 2026.10.07.(수) 개별통보
+-임용결정: 총점 1위(합격자), 합격자 임용포기 시 차순위자를 합격자로 선정
+(단, 적격자가 없을 경우 합격자 없이 재공고를 통한 업무 진행)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814477</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>경운초등학교 돌봄교실 특기적성 외부강사 공고</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>경운초등학교</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>2026학년도 경운초등학교에 근무할 외부강사를 다음과 같이 채용 공고합니다.
 1. 채용과목 : 돌봄교실 특기적성 프로그램 : 공예놀이
@@ -1695,51 +3394,51 @@
 6. 최종 합격자 발표일 : 2026. 10. 8.(목) 11:00이후 개별통보* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814577</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>방과후학교 리코더 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>수양초등학교</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>수양초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 개인 위탁 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원
@@ -1757,117 +3456,330 @@
 ※ 자세한 내용은 첨부파일을 참고해 주시기 바랍다.</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814600</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 재공고(수학)</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>꽃내중학교</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 개인위탁 외부강사 모집 재공고
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 개인위탁 외부강사 모집 공고
 꽃내중학교에서는 방과후학교 운영과 관련하여 아래와 같이 2026학년도 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야, 모집 인원
 가. 교과 수학반
 나. 2명 채용
 2. 모집 세부 사항
-가. 공고 기간: 2026년 9월 28일(월)∼2026년 10월 6일(화)
-나. 서류 접수: 2026년 9월 29일(화)∼2026년 10월 6일(화) 15:00
+가. 공고 기간: 2026년 9월 23일(수)∼2026년 9월 28일(월)
+나. 서류 접수: 2026년 9월 23일(수)∼2026년 9월 28일(월) 15:00
 다. 접수 장소: 꽃내중학교 이메일 접수(지원서, 자기소개서, 프로그램 운영 제안서)
 ※ 이메일 주소: [이메일]
 3. 계약 기간
-가. 수학C: 2026년 10월 20일 - 2027년 1월 5일(변동가능)
+가. 수학C: 2026년 10월 1일 - 2027년 1월 5일(변동가능)
 나. 수학B: 2026년 11월 1일 - 2027년 1월 5일(변동가능)
 ※ 매주 수업하는 것을 기본으로 하되 학사 일정에 따라 출근일은 모집 분야 프로그램에 의함.
 ※ 불가항력 사유 등으로 인해 정상적인 학사 운영이 이루어지 않을 경우 계약 기간이 변동될 수 있음
 ※. 자세한 사항은 첨부물을 참고하십시요.</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814587</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 80) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>진해신항초 계약제교원(전일제 강사) 채용 모집 공고</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>진해신항초등학교</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 진해신항초등학교 계약제교원(전일제강사) 다음과 같이 채용 공고합니다.
+◆ 채용내용
+가. 채용기간 및 채용인원: 1명
+- 전일제강사: 2026. 10. 26.~ 2027. 11. 13. 1명(5학년)
+◆ 전형방법
+가. 1차 전형: 서류전형(서류전형 합격한 자에 한하여 2차 전형 대상자 개별 통보)
+나. 2차 전형: 면접
+◆ 제출서류
+가. 응시자 제출서류
+◦ 응시원서 1부(붙임 서식, 사진 첨부, 연락 가능한 전화번호 반드시 기재)
+◦ 자기소개서 1부(붙임 서식)
+◦ 개인정보 수집·이용에 대한 동의서(붙임 서식)
+나. 최종합격자 제출서류
+◦ 교사 자격증 사본 또는 자격 인정 조서 1부
+◦ 졸업증명서 사본 1부(원본지참)
+◦ 주민등록 초본 1부
+◦ 공무원채용신체검사서(1년 이내) 1부
+◦ 잠복결핵검사 확인서 1부(최초 검사의 확인서를 계속 사용 가능)
+◦ 마약/대마/향정신성의약품 검사결과통보서(진단서) 1부
+◦ 초임호봉획정을 위한 경력기간 합산신청서 1부
+◦ 범죄경력조회동의서 1부
+◦ 가족 채용 제한 여부 확인서 1부
+◦ 청렴 서약서 1부
+◆ 서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간: 2026. 10. 2.(금)~10. 7.(수) 10:00까지
+◦ 접수방법: 온라인 접수
+- 메일주소: [이메일]
+- 스캔파일 제출(제출서류 미비시 접수 불가), 면접 시 해당 서류 원본 제출
+나. 1차: 서류전형 합격자(만 개별 전화 통지) 발표 예정일 &gt; 2026. 10. 8.(목), 10:00 이후
+다. 2차: 면접(서류심사 합격자에 한함) 예정일 &gt; 2026. 10. 13.(화) 16:00, 교무실
+◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
+6. 합격자 발표
+◦ 최종합격자 발표: 2026. 10. 14.(수) 18:00 이후 (최종합격자에게만 개별 통지)
+7. 유의사항
+◦ 기간제교원 인력풀 등재자는 우선 임용될 수 있습니다.
+◦ 인력풀 등재자는 최종합격 후 확인이 불가능한 서류만 제출합니다.
+◦ 상기 일정은 진행 상황에 따라 변경될 수 있으며, 변경 시 별도 통보합니다.
+◦ 기재사항이 사실과 다르거나 허위로 작성된 경우는 합격을 취소합니다.
+◦ 제출 서류의 기재착오, 누락, 서류 미제출, 연락 불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.
+◦ 최종합격자로 발표된 이후에도 결격사유가 있는 자는 합격을 취소할 수 있습니다.
+◦ 기타 자세한 사항은 진해신항초등학교(☎551-2018)로 문의하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814721</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>밀양여자중학교</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>2026. 밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)
+가. 원서접수
+◦ 접수기간 : 2026. 10. 3.(토)～10. 7(수) 11:00까지
+◦ 접수장소 : 밀양여자중학교 전자우편
+◦ 접수방법 :  e-메일 접수([이메일], 스캔본 제출, 면접 시 원본 제출)
+2026. 10. 7(수). 11:00 발송분까지 유효함
+나. 1차 : 서류전형 합격자 발표(개별 문자 통지) 예정일 : 2026. 10. 8(목) 14:00(예정)
+다. 2차 : 면접 (서류심사 합격자에 한함) 예정일: 2026. 10. 12(월) 10:30(예정)
+◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
+**자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814716</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>성주초등학교 풍물동아리 외부 강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>성주초등학교</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 성주초등학교 풍물동아리 외부 강사 모집계획을 다음과 같이 공고합니다.
+가. 공고 기간
+2026년 10월 2일 (금) ~ 10월 7일 (수)
+나. 서류 접수
+2026년 10월 2일 (금) ~ 10월 7일 (수)  12:00 까지
+다. 접수 장소
+온라인 접수(전자우편 [이메일])
+(우편) 우편번호 51491 : 경남 창원시 성산구 가음정로 127 성주초등학교
+- 10. 7.(수) 12:00 도착분까지
+라. 1차 서류 심사: 2026년 10월 7일(수)
+▶ 1차 서류 심사 합격자에 한해 2차 면접 심사를 실시하여 최종 선정
+마. 1차 서류 심사 합격 통보: 2026년 10월 7일(수) 개별 통보
+바. 2차  면접 심사: 2026년 10월 8일(목), 면접 중 수업 시연 포함
+*장소 및 시간은 추후 안내
+사. 최종합격자 통보: 2026년 10월 8일(목) 17:00 이후 개별 통보
+아. 계약: 10월중 학교장과 계약
+※ 모집 일정은 학교 사정에 따라 변경될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814722</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>화정초등학교</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
@@ -1876,51 +3788,51 @@
 * 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>주동초등학교</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>2026년 주동초등학교에서는 초등 1~2학년 맞춤형프로그램과 관련하여 아래와 같이 외부강사(문화, 예술, 음악, 놀이영어 등 다양한 분야 지원 가능)를 모집하오니, 유능한 강사님들의 많은 지원 바랍니다.
 1.  서류접수:  2026.  10. 1.(목) ~ 2026. 10.  7.(수) 16시까지 도착분
@@ -1932,51 +3844,51 @@
 ※ 접수시간을 반드시 준수해 주시길 바랍니다.</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814652</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -1989,53 +3901,94 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n">
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>남지읍 평생학습센터 강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>창녕군</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>경남 창녕군</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -2049,110 +4002,230 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="O56" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>장애인거주시설(섬진강사랑의집) 수탁운영법인 모집 공고</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>하동군</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>경남 하동군</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>1. 위탁대상시설
+가. 시설명 : 섬진강사랑의집
+나. 시설규모 : 장애인거주시설 1개소(본관 3층, 별관 2층, 신관 2층)
+다. 주소 : 하동군 하동읍 화심길 15-11
+2. 위탁기간 : 2027. 1. 1. ~ 2031. 12. 31.(5년)
+3. 위탁범위
+가. 섬진강사랑의집 운영 및 관리
+- 하동군 장애인 생활시설 설치 및 운영 조례 제4조에 규정한 사무
+나. 기타 사회복지증진을 위한 위탁자가 정하는 사업
+다. 섬진강사랑의집의 공유재산과 물품관리
+4. 공고기간 및 신청서 접수
+가. 공고기간 : 2026. 10. 1. ~ 10. 16.(15일간, 공휴일 포함)
+나. 접수기간 : 2026. 10. 7. ~ 10. 16.(7일간)
+- 접수는 근무시간(09:00~18:00)내에만 접수함. 토요일, 공휴일은 제외
+다. 접수장소 : 하동군청 주민행복과
+라. 접수방법 : 직접방문 접수(우편, 이메일, 택배 등 불가)
+5. 신청자격 등 기타사항
+- 붙임 공고문 참조</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 55) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>감계중학교</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
+1. 채용 인원: 과학 1명
+2. 채용(계약) 기간 : 2026.10.7.~2026.10.16.(7일, 약 25시간)
+3. 제출 서류
+가. 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
+나. 자기소개서 1부.(붙임서식)
+다. 개인정보 수집·이용 동의서 1부.(붙임서식)
+※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -2163,51 +4236,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="O60" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -2259,47 +4332,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -2311,51 +4384,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="O62" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -2372,97 +4445,97 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="O63" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="O64" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>함양제일고등학교</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>10.26.(월)-11.11.(수)/ 총58시간</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
 1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
@@ -2471,68 +4544,423 @@
 -자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O30" s="5" t="inlineStr">
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>마산고등학교</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>기초학력전담강사 채용 공고문</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>대암초등학교</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
+□ 모집 인원 : 1명
+□ 채용 기간
+-  2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)
+□ 보수 : 시간당 25,000원
+□ 자격 기준
+1. 교원자격증 소지자, 임용 대기, 명예퇴직 교원 중 희망자
+2. 초․중등교육법시행령 제42조제1항 관련 ‘강사’ 자격 기준에 해당하는 자
+(교과보충 지도 강사, 방과후학교 강사 등 학생 지도 관련 유경험자 등)
+3. 국가공무원법 제33조에 각 호의 결격사유가 없는 자
+4. 임용 상한 연령: 62세 (다만, 1차 공개채용 모집시 결원 교원과 동일한 급별, 과목별 교원자격증 소지자의 지원자가 없을 경우에는 만 65세까지 2순위로 채용 가능)
+※ 학습코칭단, 두드림학교 외부강사 등 기초학력 지원사업 강사와 겸직 안 됨
+5. 우대 조건: 국가유공자 등은 관계 법률에 따라 가점 부여
+※「국가유공자 등 예우 및 지원에 관한 법률」제31조에 의함
+□ 근무처 : 대암초등학교
+* 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>진주여자중학교 학교스포츠강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>진주여자중학교</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>1. 종목: 축구 1명
+2. 심사일정 및 시험장소
+1) 서류심사: 2026.10.5.(월) ⇒ 1차 서류전형 합격자(2배수) 개별통지(16:00)
+2) 면접심사: 2026.10.6.(화) 13:00시, 3층 회의실
+3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n"/>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="5" t="n"/>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O69" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>일운초등학교</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="n"/>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>함안고등학교</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O71" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>고성군</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>경남 고성군</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="n"/>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O72" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>소토초등학교</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>1. 채용 구분
+1) 구분 및 인원: 한국어 교육 강사 1명
+2) 기간 및 근무 조건
+- 2026. 10. 19.(월)~ 2027. 2. (예산 소진시까지)
+- 주당 6시간 내외(총 64시간 내외)
+- 기간과 횟수, 시간 등은 강사나 학교 사정 등으로 변경될 수 있음
+- 보수: 시간당 30,000원
+2.  자격 요건
+1) 응시 연령 : 교육공무원 관련법에 준함(만 62세 이하)
+2) 국가공무원법 제33조에 의한 결격사유가 없는 자
+3) 채용 분야별 자격요건을 갖춘 자(해당 분야 전공자 및 자격증 소지자)
+4) 우대조건 : 한국어교원 자격증 소지
+5) 채용 우선 순위
+가) 한국어 강사 자격증 소지자
+나) 초·중등교원 자격증 소지자
+다) 한국어 지도 경력이 있는 자
+라) 관련 자격 소지 또는 해당 언어 전공자 등
+3. 기타 자세한 사항은 첨부된 공고문 참고</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="5" t="n"/>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="n"/>
+      <c r="M73" s="5" t="n"/>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O73" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2914,12 +2914,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>진영장등중학교 학교스포츠클럽 외부강사(대체) 채용공고</t>
+          <t>웅상고 계약제교원(학교폭력담당자 수업경감 시간강사) 2차 채용 공고</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>진영장등중학교</t>
+          <t>웅상고등학교</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2929,68 +2929,11 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>학교스포츠클럽 강사를 다음과 같이 채용하고자 합니다.
-1. 채용 분야 및 채용 인원: 학교스포츠클럽(축구) 강사 1명
-2. 접수기간: 2026. 9. 28.~2026. 10. 4.
-3. 접수방법: 학교 전자메일([이메일])
-※ 2026년 10월 4일 10:00 도착분에 한함.
-**채용(계약)기간 수정
-*자세한 내용은 첨부파일 참고하세요.</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814581</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>웅상고 계약제교원(학교폭력담당자 수업경감 시간강사) 2차 채용 공고</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>웅상고등학교</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>2026학년도 웅상고등학교에 근무할 기간제교사를 다음과 같이 채용 공고 합니다.
 1. 채용과목 및 응모 자격
@@ -3043,51 +2986,51 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814610</t>
         </is>
       </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>김해한일여고 2026학년도 시간강사(수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>김해한일여자고등학교</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>2026학년도 김해한일여자고등학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목 : 수학(1명)
@@ -3101,53 +3044,53 @@
 * 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n">
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814611</t>
         </is>
       </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>김해한일여고 2026학년도 결원대체 시간강사(진로진학) 채용 공고</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>김해한일여자고등학교</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>2026학년도 김해한일여자고등학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목 : 진로진학(1명)
@@ -3161,53 +3104,53 @@
 * 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n">
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814557</t>
         </is>
       </c>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>호암중학교 창체동아리(연극) 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>호암중학교</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>2026학년도 호암중학교 창체동아리(연극) 강사 채용 공고
 1) 종목 및 선발인원: 창체동아리 연극 (1명)
@@ -3220,51 +3163,51 @@
 *자세한 내용은 첨부 파일을 확인하세요</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814664</t>
         </is>
       </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>율하중 계약제교원(체육,영어 시간강사) 채용 계획</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -3276,51 +3219,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814563</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>[양산고] 결원대체강사(전일제-영어,정보,화학,수학,생물) 채용공고</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>양산고등학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>경남 양산시</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>양산고등학교 공고 제2026-65호
 2026학년도 양산고등학교 결원대체강사(시간강사)를 채용 공고합니다.
@@ -3339,51 +3282,51 @@
 (단, 적격자가 없을 경우 합격자 없이 재공고를 통한 업무 진행)</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814477</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>경운초등학교 돌봄교실 특기적성 외부강사 공고</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>경운초등학교</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>2026학년도 경운초등학교에 근무할 외부강사를 다음과 같이 채용 공고합니다.
 1. 채용과목 : 돌봄교실 특기적성 프로그램 : 공예놀이
@@ -3394,51 +3337,51 @@
 6. 최종 합격자 발표일 : 2026. 10. 8.(목) 11:00이후 개별통보* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814577</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>방과후학교 리코더 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>수양초등학교</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>수양초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 개인 위탁 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원
@@ -3456,53 +3399,53 @@
 ※ 자세한 내용은 첨부파일을 참고해 주시기 바랍다.</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814600</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 재공고(수학)</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>꽃내중학교</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집 공고
 꽃내중학교에서는 방과후학교 운영과 관련하여 아래와 같이 2026학년도 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
@@ -3522,51 +3465,51 @@
 ※. 자세한 사항은 첨부물을 참고하십시요.</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814587</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 80) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>진해신항초 계약제교원(전일제 강사) 채용 모집 공고</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>진해신항초등학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진해신항초등학교 계약제교원(전일제강사) 다음과 같이 채용 공고합니다.
 ◆ 채용내용
@@ -3612,51 +3555,51 @@
 ◦ 기타 자세한 사항은 진해신항초등학교(☎551-2018)로 문의하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814721</t>
         </is>
       </c>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>밀양여자중학교</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>2026. 밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)
 가. 원서접수
@@ -3670,51 +3613,51 @@
 **자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814716</t>
         </is>
       </c>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>성주초등학교 풍물동아리 외부 강사 모집 공고</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>성주초등학교</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성주초등학교 풍물동아리 외부 강사 모집계획을 다음과 같이 공고합니다.
 가. 공고 기간
@@ -3735,13 +3678,66 @@
 ※ 모집 일정은 학교 사정에 따라 변경될 수 있습니다.</t>
         </is>
       </c>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814722</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>화정초등학교</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
+1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
+2. 서류전형 합격자 개별 통보일 : 2026. 10. 8.(목) 14:00이후
+3. 접수방법 : 직접 방문 접수
+* 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
+        </is>
+      </c>
       <c r="G51" s="5" t="n"/>
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="n"/>
       <c r="J51" s="5" t="n"/>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814722</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
         </is>
       </c>
       <c r="L51" s="5" t="n"/>
@@ -3760,12 +3756,12 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
+          <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>화정초등학교</t>
+          <t>주동초등학교</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3780,59 +3776,6 @@
       </c>
       <c r="E52" s="5" t="n"/>
       <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
-1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
-2. 서류전형 합격자 개별 통보일 : 2026. 10. 8.(목) 14:00이후
-3. 접수방법 : 직접 방문 접수
-* 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>주동초등학교</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>2026년 주동초등학교에서는 초등 1~2학년 맞춤형프로그램과 관련하여 아래와 같이 외부강사(문화, 예술, 음악, 놀이영어 등 다양한 분야 지원 가능)를 모집하오니, 유능한 강사님들의 많은 지원 바랍니다.
 1.  서류접수:  2026.  10. 1.(목) ~ 2026. 10.  7.(수) 16시까지 도착분
@@ -3844,51 +3787,51 @@
 ※ 접수시간을 반드시 준수해 주시길 바랍니다.</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814652</t>
         </is>
       </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -3901,17 +3844,58 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>남지읍 평생학습센터 강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>창녕군</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남 창녕군</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
       <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="n"/>
       <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
-        </is>
-      </c>
+      <c r="K54" s="5" t="n"/>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="5" t="n"/>
       <c r="N54" s="5" t="inlineStr">
@@ -3921,74 +3905,33 @@
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>남지읍 평생학습센터 강사 모집 공고</t>
+          <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>동원고등학교</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>경남 창녕군</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O55" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>동원고등학교 결원대체강사 채용공고(수학)</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>동원고등학교</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -4002,113 +3945,51 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>장애인거주시설(섬진강사랑의집) 수탁운영법인 모집 공고</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>하동군</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>경남 하동군</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>감계중학교</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>1. 위탁대상시설
-가. 시설명 : 섬진강사랑의집
-나. 시설규모 : 장애인거주시설 1개소(본관 3층, 별관 2층, 신관 2층)
-다. 주소 : 하동군 하동읍 화심길 15-11
-2. 위탁기간 : 2027. 1. 1. ~ 2031. 12. 31.(5년)
-3. 위탁범위
-가. 섬진강사랑의집 운영 및 관리
-- 하동군 장애인 생활시설 설치 및 운영 조례 제4조에 규정한 사무
-나. 기타 사회복지증진을 위한 위탁자가 정하는 사업
-다. 섬진강사랑의집의 공유재산과 물품관리
-4. 공고기간 및 신청서 접수
-가. 공고기간 : 2026. 10. 1. ~ 10. 16.(15일간, 공휴일 포함)
-나. 접수기간 : 2026. 10. 7. ~ 10. 16.(7일간)
-- 접수는 근무시간(09:00~18:00)내에만 접수함. 토요일, 공휴일은 제외
-다. 접수장소 : 하동군청 주민행복과
-라. 접수방법 : 직접방문 접수(우편, 이메일, 택배 등 불가)
-5. 신청자격 등 기타사항
-- 붙임 공고문 참조</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O57" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 55) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>감계중학교</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -4120,112 +4001,112 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n">
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
         </is>
       </c>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="O56" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="O57" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -4236,51 +4117,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -4332,47 +4213,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -4384,51 +4265,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="inlineStr">
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O62" s="5" t="inlineStr">
+      <c r="O60" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -4445,13 +4326,112 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고등학교</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
+1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
+2. 과목: 특수
+3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
+-자세한 내용은 공고문 참조 바랍니다.</t>
+        </is>
+      </c>
       <c r="G63" s="5" t="n"/>
       <c r="H63" s="5" t="n"/>
       <c r="I63" s="5" t="n"/>
       <c r="J63" s="5" t="n"/>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
       <c r="L63" s="5" t="n"/>
@@ -4470,12 +4450,12 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>마산고등학교</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -4487,8 +4467,7 @@
       <c r="E64" s="5" t="n"/>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
       <c r="G64" s="5" t="n"/>
@@ -4497,7 +4476,7 @@
       <c r="J64" s="5" t="n"/>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
       <c r="L64" s="5" t="n"/>
@@ -4516,12 +4495,12 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
+          <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>함양제일고등학교</t>
+          <t>대암초등학교</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -4532,108 +4511,10 @@
       <c r="D65" s="5" t="n"/>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
+          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
-1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
-2. 과목: 특수
-3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
--자세한 내용은 공고문 참조 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
-      <c r="N65" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O65" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
-      <c r="N66" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O66" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>기초학력전담강사 채용 공고문</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>대암초등학교</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -4653,49 +4534,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="n">
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L67" s="5" t="n"/>
-      <c r="M67" s="5" t="n"/>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O67" s="5" t="inlineStr">
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -4704,13 +4585,104 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>일운초등학교</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+        </is>
+      </c>
       <c r="G68" s="5" t="n"/>
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="n"/>
       <c r="J68" s="5" t="n"/>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
         </is>
       </c>
       <c r="L68" s="5" t="n"/>
@@ -4729,12 +4701,12 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>함안고등학교</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -4746,8 +4718,8 @@
       <c r="E69" s="5" t="n"/>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
       <c r="G69" s="5" t="n"/>
@@ -4756,7 +4728,7 @@
       <c r="J69" s="5" t="n"/>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
         </is>
       </c>
       <c r="L69" s="5" t="n"/>
@@ -4775,35 +4747,31 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>일운초등학교</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 고성군</t>
         </is>
       </c>
       <c r="D70" s="5" t="n"/>
       <c r="E70" s="5" t="n"/>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
         </is>
       </c>
       <c r="G70" s="5" t="n"/>
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="n"/>
       <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
-        </is>
-      </c>
+      <c r="K70" s="5" t="n"/>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="5" t="n"/>
       <c r="N70" s="5" t="inlineStr">
@@ -4820,12 +4788,12 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>함안고등학교</t>
+          <t>소토초등학교</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -4836,93 +4804,6 @@
       <c r="D71" s="5" t="n"/>
       <c r="E71" s="5" t="n"/>
       <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
-자세한 내용은 첨부파일 확인 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
-        </is>
-      </c>
-      <c r="L71" s="5" t="n"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O71" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>고성군</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>경남 고성군</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="n"/>
-      <c r="L72" s="5" t="n"/>
-      <c r="M72" s="5" t="n"/>
-      <c r="N72" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O72" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교 한국어교육 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4944,23 +4825,23 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="5" t="n"/>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L73" s="5" t="n"/>
-      <c r="M73" s="5" t="n"/>
-      <c r="N73" s="5" t="inlineStr">
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O73" s="5" t="inlineStr">
+      <c r="O71" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>한일여고 전일제 시간강사(기계) 채용 공고</t>
+          <t>성호초등학교 전일제강사 채용 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>한일여자고등학교</t>
+          <t>성호초등학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -645,108 +645,10 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026년 10월 22일~10월 30일</t>
+          <t>2026.10.7.~ 2026.10.21.(15일)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 한일여고 전일제시간강사(기계) 채용공고
-1. 채용분야: 전일제시간강사
-2. 접수기간: 2026년 9월 30일~10월 5일 10:00
-3. 채용기간: 2026년 10월 22일~10월 30일
-자세한 사항은 붙임의 공고문을 참고해주세요.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814634</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>한일여고 시간강사(청소년비즈쿨 사업운영 보결강사) 채용</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>한일여자고등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 19일~11월 6일</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 한일여고 시간강사(청소년비즈쿨 사업운영 보결강사) 채용공고
-1. 채용분야: 시간강사(영어)
-2. 접수기간: 2026년 9월 30일~10월 5일 10:00
-3. 채용기간: 2026년 10월 19일~11월 6일
-자세한 사항은 붙임의 공고문을 참고해주세요.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814635</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>성호초등학교 전일제강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>성호초등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.7.~ 2026.10.21.(15일)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 공고 합니다.
 1. 채용과목 및 인원: 특수교사 1명
@@ -757,49 +659,49 @@
 *자세한 사항은 붙임 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>합포고등학교 계약제교원(전일제 강사) 채용 재공고(국어)(3차)</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>합포고등학교</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026.10.14.(수)~2026.10.23.(금) (총 8일)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>2026학년도 합포고등학교에서 근무할 계약제교원(전일제강사) 채용을 다음과 같이 공고합니다.
 1. 채용 과목 및 인원: 국어(1)
@@ -815,47 +717,47 @@
 기타 자세한 사항은 첨부파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814629</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2026.10.30.(총16시간)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모자격
@@ -883,49 +785,49 @@
 5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>시간강사(과학과) 채용 공고</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>구산고등학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~ 2026. 10. 30. (총17시수)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>구산고등학교 공고 제2026-48호
 본교 교사의 결원을 대체할 시간강사 채용을 아래와 같이 채용 공고하고자 합니다.
@@ -942,49 +844,49 @@
 자세한 내용은 붙임파일 참조바랍니다.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814670</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>대청중학교 결원대체강사 (특수) 2차 채용 공고</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>대청중학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026.10.16.(금)~2026.10.19.(월) (2일)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목 : 특수 (시간제)
 2. 채용기간 : 2026.10.16.(금)~2026.10.19.(월) (2일)
@@ -998,47 +900,47 @@
 감사합니다.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814570</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>교방초등학교 방과후학교 개인위탁 외부강사[티볼] 모집 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>교방초등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026.11.1. ~2027.2.16.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>[ 2026학년도 교방초 방과후학교 개인위탁외부강사 모집 공고 ]
 교방초등학교에서는
@@ -1052,49 +954,49 @@
 6. 모집 세부 사항: 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814603</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 수학 시간강사 채용 공고</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026.10. 12. ~ 2026.11.18. (주당18시간)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 시간강사 채용 공고
 1. 채용내용 : 수학 1명
@@ -1108,51 +1010,51 @@
 ※ 기타 자세한 사항은 공고문을 참고 하시기 바랍니다. ※ 관심 있는 분들의 많은 지원 바랍니다</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부, 기타 구비서류(채용합격자에 한해 별도안내)</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814606</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>양산제일고등학교 전일제 강사(수학) 채용 3차 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>양산제일고등학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 07. ~ 2026. 10. 30.</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 수학(1명)
 2. 채용기간: 2026. 10. 07. ~ 2026. 10. 30.
@@ -1164,49 +1066,49 @@
 8. 기타 자세한 사항은 첨부 문서(공고문)를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814677</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>방과후학교 방송댄스 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>합성초등학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 29 ~ 2027. 2. 26.(학교사정에 따라 변동 될 수 있음)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>합성초등학교에서는 2026. 방과후학교 방송댄스 개인위탁 외부강사를 모집합니다.
 관심 있는 분들의 많은 지원 바랍니다.
@@ -1219,49 +1121,49 @@
 바. 문의사항 : 교무실 256-2696</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814636</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>마산여자고등학교 계약제교원(전일제강사-윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>마산여자고등학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.(월)~2026.10.19.(월) 총 6일 / 일당 110,000원</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산여자고등학교에 근무할 계약제교원 전일제강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 도덕·윤리(1명)
@@ -1295,53 +1197,53 @@
 자세한 사항은 첨부파일 확인바랍니다.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>동일 과목 중등교사 자격증 소지자 지원 가능</t>
         </is>
       </c>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814705</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>봉명초 돌봄교실 특기적성 프로그램 강사 추가 모집</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>봉명초등학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 12일∼2027년 2월 26일 / 학기 중 : 14:00~15:30  ,   방학 중 : 13:00~ 14:30</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>2026학년도 초등돌봄교실 특기적성 개인위탁 외부강사를 다음과 같이 추가 공고 모집하고자 합니다.
 1. 모집 분야 및 인원순
@@ -1381,47 +1283,47 @@
 ※ 자세한 사항은 첨부파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814672</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>남양초등학교 돌봄교실 특기적성프로그램 개인 위탁 외부강사 채용 공고</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>남양초등학교</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2027. 2. 24.(수) / 금요일(13:50~14:30, 14:40~15:20, 15:30~16:10)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>2026학년도 남양초등학교 돌봄교실 특기적성 프로그램 외부강사를 아래와 같이 모집하오니
 관심있는 분들의 많은 지원 바랍니다.
@@ -1437,49 +1339,49 @@
 5. 기타 자세한 내용은 첨부파일을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814493</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교 시간강사(수학) 채용</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 15~2026. 10. 23</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교에서 근무할 시간강사를 다음과 같이 채용 공고합니다.
 - 채용기간 : 2026. 10. 15~2026. 10. 23
@@ -1489,47 +1391,47 @@
 자세한 내용은 첨부파일을 참고해주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814706</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>악양초등학교. 결원 대체 강사 채용 공고(전일제강사)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>악양초등학교</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026.10.26 ~ 2026.10.30.(총5일)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>2026학년도 악양초등학교에 근무할 결원 대체 강사를 다음과 같이 채용 공고 안내
 1. 채용과목 : 초등(전일제강사 1명)
@@ -1548,59 +1450,59 @@
 * 자세한 사항은 붙임 공고문을 참조바랍니다.</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>1순위: 만 62세 미만 동일 자격 소지자
 2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
 1순위 지원자 없을 시  2순위자 채용 가능</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재), 자기소개서 1부.(붙임서식), 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814642</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>대방중학교 전일제강사(기술·가정과) 채용 공고</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>대방중학교</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 9일 ~ 2026년 11월 13일(5일)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>2026학년도 대방중학교 기술·가정과 전일제강사를 다음과 같이 채용 공고합니다.
 1. 접수기간: 2026년 10월 2일(금) ~ 2026년 10월 7일(수), 09:00까지 도착분에 한함
@@ -1612,47 +1514,47 @@
 기타 자세한 사항은 붙임 문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814661</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>계동초 방과후학교 프로그램 개인위탁 외부강사(한자속독) 모집 공고</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>계동초등학교</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 1일 ∼ 2027년 2월 28일</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>2026. 계동초 방과후학교 프로그램(한자속독) 개인위탁 외부강사를 다음과 같이 모집합니다.
 1. 계약 기간: 2026년 11월 1일 ∼ 2027년 2월 28일
@@ -1666,49 +1568,49 @@
 -자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n">
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814720</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>분성초등학교 방과후학교 외부강사 모집 공고(바이올린)</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>분성초등학교</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 3. ~ 2027. 2. 25.</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>2026. 분성초 방과후학교 바이올린 개인위탁 외부강사를 다음과 같이 모집합니다.
 1. 계약 기간: 2026. 11. 3. ~ 2027. 2. 25.
@@ -1725,47 +1627,47 @@
 -자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814693</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교 결원대체시간강사(수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고입니다.
 1. 채용과목 및 인원, 채용기간
@@ -1785,49 +1687,49 @@
 ※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n">
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814688</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교 결원대체강사(과학 전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>2026학년도 삼정자중학교 결원대체강사(과학)를 다음과 같이 채용하고자 합니다.
 1. 채용과목 및 채용 내용
@@ -1850,49 +1752,49 @@
 **자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814686</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교 결원대체 시간강사(1순위:윤리, 2순위:일반사회) 채용 공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.(월)~2026. 10. 30.(금) (총 17시간)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원중앙고등학교 결원대체 시간강사 채용을 다음과 같이 공고합니다.
 1. 채용과목 : 윤리(1순위:윤리, 2순위:일반사회)
@@ -1903,47 +1805,47 @@
 * 자세한 사항은 첨부파일 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814730</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>김해내동초 돌봄 프로그램(종이접기 1명) 외부강사 모집 공고문</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>김해내동초등학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2027.2.28.</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>2026. 김해내동초 돌봄 프로그램(종이 접기 1명)외부 강사 모집 공고를  아래와 같이 실시합니다.
 1. 모집 인원: 1명
@@ -1953,49 +1855,49 @@
 5. 기타 자세한 사항은 첨부 문서를 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814620</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>증산중학교 계약제교원(시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -2009,49 +1911,49 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814584</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>동진초등학교 2026.10.12.자 계약제교원(결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>동진초등학교</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 10. 17.(5일)</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등교사
 나. 채용 기간: 2026. 10. 12. ~ 2026. 10. 17.(5일)
@@ -2063,49 +1965,49 @@
 ※ 국가공무원법 제33조의 규정에 의한 공무원임용 결격사유가 없는 자</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814468</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -2158,49 +2060,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n">
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -2251,49 +2153,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n">
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -2317,47 +2219,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(기술 가정) 채용 공고</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고
 합니다.
@@ -2382,49 +2284,49 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n">
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -2475,19 +2377,119 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
+      <c r="H29" s="5" t="n">
+        <v>8046</v>
+      </c>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>유목초 특수학급 결원대체강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n">
-        <v>8046</v>
+        <v>1</v>
       </c>
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
         </is>
       </c>
       <c r="L31" s="5" t="n"/>
@@ -2498,12 +2500,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
+          <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>유목초등학교</t>
+          <t>내곡초등학교</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -2513,31 +2515,32 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2026.10.6.~2026.10.16.</t>
+          <t>2026.10.1.~2026.10.23.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>구체적인 내용은 공고문을 참고바랍니다.
-1. 분야: 특수학급 결원대체강사
-2. 채용인원: 1명
-3.기간: 2026.10.6.~2026.10.16.</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명
+2. 기간: 2026.10.1.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
         </is>
       </c>
       <c r="L32" s="5" t="n"/>
@@ -2548,12 +2551,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>유목초 특수학급 결원대체강사 채용 공고</t>
+          <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>유목초등학교</t>
+          <t>유영초등학교</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -2563,20 +2566,20 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>2026.10.6.~2026.10.16.</t>
+          <t>2026.10.12.~2026.10.30.(19일간)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>구체적인 내용은 공고문을 참고바랍니다.
-1. 분야: 특수학급 결원대체강사
-2. 채용인원: 1명
-3.기간: 2026.10.6.~2026.10.16.</t>
+          <t>1. 채용과목: 초등 결원대체 강사(전일제)
+2. 채용 인원: 1명
+3. 채용기간: 2026.10.12.~2026.10.30.(19일간)
+4. 자세한 사항은 첨부파일 참조</t>
         </is>
       </c>
       <c r="G33" s="5" t="n"/>
@@ -2587,7 +2590,7 @@
       <c r="J33" s="5" t="n"/>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
         </is>
       </c>
       <c r="L33" s="5" t="n"/>
@@ -2598,12 +2601,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
+          <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>내곡초등학교</t>
+          <t>남지초등학교</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2613,116 +2616,15 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2026.10.1.~2026.10.23.</t>
+          <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>아래와 같이 결원대체강사 채용을 공고합니다.
-1. 대상: 초등교사 1명
-2. 기간: 2026.10.1.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>초등교사 1명</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>유영초등학교</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.12.~2026.10.30.(19일간)</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>1. 채용과목: 초등 결원대체 강사(전일제)
-2. 채용 인원: 1명
-3. 채용기간: 2026.10.12.~2026.10.30.(19일간)
-4. 자세한 사항은 첨부파일 참조</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>남지초등학교</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등기간제교원
 나. 채용 기간: 2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)
@@ -2735,49 +2637,49 @@
 ※자세한 사항은 공고문 참고</t>
         </is>
       </c>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n">
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
 1. 채용과목: 영어(1명)
@@ -2785,49 +2687,49 @@
 상세내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n">
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
         </is>
       </c>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="n"/>
-      <c r="O37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -2882,15 +2784,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="H36" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -2900,40 +2802,40 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="n"/>
-      <c r="O38" s="5" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(학교폭력담당자 수업경감 시간강사) 2차 채용 공고</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>2026학년도 웅상고등학교에 근무할 기간제교사를 다음과 같이 채용 공고 합니다.
 1. 채용과목 및 응모 자격
@@ -2986,51 +2888,51 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814610</t>
         </is>
       </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>김해한일여고 2026학년도 시간강사(수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>김해한일여자고등학교</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>2026학년도 김해한일여자고등학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목 : 수학(1명)
@@ -3044,53 +2946,53 @@
 * 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n">
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814611</t>
         </is>
       </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>김해한일여고 2026학년도 결원대체 시간강사(진로진학) 채용 공고</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>김해한일여자고등학교</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>2026학년도 김해한일여자고등학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목 : 진로진학(1명)
@@ -3104,53 +3006,53 @@
 * 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n">
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814557</t>
         </is>
       </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>호암중학교 창체동아리(연극) 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>호암중학교</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>2026학년도 호암중학교 창체동아리(연극) 강사 채용 공고
 1) 종목 및 선발인원: 창체동아리 연극 (1명)
@@ -3163,51 +3065,51 @@
 *자세한 내용은 첨부 파일을 확인하세요</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814664</t>
         </is>
       </c>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>율하중 계약제교원(체육,영어 시간강사) 채용 계획</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -3219,51 +3121,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814563</t>
         </is>
       </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>[양산고] 결원대체강사(전일제-영어,정보,화학,수학,생물) 채용공고</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>양산고등학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>경남 양산시</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>양산고등학교 공고 제2026-65호
 2026학년도 양산고등학교 결원대체강사(시간강사)를 채용 공고합니다.
@@ -3282,51 +3184,51 @@
 (단, 적격자가 없을 경우 합격자 없이 재공고를 통한 업무 진행)</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814477</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>경운초등학교 돌봄교실 특기적성 외부강사 공고</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>경운초등학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>2026학년도 경운초등학교에 근무할 외부강사를 다음과 같이 채용 공고합니다.
 1. 채용과목 : 돌봄교실 특기적성 프로그램 : 공예놀이
@@ -3337,51 +3239,51 @@
 6. 최종 합격자 발표일 : 2026. 10. 8.(목) 11:00이후 개별통보* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814577</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>방과후학교 리코더 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>수양초등학교</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>수양초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 개인 위탁 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원
@@ -3399,53 +3301,53 @@
 ※ 자세한 내용은 첨부파일을 참고해 주시기 바랍다.</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n">
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814600</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 재공고(수학)</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>꽃내중학교</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집 공고
 꽃내중학교에서는 방과후학교 운영과 관련하여 아래와 같이 2026학년도 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
@@ -3465,51 +3367,51 @@
 ※. 자세한 사항은 첨부물을 참고하십시요.</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814587</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 80) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>진해신항초 계약제교원(전일제 강사) 채용 모집 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>진해신항초등학교</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진해신항초등학교 계약제교원(전일제강사) 다음과 같이 채용 공고합니다.
 ◆ 채용내용
@@ -3555,51 +3457,51 @@
 ◦ 기타 자세한 사항은 진해신항초등학교(☎551-2018)로 문의하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814721</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>밀양여자중학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>2026. 밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)
 가. 원서접수
@@ -3613,51 +3515,51 @@
 **자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814716</t>
         </is>
       </c>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>성주초등학교 풍물동아리 외부 강사 모집 공고</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>성주초등학교</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성주초등학교 풍물동아리 외부 강사 모집계획을 다음과 같이 공고합니다.
 가. 공고 기간
@@ -3678,51 +3580,51 @@
 ※ 모집 일정은 학교 사정에 따라 변경될 수 있습니다.</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814722</t>
         </is>
       </c>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>화정초등학교</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
@@ -3731,51 +3633,51 @@
 * 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
         </is>
       </c>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>주동초등학교</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>2026년 주동초등학교에서는 초등 1~2학년 맞춤형프로그램과 관련하여 아래와 같이 외부강사(문화, 예술, 음악, 놀이영어 등 다양한 분야 지원 가능)를 모집하오니, 유능한 강사님들의 많은 지원 바랍니다.
 1.  서류접수:  2026.  10. 1.(목) ~ 2026. 10.  7.(수) 16시까지 도착분
@@ -3787,51 +3689,51 @@
 ※ 접수시간을 반드시 준수해 주시길 바랍니다.</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814652</t>
         </is>
       </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="O50" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -3844,94 +3746,94 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n">
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
         </is>
       </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>남지읍 평생학습센터 강사 모집 공고</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>창녕군</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>경남 창녕군</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O54" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -3945,51 +3847,51 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -4001,112 +3903,112 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n">
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
         </is>
       </c>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -4117,51 +4019,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="O56" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -4213,47 +4115,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="O57" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -4265,51 +4167,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -4326,13 +4228,112 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고등학교</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
+1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
+2. 과목: 특수
+3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
+-자세한 내용은 공고문 참조 바랍니다.</t>
+        </is>
+      </c>
       <c r="G61" s="5" t="n"/>
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="n"/>
       <c r="J61" s="5" t="n"/>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
       <c r="L61" s="5" t="n"/>
@@ -4351,12 +4352,12 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>마산고등학교</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -4368,8 +4369,7 @@
       <c r="E62" s="5" t="n"/>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
       <c r="G62" s="5" t="n"/>
@@ -4378,7 +4378,7 @@
       <c r="J62" s="5" t="n"/>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
       <c r="L62" s="5" t="n"/>
@@ -4397,12 +4397,12 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
+          <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>함양제일고등학교</t>
+          <t>대암초등학교</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -4413,108 +4413,10 @@
       <c r="D63" s="5" t="n"/>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
+          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
-1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
-2. 과목: 특수
-3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
--자세한 내용은 공고문 참조 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="n"/>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
-        </is>
-      </c>
-      <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
-      <c r="N63" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O63" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
-        </is>
-      </c>
-      <c r="L64" s="5" t="n"/>
-      <c r="M64" s="5" t="n"/>
-      <c r="N64" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O64" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>기초학력전담강사 채용 공고문</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>대암초등학교</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -4534,49 +4436,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="n">
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O65" s="5" t="inlineStr">
+      <c r="O63" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -4585,13 +4487,104 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>일운초등학교</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+        </is>
+      </c>
       <c r="G66" s="5" t="n"/>
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="n"/>
       <c r="J66" s="5" t="n"/>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
         </is>
       </c>
       <c r="L66" s="5" t="n"/>
@@ -4610,12 +4603,12 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>함안고등학교</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -4627,8 +4620,8 @@
       <c r="E67" s="5" t="n"/>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
       <c r="G67" s="5" t="n"/>
@@ -4637,7 +4630,7 @@
       <c r="J67" s="5" t="n"/>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
         </is>
       </c>
       <c r="L67" s="5" t="n"/>
@@ -4656,35 +4649,31 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>일운초등학교</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 고성군</t>
         </is>
       </c>
       <c r="D68" s="5" t="n"/>
       <c r="E68" s="5" t="n"/>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
         </is>
       </c>
       <c r="G68" s="5" t="n"/>
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="n"/>
       <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
-        </is>
-      </c>
+      <c r="K68" s="5" t="n"/>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="5" t="n"/>
       <c r="N68" s="5" t="inlineStr">
@@ -4701,12 +4690,12 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>함안고등학교</t>
+          <t>소토초등학교</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -4717,93 +4706,6 @@
       <c r="D69" s="5" t="n"/>
       <c r="E69" s="5" t="n"/>
       <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
-자세한 내용은 첨부파일 확인 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
-        </is>
-      </c>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
-      <c r="N69" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O69" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>고성군</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>경남 고성군</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n"/>
-      <c r="L70" s="5" t="n"/>
-      <c r="M70" s="5" t="n"/>
-      <c r="N70" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O70" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교 한국어교육 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4825,23 +4727,23 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L71" s="5" t="n"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O71" s="5" t="inlineStr">
+      <c r="O69" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>성호초등학교 전일제강사 채용 공고</t>
+          <t>대청중학교 결원대체강사 (특수) 2차 채용 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>성호초등학교</t>
+          <t>대청중학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -640,253 +640,15 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026.10.7.~ 2026.10.21.(15일)</t>
+          <t>2026.10.16.(금)~2026.10.19.(월) (2일)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 공고 합니다.
-1. 채용과목 및 인원: 특수교사 1명
-2. 채용기간: 2026.10.7.~ 2026.10.21.(15일)
-3. 접수기간: 2026.9.29.(화) ~ 10.5.(월) 15:00까지
-4. 접수장소 및 방법: 성호초등학교 대표메일([이메일])로 제출
-(현장접수 가능/ 면접 시 원본 제출)
-*자세한 사항은 붙임 참고 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>합포고등학교 계약제교원(전일제 강사) 채용 재공고(국어)(3차)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>합포고등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.14.(수)~2026.10.23.(금) (총 8일)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 합포고등학교에서 근무할 계약제교원(전일제강사) 채용을 다음과 같이 공고합니다.
-1. 채용 과목 및 인원: 국어(1)
-2. 채용 기간: 2026.10.14.(수)~2026.10.23.(금) (총 8일)
-3. 접수기간: 2026.9.30.(수) ~ 10.05.(월) 17:00까지
-4. 접수방법: 학교전자우편 접수([이메일], 면접 시 원본 제출 요망)
-5. 서류전형 합격자 발표(개별통지): 2026.10.06.(화) 15:00 이후
-6. 면접일시: 2026.10.07.(수) 09:40
-(일시 및 장소는 서류전형 합격자에게만 개별 통보)
-7. 최종 합격자 발표: 2026.10.07.(수) 15:00 이후
-(최종 합격자에 한하여 전화 또는 문자로 개별 통지)
-8. 문의 : 합포고 교무실([전화번호])
-기타 자세한 사항은 첨부파일을 참고하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814629</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>마산가포고등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.26.~2026.10.30.(총16시간)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
-1. 채용내용 및 응모자격
-가. 채용과목 및 인원: 지리 1명(1순위: 지리, 2순위: 일반사회, 윤리)
-나. 채용기간: 2026.10.26.~2026.10.30.(총16시간)
-다. 수당: 시간당 35,000원
-라. 응모자격
-1) 1순위: 만 62세 미만의 결원 교원과 동일 학교급 및 과목 자격증 소지자
-2) 2순위: 만 62세 미만의 결원 교원과 다른 학교급 또는 유사 과목* 자격증 소지자, 정년퇴직자 혹은 명예퇴직자
-※ 1차 모집 공고부터 우선순위를 정하여 1순위 지원자가 없을 시 후 순위 지원자 채용 가능
-2. 전형방법
-가. 1차 시험 : 서류전형(채용 예정 인원의 3배수 이내 선발)
-나. 2차 시험 : 면접(1차 서류 전형 합격자에 한하여 실시하며, 대상자에게 개별 통보)
-3. 응시자 제출서류
-가. 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
-나. 자기소개서 1부.(붙임서식)
-다. 계약제교원 채용을 위한 개인정보 수집 이용 동의서 1부.(붙임서식)
-4. 서류접수 및 전형일정
-가. 원서접수
-- 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 5.(월) 24:00까지
-- 접수방법 : 온라인접수([이메일] 스캔본 제출, 면접 시 원본제출, 2026. 10. 5.(월) 24:00 발송분까지)
-나. 1차 서류 전형 합격자 발표 : 2026. 10. 6.(화) 14:00 이후(1차 서류 전형 합격자에 한해 개별 통보)
-다. 2차 면접 : 2026. 10. 7.(수) 10:00~
-라. 최종합격자 발표 : 2026. 10. 7.(수) 14:00 이후 개별통보
-5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>시간강사(과학과) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>구산고등학교</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 26.~ 2026. 10. 30. (총17시수)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>구산고등학교 공고 제2026-48호
-본교 교사의 결원을 대체할 시간강사 채용을 아래와 같이 채용 공고하고자 합니다.
-1. 채용 과목 및 인원: 과학과(지구과학, 물리, 화학, 생명과학, 공통과학) 1명
-2. 채용기간: 2026. 10. 26.~ 2026. 10. 30. (총17시수)
-3. 채용 시험 일정
-가. 응시원서접수
-1) 접수기간: 2026. 10. 1.(목)~2026. 10. 5.(월)
-2) 접수방법: 전자메일 접수
-나. 시험일정
-1) 1차서류심사: 2026. 10. 6.(화) 개별통보
-2) 2차면접심사: 2026. 10. 7.(수) 개별통보
-3) 합격자 발표: 2026. 10. 7.(수) 최종확정자 개별통보
-자세한 내용은 붙임파일 참조바랍니다.</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814670</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>대청중학교 결원대체강사 (특수) 2차 채용 공고</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>대청중학교</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.16.(금)~2026.10.19.(월) (2일)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목 : 특수 (시간제)
 2. 채용기간 : 2026.10.16.(금)~2026.10.19.(월) (2일)
@@ -900,47 +662,47 @@
 감사합니다.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814570</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>교방초등학교 방과후학교 개인위탁 외부강사[티볼] 모집 공고</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>교방초등학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026.11.1. ~2027.2.16.</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>[ 2026학년도 교방초 방과후학교 개인위탁외부강사 모집 공고 ]
 교방초등학교에서는
@@ -954,49 +716,49 @@
 6. 모집 세부 사항: 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814603</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 수학 시간강사 채용 공고</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026.10. 12. ~ 2026.11.18. (주당18시간)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 시간강사 채용 공고
 1. 채용내용 : 수학 1명
@@ -1010,51 +772,51 @@
 ※ 기타 자세한 사항은 공고문을 참고 하시기 바랍니다. ※ 관심 있는 분들의 많은 지원 바랍니다</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부, 기타 구비서류(채용합격자에 한해 별도안내)</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814606</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>양산제일고등학교 전일제 강사(수학) 채용 3차 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>양산제일고등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 07. ~ 2026. 10. 30.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 수학(1명)
 2. 채용기간: 2026. 10. 07. ~ 2026. 10. 30.
@@ -1066,49 +828,49 @@
 8. 기타 자세한 사항은 첨부 문서(공고문)를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814677</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>방과후학교 방송댄스 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>합성초등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 29 ~ 2027. 2. 26.(학교사정에 따라 변동 될 수 있음)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>합성초등학교에서는 2026. 방과후학교 방송댄스 개인위탁 외부강사를 모집합니다.
 관심 있는 분들의 많은 지원 바랍니다.
@@ -1121,49 +883,49 @@
 바. 문의사항 : 교무실 256-2696</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814636</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>마산여자고등학교 계약제교원(전일제강사-윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>마산여자고등학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.(월)~2026.10.19.(월) 총 6일 / 일당 110,000원</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산여자고등학교에 근무할 계약제교원 전일제강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 도덕·윤리(1명)
@@ -1197,53 +959,53 @@
 자세한 사항은 첨부파일 확인바랍니다.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>동일 과목 중등교사 자격증 소지자 지원 가능</t>
         </is>
       </c>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814705</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>봉명초 돌봄교실 특기적성 프로그램 강사 추가 모집</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>봉명초등학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 12일∼2027년 2월 26일 / 학기 중 : 14:00~15:30  ,   방학 중 : 13:00~ 14:30</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2026학년도 초등돌봄교실 특기적성 개인위탁 외부강사를 다음과 같이 추가 공고 모집하고자 합니다.
 1. 모집 분야 및 인원순
@@ -1283,47 +1045,47 @@
 ※ 자세한 사항은 첨부파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814672</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>남양초등학교 돌봄교실 특기적성프로그램 개인 위탁 외부강사 채용 공고</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>남양초등학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2027. 2. 24.(수) / 금요일(13:50~14:30, 14:40~15:20, 15:30~16:10)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>2026학년도 남양초등학교 돌봄교실 특기적성 프로그램 외부강사를 아래와 같이 모집하오니
 관심있는 분들의 많은 지원 바랍니다.
@@ -1339,49 +1101,49 @@
 5. 기타 자세한 내용은 첨부파일을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814493</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교 시간강사(수학) 채용</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 15~2026. 10. 23</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교에서 근무할 시간강사를 다음과 같이 채용 공고합니다.
 - 채용기간 : 2026. 10. 15~2026. 10. 23
@@ -1391,47 +1153,47 @@
 자세한 내용은 첨부파일을 참고해주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814706</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>악양초등학교. 결원 대체 강사 채용 공고(전일제강사)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>악양초등학교</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026.10.26 ~ 2026.10.30.(총5일)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>2026학년도 악양초등학교에 근무할 결원 대체 강사를 다음과 같이 채용 공고 안내
 1. 채용과목 : 초등(전일제강사 1명)
@@ -1450,59 +1212,59 @@
 * 자세한 사항은 붙임 공고문을 참조바랍니다.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>1순위: 만 62세 미만 동일 자격 소지자
 2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
 1순위 지원자 없을 시  2순위자 채용 가능</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재), 자기소개서 1부.(붙임서식), 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814642</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>대방중학교 전일제강사(기술·가정과) 채용 공고</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>대방중학교</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 9일 ~ 2026년 11월 13일(5일)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>2026학년도 대방중학교 기술·가정과 전일제강사를 다음과 같이 채용 공고합니다.
 1. 접수기간: 2026년 10월 2일(금) ~ 2026년 10월 7일(수), 09:00까지 도착분에 한함
@@ -1514,47 +1276,47 @@
 기타 자세한 사항은 붙임 문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814661</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>계동초 방과후학교 프로그램 개인위탁 외부강사(한자속독) 모집 공고</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>계동초등학교</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 1일 ∼ 2027년 2월 28일</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>2026. 계동초 방과후학교 프로그램(한자속독) 개인위탁 외부강사를 다음과 같이 모집합니다.
 1. 계약 기간: 2026년 11월 1일 ∼ 2027년 2월 28일
@@ -1568,49 +1330,49 @@
 -자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814720</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>분성초등학교 방과후학교 외부강사 모집 공고(바이올린)</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>분성초등학교</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 3. ~ 2027. 2. 25.</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>2026. 분성초 방과후학교 바이올린 개인위탁 외부강사를 다음과 같이 모집합니다.
 1. 계약 기간: 2026. 11. 3. ~ 2027. 2. 25.
@@ -1627,47 +1389,47 @@
 -자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814693</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교 결원대체시간강사(수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고입니다.
 1. 채용과목 및 인원, 채용기간
@@ -1687,49 +1449,49 @@
 ※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814688</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교 결원대체강사(과학 전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>2026학년도 삼정자중학교 결원대체강사(과학)를 다음과 같이 채용하고자 합니다.
 1. 채용과목 및 채용 내용
@@ -1752,49 +1514,49 @@
 **자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814686</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교 결원대체 시간강사(1순위:윤리, 2순위:일반사회) 채용 공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.(월)~2026. 10. 30.(금) (총 17시간)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원중앙고등학교 결원대체 시간강사 채용을 다음과 같이 공고합니다.
 1. 채용과목 : 윤리(1순위:윤리, 2순위:일반사회)
@@ -1805,47 +1567,47 @@
 * 자세한 사항은 첨부파일 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814730</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>김해내동초 돌봄 프로그램(종이접기 1명) 외부강사 모집 공고문</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>김해내동초등학교</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2027.2.28.</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>2026. 김해내동초 돌봄 프로그램(종이 접기 1명)외부 강사 모집 공고를  아래와 같이 실시합니다.
 1. 모집 인원: 1명
@@ -1855,49 +1617,49 @@
 5. 기타 자세한 사항은 첨부 문서를 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n">
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814620</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>증산중학교 계약제교원(시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1911,49 +1673,49 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n">
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814584</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>동진초등학교 2026.10.12.자 계약제교원(결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>동진초등학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 10. 17.(5일)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등교사
 나. 채용 기간: 2026. 10. 12. ~ 2026. 10. 17.(5일)
@@ -1965,49 +1727,49 @@
 ※ 국가공무원법 제33조의 규정에 의한 공무원임용 결격사유가 없는 자</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814468</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -2060,49 +1822,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -2153,49 +1915,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -2219,47 +1981,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(기술 가정) 채용 공고</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고
 합니다.
@@ -2284,49 +2046,49 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -2377,19 +2139,220 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
+      <c r="H25" s="5" t="n">
+        <v>8046</v>
+      </c>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>유목초 특수학급 결원대체강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>내곡초등학교</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.1.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명
+2. 기간: 2026.10.1.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>유영초등학교</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.12.~2026.10.30.(19일간)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>1. 채용과목: 초등 결원대체 강사(전일제)
+2. 채용 인원: 1명
+3. 채용기간: 2026.10.12.~2026.10.30.(19일간)
+4. 자세한 사항은 첨부파일 참조</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n">
-        <v>8046</v>
+        <v>1</v>
       </c>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
         </is>
       </c>
       <c r="L29" s="5" t="n"/>
@@ -2400,12 +2363,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
+          <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>유목초등학교</t>
+          <t>남지초등학교</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2415,216 +2378,15 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2026.10.6.~2026.10.16.</t>
+          <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>구체적인 내용은 공고문을 참고바랍니다.
-1. 분야: 특수학급 결원대체강사
-2. 채용인원: 1명
-3.기간: 2026.10.6.~2026.10.16.</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>유목초 특수학급 결원대체강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>유목초등학교</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.6.~2026.10.16.</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>구체적인 내용은 공고문을 참고바랍니다.
-1. 분야: 특수학급 결원대체강사
-2. 채용인원: 1명
-3.기간: 2026.10.6.~2026.10.16.</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>내곡초등학교</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.1.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>아래와 같이 결원대체강사 채용을 공고합니다.
-1. 대상: 초등교사 1명
-2. 기간: 2026.10.1.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>초등교사 1명</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>유영초등학교</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.12.~2026.10.30.(19일간)</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>1. 채용과목: 초등 결원대체 강사(전일제)
-2. 채용 인원: 1명
-3. 채용기간: 2026.10.12.~2026.10.30.(19일간)
-4. 자세한 사항은 첨부파일 참조</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>남지초등학교</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등기간제교원
 나. 채용 기간: 2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)
@@ -2637,49 +2399,49 @@
 ※자세한 사항은 공고문 참고</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n">
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
 1. 채용과목: 영어(1명)
@@ -2687,49 +2449,49 @@
 상세내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n">
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
         </is>
       </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -2784,15 +2546,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="H32" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -2802,488 +2564,40 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>웅상고 계약제교원(학교폭력담당자 수업경감 시간강사) 2차 채용 공고</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>웅상고등학교</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 웅상고등학교에 근무할 기간제교사를 다음과 같이 채용 공고 합니다.
-1. 채용과목 및 응모 자격
-물리(과학), 1명, 시간강사
-2026.10. 1. ~ 2026.12.31.
-주당 5시간, 시간당 25,000원.
-물리교사자격증 소지자
-- 공통과학, 지구과학, 생물, 화학 교사자격증 지원가능
-- 정년퇴직자 및 명예퇴직자
-- 만 62세까지 지원가능
-❈ 채용의 1순위: 결원 교원과
-동일한 급별‧과목별
-교원자격증소지자, 만 62세 미만
-동일 자격소지자를 우선 임용.
-2순위: 명예퇴직자, 정년퇴직자,
-다른 학교급·유사과목 자격증 소지자 등, 만 62세 미만.
-2. 전형방법
-가. 1차 시험 : 서류전형
-나. 2차 시험 : 면접
-3. 제출서류
-가. 응시자 제출서류
-◦ 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
-◦ 자기소개서 1부.(붙임서식)
-◦ 개인정보동의서(붙임서식)
-나. 최종합격자 제출서류
-◦ 교사 자격증 사본 또는 자격 인정 조서 1부.
-◦ 졸업증명서 사본 1부.(원본지참)
-◦ 기본증명서 및 병적증명서 또는 주민등록 초본 1부.
-◦ 범죄경력조회동의서 1부.
-◦ 공무원채용신체검사서 1부.
-4. 서류접수 및 전형일정
-가. 원서접수
-◦ 접수기간 : 2026. 9. 29.(화) 9:00 ~ 2026. 10. 5.(월) 16:00까지
-◦ 접수장소 : 웅상고등학교 3층 1교무실
-◦ 접수방법 : 이메일접수 ([이메일](영타), 2026. 10. 5.(월) 16:00까지)
-나. 1차 : 서류전형 합격자 발표(개별 전화 통지) 예정일 : 2026. 10. 6.(화) 15:00 이후
-다. 2차 : 면접예정일 : 2026. 10. 7.(수), 10:00 예정
-* 일시 및 장소는 서류전형 합격자에게만 개별 통보
-5. 합격자 발표
-◦ 최종합격자 발표 : 2026. 10. 7.(수) 17:00 이후 개별통보
-6. 유의사항
-◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 우선 임용될 수 있음
-◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 최종합격 후 확인이 불가능한 서류만 제출
-◦ 상기 일정은 진행상황에 따라 변경될 수 있으며 별도 통보함
-◦ 기재사항이 사실과 다르거나 허위로 작성된 경우는 합격을 취소합니다.
-◦ 제출서류의 기재착오, 누락, 서류 미제출, 연락불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.
-◦ 최종합격자로 발표된 이후에도 결격사유가 있는 자는 합격을 취소합니다.
-◦ 기타 자세한 사항은 웅상고등학교(☎[전화번호])로 문의하시기 바랍니다.
-2026년 9월 29일
-웅상고등학교장</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814610</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>김해한일여고 2026학년도 시간강사(수학) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>김해한일여자고등학교</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 김해한일여자고등학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
-1. 채용과목 : 수학(1명)
-2. 채용예정기간: 2026. 10.26.~2026.10.30.
-3 접수기간 : 2026. 9. 29.(화)~2026. 10. 5.(월) 16:00까지
-4. 접수방법 : 온라인접수, 방문접수, 우편접수
-5. 1차 합격자 발표일 : 2026. 10. 6.(화) 13:00이후 개별통보
-6. 2차 면접일 : 2026. 10. 7.(수)
-*면접시간 및 장소는 1차서류전형 합격자에게만 개별통보
-7. 최종 합격자 발표일 : 2026. 10. 7.(수) 13:00이후 개별통보
-* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814611</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>김해한일여고 2026학년도 결원대체 시간강사(진로진학) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>김해한일여자고등학교</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 김해한일여자고등학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
-1. 채용과목 : 진로진학(1명)
-2. 채용예정기간: 2026. 10.12.~2026.10.16.
-3 접수기간 : 2026. 9. 28.(월)~2026. 10. 5.(월) 16:00까지
-4. 접수방법 : 온라인접수, 방문접수, 우편접수
-5. 1차 합격자 발표일 : 2026. 10. 6.(화) 13:00이후 개별통보
-6. 2차 면접일 : 2026. 10. 7.(수)
-*면접시간 및 장소는 1차서류전형 합격자에게만 개별통보
-7. 최종 합격자 발표일 : 2026. 10. 7.(수) 13:00이후 개별통보
-* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814557</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>호암중학교 창체동아리(연극) 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>호암중학교</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 호암중학교 창체동아리(연극) 강사 채용 공고
-1) 종목 및 선발인원: 창체동아리 연극 (1명)
-2) 접수기간: 2026.10.1.(목) ~2026.10.5.(월) 16:00까지
-3) 접수방법: 호암중학교 교무실(방문접수) 또는
-전자우편([이메일])
-4) 서류심사 발표 : 2026.10.6.(화) 16:00 이후(합격자만 개별통지)
-5) 면접심사 : 2026.10.7.(수) 10:00 본교 2층 소통실
-6) 합격자 발표 : 2026.10.7.(수) 14:00 이후 개별 통지
-*자세한 내용은 첨부 파일을 확인하세요</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814664</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>율하중 계약제교원(체육,영어 시간강사) 채용 계획</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>율하중학교</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>1. 채용과목: 체육(1), 영어(1)
-2. 서류접수 및 전형방법
--1차: 서류전형 합격자 발표(개별 통지) 예정일: 2026.10.6. 15:30이후
-*접수기간: 2026.9.28.~2026.10.5. 23:00
--2차: 면접심사
-*면접일시: 2026.10.7.(12:30 또는 12:40)
-*강사비: 시간당 22,000원
-*자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814563</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>[양산고] 결원대체강사(전일제-영어,정보,화학,수학,생물) 채용공고</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>양산고등학교</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>경남 양산시</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>양산고등학교 공고 제2026-65호
-2026학년도 양산고등학교 결원대체강사(시간강사)를 채용 공고합니다.
-1. 서류접수 및 전형방법
-가. 원서접수
-◦ 접수기간 : 2026.09.29.(화) ~ 2026.10.05.(월)
-◦ 접수장소 : 양산고등학교 전자우편
-◦ 접수방법 : 전자우편(주소: [이메일])
-나. 1차 : 서류전형 합격자 발표(개별 통지) 예정일 : 2026.10.06.(화)
-다. 2차 : 면접심사(개별통지)
-◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보(예정일 : 2026.10.07.(수)
-◦ 응시자 1인 시 서류심사 적합 여부에 따라 면접 생략할 수 있음
-2. 합격자 발표
-◦ 최종합격자 발표 : 2026.10.07.(수) 개별통보
--임용결정: 총점 1위(합격자), 합격자 임용포기 시 차순위자를 합격자로 선정
-(단, 적격자가 없을 경우 합격자 없이 재공고를 통한 업무 진행)</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814477</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>경운초등학교 돌봄교실 특기적성 외부강사 공고</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>경운초등학교</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 경운초등학교에 근무할 외부강사를 다음과 같이 채용 공고합니다.
-1. 채용과목 : 돌봄교실 특기적성 프로그램 : 공예놀이
-2. 접수기간: 2026. 09. 28 .~2026. 10. 05.
-3 접수방법 : 전자메일 [이메일]
-4. 1차 합격자 발표일 : 2026. 10. 6.(화) 15:00이후 개별통보
-5. 2차 면접일 : 2026. 10. 7.(수)*면접시간 및 장소는 1차서류전형 합격자에게만 개별통보
-6. 최종 합격자 발표일 : 2026. 10. 8.(목) 11:00이후 개별통보* 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814577</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>방과후학교 리코더 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>수양초등학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>수양초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 개인 위탁 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원
@@ -3301,53 +2615,53 @@
 ※ 자세한 내용은 첨부파일을 참고해 주시기 바랍다.</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n">
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814600</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 재공고(수학)</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>꽃내중학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집 공고
 꽃내중학교에서는 방과후학교 운영과 관련하여 아래와 같이 2026학년도 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
@@ -3367,51 +2681,51 @@
 ※. 자세한 사항은 첨부물을 참고하십시요.</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814587</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 80) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>진해신항초 계약제교원(전일제 강사) 채용 모집 공고</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>진해신항초등학교</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진해신항초등학교 계약제교원(전일제강사) 다음과 같이 채용 공고합니다.
 ◆ 채용내용
@@ -3457,51 +2771,51 @@
 ◦ 기타 자세한 사항은 진해신항초등학교(☎551-2018)로 문의하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814721</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>밀양여자중학교</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>2026. 밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)
 가. 원서접수
@@ -3515,51 +2829,51 @@
 **자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814716</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>성주초등학교 풍물동아리 외부 강사 모집 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>성주초등학교</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성주초등학교 풍물동아리 외부 강사 모집계획을 다음과 같이 공고합니다.
 가. 공고 기간
@@ -3580,51 +2894,51 @@
 ※ 모집 일정은 학교 사정에 따라 변경될 수 있습니다.</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814722</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>화정초등학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
@@ -3633,51 +2947,51 @@
 * 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
         </is>
       </c>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>주동초등학교</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>2026년 주동초등학교에서는 초등 1~2학년 맞춤형프로그램과 관련하여 아래와 같이 외부강사(문화, 예술, 음악, 놀이영어 등 다양한 분야 지원 가능)를 모집하오니, 유능한 강사님들의 많은 지원 바랍니다.
 1.  서류접수:  2026.  10. 1.(목) ~ 2026. 10.  7.(수) 16시까지 도착분
@@ -3689,51 +3003,51 @@
 ※ 접수시간을 반드시 준수해 주시길 바랍니다.</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814652</t>
         </is>
       </c>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -3746,94 +3060,94 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n">
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
         </is>
       </c>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>남지읍 평생학습센터 강사 모집 공고</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>창녕군</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>경남 창녕군</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="n"/>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -3847,51 +3161,51 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -3903,112 +3217,112 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n">
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
         </is>
       </c>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O54" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -4019,51 +3333,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -4115,47 +3429,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -4167,51 +3481,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -4228,97 +3542,97 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
         </is>
       </c>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>함양제일고등학교</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>10.26.(월)-11.11.(수)/ 총58시간</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
 1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
@@ -4327,96 +3641,96 @@
 -자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="O50" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>마산고등학교</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="inlineStr">
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O62" s="5" t="inlineStr">
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>대암초등학교</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -4436,49 +3750,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="n">
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -4487,225 +3801,225 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
         </is>
       </c>
-      <c r="L64" s="5" t="n"/>
-      <c r="M64" s="5" t="n"/>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O64" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
         </is>
       </c>
-      <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O65" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>일운초등학교</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="inlineStr">
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
         </is>
       </c>
-      <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
-      <c r="N66" s="5" t="inlineStr">
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O66" s="5" t="inlineStr">
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>함안고등학교</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
 자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
         </is>
       </c>
-      <c r="L67" s="5" t="n"/>
-      <c r="M67" s="5" t="n"/>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O67" s="5" t="inlineStr">
+      <c r="O56" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>고성군</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>경남 고성군</t>
         </is>
       </c>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
         </is>
       </c>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="n"/>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="n"/>
-      <c r="L68" s="5" t="n"/>
-      <c r="M68" s="5" t="n"/>
-      <c r="N68" s="5" t="inlineStr">
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O68" s="5" t="inlineStr">
+      <c r="O57" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>소토초등학교 한국어교육 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>소토초등학교</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4727,23 +4041,23 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="inlineStr">
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O69" s="5" t="inlineStr">
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>대청중학교 결원대체강사 (특수) 2차 채용 공고</t>
+          <t>교방초등학교 방과후학교 개인위탁 외부강사[티볼] 모집 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>대청중학교</t>
+          <t>교방초등학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -645,64 +645,10 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026.10.16.(금)~2026.10.19.(월) (2일)</t>
+          <t>2026.11.1. ~2027.2.16.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>1. 채용과목 : 특수 (시간제)
-2. 채용기간 : 2026.10.16.(금)~2026.10.19.(월) (2일)
-3. 접수기간 : 2026.10.02.(금)~2026.10.06.(화) 09:00 도착분까지
-4. 서류전형 : 2026.10.06.(화) 11:00 이후 (합격자에게 개별 통보)
-5. 최종면접 : 2026.10.06.(화) 15:30~
-- 1인 지원시, 1차 심사 결과 적격자라고 판단 될 경우 2차 면접 심사 생략 할 수 있음
-6. 최종합격자 발표 : 2026.10.07.(수) 11:00 이후
-7. 접수방법 : [이메일]
-상세한 내용은 첨부파일 참고 바랍니다.
-감사합니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814570</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>교방초등학교 방과후학교 개인위탁 외부강사[티볼] 모집 공고</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>교방초등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026.11.1. ~2027.2.16.</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>[ 2026학년도 교방초 방과후학교 개인위탁외부강사 모집 공고 ]
 교방초등학교에서는
@@ -716,49 +662,49 @@
 6. 모집 세부 사항: 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814603</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 수학 시간강사 채용 공고</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026.10. 12. ~ 2026.11.18. (주당18시간)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>하동여자고등학교 시간강사 채용 공고
 1. 채용내용 : 수학 1명
@@ -772,51 +718,51 @@
 ※ 기타 자세한 사항은 공고문을 참고 하시기 바랍니다. ※ 관심 있는 분들의 많은 지원 바랍니다</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부, 기타 구비서류(채용합격자에 한해 별도안내)</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814606</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>양산제일고등학교 전일제 강사(수학) 채용 3차 공고</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>양산제일고등학교</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 07. ~ 2026. 10. 30.</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 수학(1명)
 2. 채용기간: 2026. 10. 07. ~ 2026. 10. 30.
@@ -828,49 +774,49 @@
 8. 기타 자세한 사항은 첨부 문서(공고문)를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814677</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>방과후학교 방송댄스 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>합성초등학교</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 29 ~ 2027. 2. 26.(학교사정에 따라 변동 될 수 있음)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>합성초등학교에서는 2026. 방과후학교 방송댄스 개인위탁 외부강사를 모집합니다.
 관심 있는 분들의 많은 지원 바랍니다.
@@ -883,49 +829,49 @@
 바. 문의사항 : 교무실 256-2696</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814636</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>마산여자고등학교 계약제교원(전일제강사-윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>마산여자고등학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.(월)~2026.10.19.(월) 총 6일 / 일당 110,000원</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산여자고등학교에 근무할 계약제교원 전일제강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 도덕·윤리(1명)
@@ -959,53 +905,53 @@
 자세한 사항은 첨부파일 확인바랍니다.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>동일 과목 중등교사 자격증 소지자 지원 가능</t>
         </is>
       </c>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814705</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>봉명초 돌봄교실 특기적성 프로그램 강사 추가 모집</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>봉명초등학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 12일∼2027년 2월 26일 / 학기 중 : 14:00~15:30  ,   방학 중 : 13:00~ 14:30</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026학년도 초등돌봄교실 특기적성 개인위탁 외부강사를 다음과 같이 추가 공고 모집하고자 합니다.
 1. 모집 분야 및 인원순
@@ -1045,47 +991,47 @@
 ※ 자세한 사항은 첨부파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814672</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>남양초등학교 돌봄교실 특기적성프로그램 개인 위탁 외부강사 채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>남양초등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2027. 2. 24.(수) / 금요일(13:50~14:30, 14:40~15:20, 15:30~16:10)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2026학년도 남양초등학교 돌봄교실 특기적성 프로그램 외부강사를 아래와 같이 모집하오니
 관심있는 분들의 많은 지원 바랍니다.
@@ -1101,49 +1047,49 @@
 5. 기타 자세한 내용은 첨부파일을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814493</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교 시간강사(수학) 채용</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 15~2026. 10. 23</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교에서 근무할 시간강사를 다음과 같이 채용 공고합니다.
 - 채용기간 : 2026. 10. 15~2026. 10. 23
@@ -1153,47 +1099,47 @@
 자세한 내용은 첨부파일을 참고해주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814706</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>악양초등학교. 결원 대체 강사 채용 공고(전일제강사)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>악양초등학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026.10.26 ~ 2026.10.30.(총5일)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>2026학년도 악양초등학교에 근무할 결원 대체 강사를 다음과 같이 채용 공고 안내
 1. 채용과목 : 초등(전일제강사 1명)
@@ -1212,59 +1158,59 @@
 * 자세한 사항은 붙임 공고문을 참조바랍니다.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>1순위: 만 62세 미만 동일 자격 소지자
 2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
 1순위 지원자 없을 시  2순위자 채용 가능</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재), 자기소개서 1부.(붙임서식), 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814642</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>대방중학교 전일제강사(기술·가정과) 채용 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>대방중학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 9일 ~ 2026년 11월 13일(5일)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>2026학년도 대방중학교 기술·가정과 전일제강사를 다음과 같이 채용 공고합니다.
 1. 접수기간: 2026년 10월 2일(금) ~ 2026년 10월 7일(수), 09:00까지 도착분에 한함
@@ -1276,47 +1222,47 @@
 기타 자세한 사항은 붙임 문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814661</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>계동초 방과후학교 프로그램 개인위탁 외부강사(한자속독) 모집 공고</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>계동초등학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 1일 ∼ 2027년 2월 28일</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>2026. 계동초 방과후학교 프로그램(한자속독) 개인위탁 외부강사를 다음과 같이 모집합니다.
 1. 계약 기간: 2026년 11월 1일 ∼ 2027년 2월 28일
@@ -1330,49 +1276,49 @@
 -자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814720</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>분성초등학교 방과후학교 외부강사 모집 공고(바이올린)</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>분성초등학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 3. ~ 2027. 2. 25.</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>2026. 분성초 방과후학교 바이올린 개인위탁 외부강사를 다음과 같이 모집합니다.
 1. 계약 기간: 2026. 11. 3. ~ 2027. 2. 25.
@@ -1389,47 +1335,47 @@
 -자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814693</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교 결원대체시간강사(수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고입니다.
 1. 채용과목 및 인원, 채용기간
@@ -1449,49 +1395,49 @@
 ※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814688</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교 결원대체강사(과학 전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>2026학년도 삼정자중학교 결원대체강사(과학)를 다음과 같이 채용하고자 합니다.
 1. 채용과목 및 채용 내용
@@ -1514,49 +1460,49 @@
 **자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814686</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교 결원대체 시간강사(1순위:윤리, 2순위:일반사회) 채용 공고</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.(월)~2026. 10. 30.(금) (총 17시간)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원중앙고등학교 결원대체 시간강사 채용을 다음과 같이 공고합니다.
 1. 채용과목 : 윤리(1순위:윤리, 2순위:일반사회)
@@ -1567,13 +1513,78 @@
 * 자세한 사항은 첨부파일 참조 바랍니다.</t>
         </is>
       </c>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814730</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>밀양고 전일제 강사(수학) 채용 공고(2차)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>밀양고등학교</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 19. ~ 2026. 10. 23.(5일, 17시수)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 밀양고등학교 전일제 강사 채용 공고
+2026학년도 밀양고등학교에 근무할 전일제 강사를 다음과 같이 채용 공고합니다.
+1. 채용내용 및 응모자격
+가. 채용 교과 및 인원
+1) 과목: 수학(미적분1, 기하, 인공지능수학)
+2) 채용인원 1명
+3) 채용사유: 특별휴가
+4) 채용기간: 2026. 10. 19. ~ 2026. 10. 23.(5일, 17시수)
+5) 비고: 전일제 강사 일일 110,000원
+2. 서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간: 2026. 10. 6.(화) ~ 2026. 10. 8.(목) 16:30까지
+◦ 접수방법: 전자우편(주소: [이메일] 스캔본 제출, 면접 시 원본 제출
+나. 1차 시험:
+◦ 서류전형: 2026. 10. 12(월) 09:00, 교무실
+◦ 합격자 발표(개별 통보)는 2026. 10. 12.(월) 12:30 이후
+다. 2차 시험: 면접 예정, 2026. 10. 12.(월) 15:00, 학생회실
+◦ 서류심사 합격자에 한함
+◦ 응시자가 1인 이하일 경우 서류심사와 면접시험을 병행하여 실시 가능
+라. 최종합격자 발표: 2026. 10. 12.(월) 16:30 이후 (합격자에게만 개별 통보)
+자세한 사항은 첨부파일을 참고</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814730</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814743</t>
         </is>
       </c>
       <c r="L17" s="5" t="n"/>
@@ -1692,30 +1703,86 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>증산중학교 시간강사 채용 공고(수학)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>증산중학교</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>증산중학교 시간강사 채용
+1. 채용과목: 수학 1명
+2. 채용기간: 2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)
+2. 일정
+가. 원서접수:2026.9.28.(월)∼10.11.(일) 24:00까지 도착분에 한함
+나. 접수방법: 전자우편([이메일])으로 1개의 PDF 파일로 제출
+다. 1차 서류전형 발표일: 2026.10.12.(월) 15:00 이후
+라. 2차 면접일: 2026.10.13.(화) 11:30~
+마. 합격자 발표: 2026.10.13.(화)  16:00 이후 (합격자에 한해 개별 통지)
+* 기타 사항은 첨부파일 참고</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814744</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>동진초등학교 2026.10.12.자 계약제교원(결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>동진초등학교</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 10. 17.(5일)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등교사
 나. 채용 기간: 2026. 10. 12. ~ 2026. 10. 17.(5일)
@@ -1727,49 +1794,49 @@
 ※ 국가공무원법 제33조의 규정에 의한 공무원임용 결격사유가 없는 자</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814468</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -1822,49 +1889,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -1915,49 +1982,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -1981,47 +2048,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(기술 가정) 채용 공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고
 합니다.
@@ -2046,49 +2113,49 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n">
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -2139,53 +2206,53 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H26" s="5" t="n">
         <v>8046</v>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>유목초등학교</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>구체적인 내용은 공고문을 참고바랍니다.
 1. 분야: 특수학급 결원대체강사
@@ -2193,49 +2260,49 @@
 3.기간: 2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n">
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>유목초 특수학급 결원대체강사 채용 공고</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>유목초등학교</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>구체적인 내용은 공고문을 참고바랍니다.
 1. 분야: 특수학급 결원대체강사
@@ -2243,66 +2310,15 @@
 3.기간: 2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n">
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>내곡초등학교</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.1.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>아래와 같이 결원대체강사 채용을 공고합니다.
-1. 대상: 초등교사 1명
-2. 기간: 2026.10.1.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>초등교사 1명</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
         </is>
       </c>
       <c r="L28" s="5" t="n"/>
@@ -2313,30 +2329,81 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>내곡초등학교</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.1.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명
+2. 기간: 2026.10.1.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>유영초등학교</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~2026.10.30.(19일간)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 초등 결원대체 강사(전일제)
 2. 채용 인원: 1명
@@ -2344,49 +2411,49 @@
 4. 자세한 사항은 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n">
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>남지초등학교</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등기간제교원
 나. 채용 기간: 2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)
@@ -2399,49 +2466,49 @@
 ※자세한 사항은 공고문 참고</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n">
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
 1. 채용과목: 영어(1명)
@@ -2449,49 +2516,49 @@
 상세내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n">
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -2546,15 +2613,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H33" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -2564,40 +2631,40 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>방과후학교 리코더 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>수양초등학교</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>수양초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 개인 위탁 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원
@@ -2615,53 +2682,53 @@
 ※ 자세한 내용은 첨부파일을 참고해 주시기 바랍다.</t>
         </is>
       </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n">
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814600</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 재공고(수학)</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>꽃내중학교</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집 공고
 꽃내중학교에서는 방과후학교 운영과 관련하여 아래와 같이 2026학년도 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
@@ -2681,51 +2748,51 @@
 ※. 자세한 사항은 첨부물을 참고하십시요.</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814587</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 80) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>진해신항초 계약제교원(전일제 강사) 채용 모집 공고</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>진해신항초등학교</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진해신항초등학교 계약제교원(전일제강사) 다음과 같이 채용 공고합니다.
 ◆ 채용내용
@@ -2771,51 +2838,51 @@
 ◦ 기타 자세한 사항은 진해신항초등학교(☎551-2018)로 문의하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814721</t>
         </is>
       </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>밀양여자중학교</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>2026. 밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)
 가. 원서접수
@@ -2829,51 +2896,51 @@
 **자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814716</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>성주초등학교 풍물동아리 외부 강사 모집 공고</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>성주초등학교</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성주초등학교 풍물동아리 외부 강사 모집계획을 다음과 같이 공고합니다.
 가. 공고 기간
@@ -2894,51 +2961,51 @@
 ※ 모집 일정은 학교 사정에 따라 변경될 수 있습니다.</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814722</t>
         </is>
       </c>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>화정초등학교</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
@@ -2947,51 +3014,51 @@
 * 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>주동초등학교</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>2026년 주동초등학교에서는 초등 1~2학년 맞춤형프로그램과 관련하여 아래와 같이 외부강사(문화, 예술, 음악, 놀이영어 등 다양한 분야 지원 가능)를 모집하오니, 유능한 강사님들의 많은 지원 바랍니다.
 1.  서류접수:  2026.  10. 1.(목) ~ 2026. 10.  7.(수) 16시까지 도착분
@@ -3003,51 +3070,51 @@
 ※ 접수시간을 반드시 준수해 주시길 바랍니다.</t>
         </is>
       </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814652</t>
         </is>
       </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -3060,58 +3127,17 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n">
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>남지읍 평생학습센터 강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>창녕군</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>경남 창녕군</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
+        </is>
+      </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="5" t="n"/>
       <c r="N41" s="5" t="inlineStr">
@@ -3121,33 +3147,74 @@
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
+          <t>남지읍 평생학습센터 강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>창녕군</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>경남 창녕군</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -3161,51 +3228,51 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -3217,112 +3284,112 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n">
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
         </is>
       </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -3333,51 +3400,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -3429,47 +3496,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -3481,51 +3548,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -3542,59 +3609,13 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
-        </is>
-      </c>
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="n"/>
       <c r="J49" s="5" t="n"/>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
         </is>
       </c>
       <c r="L49" s="5" t="n"/>
@@ -3606,33 +3627,79 @@
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
+          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>함양제일고등학교</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>10.26.(월)-11.11.(수)/ 총58시간</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
 1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
@@ -3641,58 +3708,13 @@
 -자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O50" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
-        </is>
-      </c>
       <c r="G51" s="5" t="n"/>
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="n"/>
       <c r="J51" s="5" t="n"/>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
       <c r="L51" s="5" t="n"/>
@@ -3704,33 +3726,78 @@
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
           <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>대암초등학교</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -3750,49 +3817,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n">
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -3801,59 +3868,13 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O53" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
-        </is>
-      </c>
       <c r="G54" s="5" t="n"/>
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="n"/>
       <c r="J54" s="5" t="n"/>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
         </is>
       </c>
       <c r="L54" s="5" t="n"/>
@@ -3872,12 +3893,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>일운초등학교</t>
+          <t>김해생명과학고등학교</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -3889,7 +3910,8 @@
       <c r="E55" s="5" t="n"/>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
       <c r="G55" s="5" t="n"/>
@@ -3898,7 +3920,7 @@
       <c r="J55" s="5" t="n"/>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
         </is>
       </c>
       <c r="L55" s="5" t="n"/>
@@ -3917,12 +3939,12 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>함안고등학교</t>
+          <t>일운초등학교</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -3934,8 +3956,7 @@
       <c r="E56" s="5" t="n"/>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
-자세한 내용은 첨부파일 확인 바랍니다.</t>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
       <c r="G56" s="5" t="n"/>
@@ -3944,7 +3965,7 @@
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
         </is>
       </c>
       <c r="L56" s="5" t="n"/>
@@ -3963,31 +3984,36 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>함안고등학교</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>경남 고성군</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D57" s="5" t="n"/>
       <c r="E57" s="5" t="n"/>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
       <c r="G57" s="5" t="n"/>
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="n"/>
       <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
+        </is>
+      </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="inlineStr">
@@ -4004,22 +4030,63 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>소토초등학교 한국어교육 강사 채용 공고</t>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>소토초등학교</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 고성군</t>
         </is>
       </c>
       <c r="D58" s="5" t="n"/>
       <c r="E58" s="5" t="n"/>
       <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>소토초등학교</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4041,23 +4108,23 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>교방초등학교 방과후학교 개인위탁 외부강사[티볼] 모집 공고</t>
+          <t>통영여자중학교 시간강사(수학) 채용</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>교방초등학교</t>
+          <t>통영여자중학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -640,456 +640,15 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026.11.1. ~2027.2.16.</t>
+          <t>2026. 10. 15~2026. 10. 23</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>[ 2026학년도 교방초 방과후학교 개인위탁외부강사 모집 공고 ]
-교방초등학교에서는
-2026학년도 방과후학교 토요 프로그램(티볼)을 운영할 개인위탁외부강사를 모집합니다.
-관심있는 분들의 많은 지원 바랍니다.
-1. 모집 분야: 방과후학교 외부강사
-2. 모집 강좌: 티볼(1명)
-3. 접수기간: 2026.9.29.(화)~10.6.(화) 10:00까지
-4. 접수방법: 이메일 접수
-5. 계약기간: 2026.11.1. ~2027.2.16.
-6. 모집 세부 사항: 첨부파일 참조</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814603</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>하동여자고등학교 수학 시간강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>하동여자고등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026.10. 12. ~ 2026.11.18. (주당18시간)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>하동여자고등학교 시간강사 채용 공고
-1. 채용내용 : 수학 1명
-2. 채용기간 : 2026.10. 12. ~ 2026.11.18. (주당18시간)
-3. 제출서류 : 응시원서 1부, 기타 구비서류(채용합격자에 한해 별도안내)
-4. 접수기간 : 2026.9.29.(화) ~ 10.6.(화) 10시까지 접수분에 한함.
-5. 서류전형 접수방법 : 본인 방문 접수 및 온라인 접수(메일주소: [이메일])
-6. 전형일정: 1차 서류전형 합격자 발표(개별 전화 통지) : 2026. 10.6 .(화) 11:00 이후 개별 통보
-2차 면접 (서류 전형 합격자에 한함) : 2026.10.6.(화) 14:00 ~
-7. 합격자 발표(합격자에게만 개별 통보) : 2026.10.7.(수) 14:00 이후 개별 통보
-※ 기타 자세한 사항은 공고문을 참고 하시기 바랍니다. ※ 관심 있는 분들의 많은 지원 바랍니다</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>응시원서 1부, 기타 구비서류(채용합격자에 한해 별도안내)</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814606</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>양산제일고등학교 전일제 강사(수학) 채용 3차 공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>양산제일고등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 07. ~ 2026. 10. 30.</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>1. 채용과목: 수학(1명)
-2. 채용기간: 2026. 10. 07. ~ 2026. 10. 30.
-3. 서류 접수기간: 2026. 10. 01.(목) ~ 2026. 10. 06.(화) 10:00까지
-4. 접수방법: 전자우편 제출(주소: [이메일])
-5. 서류 심사결과 발표: 2026. 10. 06.(화) 11시 이후 합격자 개별 통보
-6. 면접전형(서류심사 합격자): 2026. 10. 06.(화) 오후 14시
-7. 최종합격자발표: 2026. 10. 06.(화) 15시 이후 (합격자 유선 통보)
-8. 기타 자세한 사항은 첨부 문서(공고문)를 참고하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814677</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 방송댄스 개인위탁 외부강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>합성초등학교</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 29 ~ 2027. 2. 26.(학교사정에 따라 변동 될 수 있음)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>합성초등학교에서는 2026. 방과후학교 방송댄스 개인위탁 외부강사를 모집합니다.
-관심 있는 분들의 많은 지원 바랍니다.
-1. 모집 세부 사항
-가. 모집강좌 : 방송댄스 1명
-나. 계약기간 : 2026. 10. 29 ~ 2027. 2. 26.(학교사정에 따라 변동 될 수 있음)
-다. 접수기간 : 2026. 10. 1. ~ 2026. 10.6 . 12:00 도착에 한함.
-라. 접수장소 : 합성초등학교 1층 교무실로 직접 제출
-마. 기타사항 : 자세한 사항은 첨부파일 참고
-바. 문의사항 : 교무실 256-2696</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814636</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>마산여자고등학교 계약제교원(전일제강사-윤리) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>마산여자고등학교</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.12.(월)~2026.10.19.(월) 총 6일 / 일당 110,000원</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 마산여자고등학교에 근무할 계약제교원 전일제강사를 다음과 같이 채용 공고합니다.
-1. 채용과목: 도덕·윤리(1명)
-2. 채용기간: 2026.10.12.(월)~2026.10.19.(월) 총 6일 / 일당 110,000원
-3. 접수기간: 2026. 10. 1.(목) ~ 2026. 10. 6.(화) 16:00 도착에 한함
-4. 응시자격: 동일 과목 중등교사 자격증 소지자 지원 가능
-5. 전형방법
-가. 1차 전형: 서류심사(1차 합격자 발표 2026. 10. 7.(수) 10:00이후 (합격자 개별 통보))
-(※면접 대상자에 한하여 전화 혹은 문자로 통지)
-나. 2차 전형: 면접(1차 합격자 기준 2026. 10. 7.(수) 14:00~)
-(※면접 대상자에 한하여 전화 혹은 문자로 통지)
-6. 접수방법 : 전자우편 [이메일](우편, 방문 접수 불가)
-7. 최종 합격자 발표: 2026. 10. 7.(수) 16:00이후 (최종합격자에 한하여 전화 또는 문자로 개별 통지)
-8. 제출서류
-가. 응시원서 1부(붙임 서식, 사진 첨부, 연락 가능한 전화번호 반드시 기재)
-나. 자기소개서 1부(붙임 서식)
-다. 개인정보 수집·이용 동의서 1부(붙임 서식)
-※ 파일명을 '과목명-본인 이름'으로 수정 후 제출(파일 하나로 보내시면 됩니다.)
-9. 최종합격시 제출서류
-가. 교사 자격증 사본 또는 자격인정조서 1부.
-나. 졸업증명서 사본 1부(전문대학 이상, 2개 이상이면 모두 제출).
-다. 공무원채용신체검사서 1부. (유효기간 1년 내)
-라. 잠복결핵검사 확인서 1부
-마. 마약류 투약 또는 중독 여부 판별 결과 통보서 또는 의사 진단서 (유효기간 1년 내)
-바. 개인정보 수집 및 활용 동의서 1부
-사. 결격사유, 범죄경력조회동의서, 행정정보공동이용 동의서 각 1부.
-아. 가족 채용 제한 여부 확인서
-자. 병적증명서 또는 주민등록표 초본
-차. 경력증명서(사립학교: 경력확인서)
-(바~아 항목은 학교에서 작성합니다.)
-자세한 사항은 첨부파일 확인바랍니다.</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>동일 과목 중등교사 자격증 소지자 지원 가능</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814705</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>봉명초 돌봄교실 특기적성 프로그램 강사 추가 모집</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>봉명초등학교</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 12일∼2027년 2월 26일 / 학기 중 : 14:00~15:30  ,   방학 중 : 13:00~ 14:30</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 초등돌봄교실 특기적성 개인위탁 외부강사를 다음과 같이 추가 공고 모집하고자 합니다.
-1. 모집 분야 및 인원순
-채용분야
-모집영역(강좌명)
-채용인원
-프로그램 운영 방법강사료1
-특기적성 프로그램
-동화구연(월), 전래놀이(화),
-종이접기(수),보드게임(목)
-강좌별 1명
-주1회 40분 2차시
-차시당 40,000원2
-운영 시간
-학기 중 : 14:00~15:30  ,   방학 중 : 13:00~ 14:30
-* 프로그램 운영에 필요한 재료비는 별도로 지원하지 않음.(단, 운영 상황에 따라 조정될 수 있음)
-※ 프로그램 운영 요일 및 시간은 강사와 협의하여 조정될 수 있음
-2. 모집 세부 사항
-가. 공고 기간: 2026년 10월 01일(목) ∼ 2026년 10월 06일(화)
-나. 서류 접수: 2026년 10월 01일(목) ∼ 2026년 10월 06일(화) 16:00까지
-다. 접수 장소: 봉명초등학교 교무실로 본인 직접 접수
-라.선정 및 계약방법: 1차 제안서 평가 합격자에 한해 2차 프로그램 운영 능력평가를 실시하여 계약 예정자를 선정
-마. 합격자 통보1차
-제안서(서류) 심사
-2026. 10. 06.(화)
-• 17:00시 까지 개별통보 예정
-• 1차 제안서 평가 통과자에 한하여 개별 통보2차
-운영능력(면접) 심사
-2026. 10. 07.(수)
-• 운영능력(면접)
-※ 면접 인원에 따라 일정 및 시간이 조정될 수 있음.
-※ 학교 사정에 의해 운영능력(면접) 심사 일정이 조정될 수 있음
-최종 심사 결과 발표
-2026. 10.08(목). 17:00까지 개별 통보 예정
-바. 계약 기간: 2026년 10월 12일∼2027년 2월 26일
-※ 학사 일정 등 불가피한 사유로 인해 계약 기간이 조정될 수 있음,
-※ 자세한 사항은 첨부파일을 참고하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814672</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>남양초등학교 돌봄교실 특기적성프로그램 개인 위탁 외부강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>남양초등학교</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 16.(금) ~ 2027. 2. 24.(수) / 금요일(13:50~14:30, 14:40~15:20, 15:30~16:10)</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 남양초등학교 돌봄교실 특기적성 프로그램 외부강사를 아래와 같이 모집하오니
-관심있는 분들의 많은 지원 바랍니다.
-1. 모집분야 및 인원 : 전통놀이(1명)
-2. 계약기간 : 2026. 10. 16.(금) ~ 2027. 2. 24.(수)
-3. 운영요일 : 금요일(13:50~14:30, 14:40~15:20, 15:30~16:10)
-4. 모집 세부 사항
-가. 접수기간 : 2026. 9. 28.(월) ~ 2026. 10. 6.(화) 17:00까지
-나. 접수방법 : 남양초 돌봄2실 (방문접수만 가능)
-다. 1차 제안서 심사: 2026. 10. 7.(수)
-라. 2차 프로그램 운영 능력 심사 : 2026. 10. 12.(월) 10:00~
-마. 최종 합격자 발표: 2026. 10. 13.(화) 13:00~
-5. 기타 자세한 내용은 첨부파일을 참고바랍니다.</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814493</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>통영여자중학교 시간강사(수학) 채용</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>통영여자중학교</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 15~2026. 10. 23</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교에서 근무할 시간강사를 다음과 같이 채용 공고합니다.
 - 채용기간 : 2026. 10. 15~2026. 10. 23
@@ -1099,47 +658,47 @@
 자세한 내용은 첨부파일을 참고해주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814706</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>악양초등학교. 결원 대체 강사 채용 공고(전일제강사)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>악양초등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026.10.26 ~ 2026.10.30.(총5일)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>2026학년도 악양초등학교에 근무할 결원 대체 강사를 다음과 같이 채용 공고 안내
 1. 채용과목 : 초등(전일제강사 1명)
@@ -1158,59 +717,59 @@
 * 자세한 사항은 붙임 공고문을 참조바랍니다.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>1순위: 만 62세 미만 동일 자격 소지자
 2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
 1순위 지원자 없을 시  2순위자 채용 가능</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재), 자기소개서 1부.(붙임서식), 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814642</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>대방중학교 전일제강사(기술·가정과) 채용 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>대방중학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 9일 ~ 2026년 11월 13일(5일)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026학년도 대방중학교 기술·가정과 전일제강사를 다음과 같이 채용 공고합니다.
 1. 접수기간: 2026년 10월 2일(금) ~ 2026년 10월 7일(수), 09:00까지 도착분에 한함
@@ -1222,47 +781,47 @@
 기타 자세한 사항은 붙임 문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814661</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>계동초 방과후학교 프로그램 개인위탁 외부강사(한자속독) 모집 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>계동초등학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 1일 ∼ 2027년 2월 28일</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026. 계동초 방과후학교 프로그램(한자속독) 개인위탁 외부강사를 다음과 같이 모집합니다.
 1. 계약 기간: 2026년 11월 1일 ∼ 2027년 2월 28일
@@ -1276,49 +835,49 @@
 -자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814720</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>분성초등학교 방과후학교 외부강사 모집 공고(바이올린)</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>분성초등학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 3. ~ 2027. 2. 25.</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>2026. 분성초 방과후학교 바이올린 개인위탁 외부강사를 다음과 같이 모집합니다.
 1. 계약 기간: 2026. 11. 3. ~ 2027. 2. 25.
@@ -1335,47 +894,47 @@
 -자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814693</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교 결원대체시간강사(수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고입니다.
 1. 채용과목 및 인원, 채용기간
@@ -1395,49 +954,49 @@
 ※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814688</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교 결원대체강사(과학 전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2026학년도 삼정자중학교 결원대체강사(과학)를 다음과 같이 채용하고자 합니다.
 1. 채용과목 및 채용 내용
@@ -1460,49 +1019,49 @@
 **자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814686</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교 결원대체 시간강사(1순위:윤리, 2순위:일반사회) 채용 공고</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.(월)~2026. 10. 30.(금) (총 17시간)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원중앙고등학교 결원대체 시간강사 채용을 다음과 같이 공고합니다.
 1. 채용과목 : 윤리(1순위:윤리, 2순위:일반사회)
@@ -1513,47 +1072,47 @@
 * 자세한 사항은 첨부파일 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814730</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>밀양고 전일제 강사(수학) 채용 공고(2차)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>밀양고등학교</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 19. ~ 2026. 10. 23.(5일, 17시수)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>2026학년도 밀양고등학교 전일제 강사 채용 공고
 2026학년도 밀양고등학교에 근무할 전일제 강사를 다음과 같이 채용 공고합니다.
@@ -1578,47 +1137,47 @@
 자세한 사항은 첨부파일을 참고</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814743</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>김해내동초 돌봄 프로그램(종이접기 1명) 외부강사 모집 공고문</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>김해내동초등학교</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2027.2.28.</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>2026. 김해내동초 돌봄 프로그램(종이 접기 1명)외부 강사 모집 공고를  아래와 같이 실시합니다.
 1. 모집 인원: 1명
@@ -1628,49 +1187,267 @@
 5. 기타 자세한 사항은 첨부 문서를 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814620</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>성호초등학교 전일제강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>성호초등학교</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.13.~ 2026.10.21.(9일)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 (재)공고 합니다.
+1. 채용과목 및 인원: 특수교사 1명
+2. 채용기간: 2026.10.13.~ 2026.10.21.(9일)
+3. 접수기간: 2026.10.6.(화) ~ 10.11.(일) 15:00까지
+4. 접수장소 및 방법: 성호초등학교 대표메일([이메일])로 제출
+(현장접수 가능/ 면접 시 원본 제출)
+*자세한 사항은 붙임 참고 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>웅상고 계약제교원(학교폭력담당자 수업경감 시간강사) 2차 채용 공고</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>웅상고등학교</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.19. ~ 2026.12.31.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>웅상고등학교 공고 제2026 – 50호
+웅상고등학교 학교폭력담당자 수업경감 강사 3차 채용 공고
+2026학년도 웅상고등학교에 근무할 기간제교사를 다음과 같이 채용 공고 합니다.
+1. 채용과목 및 응모 자격
+물리(과학), 1명, 시간강사
+2026.10.19. ~ 2026.12.31.
+주당 5시간, 시간당 25,000원.
+물리교사자격증 소지자
+- 공통과학, 지구과학, 생물, 화학 교사자격증 지원가능
+- 정년퇴직자 및 명예퇴직자
+- 만 62세까지 지원가능
+❈ 채용의 1순위: 결원 교원과
+동일한 급별‧과목별
+교원자격증소지자, 만 62세 미만
+동일 자격소지자를 우선 임용.
+2순위: 명예퇴직자, 정년퇴직자,
+다른 학교급·유사과목 자격증 소지자 등, 만 62세 미만.
+2. 전형방법
+가. 1차 시험 : 서류전형
+나. 2차 시험 : 면접
+3. 제출서류
+가. 응시자 제출서류
+◦ 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
+◦ 자기소개서 1부.(붙임서식)
+◦ 개인정보동의서(붙임서식)
+나. 최종합격자 제출서류
+◦ 교사 자격증 사본 또는 자격 인정 조서 1부.
+◦ 졸업증명서 사본 1부.(원본지참)
+◦ 기본증명서 및 병적증명서 또는 주민등록 초본 1부.
+◦ 범죄경력조회동의서 1부.
+◦ 공무원채용신체검사서 1부.
+4. 서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간 : 2026. 10. 7.(수) 9:00 ~ 2026. 10. 11.(일) 21:00까지
+◦ 접수장소 : 웅상고등학교 3층 1교무실
+◦ 접수방법 : 이메일접수 ([이메일](영타), 2026. 10. 11.(일) 21:00까지)
+나. 1차 : 서류전형 합격자 발표(개별 전화 통지) 예정일 : 2026. 10. 12.(월) 15:00 이후
+다. 2차 : 면접예정일 : 2026. 10. 13.(화), 10:00 예정
+* 일시 및 장소는 서류전형 합격자에게만 개별 통보
+5. 합격자 발표
+◦ 최종합격자 발표 : 2026. 10. 13.(화) 17:00 이후 개별통보
+6. 유의사항
+◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 우선 임용될 수 있음
+◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 최종합격 후 확인이 불가능한 서류만 제출
+◦ 상기 일정은 진행상황에 따라 변경될 수 있으며 별도 통보함
+◦ 기재사항이 사실과 다르거나 허위로 작성된 경우는 합격을 취소합니다.
+◦ 제출서류의 기재착오, 누락, 서류 미제출, 연락불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.
+◦ 최종합격자로 발표된 이후에도 결격사유가 있는 자는 합격을 취소합니다.
+◦ 기타 자세한 사항은 웅상고등학교(☎[전화번호])로 문의하시기 바랍니다.
+2026년 10월 7일
+웅상고등학교장</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814610</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>마산가포고등학교</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.26.~2026.10.30.(총16시간)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
+1. 채용내용 및 응모자격
+가. 채용과목 및 인원: 지리 1명(1순위: 지리, 2순위: 일반사회, 윤리)
+나. 채용기간: 2026.10.26.~2026.10.30.(총16시간)
+다. 수당: 시간당 35,000원
+라. 응모자격
+1) 1순위: 만 62세 미만의 결원 교원과 동일 학교급 및 과목 자격증 소지자
+2) 2순위: 만 62세 미만의 결원 교원과 다른 학교급 또는 유사 과목* 자격증 소지자, 정년퇴직자 혹은 명예퇴직자
+※ 1차 모집 공고부터 우선순위를 정하여 1순위 지원자가 없을 시 후 순위 지원자 채용 가능
+2. 전형방법
+가. 1차 시험 : 서류전형(채용 예정 인원의 3배수 이내 선발)
+나. 2차 시험 : 면접(1차 서류 전형 합격자에 한하여 실시하며, 대상자에게 개별 통보)
+3. 응시자 제출서류
+가. 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
+나. 자기소개서 1부.(붙임서식)
+다. 계약제교원 채용을 위한 개인정보 수집 이용 동의서 1부.(붙임서식)
+4. 서류접수 및 전형일정
+가. 서류접수
+◦ 접수기간 : 2026. 10. 6.(화) ~ 2026. 10. 11.(일) 24:00까지
+◦ 접수방법 : 온라인접수([이메일] 스캔본 제출, 면접 시 원본제출, 2026. 10. 11.(일) 24:00 발송분까지)
+나. 1차 서류 전형 합격자 발표 : 2026. 10. 12.(월) 14:00 이후(1차 서류 전형 합격자에 한해 개별 통보)
+다. 2차 면접 : 2026. 10. 13.(화) 13:30~
+라. 최종합격자 발표 : 2026. 10. 13.(화) 15:00 이후 개별통보
+5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>증산중학교 계약제교원(시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1684,49 +1461,49 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814584</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용 공고(수학)</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1740,49 +1517,101 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814744</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>김해수남고 학교폭력 업무담당자 수업경감 시간강사 채용 재공고8차(일반사회)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>김해수남고등학교</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 16. ~ 2027. 2. 5. (일반사회-시간강사) 주4시간(금요일), 시간당 25,000원</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 김해수남고등학교에 근무할 시간강사를 다음과 같이 채용 재공고합니다.
+1. 과목: 일반사회(사회계열 모두 가능) 1명
+2. 채용기간: 2026. 10. 16. ~ 2027. 2. 5. (일반사회-시간강사) 주4시간(금요일), 시간당 25,000원
+3. 서류접수 : 2026. 10. 6.(화)～ 2026. 10. 12.(월) 15:00까지, 전자우편 ( [이메일] )
+4. 1차 : 서류전형 합격자 발표(개별 문자 통지): 2026. 10. 13.(화) 17:00~
+5. 2차 : 면접 (서류심사 합격자에 한함) 예정일 : 2026. 10. 14.(수) 13:00~
+6. 최종합격자 발표 : 2026. 10. 14.(수) 17:00~ 합격자 개별 통보
+7. 문의전화: 김해수남고 교무센터 ☎724-9350, 기타 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814759</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>동진초등학교 2026.10.12.자 계약제교원(결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>동진초등학교</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 10. 17.(5일)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등교사
 나. 채용 기간: 2026. 10. 12. ~ 2026. 10. 17.(5일)
@@ -1794,49 +1623,49 @@
 ※ 국가공무원법 제33조의 규정에 의한 공무원임용 결격사유가 없는 자</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n">
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814468</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -1889,49 +1718,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n">
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -1982,49 +1811,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -2048,47 +1877,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(기술 가정) 채용 공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고
 합니다.
@@ -2113,49 +1942,118 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>하동고등학교 결원대체강사(국어) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>하동고등학교</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>2026.11.09.~2026.11.13.(5일), 2026.12.21.~2026.12.22.(2일)(총 7일)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 하동고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
+1. 채용내용 및 응모 자격(결원대체강사;전일제/시간제)
+가. 채용 과목 : 국어
+나. 채용 기간 : 2026.11.09.~2026.11.13.(5일), 2026.12.21.~2026.12.22.(2일)(총 7일)
+다. 채용 인원 : 1명
+라. 응모자격 : 1순위: 채용 과목 중등 자격증 소지자
+2. 전형방법
+가. 1차 시험: 서류전형
+나. 2차 시험: 면접(서류전형 합격한 자에 한하여 개별 통보)
+3. 서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간: 2026. 10. 12.(월) - 2026. 10. 14.(수). 12:00까지
+◦ 접수방법 : 이메일: [이메일](스캔본 제출 후 면접 시 원본 제출)
+나. 1차: 서류전형 합격자 발표(개별 전화 통지) 예정일: 2026. 10. 15.(목). 10:00 이후
+다. 2차: 면접(서류심사 합격자에 한함) 예정일: 2026. 10. 19.(월). 16:40~ 1층 회의실
+◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
+4. 합격자 발표
+◦ 최종합격자 발표 : 2026. 10. 20.(화). 12:00 이후(합격자에게만 개별 통보)
+자세한 내용은 붙임파일을 참고해 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>1순위: 채용 과목 중등 자격증 소지자</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814762</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -2206,19 +2104,119 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
+      <c r="H24" s="5" t="n">
+        <v>8046</v>
+      </c>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>유목초 특수학급 결원대체강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>8046</v>
+        <v>1</v>
       </c>
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
         </is>
       </c>
       <c r="L26" s="5" t="n"/>
@@ -2229,12 +2227,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
+          <t>웅남중 학교운동부지도자 채용공고(태권도)</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>유목초등학교</t>
+          <t>웅남중학교</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -2244,31 +2242,34 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>2026.10.6.~2026.10.16.</t>
+          <t>2026.12.01.(화)~2027.2.28.(일)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>구체적인 내용은 공고문을 참고바랍니다.
-1. 분야: 특수학급 결원대체강사
-2. 채용인원: 1명
-3.기간: 2026.10.6.~2026.10.16.</t>
+          <t>웅남중학교 운동부 지도자 채용 공고
+- 채용분야: 운동부지도자
+- 임용기간:2026.12.01.(화)~2027.2.28.(일)
+- 전형방법: 서류전형 및 면접을 통해 채용
+- 원서접수: 2026.10.7.(수)~2026.10.23.(금) 14:00까지
+-서류심사 결과발표: 2026.10.26. 15:00 이후
+-면접심사: 서류전형 합격자에 한하여 개별 통보
+붙임 운동부지도자 채용공고 1부.
+자세한 사항은 붙임 문서를 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
       <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814764</t>
         </is>
       </c>
       <c r="L27" s="5" t="n"/>
@@ -2279,12 +2280,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>유목초 특수학급 결원대체강사 채용 공고</t>
+          <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>유목초등학교</t>
+          <t>내곡초등학교</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2294,31 +2295,32 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2026.10.6.~2026.10.16.</t>
+          <t>2026.10.1.~2026.10.23.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>구체적인 내용은 공고문을 참고바랍니다.
-1. 분야: 특수학급 결원대체강사
-2. 채용인원: 1명
-3.기간: 2026.10.6.~2026.10.16.</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명
+2. 기간: 2026.10.1.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
         </is>
       </c>
       <c r="L28" s="5" t="n"/>
@@ -2329,12 +2331,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
+          <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>내곡초등학교</t>
+          <t>유영초등학교</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2344,32 +2346,31 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2026.10.1.~2026.10.23.</t>
+          <t>2026.10.12.~2026.10.30.(19일간)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>아래와 같이 결원대체강사 채용을 공고합니다.
-1. 대상: 초등교사 1명
-2. 기간: 2026.10.1.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>초등교사 1명</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="n"/>
+          <t>1. 채용과목: 초등 결원대체 강사(전일제)
+2. 채용 인원: 1명
+3. 채용기간: 2026.10.12.~2026.10.30.(19일간)
+4. 자세한 사항은 첨부파일 참조</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
         </is>
       </c>
       <c r="L29" s="5" t="n"/>
@@ -2380,12 +2381,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
+          <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>유영초등학교</t>
+          <t>남지초등학교</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2395,65 +2396,15 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2026.10.12.~2026.10.30.(19일간)</t>
+          <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>1. 채용과목: 초등 결원대체 강사(전일제)
-2. 채용 인원: 1명
-3. 채용기간: 2026.10.12.~2026.10.30.(19일간)
-4. 자세한 사항은 첨부파일 참조</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>남지초등학교</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등기간제교원
 나. 채용 기간: 2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)
@@ -2466,6 +2417,56 @@
 ※자세한 사항은 공고문 참고</t>
         </is>
       </c>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>칠원고등학교</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
+1. 채용과목: 영어(1명)
+2. 채용기간: 2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)
+상세내용은 첨부파일 확인 바랍니다.</t>
+        </is>
+      </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n">
         <v>1</v>
@@ -2474,7 +2475,7 @@
       <c r="J31" s="5" t="n"/>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
         </is>
       </c>
       <c r="L31" s="5" t="n"/>
@@ -2485,80 +2486,30 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
+          <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>칠원고등학교</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 김해시</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
+          <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
-1. 채용과목: 영어(1명)
-2. 채용기간: 2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)
-상세내용은 첨부파일 확인 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>김해시</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>경남 김해시</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>2027. 01. ~ 12. (1년)</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -2613,15 +2564,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H32" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -2631,168 +2582,40 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 리코더 프로그램 개인위탁 외부강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>수양초등학교</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>수양초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 개인 위탁 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
-1. 모집 분야 및 인원
-- 모집 프로그램: 리코더 1명
-2. 모집 세부 사항
-- 공고 기간: 2026. 9. 29.(화) ~ 2026. 10. 6.(화)
-- 서류 접수: 2026. 9. 30.(수) ~ 2026. 10. 6.(화) 11:00까지
-- 접수 방법: 수양초등학교 교무실로 본인접수 또는 우편, 온라인 접수
-※ 우편 및 온라인 접수 시 2026년 10월 6일(화) 11시까지 도착 분에 한하여 인정함
-※ 온라인 접수 시 서명  또는  인 란 꼭 작성하여 hwp, pdf 파일로 제출할 것
-- 1차 제안서 심사: 2026. 10. 7.(수)
-- 2차 운영 능력 심사: 2026. 10. 8.(목)  오후 14:00 ~  본교 1층 다온실
-(강사 및 학교사정에 따라 면접시간 조율가능)
-- 최종 합격자 통보: 2026. 10. 12.(월) 15:00, 개별통보
-※ 자세한 내용은 첨부파일을 참고해 주시기 바랍다.</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814600</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 개인위탁 외부강사 재공고(수학)</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>꽃내중학교</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 개인위탁 외부강사 모집 공고
-꽃내중학교에서는 방과후학교 운영과 관련하여 아래와 같이 2026학년도 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
-1. 모집 분야, 모집 인원
-가. 교과 수학반
-나. 2명 채용
-2. 모집 세부 사항
-가. 공고 기간: 2026년 9월 23일(수)∼2026년 9월 28일(월)
-나. 서류 접수: 2026년 9월 23일(수)∼2026년 9월 28일(월) 15:00
-다. 접수 장소: 꽃내중학교 이메일 접수(지원서, 자기소개서, 프로그램 운영 제안서)
-※ 이메일 주소: [이메일]
-3. 계약 기간
-가. 수학C: 2026년 10월 1일 - 2027년 1월 5일(변동가능)
-나. 수학B: 2026년 11월 1일 - 2027년 1월 5일(변동가능)
-※ 매주 수업하는 것을 기본으로 하되 학사 일정에 따라 출근일은 모집 분야 프로그램에 의함.
-※ 불가항력 사유 등으로 인해 정상적인 학사 운영이 이루어지 않을 경우 계약 기간이 변동될 수 있음
-※. 자세한 사항은 첨부물을 참고하십시요.</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814587</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 80) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>진해신항초 계약제교원(전일제 강사) 채용 모집 공고</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>진해신항초등학교</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진해신항초등학교 계약제교원(전일제강사) 다음과 같이 채용 공고합니다.
 ◆ 채용내용
@@ -2838,51 +2661,51 @@
 ◦ 기타 자세한 사항은 진해신항초등학교(☎551-2018)로 문의하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814721</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>밀양여자중학교</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>2026. 밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)
 가. 원서접수
@@ -2896,51 +2719,51 @@
 **자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814716</t>
         </is>
       </c>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>성주초등학교 풍물동아리 외부 강사 모집 공고</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>성주초등학교</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성주초등학교 풍물동아리 외부 강사 모집계획을 다음과 같이 공고합니다.
 가. 공고 기간
@@ -2961,51 +2784,51 @@
 ※ 모집 일정은 학교 사정에 따라 변경될 수 있습니다.</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814722</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>화정초등학교</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
@@ -3014,51 +2837,51 @@
 * 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
         </is>
       </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>주동초등학교</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>2026년 주동초등학교에서는 초등 1~2학년 맞춤형프로그램과 관련하여 아래와 같이 외부강사(문화, 예술, 음악, 놀이영어 등 다양한 분야 지원 가능)를 모집하오니, 유능한 강사님들의 많은 지원 바랍니다.
 1.  서류접수:  2026.  10. 1.(목) ~ 2026. 10.  7.(수) 16시까지 도착분
@@ -3070,51 +2893,51 @@
 ※ 접수시간을 반드시 준수해 주시길 바랍니다.</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814652</t>
         </is>
       </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -3127,15 +2950,172 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>남지읍 평생학습센터 강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>창녕군</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>경남 창녕군</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>율하중 계약제교원(체육 시간강사) 채용 계획(3차 공고)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>율하중학교</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>1. 채용과목: 체육(1)
+2. 서류접수 및 전형방법
+-1차: 서류전형 합격자 발표(개별 통지) 예정일: 2026.10.12. 10:30이후
+*접수기간: 2026.10.6.~2026.10.9. 23:00
+-2차: 면접심사
+*면접일시: 2026.10.12. 12:30
+*강사비: 시간당 22,000원
+*자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814756</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 개인위탁 외부강사 모집공고(수학)</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>거제고현중학교</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>★  모집 세부 사항
+가. 공고 기간: 2026.10.7.(수)~2026.10.14.(수)
+나. 접수 기간: 2026.10.7.(수)~2026.10.14.(수) 16:00
+다. 접수 방법: 거제고현중 전자우편 접수([이메일], 파일명: 프로그램명-응시자 성명)
+라. 1차 서류전형 합격자 발표(개별 전화 통지) 예정일: 2026.10.14.(수) 16:30 이후
+마. 2차 면접(서류심사 합격자에 한함) 예정일: 2026.10.15.(목) 10:00
+- 일시 및 장소는 1차 서류전형 합격자에게만 개별 통보
+바. 최종합격자 발표: 2026.10.15.(목) 16:00 이후 최종합격자에게만 개별 통보
+★ 지원 조건
+가. 해당 분야에 전문적인 능력을 가진 자 또는 자격증 소지자
+나. 직무 수행의 결격사유나 학생 지도 시 건강에 이상이 없는 자
+다. 방과후학교 개인위탁 외부강사 활동에 제한이 없는 자</t>
+        </is>
+      </c>
       <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="5" t="n"/>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814746</t>
         </is>
       </c>
       <c r="L41" s="5" t="n"/>
@@ -3154,67 +3134,26 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>남지읍 평생학습센터 강사 모집 공고</t>
+          <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>동원고등학교</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>경남 창녕군</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>동원고등학교 결원대체강사 채용공고(수학)</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>동원고등학교</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -3228,51 +3167,51 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -3284,15 +3223,74 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n">
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>내곡초등학교</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명(전일제 또는 시간제)
+2. 기간: 2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명(전일제 또는 시간제)</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n"/>
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="5" t="n"/>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
       <c r="L44" s="5" t="n"/>
@@ -3304,19 +3302,19 @@
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
+          <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>내곡초등학교</t>
+          <t>율하중학교</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -3326,70 +3324,11 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n"/>
       <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>아래와 같이 결원대체강사 채용을 공고합니다.
-1. 대상: 초등교사 1명(전일제 또는 시간제)
-2. 기간: 2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>초등교사 1명(전일제 또는 시간제)</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>계약제 교원(시간 강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>율하중학교</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -3400,51 +3339,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -3496,47 +3435,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -3548,51 +3487,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -3609,13 +3548,59 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="n"/>
       <c r="J49" s="5" t="n"/>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
       <c r="L49" s="5" t="n"/>
@@ -3627,19 +3612,19 @@
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>함양제일고등학교</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3648,11 +3633,18 @@
         </is>
       </c>
       <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
+        </is>
+      </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
+1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
+2. 과목: 특수
+3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
+-자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
       <c r="G50" s="5" t="n"/>
@@ -3661,7 +3653,7 @@
       <c r="J50" s="5" t="n"/>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
       <c r="L50" s="5" t="n"/>
@@ -3673,19 +3665,19 @@
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>함양제일고등학교</t>
+          <t>마산고등학교</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3694,18 +3686,10 @@
         </is>
       </c>
       <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
-        </is>
-      </c>
+      <c r="E51" s="5" t="n"/>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
-1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
-2. 과목: 특수
-3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
--자세한 내용은 공고문 참조 바랍니다.</t>
+          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
       <c r="G51" s="5" t="n"/>
@@ -3714,7 +3698,7 @@
       <c r="J51" s="5" t="n"/>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
       <c r="L51" s="5" t="n"/>
@@ -3726,19 +3710,19 @@
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
+          <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>마산고등학교</t>
+          <t>대암초등학교</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3747,57 +3731,12 @@
         </is>
       </c>
       <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
+        </is>
+      </c>
       <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>기초학력전담강사 채용 공고문</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>대암초등학교</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -3817,49 +3756,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n">
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -3868,13 +3807,59 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
       <c r="G54" s="5" t="n"/>
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="n"/>
       <c r="J54" s="5" t="n"/>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
         </is>
       </c>
       <c r="L54" s="5" t="n"/>
@@ -3893,12 +3878,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>일운초등학교</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -3910,8 +3895,7 @@
       <c r="E55" s="5" t="n"/>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
       <c r="G55" s="5" t="n"/>
@@ -3920,7 +3904,7 @@
       <c r="J55" s="5" t="n"/>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
         </is>
       </c>
       <c r="L55" s="5" t="n"/>
@@ -3939,12 +3923,12 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>일운초등학교</t>
+          <t>함안고등학교</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -3956,7 +3940,8 @@
       <c r="E56" s="5" t="n"/>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
       <c r="G56" s="5" t="n"/>
@@ -3965,7 +3950,7 @@
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
         </is>
       </c>
       <c r="L56" s="5" t="n"/>
@@ -3984,36 +3969,31 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>함안고등학교</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 고성군</t>
         </is>
       </c>
       <c r="D57" s="5" t="n"/>
       <c r="E57" s="5" t="n"/>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
-자세한 내용은 첨부파일 확인 바랍니다.</t>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
         </is>
       </c>
       <c r="G57" s="5" t="n"/>
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="n"/>
       <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
-        </is>
-      </c>
+      <c r="K57" s="5" t="n"/>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="inlineStr">
@@ -4030,63 +4010,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>소토초등학교</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>경남 고성군</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D58" s="5" t="n"/>
       <c r="E58" s="5" t="n"/>
       <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n"/>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교 한국어교육 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4108,13 +4047,58 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>경남혜림학교</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
+        </is>
+      </c>
       <c r="G59" s="5" t="n"/>
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="n"/>
       <c r="J59" s="5" t="n"/>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
         </is>
       </c>
       <c r="L59" s="5" t="n"/>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3250,85 +3250,157 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>경상남도 청소년수련원 위탁운영 단체(법인) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>고성군</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남 고성군</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>경상남도 청소년수련원 재개장을 앞두고 해당 시설의 운영 및 관리를 위한 위탁운영 단체(법인)을  모집하고자 첨부와 같이 공고합니다.
+고성군 공고 제2026-1750호
+경상남도 청소년수련원 위탁운영 단체(법인) 모집 공고
+경상남도 청소년수련원의 재개장을 앞두고 「청소년 기본법」제18조, 「청소년활동 진흥법」제16조, 「경상남도 청소년수련원 설치 및 운영 조례」제5조에 따라해당 시설의 운영 및 관리를 위한 위탁운영 단체(법인)를 모집하고자 다음과 같이 공고합니다.
+2026년 10월 7일
+고 성 군 수
+1. 위탁대상 시설 현황
+가. 시 설 명: 경상남도 청소년수련원
+나. 위 치: 경남 고성군 하이면 자란만로 646(대지면적 43,917㎡)
+다. 시설규모: 건축면적 3,007.67㎡, 연면적 6,923.44㎡(지상 3층, 지하 1층)
+- 본관동: 생활관(51실), 대강당(1), 회의실(중 1, 소 2), 식당(1) 등
+- 수련시설: 운동장, 수련활동장 등
+라. 수용인원: 204명(4인실 44실, 가족실 7실)
+2. 위탁내용: 경상남도 청소년수련원 시설물 및 운영 관련 전반 사항
+가.「경상남도 청소년수련원 설치 및 운영 조례」제4조에 명시된 기능 수행
+1) 청소년의 심신단련, 자질배양, 취미개발 및 정서함양을 위한 수련활동2) 청소년 복지증진을 위한 각종 교육, 연수 및 상담3) 청소년지도자 연수 및 각종 수련거리 개발·운영 및 보급 등
+1) 청소년의 심신단련, 자질배양, 취미개발 및 정서함양을 위한 수련활동
+2) 청소년 복지증진을 위한 각종 교육, 연수 및 상담
+3) 청소년지도자 연수 및 각종 수련거리 개발·운영 및 보급 등
+나. 청소년수련원 시설 내외부 유지 관리
+다. 본관동 및 수련시설 운영 전반
+라. 청소년 관련 프로그램 개발 및 운영 등
+3. 위탁비용: 청소년수련원 운영 및 관리에 따른 비용은 수탁자 부담
+4. 위탁기간: 3년 간 (2027. 1. ~ 2029. 12.)
+* 위탁기간의 개시일은 사정에 따라 변경될 수 있음
+5. 신청자격: 「청소년 기본법」제3조 및 같은법 시행령 제2조에 따른 청소년단체
+&lt; 청소년단체 &gt;【청소년 기본법】 제3조(정의) 8.“청소년단체”란 청소년육성을 주된 목적으로 설립된 법인이나 대통령령으로 정하는 단체를 말한다.【청소년 기본법 시행령】제2조(정의) 「청소년 기본법」 제3조제8호에서 “대통령령으로 정하는 단체”란 청소년활동, 청소년복지 또는 청소년보호를 주요사업으로 하는 단체로서 성평등가족부장관이 인정하는 단체를 말한다. 아래 각항중 하나에 해당되는 경우는 청소년기본법 시행령 제2조에 따라 “성평등가족부장관이 인정하는 청소년단체”로 본다. ① 정관의 설립목적 또는 목적사업에 청소년활동, 청소년복지, 청소년보호를 주요사업으로 하고 청소년관련 활동실적이 있는 비영리 법인 ② 청소년활동, 청소년복지, 청소년보호를 주요사업으로 하는 단체로서 비영리민간단체지원법에 따라 등록된 단체 ③ 청소년학과·교육학과 등 청소년 관련학과가 개설되어 있고 청소년활동 실적이 있는 대학(학교법인을 포함한다)
+&lt; 청소년단체 &gt;</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -3339,51 +3411,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -3435,47 +3507,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -3487,51 +3559,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -3548,59 +3620,13 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
-        </is>
-      </c>
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="n"/>
       <c r="J49" s="5" t="n"/>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
         </is>
       </c>
       <c r="L49" s="5" t="n"/>
@@ -3612,33 +3638,79 @@
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
+          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>함양제일고등학교</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>10.26.(월)-11.11.(수)/ 총58시간</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
 1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
@@ -3647,58 +3719,13 @@
 -자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O50" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
-        </is>
-      </c>
       <c r="G51" s="5" t="n"/>
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="n"/>
       <c r="J51" s="5" t="n"/>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
       <c r="L51" s="5" t="n"/>
@@ -3710,33 +3737,78 @@
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
           <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>대암초등학교</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -3756,49 +3828,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n">
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -3807,59 +3879,13 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O53" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
-        </is>
-      </c>
       <c r="G54" s="5" t="n"/>
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="n"/>
       <c r="J54" s="5" t="n"/>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
         </is>
       </c>
       <c r="L54" s="5" t="n"/>
@@ -3878,12 +3904,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>일운초등학교</t>
+          <t>김해생명과학고등학교</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -3895,7 +3921,8 @@
       <c r="E55" s="5" t="n"/>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
       <c r="G55" s="5" t="n"/>
@@ -3904,7 +3931,7 @@
       <c r="J55" s="5" t="n"/>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
         </is>
       </c>
       <c r="L55" s="5" t="n"/>
@@ -3923,12 +3950,12 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>함안고등학교</t>
+          <t>일운초등학교</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -3940,8 +3967,7 @@
       <c r="E56" s="5" t="n"/>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
-자세한 내용은 첨부파일 확인 바랍니다.</t>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
       <c r="G56" s="5" t="n"/>
@@ -3950,7 +3976,7 @@
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
         </is>
       </c>
       <c r="L56" s="5" t="n"/>
@@ -3969,31 +3995,36 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>함안고등학교</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>경남 고성군</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D57" s="5" t="n"/>
       <c r="E57" s="5" t="n"/>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
       <c r="G57" s="5" t="n"/>
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="n"/>
       <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
+        </is>
+      </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="inlineStr">
@@ -4010,22 +4041,63 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>소토초등학교 한국어교육 강사 채용 공고</t>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>소토초등학교</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 고성군</t>
         </is>
       </c>
       <c r="D58" s="5" t="n"/>
       <c r="E58" s="5" t="n"/>
       <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>소토초등학교</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4047,58 +4119,13 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>경남혜림학교</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
-        </is>
-      </c>
       <c r="G59" s="5" t="n"/>
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="n"/>
       <c r="J59" s="5" t="n"/>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
       <c r="L59" s="5" t="n"/>
@@ -4109,6 +4136,51 @@
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>경남혜림학교</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2596,17 +2596,17 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>진해신항초 계약제교원(전일제 강사) 채용 모집 공고</t>
+          <t>성주초등학교 풍물동아리 외부 강사 모집 공고</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>진해신항초등학교</t>
+          <t>성주초등학교</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 창원시</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2616,154 +2616,6 @@
       </c>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 진해신항초등학교 계약제교원(전일제강사) 다음과 같이 채용 공고합니다.
-◆ 채용내용
-가. 채용기간 및 채용인원: 1명
-- 전일제강사: 2026. 10. 26.~ 2027. 11. 13. 1명(5학년)
-◆ 전형방법
-가. 1차 전형: 서류전형(서류전형 합격한 자에 한하여 2차 전형 대상자 개별 통보)
-나. 2차 전형: 면접
-◆ 제출서류
-가. 응시자 제출서류
-◦ 응시원서 1부(붙임 서식, 사진 첨부, 연락 가능한 전화번호 반드시 기재)
-◦ 자기소개서 1부(붙임 서식)
-◦ 개인정보 수집·이용에 대한 동의서(붙임 서식)
-나. 최종합격자 제출서류
-◦ 교사 자격증 사본 또는 자격 인정 조서 1부
-◦ 졸업증명서 사본 1부(원본지참)
-◦ 주민등록 초본 1부
-◦ 공무원채용신체검사서(1년 이내) 1부
-◦ 잠복결핵검사 확인서 1부(최초 검사의 확인서를 계속 사용 가능)
-◦ 마약/대마/향정신성의약품 검사결과통보서(진단서) 1부
-◦ 초임호봉획정을 위한 경력기간 합산신청서 1부
-◦ 범죄경력조회동의서 1부
-◦ 가족 채용 제한 여부 확인서 1부
-◦ 청렴 서약서 1부
-◆ 서류접수 및 전형일정
-가. 원서접수
-◦ 접수기간: 2026. 10. 2.(금)~10. 7.(수) 10:00까지
-◦ 접수방법: 온라인 접수
-- 메일주소: [이메일]
-- 스캔파일 제출(제출서류 미비시 접수 불가), 면접 시 해당 서류 원본 제출
-나. 1차: 서류전형 합격자(만 개별 전화 통지) 발표 예정일 &gt; 2026. 10. 8.(목), 10:00 이후
-다. 2차: 면접(서류심사 합격자에 한함) 예정일 &gt; 2026. 10. 13.(화) 16:00, 교무실
-◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
-6. 합격자 발표
-◦ 최종합격자 발표: 2026. 10. 14.(수) 18:00 이후 (최종합격자에게만 개별 통지)
-7. 유의사항
-◦ 기간제교원 인력풀 등재자는 우선 임용될 수 있습니다.
-◦ 인력풀 등재자는 최종합격 후 확인이 불가능한 서류만 제출합니다.
-◦ 상기 일정은 진행 상황에 따라 변경될 수 있으며, 변경 시 별도 통보합니다.
-◦ 기재사항이 사실과 다르거나 허위로 작성된 경우는 합격을 취소합니다.
-◦ 제출 서류의 기재착오, 누락, 서류 미제출, 연락 불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.
-◦ 최종합격자로 발표된 이후에도 결격사유가 있는 자는 합격을 취소할 수 있습니다.
-◦ 기타 자세한 사항은 진해신항초등학교(☎551-2018)로 문의하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814721</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>밀양여자중학교</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>2026. 밀양여자중학교 계약제교원(전일제강사)채용 공고(사회)
-가. 원서접수
-◦ 접수기간 : 2026. 10. 3.(토)～10. 7(수) 11:00까지
-◦ 접수장소 : 밀양여자중학교 전자우편
-◦ 접수방법 :  e-메일 접수([이메일], 스캔본 제출, 면접 시 원본 제출)
-2026. 10. 7(수). 11:00 발송분까지 유효함
-나. 1차 : 서류전형 합격자 발표(개별 문자 통지) 예정일 : 2026. 10. 8(목) 14:00(예정)
-다. 2차 : 면접 (서류심사 합격자에 한함) 예정일: 2026. 10. 12(월) 10:30(예정)
-◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
-**자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814716</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>성주초등학교 풍물동아리 외부 강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>성주초등학교</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>경남 창원시</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성주초등학교 풍물동아리 외부 강사 모집계획을 다음과 같이 공고합니다.
 가. 공고 기간
@@ -2784,51 +2636,51 @@
 ※ 모집 일정은 학교 사정에 따라 변경될 수 있습니다.</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814722</t>
         </is>
       </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>화정초등학교</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
@@ -2837,51 +2689,51 @@
 * 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>주동초등학교</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>2026년 주동초등학교에서는 초등 1~2학년 맞춤형프로그램과 관련하여 아래와 같이 외부강사(문화, 예술, 음악, 놀이영어 등 다양한 분야 지원 가능)를 모집하오니, 유능한 강사님들의 많은 지원 바랍니다.
 1.  서류접수:  2026.  10. 1.(목) ~ 2026. 10.  7.(수) 16시까지 도착분
@@ -2893,51 +2745,51 @@
 ※ 접수시간을 반드시 준수해 주시길 바랍니다.</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814652</t>
         </is>
       </c>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -2950,94 +2802,94 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n">
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>남지읍 평생학습센터 강사 모집 공고</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>창녕군</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>경남 창녕군</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>율하중 계약제교원(체육 시간강사) 채용 계획(3차 공고)</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1)
 2. 서류접수 및 전형방법
@@ -3049,51 +2901,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814756</t>
         </is>
       </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집공고(수학)</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>거제고현중학교</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>★  모집 세부 사항
 가. 공고 기간: 2026.10.7.(수)~2026.10.14.(수)
@@ -3109,51 +2961,51 @@
 다. 방과후학교 개인위탁 외부강사 활동에 제한이 없는 자</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814746</t>
         </is>
       </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -3167,51 +3019,51 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -3223,53 +3075,53 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n">
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
         </is>
       </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 위탁운영 단체(법인) 모집 공고</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>고성군</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>경남 고성군</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 재개장을 앞두고 해당 시설의 운영 및 관리를 위한 위탁운영 단체(법인)을  모집하고자 첨부와 같이 공고합니다.
 고성군 공고 제2026-1750호
@@ -3301,106 +3153,106 @@
 &lt; 청소년단체 &gt;</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -3411,51 +3263,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -3507,47 +3359,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -3559,51 +3411,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -3620,13 +3472,112 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고등학교</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
+1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
+2. 과목: 특수
+3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
+-자세한 내용은 공고문 참조 바랍니다.</t>
+        </is>
+      </c>
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="n"/>
       <c r="J49" s="5" t="n"/>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
       <c r="L49" s="5" t="n"/>
@@ -3645,12 +3596,12 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>마산고등학교</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3662,8 +3613,7 @@
       <c r="E50" s="5" t="n"/>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
       <c r="G50" s="5" t="n"/>
@@ -3672,7 +3622,7 @@
       <c r="J50" s="5" t="n"/>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
       <c r="L50" s="5" t="n"/>
@@ -3691,12 +3641,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
+          <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>함양제일고등학교</t>
+          <t>대암초등학교</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3707,108 +3657,10 @@
       <c r="D51" s="5" t="n"/>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
+          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
-1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
-2. 과목: 특수
-3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
--자세한 내용은 공고문 참조 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
-      <c r="N51" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O51" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>기초학력전담강사 채용 공고문</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>대암초등학교</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -3828,49 +3680,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n">
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -3879,13 +3731,104 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>일운초등학교</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+        </is>
+      </c>
       <c r="G54" s="5" t="n"/>
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="n"/>
       <c r="J54" s="5" t="n"/>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
         </is>
       </c>
       <c r="L54" s="5" t="n"/>
@@ -3904,12 +3847,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>함안고등학교</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -3921,8 +3864,8 @@
       <c r="E55" s="5" t="n"/>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
       <c r="G55" s="5" t="n"/>
@@ -3931,7 +3874,7 @@
       <c r="J55" s="5" t="n"/>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
         </is>
       </c>
       <c r="L55" s="5" t="n"/>
@@ -3950,35 +3893,31 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>일운초등학교</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 고성군</t>
         </is>
       </c>
       <c r="D56" s="5" t="n"/>
       <c r="E56" s="5" t="n"/>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
         </is>
       </c>
       <c r="G56" s="5" t="n"/>
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="n"/>
       <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
-        </is>
-      </c>
+      <c r="K56" s="5" t="n"/>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="5" t="n"/>
       <c r="N56" s="5" t="inlineStr">
@@ -3995,12 +3934,12 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>함안고등학교</t>
+          <t>소토초등학교</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -4011,93 +3950,6 @@
       <c r="D57" s="5" t="n"/>
       <c r="E57" s="5" t="n"/>
       <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
-자세한 내용은 첨부파일 확인 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O57" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>고성군</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>경남 고성군</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n"/>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교 한국어교육 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4119,68 +3971,68 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="O57" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
         </is>
       </c>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>통영여자중학교 시간강사(수학) 채용</t>
+          <t>계동초 방과후학교 프로그램 개인위탁 외부강사(한자속독) 모집 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>통영여자중학교</t>
+          <t>계동초등학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -640,188 +640,15 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026. 10. 15~2026. 10. 23</t>
+          <t>2026년 11월 1일 ∼ 2027년 2월 28일</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>통영여자중학교에서 근무할 시간강사를 다음과 같이 채용 공고합니다.
-- 채용기간 : 2026. 10. 15~2026. 10. 23
-- 접수기간 : 2026. 10. 2～2026. 10. 7. 12:00시까지
-- 접수장소 : 통영여자중학교 전자우편
-- 접수방법 : 전자우편(주소: [이메일], 스캔본 제출, 면접 시 원본 제출, 2026. 10. 7. 12:00시 발송분까지)
-자세한 내용은 첨부파일을 참고해주시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814706</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>악양초등학교. 결원 대체 강사 채용 공고(전일제강사)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>악양초등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.26 ~ 2026.10.30.(총5일)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 악양초등학교에 근무할 결원 대체 강사를 다음과 같이 채용 공고 안내
-1. 채용과목 : 초등(전일제강사 1명)
-2. 채용기간 : 2026.10.26 ~ 2026.10.30.(총5일)
-3. 응시자격
-1순위: 만 62세 미만 동일 자격 소지자
-2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
-*  1순위 지원자 없을 시  2순위자 채용 가능
-4. 서류 접수 : 2026.9.30.(수)~10.7.(수)15:00까지
-악양초등학교 전자우편 ([이메일])
-스캔본 제출, 면접 시 원본 제출,
-5. 제출서류
-◦ 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
-◦ 자기소개서 1부.(붙임서식)
-◦ 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)
-* 자세한 사항은 붙임 공고문을 참조바랍니다.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>1순위: 만 62세 미만 동일 자격 소지자
-2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
-1순위 지원자 없을 시  2순위자 채용 가능</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재), 자기소개서 1부.(붙임서식), 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814642</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>대방중학교 전일제강사(기술·가정과) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>대방중학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026년 11월 9일 ~ 2026년 11월 13일(5일)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 대방중학교 기술·가정과 전일제강사를 다음과 같이 채용 공고합니다.
-1. 접수기간: 2026년 10월 2일(금) ~ 2026년 10월 7일(수), 09:00까지 도착분에 한함
-2. 접수방법: 이메일 접수([이메일])
-3. 서류심사결과 발표: 2026년 10월 7일(수), 13:30 이후(개별 알림)
-4. 면접심사: 2026년 10월 8일(목), 12:30 (장소 개별 알림)
-5. 최종합격자 발표: 2026년 10월 8일(목), 14:30 이후(합격자 개별 알림)
-※채용기간: 2026년 11월 9일 ~ 2026년 11월 13일(5일)
-기타 자세한 사항은 붙임 문서를 참고하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814661</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>계동초 방과후학교 프로그램 개인위탁 외부강사(한자속독) 모집 공고</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>계동초등학교</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2026년 11월 1일 ∼ 2027년 2월 28일</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026. 계동초 방과후학교 프로그램(한자속독) 개인위탁 외부강사를 다음과 같이 모집합니다.
 1. 계약 기간: 2026년 11월 1일 ∼ 2027년 2월 28일
@@ -835,49 +662,49 @@
 -자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814720</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>분성초등학교 방과후학교 외부강사 모집 공고(바이올린)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>분성초등학교</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 3. ~ 2027. 2. 25.</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>2026. 분성초 방과후학교 바이올린 개인위탁 외부강사를 다음과 같이 모집합니다.
 1. 계약 기간: 2026. 11. 3. ~ 2027. 2. 25.
@@ -894,47 +721,47 @@
 -자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814693</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교 결원대체시간강사(수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고입니다.
 1. 채용과목 및 인원, 채용기간
@@ -954,49 +781,49 @@
 ※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814688</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교 결원대체강사(과학 전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026학년도 삼정자중학교 결원대체강사(과학)를 다음과 같이 채용하고자 합니다.
 1. 채용과목 및 채용 내용
@@ -1019,49 +846,49 @@
 **자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814686</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교 결원대체 시간강사(1순위:윤리, 2순위:일반사회) 채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.(월)~2026. 10. 30.(금) (총 17시간)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원중앙고등학교 결원대체 시간강사 채용을 다음과 같이 공고합니다.
 1. 채용과목 : 윤리(1순위:윤리, 2순위:일반사회)
@@ -1072,47 +899,47 @@
 * 자세한 사항은 첨부파일 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814730</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>밀양고 전일제 강사(수학) 채용 공고(2차)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>밀양고등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 19. ~ 2026. 10. 23.(5일, 17시수)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026학년도 밀양고등학교 전일제 강사 채용 공고
 2026학년도 밀양고등학교에 근무할 전일제 강사를 다음과 같이 채용 공고합니다.
@@ -1137,47 +964,47 @@
 자세한 사항은 첨부파일을 참고</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814743</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>김해내동초 돌봄 프로그램(종이접기 1명) 외부강사 모집 공고문</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>김해내동초등학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2027.2.28.</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2026. 김해내동초 돌봄 프로그램(종이 접기 1명)외부 강사 모집 공고를  아래와 같이 실시합니다.
 1. 모집 인원: 1명
@@ -1187,49 +1014,49 @@
 5. 기타 자세한 사항은 첨부 문서를 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814620</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>성호초등학교 전일제강사 채용 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>성호초등학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026.10.13.~ 2026.10.21.(9일)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 (재)공고 합니다.
 1. 채용과목 및 인원: 특수교사 1명
@@ -1240,49 +1067,109 @@
 *자세한 사항은 붙임 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>창원남산고등학교 계약제교원 채용공고(체육 기간제 또는 강사)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>창원남산고등학교</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.14.(수)~2026.12.4.(금)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>창원남산고등학교 계약제교원 채용공고
+1. 채용인원 : 체육 기간제 교사 또는 강사
+2. 채용과목: 체육
+3. 채용기간: 2026.10.14.(수)~2026.12.4.(금)
+4. 지원자격: 해당교과목 자격증 소지자
+5. 채용일정
+가. 응시원서접수기간: 2026.10.07.(수)~10.11.(일)16:30 까지 도착분에 한함.
+나. 접수방법:  e-mail접수 [이메일]
+다. 서류전형 합격자 발표: 2026.10.12. (월) 11:00 이후 (합격자에 한해 개별통보)
+라. 면접일시: 2026.10.13.(화)11시
+마. 최종합격자 발표: 2026.10.13.(화) 14시 이후
+6. 자세한 사항은 채용공고문을 참고하시기 바랍니다</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>해당교과목 자격증 소지자</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814789</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(학교폭력담당자 수업경감 시간강사) 2차 채용 공고</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026.10.19. ~ 2026.12.31.</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 50호
 웅상고등학교 학교폭력담당자 수업경감 강사 3차 채용 공고
@@ -1337,47 +1224,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814610</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2026.10.30.(총16시간)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모자격
@@ -1405,49 +1292,49 @@
 5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>증산중학교 계약제교원(시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1461,49 +1348,49 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814584</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용 공고(수학)</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1517,49 +1404,99 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814744</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>통영여자중학교 시간강사(수학) 채용</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>통영여자중학교</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 15~2026. 10. 23</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>통영여자중학교에서 근무할 시간강사를 다음과 같이 채용 공고합니다.
+- 채용기간 : 2026. 10. 15~2026. 10. 23
+- 접수기간 : 2026. 10. 7～2026. 10. 12. 15:00시까지
+- 접수장소 : 통영여자중학교 전자우편
+- 접수방법 : 전자우편(주소: [이메일], 스캔본 제출, 면접 시 원본 제출, 2026. 10. 12. 15:00시 발송분까지)
+자세한 내용은 첨부파일을 참고해주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814706</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>김해수남고 학교폭력 업무담당자 수업경감 시간강사 채용 재공고8차(일반사회)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>김해수남고등학교</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16. ~ 2027. 2. 5. (일반사회-시간강사) 주4시간(금요일), 시간당 25,000원</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>2026학년도 김해수남고등학교에 근무할 시간강사를 다음과 같이 채용 재공고합니다.
 1. 과목: 일반사회(사회계열 모두 가능) 1명
@@ -1571,47 +1508,47 @@
 7. 문의전화: 김해수남고 교무센터 ☎724-9350, 기타 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814759</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>동진초등학교 2026.10.12.자 계약제교원(결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>동진초등학교</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 10. 17.(5일)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등교사
 나. 채용 기간: 2026. 10. 12. ~ 2026. 10. 17.(5일)
@@ -1623,15 +1560,72 @@
 ※ 국가공무원법 제33조의 규정에 의한 공무원임용 결격사유가 없는 자</t>
         </is>
       </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814468</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>증산고등학교 결원대체강사(전일제강사/수학) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>증산고등학교</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 15.(목) ~ 2026. 11. 6.(금) 17일, 110,000/일</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>증산고등학교에서 근무할 결원대체강사(전일제강사/수학) 를 다음과 같이 채용하고자 합니다.
+1. 채용과목: 수학
+2. 채용기간: 2026. 10. 15.(목) ~ 2026. 11. 6.(금) 17일, 110,000/일
+3. 서류접수 및 전형일정
+가. 서류접수
+- 접수기간: 2026년10월7일(수) ∼ 2026년10월13일(화) 12:00 까지
+- 접수방법: 채용 담당자 이메일([이메일])로 온라인 접수
+나. 1차 서류전형 합격자 발표(개별 통지): 2026년10월13일(화) 15:00이후
+다. 2차 면접 및 수업시연(서류심사 합격자에 한함)
+- 면접 일시 및 장소: 2026년10월14일(수)10:00~ (1층 교무실)
+- 일시 및 장소는 서류전형 합격자에게 개별 통보
+4. 최종합격자발표 : 2026년10월14일(수)12:00 이후(합격자 개별 통보)
+* 자세한 사항은 첨부파일 확인 바랍니다.</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814468</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814809</t>
         </is>
       </c>
       <c r="L18" s="5" t="n"/>
@@ -1961,30 +1955,82 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>대방중학교 전일제강사(기술·가정과) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>대방중학교</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>2026년 11월 9일 ~ 2026년 11월 13일(5일)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 대방중학교 기술·가정과 전일제강사를 다음과 같이 채용 공고(2차)합니다.
+1. 접수기간: 2026년 10월 8일(목) ~ 2026년 10월 14일(수), 09:00까지 도착분에 한함
+2. 접수방법: 이메일 접수([이메일])
+3. 서류심사결과 발표: 2026년 10월 14일(수), 13:30 이후(개별 알림)
+4. 면접심사: 2026년 10월 15일(목), 12:30 (장소 개별 알림)
+5. 최종합격자 발표: 2026년 10월 15일(목), 14:30 이후(합격자 개별 알림)
+※채용기간: 2026년 11월 9일 ~ 2026년 11월 13일(5일)
+기타 자세한 사항은 붙임 문서를 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814661</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t>하동고등학교 결원대체강사(국어) 채용 공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>하동고등학교</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026.11.09.~2026.11.13.(5일), 2026.12.21.~2026.12.22.(2일)(총 7일)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>2026학년도 하동고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모 자격(결원대체강사;전일제/시간제)
@@ -2007,53 +2053,109 @@
 자세한 내용은 붙임파일을 참고해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>1순위: 채용 과목 중등 자격증 소지자</t>
         </is>
       </c>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814762</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>사회과(역사 또는 일반사회 또는 지리) 중등수업지원강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>창원상남중학교</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 16.~2026. 12. 31.(2학년 역사수업, 주당 7시간, 월요일 2,3,4교시/목요일 1,2,3,4교시)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 창원상남중학교에서 근무할 중등수업지원강사를 다음과 같이 채용 공고합니다.
+1. 채용과목(인원): 사회(역사 또는 일반사회 또는 지리)(1명)
+2. 채용기간: 2026. 11. 16.~2026. 12. 31.(2학년 역사수업, 주당 7시간, 월요일 2,3,4교시/목요일 1,2,3,4교시)
+3. 채용 방법 및 일정
+가. 원서 접수 기간: 2026. 10. 12.(월)～ 2026. 10. 16.(금) 16:00까지
+나. 원서 접수 방법: 창원상남중학교 전자우편(주소: [이메일], 2026. 10. 16.(금) 16:00 발송분까지)
+다. 서류전형 합격자 발표: 2026. 10. 19.(월)
+라. 면접: 2026. 10. 20.(화) (일시, 장소의 구체적인 내용은 서류전형 합격자에게만 문자로 개별 통보)
+마. 최종합격자 발표: 2026. 10. 20.(화)
+*자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814787</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -2104,53 +2206,53 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H26" s="5" t="n">
         <v>8046</v>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>유목초등학교</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>구체적인 내용은 공고문을 참고바랍니다.
 1. 분야: 특수학급 결원대체강사
@@ -2158,49 +2260,49 @@
 3.기간: 2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n">
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>유목초 특수학급 결원대체강사 채용 공고</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>유목초등학교</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>구체적인 내용은 공고문을 참고바랍니다.
 1. 분야: 특수학급 결원대체강사
@@ -2208,49 +2310,49 @@
 3.기간: 2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n">
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>웅남중 학교운동부지도자 채용공고(태권도)</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>웅남중학교</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>2026.12.01.(화)~2027.2.28.(일)</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>웅남중학교 운동부 지도자 채용 공고
 - 채용분야: 운동부지도자
@@ -2263,98 +2365,98 @@
 자세한 사항은 붙임 문서를 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814764</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>2026.10.1.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명
 2. 기간: 2026.10.1.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>유영초등학교</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~2026.10.30.(19일간)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 초등 결원대체 강사(전일제)
 2. 채용 인원: 1명
@@ -2362,49 +2464,49 @@
 4. 자세한 사항은 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n">
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>남지초등학교</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등기간제교원
 나. 채용 기간: 2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)
@@ -2417,49 +2519,49 @@
 ※자세한 사항은 공고문 참고</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n">
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
 1. 채용과목: 영어(1명)
@@ -2467,49 +2569,49 @@
 상세내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n">
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -2564,15 +2666,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H34" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -2582,144 +2684,26 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>성주초등학교 풍물동아리 외부 강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>성주초등학교</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>경남 창원시</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 성주초등학교 풍물동아리 외부 강사 모집계획을 다음과 같이 공고합니다.
-가. 공고 기간
-2026년 10월 2일 (금) ~ 10월 7일 (수)
-나. 서류 접수
-2026년 10월 2일 (금) ~ 10월 7일 (수)  12:00 까지
-다. 접수 장소
-온라인 접수(전자우편 [이메일])
-(우편) 우편번호 51491 : 경남 창원시 성산구 가음정로 127 성주초등학교
-- 10. 7.(수) 12:00 도착분까지
-라. 1차 서류 심사: 2026년 10월 7일(수)
-▶ 1차 서류 심사 합격자에 한해 2차 면접 심사를 실시하여 최종 선정
-마. 1차 서류 심사 합격 통보: 2026년 10월 7일(수) 개별 통보
-바. 2차  면접 심사: 2026년 10월 8일(목), 면접 중 수업 시연 포함
-*장소 및 시간은 추후 안내
-사. 최종합격자 통보: 2026년 10월 8일(목) 17:00 이후 개별 통보
-아. 계약: 10월중 학교장과 계약
-※ 모집 일정은 학교 사정에 따라 변경될 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814722</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 영어 프로그램 개인위탁 강사 모집공고</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>화정초등학교</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>화정초등학교에서는 돌봄·방과후학교교 운영과 관련하여 아래와 같이 방과후학교 프로그램 개인위탁 강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
-1. 접수기간 : 2026. 9. 29.(화) ~ 2026. 10. 7.(수) 15:00까지
-2. 서류전형 합격자 개별 통보일 : 2026. 10. 8.(목) 14:00이후
-3. 접수방법 : 직접 방문 접수
-* 자세한 사항은 첨부파일을 참조해 주시면 감사하겠습니다.</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814592</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>주동초등학교 맞춤형프로그램 외부강사 모집 공고</t>
+          <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>주동초등학교</t>
+          <t>어방초등학교</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2729,67 +2713,11 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>2026년 주동초등학교에서는 초등 1~2학년 맞춤형프로그램과 관련하여 아래와 같이 외부강사(문화, 예술, 음악, 놀이영어 등 다양한 분야 지원 가능)를 모집하오니, 유능한 강사님들의 많은 지원 바랍니다.
-1.  서류접수:  2026.  10. 1.(목) ~ 2026. 10.  7.(수) 16시까지 도착분
-2. 서류심사 결과:  2026. 10. 8.(목) 10:00~ 합격자에 한하여 개별 통보(문자)
-3. 2차 면접심사(운영능력):  2026. 10. 13.(화) 10:00~  면접일정은 합격자에게 별도 안내(문자)
-4. 최종합격자발표:  2026. 10. 14.(수) 10:00~ 최종합격자 개별 통보(문자)
-※ 학교 사정에 따라 추후 일정은 변경될 수 있습니다.
-※ 자세한 사항은 첨부파일을 확인하시기 바랍니다.
-※ 접수시간을 반드시 준수해 주시길 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814652</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>어방초등학교</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -2802,17 +2730,58 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>남지읍 평생학습센터 강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>창녕군</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>경남 창녕군</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
-        </is>
-      </c>
+      <c r="K36" s="5" t="n"/>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="5" t="n"/>
       <c r="N36" s="5" t="inlineStr">
@@ -2822,74 +2791,33 @@
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>남지읍 평생학습센터 강사 모집 공고</t>
+          <t>율하중 계약제교원(체육 시간강사) 채용 계획(3차 공고)</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>율하중학교</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>경남 창녕군</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>율하중 계약제교원(체육 시간강사) 채용 계획(3차 공고)</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>율하중학교</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1)
 2. 서류접수 및 전형방법
@@ -2901,13 +2829,68 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814756</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>진주중앙고 전일제 강사(체육) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>진주중앙고등학교</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 진주중앙고등학교 전일제 강사를 다음과 같이 채용 공고 합니다.
+1. 채용 과목 및 인원: 체육 1명.
+2. 접수 기간: 2026. 10. 7.(수) ~ 10. 11.(일) 15시 발송분까지
+3. 접수장소: 진주중앙고등학교 전자우편([이메일])
+4. 자세한 사항은 붙임 문서를 참고 하시기 바랍니다.</t>
+        </is>
+      </c>
       <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
+      <c r="H38" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I38" s="5" t="n"/>
       <c r="J38" s="5" t="n"/>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814756</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814791</t>
         </is>
       </c>
       <c r="L38" s="5" t="n"/>
@@ -2926,12 +2909,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 개인위탁 외부강사 모집공고(수학)</t>
+          <t>진해용원고등학교 물리 계약제교원(전일제/시간제강사) 채용 공고</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>거제고현중학교</t>
+          <t>진해용원고등학교</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2941,11 +2924,187 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 진해용원고등학교에 근무할 계약제교원(전일제강사/시간강사)을 다음과 같이 채용 공고 합니다.
+1. 채용과목: 물리
+2. 채용예정기간: 2026.10.19.~2026.10.23.
+3. 전형방법
+가. 1차 시험: 서류전형
+나. 2차 시험: 면접(서류전형 합격한 자에 한하여 개별 통보)
+**수업실연(서류전형 합격자에 한하여 필요한 경우 실시)
+4. 서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간: 2026. 10. 8.(목) ~ 2026. 10. 11.(일)
+◦ 접수방법: 온라인(E-mail) 접수 ([이메일]) 2026. 10. 11.(일) 발송분까지
+- 파일명은 교과목-성명으로 첨부(예시: 영어-홍길동)
+※ 개인 서명한 스캔파일(PDF파일), 면접시 원본 제출
+나. 1차: 서류전형 합격자 발표(합격자에 한해 개별 전화 통지) 예정일: 2026. 10. 12.(월) 14시 이후
+다. 2차: 면접 (서류심사 합격자에 한함) 예정일: 2026. 10. 13.(화) 14시 2층 소회의실
+5. 합격자 발표
+◦ 최종합격자 발표: 2026. 10. 14.(수) 10시 이후 합격자에 한해 개별 전화 통지</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814797</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>산양초등학교 돌봄교실 특기적성 프로그램 외부강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>산양초등학교</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>본교 돌봄교실 운영과 관련하여 특기적성 프로그램 개인 위탁 강사님을 모시고자 하오니,  관심있으신 분들의 지원을 바랍니다.
+1. 모집분야: 보드게임 1명
+2. 모집기간: 2026.10. 7.(수)~2026.10.13.(화), 16:00까지
+3. 서류체출: 전자접수([이메일])
+4. 기타 자세한 사항은 첨부파일 공고문을 참고 하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814814</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>교원 장기재직 휴가 대체 시간 강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>삼천포여자중학교</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2026 교원 장기재직 휴가 대체 시간 강사 채용 계획을 붙임과 같이 공고합니다.
+1. 채용내용: 장기재직 휴가 데체 시간 강사(과학)
+2. 임용기간, 접수시간:
+가. 원서 접수 기 간 : 2026. 10. 12.(월) ~ 10. 14.(수) 12:00까지
+나. 접수처 : E-mail 접수([이메일])
+다. 1차 서류전형 발표: 10. 15.(목) 13:00시 이후
+라. 2차 면접일: 10. 16.(금) 12:00시 / 장소: 법인 사무국
+마. 최종 합격자 발표: 10. 16.(금) 16:00 이후 개별 통보</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814790</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 개인위탁 외부강사 모집공고(수학)</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>거제고현중학교</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>★  모집 세부 사항
 가. 공고 기간: 2026.10.7.(수)~2026.10.14.(수)
@@ -2961,51 +3120,51 @@
 다. 방과후학교 개인위탁 외부강사 활동에 제한이 없는 자</t>
         </is>
       </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814746</t>
         </is>
       </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -3019,51 +3178,123 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>마산공업고등학교(직업교육 혁신지구 전공심화연구동아리 멘토 교육(전기제어) 외부강사) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>마산공업고등학교</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>마산공업고등학교 공고 제2026 – 65호
+2026학년도 마산공업고등학교에 근무할 전공심화연구동아리 멘토 교육(전기제어) 외부 강사 모집을 다음과 같이 공고 합니다.
+2026. 10. 7.
+마산공업고등학교장
+1. 모집 분야: 전공심화연구동아리 멘토 교육(전기제어) 외부강사 (1명)
+2. 프로그램 운영 방법(계약방법)
+가. 프로그램의 운영기간: 2026. 10. 31.(토) ~ 2026. 11. 8.(일) 4일간 총32시간
+나. 강사료: 시간당 50,000원
+3. 모집 세부 사항
+가. 서류 접수: 2026년 10월 7일(수) - 2026년 10월 16일(금) 13:00까지
+※2026.10.9.(금) 한글날 방문접수 불가
+나. 접수 방법: 방문접수, 우편접수, 전자우편 접수가능([이메일])
+다. 제 출 처 : 창원시 마산회원구 합성동 학교단지로 53
+마산공업고등학교 행정실 ☎[전화번호]
+라. 합격자 통보: 1차 서류전형 합격자에 한하여 개별통보 후 2차 전형 실시
+1) 1차 서류전형 합격자 개별통보 후 면접 실시 - 10월 20일(화) 10:00 본교 교장실
+2) 2차 면접전형 심사 후 최종합격자에 한하여 개별 통보
+※ 상기 일정은 진행상황에 따라 변경될 수 있으며 별도 통보함.
+마. 채용 기간
+1) 2026년 10월 31일 ∼ 2026년 11월 8일(총32시간)
+※ 방과후학교 운영 기간 변경으로 계약기간이 변경될 수 있음.
+* 자세한 사항은 붙임 공고문을 참고바랍니다.</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814792</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -3075,53 +3306,53 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n">
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
         </is>
       </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 위탁운영 단체(법인) 모집 공고</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>고성군</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>경남 고성군</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 재개장을 앞두고 해당 시설의 운영 및 관리를 위한 위탁운영 단체(법인)을  모집하고자 첨부와 같이 공고합니다.
 고성군 공고 제2026-1750호
@@ -3153,106 +3384,106 @@
 &lt; 청소년단체 &gt;</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -3263,51 +3494,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -3359,47 +3590,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -3411,51 +3642,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O50" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -3472,97 +3703,97 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>함양제일고등학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>10.26.(월)-11.11.(수)/ 총58시간</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
 1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
@@ -3571,96 +3802,96 @@
 -자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>마산고등학교</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>대암초등학교</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -3680,49 +3911,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n">
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -3731,193 +3962,15 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O53" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 배드민턴 외부강사 채용공고</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>일운초등학교</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>함안고등학교</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
-자세한 내용은 첨부파일 확인 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O55" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>고성군</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>경남 고성군</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
-        </is>
-      </c>
       <c r="G56" s="5" t="n"/>
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="n"/>
       <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+        </is>
+      </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="5" t="n"/>
       <c r="N56" s="5" t="inlineStr">
@@ -3934,12 +3987,12 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>소토초등학교 한국어교육 강사 채용 공고</t>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>소토초등학교</t>
+          <t>김해생명과학고등학교</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -3950,6 +4003,184 @@
       <c r="D57" s="5" t="n"/>
       <c r="E57" s="5" t="n"/>
       <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>일운초등학교</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>함안고등학교</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>고성군</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>경남 고성군</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>소토초등학교</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -3971,68 +4202,170 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
         </is>
       </c>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>진영중앙초 2학기 집중돌봄 특기적성 프로그램 개인위탁 외부강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>진영중앙초등학교</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>월,수/수,금/월,금 선택가능(주2회, 총 4차시)</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>1. 모집 분야 및 인원
+가. 모집분야: 창의놀이(예: 영어놀이, 음악놀이, 미술놀이, 보드게임, 마술 등)
+나. 모집인원: 2명
+다. 운영요일: 월,수/수,금/월,금 선택가능(주2회, 총 4차시)
+라. 운영시간: 월,수 12:50~14:20  금: 13:40~15:10
+2. 자세한 사항은 첨부파일 확인 바랍니다.
+3. 문의사항: 돌봄교실 [전화번호](11시~18시)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814812</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>돌봄·방과후학교 배드민턴 외부강사 채용공고</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>능포초등학교</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>돌봄·방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814781</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>계동초 방과후학교 프로그램 개인위탁 외부강사(한자속독) 모집 공고</t>
+          <t>태봉고등학교 결원대체시간강사(수학) 채용 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>계동초등학교</t>
+          <t>태봉고등학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -645,123 +645,10 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026년 11월 1일 ∼ 2027년 2월 28일</t>
+          <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>2026. 계동초 방과후학교 프로그램(한자속독) 개인위탁 외부강사를 다음과 같이 모집합니다.
-1. 계약 기간: 2026년 11월 1일 ∼ 2027년 2월 28일
-*불가항력 사유 등으로 인해 정상적인 학사운영이 이루어지지 않을 경우 계약기간이 변동될 수 있음
-2. 모집 분야: 한자속독(1명)
-3. 모집 세부 사항
-가. 공고 및 접수기간: 2026년 10월 2일(금) ~ 10월 8일(목) 12:00까지
-나. 접수장소: 전자우편 접수 ([이메일])
-다. 문의전화: [전화번호] 또는 [전화번호]
-라. 합격자 통보: 1차 서류 전형 합격자에 한하여 개별 통보 후 2차 전형 실시
--자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814720</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>분성초등학교 방과후학교 외부강사 모집 공고(바이올린)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>분성초등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026. 11. 3. ~ 2027. 2. 25.</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>2026. 분성초 방과후학교 바이올린 개인위탁 외부강사를 다음과 같이 모집합니다.
-1. 계약 기간: 2026. 11. 3. ~ 2027. 2. 25.
-※ 학생 개인 악기 및 학교 보유 악기 우선 활용, 수량 부족 시 악기 무료 대여(지원)가 가능한 강사
-※ 실제 프로그램 운영 기간과 계약 기간은 일치하며, 공사 등 불가피한 사유 등으로 학사 일정이 변경 될     경우 운영 기간·계약 기간·운영 요일·운영 시간은 변경될 수 있음.
-※ 요일 변경 불가
-2. 모집 분야: 바이올린(주 2회(화, 목요일), 회당 2차시(차시당 40분) 운영 [주당 총 4차시])
-3. 모집 절차 및 내용(일정은 학교 사정에 의해 변경될 수 있음)
-가. 공고 및 접수기간: 2026.10.3.(토)~10.8.(목) 12:00까지 도착분에 한함
-나. 제출방법:인편/우편/공직자통합메일(메일주소:[이메일])
-(인편제출장소: 본교 교무실 본인이 직접제출)
-다. 문의전화: [전화번호]
-라. 합격자 통보: 1차 서류 전형 합격자에 한하여 개별 통보 후 2차 전형 실시
--자세한 사항은 첨부파일을 확인해주시면 감사하겠습니다.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814693</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>태봉고등학교 결원대체시간강사(수학) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>태봉고등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고입니다.
 1. 채용과목 및 인원, 채용기간
@@ -781,49 +668,49 @@
 ※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814688</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교 결원대체강사(과학 전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>삼정자중학교</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>2026학년도 삼정자중학교 결원대체강사(과학)를 다음과 같이 채용하고자 합니다.
 1. 채용과목 및 채용 내용
@@ -846,49 +733,49 @@
 **자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814686</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교 결원대체 시간강사(1순위:윤리, 2순위:일반사회) 채용 공고</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>창원중앙고등학교</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.(월)~2026. 10. 30.(금) (총 17시간)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원중앙고등학교 결원대체 시간강사 채용을 다음과 같이 공고합니다.
 1. 채용과목 : 윤리(1순위:윤리, 2순위:일반사회)
@@ -899,47 +786,47 @@
 * 자세한 사항은 첨부파일 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814730</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>밀양고 전일제 강사(수학) 채용 공고(2차)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>밀양고등학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 19. ~ 2026. 10. 23.(5일, 17시수)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026학년도 밀양고등학교 전일제 강사 채용 공고
 2026학년도 밀양고등학교에 근무할 전일제 강사를 다음과 같이 채용 공고합니다.
@@ -964,47 +851,47 @@
 자세한 사항은 첨부파일을 참고</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814743</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>김해내동초 돌봄 프로그램(종이접기 1명) 외부강사 모집 공고문</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>김해내동초등학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2027.2.28.</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>2026. 김해내동초 돌봄 프로그램(종이 접기 1명)외부 강사 모집 공고를  아래와 같이 실시합니다.
 1. 모집 인원: 1명
@@ -1014,49 +901,49 @@
 5. 기타 자세한 사항은 첨부 문서를 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814620</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>성호초등학교 전일제강사 채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>성호초등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026.10.13.~ 2026.10.21.(9일)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 (재)공고 합니다.
 1. 채용과목 및 인원: 특수교사 1명
@@ -1067,49 +954,49 @@
 *자세한 사항은 붙임 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>창원남산고등학교 계약제교원 채용공고(체육 기간제 또는 강사)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>창원남산고등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026.10.14.(수)~2026.12.4.(금)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>창원남산고등학교 계약제교원 채용공고
 1. 채용인원 : 체육 기간제 교사 또는 강사
@@ -1125,51 +1012,51 @@
 6. 자세한 사항은 채용공고문을 참고하시기 바랍니다</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>해당교과목 자격증 소지자</t>
         </is>
       </c>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814789</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(학교폭력담당자 수업경감 시간강사) 2차 채용 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026.10.19. ~ 2026.12.31.</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 50호
 웅상고등학교 학교폭력담당자 수업경감 강사 3차 채용 공고
@@ -1224,47 +1111,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814610</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2026.10.30.(총16시간)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모자격
@@ -1292,49 +1179,49 @@
 5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>증산중학교 계약제교원(시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1348,49 +1235,49 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814584</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용 공고(수학)</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1404,49 +1291,49 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814744</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교 시간강사(수학) 채용</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 15~2026. 10. 23</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교에서 근무할 시간강사를 다음과 같이 채용 공고합니다.
 - 채용기간 : 2026. 10. 15~2026. 10. 23
@@ -1456,47 +1343,47 @@
 자세한 내용은 첨부파일을 참고해주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814706</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>김해수남고 학교폭력 업무담당자 수업경감 시간강사 채용 재공고8차(일반사회)</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>김해수남고등학교</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16. ~ 2027. 2. 5. (일반사회-시간강사) 주4시간(금요일), 시간당 25,000원</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>2026학년도 김해수남고등학교에 근무할 시간강사를 다음과 같이 채용 재공고합니다.
 1. 과목: 일반사회(사회계열 모두 가능) 1명
@@ -1508,47 +1395,47 @@
 7. 문의전화: 김해수남고 교무센터 ☎724-9350, 기타 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814759</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>동진초등학교 2026.10.12.자 계약제교원(결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>동진초등학교</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 10. 17.(5일)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등교사
 나. 채용 기간: 2026. 10. 12. ~ 2026. 10. 17.(5일)
@@ -1560,49 +1447,49 @@
 ※ 국가공무원법 제33조의 규정에 의한 공무원임용 결격사유가 없는 자</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814468</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>증산고등학교 결원대체강사(전일제강사/수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>증산고등학교</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 15.(목) ~ 2026. 11. 6.(금) 17일, 110,000/일</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>증산고등학교에서 근무할 결원대체강사(전일제강사/수학) 를 다음과 같이 채용하고자 합니다.
 1. 채용과목: 수학
@@ -1619,47 +1506,47 @@
 * 자세한 사항은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814809</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -1712,49 +1599,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n">
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -1805,49 +1692,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n">
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -1871,47 +1758,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(기술 가정) 채용 공고</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고
 합니다.
@@ -1936,49 +1823,49 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>대방중학교 전일제강사(기술·가정과) 채용 공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>대방중학교</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 9일 ~ 2026년 11월 13일(5일)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>2026학년도 대방중학교 기술·가정과 전일제강사를 다음과 같이 채용 공고(2차)합니다.
 1. 접수기간: 2026년 10월 8일(목) ~ 2026년 10월 14일(수), 09:00까지 도착분에 한함
@@ -1990,47 +1877,47 @@
 기타 자세한 사항은 붙임 문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814661</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>하동고등학교 결원대체강사(국어) 채용 공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>하동고등학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>2026.11.09.~2026.11.13.(5일), 2026.12.21.~2026.12.22.(2일)(총 7일)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>2026학년도 하동고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모 자격(결원대체강사;전일제/시간제)
@@ -2053,53 +1940,53 @@
 자세한 내용은 붙임파일을 참고해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>1순위: 채용 과목 중등 자격증 소지자</t>
         </is>
       </c>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814762</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>사회과(역사 또는 일반사회 또는 지리) 중등수업지원강사 채용 공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>창원상남중학교</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 12. 31.(2학년 역사수업, 주당 7시간, 월요일 2,3,4교시/목요일 1,2,3,4교시)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원상남중학교에서 근무할 중등수업지원강사를 다음과 같이 채용 공고합니다.
 1. 채용과목(인원): 사회(역사 또는 일반사회 또는 지리)(1명)
@@ -2113,49 +2000,49 @@
 *자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814787</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -2206,19 +2093,119 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
+      <c r="H24" s="5" t="n">
+        <v>8046</v>
+      </c>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>유목초 특수학급 결원대체강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>8046</v>
+        <v>1</v>
       </c>
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
         </is>
       </c>
       <c r="L26" s="5" t="n"/>
@@ -2229,12 +2216,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
+          <t>웅남중 학교운동부지도자 채용공고(태권도)</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>유목초등학교</t>
+          <t>웅남중학교</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -2244,115 +2231,15 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>2026.10.6.~2026.10.16.</t>
+          <t>2026.12.01.(화)~2027.2.28.(일)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>구체적인 내용은 공고문을 참고바랍니다.
-1. 분야: 특수학급 결원대체강사
-2. 채용인원: 1명
-3.기간: 2026.10.6.~2026.10.16.</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>유목초 특수학급 결원대체강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>유목초등학교</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.6.~2026.10.16.</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>구체적인 내용은 공고문을 참고바랍니다.
-1. 분야: 특수학급 결원대체강사
-2. 채용인원: 1명
-3.기간: 2026.10.6.~2026.10.16.</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>웅남중 학교운동부지도자 채용공고(태권도)</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>웅남중학교</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>2026.12.01.(화)~2027.2.28.(일)</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>웅남중학교 운동부 지도자 채용 공고
 - 채용분야: 운동부지도자
@@ -2365,13 +2252,114 @@
 자세한 사항은 붙임 문서를 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814764</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>내곡초등학교</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.1.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명
+2. 기간: 2026.10.1.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>유영초등학교</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.12.~2026.10.30.(19일간)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>1. 채용과목: 초등 결원대체 강사(전일제)
+2. 채용 인원: 1명
+3. 채용기간: 2026.10.12.~2026.10.30.(19일간)
+4. 자세한 사항은 첨부파일 참조</t>
+        </is>
+      </c>
       <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
+      <c r="H29" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814764</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
         </is>
       </c>
       <c r="L29" s="5" t="n"/>
@@ -2382,12 +2370,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
+          <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>내곡초등학교</t>
+          <t>남지초등학교</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2397,116 +2385,15 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2026.10.1.~2026.10.23.</t>
+          <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>아래와 같이 결원대체강사 채용을 공고합니다.
-1. 대상: 초등교사 1명
-2. 기간: 2026.10.1.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>초등교사 1명</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>유영초등학교</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.12.~2026.10.30.(19일간)</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>1. 채용과목: 초등 결원대체 강사(전일제)
-2. 채용 인원: 1명
-3. 채용기간: 2026.10.12.~2026.10.30.(19일간)
-4. 자세한 사항은 첨부파일 참조</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>남지초등학교</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등기간제교원
 나. 채용 기간: 2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)
@@ -2519,49 +2406,49 @@
 ※자세한 사항은 공고문 참고</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n">
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
 1. 채용과목: 영어(1명)
@@ -2569,49 +2456,49 @@
 상세내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n">
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -2666,15 +2553,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H32" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -2684,140 +2571,81 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>어방초 방과후학교 개인위탁 외부강사 모집 공고(컴퓨터)</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>어방초등학교</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>남지읍 평생학습센터 강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>창녕군</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>경남 창녕군</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
-1. 모집 분야 및 인원: 컴퓨터 1명
-2.모집 세부 사항
-가. 공고 기간: 2026.9.30.(수)∼2026.10.8.(목) 12:00까지
-나. 접수 장소: 어방초등학교 교무실로 직접 제출(우편접수 불가)
-※ 서류 제출 시 교무실에 강사 접수 대장을 작성하시고 봉투 겉면에 프로그램명, 강사명, 연락처를 정확히 기재하여 제출
-(서류는 스템플러가 아닌 집게나 클립 사용)
-※ 공휴일, 토, 일 서류 접수 불가, 평일 16시 30분 이후 접수 불가
-※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814647</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>남지읍 평생학습센터 강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>창녕군</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>경남 창녕군</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>율하중 계약제교원(체육 시간강사) 채용 계획(3차 공고)</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1)
 2. 서류접수 및 전형방법
@@ -2829,51 +2657,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814756</t>
         </is>
       </c>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>진주중앙고 전일제 강사(체육) 채용 공고</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>진주중앙고등학교</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진주중앙고등학교 전일제 강사를 다음과 같이 채용 공고 합니다.
 1. 채용 과목 및 인원: 체육 1명.
@@ -2882,53 +2710,53 @@
 4. 자세한 사항은 붙임 문서를 참고 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n">
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814791</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>진해용원고등학교 물리 계약제교원(전일제/시간제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>진해용원고등학교</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진해용원고등학교에 근무할 계약제교원(전일제강사/시간강사)을 다음과 같이 채용 공고 합니다.
 1. 채용과목: 물리
@@ -2949,51 +2777,51 @@
 ◦ 최종합격자 발표: 2026. 10. 14.(수) 10시 이후 합격자에 한해 개별 전화 통지</t>
         </is>
       </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814797</t>
         </is>
       </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>산양초등학교 돌봄교실 특기적성 프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>산양초등학교</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>본교 돌봄교실 운영과 관련하여 특기적성 프로그램 개인 위탁 강사님을 모시고자 하오니,  관심있으신 분들의 지원을 바랍니다.
 1. 모집분야: 보드게임 1명
@@ -3002,53 +2830,53 @@
 4. 기타 자세한 사항은 첨부파일 공고문을 참고 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n">
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814814</t>
         </is>
       </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>교원 장기재직 휴가 대체 시간 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>삼천포여자중학교</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>2026 교원 장기재직 휴가 대체 시간 강사 채용 계획을 붙임과 같이 공고합니다.
 1. 채용내용: 장기재직 휴가 데체 시간 강사(과학)
@@ -3060,51 +2888,51 @@
 마. 최종 합격자 발표: 10. 16.(금) 16:00 이후 개별 통보</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814790</t>
         </is>
       </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집공고(수학)</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>거제고현중학교</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>★  모집 세부 사항
 가. 공고 기간: 2026.10.7.(수)~2026.10.14.(수)
@@ -3120,51 +2948,51 @@
 다. 방과후학교 개인위탁 외부강사 활동에 제한이 없는 자</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814746</t>
         </is>
       </c>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -3178,51 +3006,51 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교(직업교육 혁신지구 전공심화연구동아리 멘토 교육(전기제어) 외부강사) 모집 공고</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교 공고 제2026 – 65호
 2026학년도 마산공업고등학교에 근무할 전공심화연구동아리 멘토 교육(전기제어) 외부 강사 모집을 다음과 같이 공고 합니다.
@@ -3248,53 +3076,53 @@
 * 자세한 사항은 붙임 공고문을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n">
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814792</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -3306,53 +3134,53 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 위탁운영 단체(법인) 모집 공고</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>고성군</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>경남 고성군</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 재개장을 앞두고 해당 시설의 운영 및 관리를 위한 위탁운영 단체(법인)을  모집하고자 첨부와 같이 공고합니다.
 고성군 공고 제2026-1750호
@@ -3384,106 +3212,106 @@
 &lt; 청소년단체 &gt;</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -3494,51 +3322,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -3590,47 +3418,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -3642,51 +3470,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -3703,13 +3531,157 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고등학교</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
+1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
+2. 과목: 특수
+3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
+-자세한 내용은 공고문 참조 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
+        </is>
+      </c>
       <c r="G51" s="5" t="n"/>
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="n"/>
       <c r="J51" s="5" t="n"/>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
       <c r="L51" s="5" t="n"/>
@@ -3721,19 +3693,19 @@
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+          <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>대암초등학교</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3742,156 +3714,12 @@
         </is>
       </c>
       <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
+        </is>
+      </c>
       <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>함양제일고등학교</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
-1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
-2. 과목: 특수
-3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
--자세한 내용은 공고문 참조 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O53" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>기초학력전담강사 채용 공고문</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>대암초등학교</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -3911,49 +3739,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n">
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -3962,13 +3790,150 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>일운초등학교</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>함안고등학교</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
+        </is>
+      </c>
       <c r="G56" s="5" t="n"/>
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="n"/>
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
         </is>
       </c>
       <c r="L56" s="5" t="n"/>
@@ -3987,36 +3952,31 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 고성군</t>
         </is>
       </c>
       <c r="D57" s="5" t="n"/>
       <c r="E57" s="5" t="n"/>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
         </is>
       </c>
       <c r="G57" s="5" t="n"/>
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="n"/>
       <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
-        </is>
-      </c>
+      <c r="K57" s="5" t="n"/>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="inlineStr">
@@ -4033,12 +3993,12 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>일운초등학교</t>
+          <t>소토초등학교</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4049,138 +4009,6 @@
       <c r="D58" s="5" t="n"/>
       <c r="E58" s="5" t="n"/>
       <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>함안고등학교</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
-자세한 내용은 첨부파일 확인 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O59" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>고성군</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>경남 고성군</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="n"/>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교 한국어교육 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4202,96 +4030,96 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="inlineStr">
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
         </is>
       </c>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O62" s="5" t="inlineStr">
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>진영중앙초 2학기 집중돌봄 특기적성 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>진영중앙초등학교</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>월,수/수,금/월,금 선택가능(주2회, 총 4차시)</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>1. 모집 분야 및 인원
 가. 모집분야: 창의놀이(예: 영어놀이, 음악놀이, 미술놀이, 보드게임, 마술 등)
@@ -4302,70 +4130,70 @@
 3. 문의사항: 돌봄교실 [전화번호](11시~18시)</t>
         </is>
       </c>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="n">
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814812</t>
         </is>
       </c>
-      <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="O60" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>돌봄·방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>능포초등학교</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>돌봄·방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814781</t>
         </is>
       </c>
-      <c r="L64" s="5" t="n"/>
-      <c r="M64" s="5" t="n"/>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O64" s="5" t="inlineStr">
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>태봉고등학교 결원대체시간강사(수학) 채용 공고</t>
+          <t>성호초등학교 전일제강사 채용 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>태봉고등학교</t>
+          <t>성호초등학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -640,310 +640,15 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
+          <t>2026.10.13.~ 2026.10.21.(9일)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고입니다.
-1. 채용과목 및 인원, 채용기간
-가. 채용과목: 수학
-나. 채용인원: 1명
-다. 채용기간: 2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)
-라. 수업시수 및 수당: 총 9시간(주당 6시간)/시간당 26,000원
-2. 서류접수 및 전형일정
-가. 원서접수
-◦ 접수기간 : 2026.10.02.(금)~2026.10.08.(목) 14:00까지(시간내 도착분에 한함)
-◦ 접수장소 : 태봉고등학교 전자우편(주소: [이메일], 스캔본 제출, 면접 시 반드시 원본 제출)
-나. 1차 : 서류전형 합격자 발표(개별 전화 통지) 예정일 : 2026. 10. 12.(월) 14:00 이후
-다. 2차 : 면접전형(서류심사 합격자에 한함) 예정일 : 2026. 10. 13.(화) 11:00 예정
-◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
-라. 최종합격자 발표 : 2026. 10. 14.(수) 10:00 이후(합격자 개별 통보)
-바. 비고: 오전수업만 있음
-※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814688</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>삼정자중학교 결원대체강사(과학 전일제강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>삼정자중학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 삼정자중학교 결원대체강사(과학)를 다음과 같이 채용하고자 합니다.
-1. 채용과목 및 채용 내용
-가. 채용과목: 과학 1명
-나. 근무기간: 2026. 11. 5.(목)~2026. 11. 18.(수), 11.20.(금)~11.30.(월) [총 17일]
-2. 원서접수
-가. 원서접수
-1) 접수기간 : 2026. 10. 1.(목)~2026. 10. 8.(목) 15:00
-2) 접수방법 : 온라인 접수
-(주소: [이메일], 응시원서 및 자기소개서 스캔본 제출)
-나. 1차 서류전형 합격자 발표(개별 전화 통지)예정 : 2026. 10. 8.(목) 16:00
-다. 2차 면접 (서류심사 합격자(3배수)에 한함) : 2026. 10. 12.(월) 10:00~
--일시 및 장소는 서류전형 합격자에게만 개별 통보하며 학사일정에 따라 면접 시간이 변경될 수 있음
-라. 최종합격자 발표: 2026. 10. 12.(월) 오후 예정. 합격자에게 개별 통보
--최종합격자를 채용 못 할 경우 차순위를 채용함.
-3. 제출서류
-가. 응시원서 1부(붙임서식, 사진첨부, 연락가능한 전화번호 반드시 기재)
-나. 자기소개서 1부(붙임서식)
-다. 개인정보 동의서 1부(붙임서식)
-**자세한 사항은 첨부파일을 참고해 주시기 바랍니다.**</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814686</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>창원중앙고등학교 결원대체 시간강사(1순위:윤리, 2순위:일반사회) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>창원중앙고등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 26.(월)~2026. 10. 30.(금) (총 17시간)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 창원중앙고등학교 결원대체 시간강사 채용을 다음과 같이 공고합니다.
-1. 채용과목 : 윤리(1순위:윤리, 2순위:일반사회)
-2. 채용기간 : 2026. 10. 26.(월)~2026. 10. 30.(금) (총 17시간)
-3. 서류 접수
-- 공고 및 서류 접수 기간: 2026. 10. 2.(금)~2026. 10. 8.(목) 15:00까지
-- 방법: 이메일 접수(([이메일])
-* 자세한 사항은 첨부파일 참조 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814730</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>밀양고 전일제 강사(수학) 채용 공고(2차)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>밀양고등학교</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 19. ~ 2026. 10. 23.(5일, 17시수)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 밀양고등학교 전일제 강사 채용 공고
-2026학년도 밀양고등학교에 근무할 전일제 강사를 다음과 같이 채용 공고합니다.
-1. 채용내용 및 응모자격
-가. 채용 교과 및 인원
-1) 과목: 수학(미적분1, 기하, 인공지능수학)
-2) 채용인원 1명
-3) 채용사유: 특별휴가
-4) 채용기간: 2026. 10. 19. ~ 2026. 10. 23.(5일, 17시수)
-5) 비고: 전일제 강사 일일 110,000원
-2. 서류접수 및 전형일정
-가. 원서접수
-◦ 접수기간: 2026. 10. 6.(화) ~ 2026. 10. 8.(목) 16:30까지
-◦ 접수방법: 전자우편(주소: [이메일] 스캔본 제출, 면접 시 원본 제출
-나. 1차 시험:
-◦ 서류전형: 2026. 10. 12(월) 09:00, 교무실
-◦ 합격자 발표(개별 통보)는 2026. 10. 12.(월) 12:30 이후
-다. 2차 시험: 면접 예정, 2026. 10. 12.(월) 15:00, 학생회실
-◦ 서류심사 합격자에 한함
-◦ 응시자가 1인 이하일 경우 서류심사와 면접시험을 병행하여 실시 가능
-라. 최종합격자 발표: 2026. 10. 12.(월) 16:30 이후 (합격자에게만 개별 통보)
-자세한 사항은 첨부파일을 참고</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814743</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>김해내동초 돌봄 프로그램(종이접기 1명) 외부강사 모집 공고문</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>김해내동초등학교</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.26.~2027.2.28.</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>2026. 김해내동초 돌봄 프로그램(종이 접기 1명)외부 강사 모집 공고를  아래와 같이 실시합니다.
-1. 모집 인원: 1명
-2. 채용 기간: 2026.10.26.~2027.2.28.
-3. 접수 기간: 2026. 10. 1. (목) ～ 10. 8. (목) 18:00까지
-4. 접수 방법: 학교 메일 접수([이메일])
-5. 기타 자세한 사항은 첨부 문서를 확인 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814620</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>성호초등학교 전일제강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>성호초등학교</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.13.~ 2026.10.21.(9일)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 (재)공고 합니다.
 1. 채용과목 및 인원: 특수교사 1명
@@ -954,49 +659,49 @@
 *자세한 사항은 붙임 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>창원남산고등학교 계약제교원 채용공고(체육 기간제 또는 강사)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>창원남산고등학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026.10.14.(수)~2026.12.4.(금)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>창원남산고등학교 계약제교원 채용공고
 1. 채용인원 : 체육 기간제 교사 또는 강사
@@ -1012,51 +717,51 @@
 6. 자세한 사항은 채용공고문을 참고하시기 바랍니다</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>해당교과목 자격증 소지자</t>
         </is>
       </c>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814789</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(학교폭력담당자 수업경감 시간강사) 2차 채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026.10.19. ~ 2026.12.31.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 50호
 웅상고등학교 학교폭력담당자 수업경감 강사 3차 채용 공고
@@ -1111,47 +816,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814610</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2026.10.30.(총16시간)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모자격
@@ -1179,49 +884,49 @@
 5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>증산중학교 계약제교원(시간강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1235,49 +940,49 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814584</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용 공고(수학)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>증산중학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>증산중학교 시간강사 채용
 1. 채용과목: 수학 1명
@@ -1291,49 +996,49 @@
 * 기타 사항은 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814744</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교 시간강사(수학) 채용</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 15~2026. 10. 23</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교에서 근무할 시간강사를 다음과 같이 채용 공고합니다.
 - 채용기간 : 2026. 10. 15~2026. 10. 23
@@ -1343,47 +1048,47 @@
 자세한 내용은 첨부파일을 참고해주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814706</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>김해수남고 학교폭력 업무담당자 수업경감 시간강사 채용 재공고8차(일반사회)</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>김해수남고등학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16. ~ 2027. 2. 5. (일반사회-시간강사) 주4시간(금요일), 시간당 25,000원</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>2026학년도 김해수남고등학교에 근무할 시간강사를 다음과 같이 채용 재공고합니다.
 1. 과목: 일반사회(사회계열 모두 가능) 1명
@@ -1395,47 +1100,47 @@
 7. 문의전화: 김해수남고 교무센터 ☎724-9350, 기타 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814759</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>동진초등학교 2026.10.12.자 계약제교원(결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>동진초등학교</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 10. 17.(5일)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등교사
 나. 채용 기간: 2026. 10. 12. ~ 2026. 10. 17.(5일)
@@ -1447,49 +1152,49 @@
 ※ 국가공무원법 제33조의 규정에 의한 공무원임용 결격사유가 없는 자</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814468</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>증산고등학교 결원대체강사(전일제강사/수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>증산고등학교</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 15.(목) ~ 2026. 11. 6.(금) 17일, 110,000/일</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>증산고등학교에서 근무할 결원대체강사(전일제강사/수학) 를 다음과 같이 채용하고자 합니다.
 1. 채용과목: 수학
@@ -1506,47 +1211,99 @@
 * 자세한 사항은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814809</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 개인위탁 외부강사 쿠키클레이 재모집 공고</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>중부초등학교</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2026년 11월 1일∼2027년 2월 28일(4개월)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>가. 모집 분야: 쿠키클레이 1명
+나. 접수 기간: 2026년 10월 8일(목) ∼ 2026년 10월 13일(화) 14:00까지
+다. 1차 제안서 평가: 1차 제안서 평가 통과자에 한하여 개별 통보
+라. 2차 프로그램 운영 능력평가: 2026년 10월 15일 16:00, 2층 회의실
+마. 계약 기간: 2026년 11월 1일∼2027년 2월 28일(4개월)
+*자세한 사항 및 필요 제출서류는 첨부파일을 확인하시고 기한내에 제출해 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814838</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -1599,49 +1356,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -1692,49 +1449,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -1758,47 +1515,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(기술 가정) 채용 공고</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고
 합니다.
@@ -1823,6 +1580,245 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>마산중앙중학교 강사(과학) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>마산중앙중학교</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 16.(금) ~ 2026. 11. 11.(수)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 마산중앙중학교 강사 채용 공고를 다음과 같이 합니다.
+공고 기간: 2026. 10. 8.(목) ~ 2026. 10. 14.(수) 13:00까지
+채용 과목: 과학(1명)
+채용 기간: 2026. 10. 16.(금) ~ 2026. 11. 11.(수)
+전형 일시
+1) 1차: 서류심사 (2026. 10. 14.(수))
+2) 2차: 면접심사 (2026. 10. 15.(목) 09:00 예정)(서류전형 합격자에 한하여 개별통보)
+3) 최종 합격자 발표: 2026. 10. 15.(목) 개별통보
+* 기타 자세한 사항은 채용공고 첨부파일을 참조 하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814851</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>악양초등학교 계약제 교원(결원대체강사)-전일제강사 채용</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>악양초등학교</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.26 ~ 2026.10.30.(총5일)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 악양초등학교에 근무할 결원 대체 강사를 다음과 같이 채용 공고 안내
+1. 채용과목 : 초등(전일제강사 1명)
+2. 채용기간 : 2026.10.26 ~ 2026.10.30.(총5일)
+3. 응시자격
+1순위: 만 62세 미만 동일 자격 소지자
+2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
+* 1순위 지원자 없을 시 2순위자 채용 가능
+4. 서류 접수 : 2026.10.8.(목)~10.14.(수)15:00까지
+악양초등학교 전자우편 ([이메일])
+스캔본 제출, 면접 시 원본 제출,
+5. 제출서류
+◦ 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
+◦ 자기소개서 1부.(붙임서식)
+◦ 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)
+* 자세한 사항은 붙임 공고문을 참조바랍니다.</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>1순위: 만 62세 미만 동일 자격 소지자
+2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
+1순위 지원자 없을 시 2순위자 채용 가능</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재), 자기소개서 1부.(붙임서식), 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814828</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>팔룡중학교 결원대체강사(진로진학상담)채용 공고</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>팔룡중학교</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 3.~2026. 11. 6.(총 13시간)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>[팔룡중학교 공고 제2026 - 39호]
+팔룡중학교 결원대체강사(진로진학상담 시간강사) 채용 공고
+2026학년도 팔룡중학교에 근무할 결원대체강사(진로진학상담 시간강사)를 다음과 같이 채용 공고합니다.
+1. 채용과목: 진로진학상담
+2. 채용기간: 2026. 11. 3.~2026. 11. 6.(총 13시간)
+3.  서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간 : 2026. 10. 12.(월)～2026. 10. 14.(수) 15:00
+◦ 접수방법 : 전자우편(주소: [이메일], 스캔본 제출, 면접 시 원본 제출,                    - 이메일 제목명: 과목_이름
+- 파일명(예시): 과목_이름
+나. 1차 : 서류전형 합격자 발표(개별 전화 통지) : 2026. 10. 14.(수) 16:00
+다. 2차 : 면접 (서류심사 합격자(3배수)에 한함) : 2026. 10. 15.(목) 10:00~
+◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보하며 학사일정에 따라 면접 시간이
+변경될 수 있음
+라. 최종합격자 발표: 2026. 10. 15.(목) 오후 합격자에게 개별 통보함.
+◦ 최종합격자를 채용 못 할 경우 차순위를 채용함.
+※기타 자세한 사항은 첨부파일 확인 및 팔룡중학교 교무실 [전화번호] 문의 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814841</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>전일제강사 채용공고(사회)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>덕산중학교</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 9.(월) ~2026. 11. 23.(월) (11일)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 덕산중학교에 근무할 전일제 강사를 다음과 같이 채용 공고합니다.
+1. 채용과목: 사회
+2. 채용기간: 2026. 11. 9.(월) ~2026. 11. 23.(월) (11일)
+3. 채용인원: 1명
+4. 원서접수기간: 2026. 10. 12.(월) ~2026. 10. 14.(수) 17:00
+기타사항은 첨부파일 참고바랍니다.</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n">
         <v>1</v>
@@ -1831,7 +1827,7 @@
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814821</t>
         </is>
       </c>
       <c r="L20" s="5" t="n"/>
@@ -1963,30 +1959,86 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>거창중학교 스포츠강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>거창중학교</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 20.(화) ~ 2027. 2. 10.(수)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>거창중학교 학교스포츠클럽 강사 공고
+1. 계약기간 : 2026. 10. 20.(화) ~ 2027. 2. 10.(수)
+2. 응시원서 접수
+가. 기    간 : 2026. 10. 8.(목) ~ 10. 15.(목) 10:00까지
+나. 장    소 : 전자우편(주소: [이메일], 스캔본 제출, 면접 시 원본 제출) 또는 본교에 직접 접수
+3. 시험일정 및 합격자 발표
+가. 시험일정 및 시험장소
+1) 서류심사 : 10월 15일(목), 13시
+2) 면접심사 : 10월 16일(금), 13시 교무실
+※ 응시자 예비소집은 없으니 반드시 응시자 유의사항 및 공고 내용을 숙지하고, 개인별로 사전에 시험장소를 확인하여 시험에 차질이 없도록 하시기 바람
+나. 합격자 발표 및 장소 : 10월 16일(금), 16시 이후 개별 통보
+자세한 사항은 첨부파일을 참조하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814839</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t>사회과(역사 또는 일반사회 또는 지리) 중등수업지원강사 채용 공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>창원상남중학교</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 12. 31.(2학년 역사수업, 주당 7시간, 월요일 2,3,4교시/목요일 1,2,3,4교시)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원상남중학교에서 근무할 중등수업지원강사를 다음과 같이 채용 공고합니다.
 1. 채용과목(인원): 사회(역사 또는 일반사회 또는 지리)(1명)
@@ -2000,49 +2052,102 @@
 *자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814787</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>신문초등학교 초등돌봄교실 특기‧적성 프로그램 외부강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>신문초등학교</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 6.(금) ~ 2027. 2. 26.(금)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>신문초등학교에서는 2026학년도 초등돌봄교실 운영과 관련하여 아래와 같이 특기‧적성 프로그램 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
+1. 선정 인원: 초등돌봄교실 특기·적성 프로그램 외부강사 1명
+2. 모집 분야: 신체·미술놀이(스포츠스태킹 또는 종이접기 위주의 활동)
+3. 계약 기간: 2026. 11. 6.(금) ~ 2027. 2. 26.(금)
+4. 세부 사항
+가. 서류접수: 2026. 10. 12.(월) ~ 2026. 10. 16.(금) 16:00까지
+나. 접수방법: 인편 제출(신문초 돌봄교실 2반)
+다. 문의 전화: [전화번호](신문초 돌봄교실 2반)
+※ 자세한 사항은 첨부파일 참고 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814822</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -2093,53 +2198,53 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H26" s="5" t="n">
         <v>8046</v>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>유목초등학교</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>구체적인 내용은 공고문을 참고바랍니다.
 1. 분야: 특수학급 결원대체강사
@@ -2147,49 +2252,49 @@
 3.기간: 2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n">
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>유목초 특수학급 결원대체강사 채용 공고</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>유목초등학교</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>구체적인 내용은 공고문을 참고바랍니다.
 1. 분야: 특수학급 결원대체강사
@@ -2197,49 +2302,375 @@
 3.기간: 2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n">
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단(내서스포츠센터팀)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 1. ~ 12. 31.</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>1. 모집인원: 2개분야 3명
+2. 접수기간: 10. 12.(월) 09:00 ~ 10. 19.(월) 18:00
+3. 접수방법: 방문접수(※ 우편접수 불가, 토ᆞ일요일 및 공휴일 접수 불가)
+4. 접 수 처
+- 내서스포츠센터 2층 관리사무실
+5. 문 의 처 : [전화번호]
+※ 자세한 내용과 제출서류는 붙임 문서 참고 바랍니다.
+내서스포츠센터팀 공고 제2026-7호
+내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고
+내서스포츠센터 프로그램 운영을 위한 우수 강사진을 공개 모집하오니 많은 지원 바랍니다.
+2026년 10월 8일
+내서스포츠센터팀장Ⅰ
+모집인원: 3명
+○ 계약기간: 2026. 11. 1. ~ 12. 31.
+○ 모집종목: TRX 필라테스, 바레운동
+모집분야강습일
+강습시간
+배분율(%)
+(공단:강사)인원
+지원자격
+TRX 필라테스
+월, 수
+07:00 ~ 07:50
+50:501명
+- TRX 및 필라테스 관련 자격
+동시 소지자 중 각 종목별
+지도경력 6개월 이상인 자
+- TRX 필라테스 자격 소지자 중
+지도경력 6개월 이상인 자
+※ 위의 지원자격 중 1가지 이상
+요건을 충족하여야 함.토
+(월 4회)
+09:00 ~ 09:50
+50:501명
+10:00 ~ 10:50
+바레운동
+화, 목
+06:00 ~ 06:50
+50:501명
+- 관련 자격 소지자 중
+지도경력 6개월 이상인 자
+07:00 ~ 07:50Ⅱ
+기본(공통)자격
+1. 주소지, 성별, 학력 제한 없음
+2. 만 18세 이상인 자로서 응시자격을 충족하는 자
+3. 남성의 경우 병역법상 문제가 없는 자(병역기피 사실이 없는 자)
+4. 아동 청소년의 성보호에 관한 법률 시행령에 의거 성범죄의 해당자는 선발될 수 없음.
+5. 창원시설공단 도급강사 운영계약 지침 제12조 결격사유에 해당하지 않는 자
+제12조(결격사유) 다음 각 호의 어느 하나에 해당하는 자는 도급강사로 계약할 수 없다.
+1. 피성년후견인
+2. 파산선고를 받은 자로서 복권되지 아니한 자
+3. 금고 이상의 형을 선고받고 그 집행이 끝나거나 집행을 받지 아니하기로 확정된 후 5년이 지나지 아니한 자
+4. 금고 이상의 형을 선고받고 그 집행유예기간이 끝난 날부터 2년이 지나지 아니한 자
+5. 금고 이상의 형의 선고유예를 선고받고 그 선고유예기간 중에 있는 자
+6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 자
+7. 징계로 파면처분을 받은 날부터 5년이 지나지 아니한 자
+8. 징계로 해임처분을 받은 날부터 3년이 지나지 아니한 자
+9. 부패방지 및 국민권익위원회의 설치와 운영에 관한 법률 제82조에 따른 비위면직자 등의 취업제한 적용을 받는 자
+10. 재직기간 중 직무와 관련하여 「형법」 제355조 및 제356조에 규정된 죄를 범한 사람
+으로서 300만원 이상의 벌금형을 선고받고 그 형이 확정된 후 2년이 지나지 아니한 사람
+11. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 규정된 죄를 범한 사람으로서 100만원 이상의
+벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>여부</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>TRX 필라테스</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5003</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>[내서스포츠센터] 프로그램 도급강사 공개경쟁모집 공고</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단 채용정보</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 1. ~ 12. 31.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>내서스포츠센터팀 공고 제2026-7호
+내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고
+내서스포츠센터 프로그램 운영을 위한 우수 강사진을 공개 모집하오니 많은 지원 바랍니다.
+2026년 10월 8일
+내서스포츠센터팀장Ⅰ
+모집인원: 3명
+○ 계약기간: 2026. 11. 1. ~ 12. 31.
+○ 모집종목: TRX 필라테스, 바레운동
+모집분야강습일
+강습시간
+배분율(%)
+(공단:강사)인원
+지원자격
+TRX 필라테스
+월, 수
+07:00 ~ 07:50
+50:501명
+- TRX 및 필라테스 관련 자격
+동시 소지자 중 각 종목별
+지도경력 6개월 이상인 자
+- TRX 필라테스 자격 소지자 중
+지도경력 6개월 이상인 자
+※ 위의 지원자격 중 1가지 이상
+요건을 충족하여야 함.토
+(월 4회)
+09:00 ~ 09:50
+50:501명
+10:00 ~ 10:50
+바레운동
+화, 목
+06:00 ~ 06:50
+50:501명
+- 관련 자격 소지자 중
+지도경력 6개월 이상인 자
+07:00 ~ 07:50Ⅱ
+기본(공통)자격
+1. 주소지, 성별, 학력 제한 없음
+2. 만 18세 이상인 자로서 응시자격을 충족하는 자
+3. 남성의 경우 병역법상 문제가 없는 자(병역기피 사실이 없는 자)
+4. 아동 청소년의 성보호에 관한 법률 시행령에 의거 성범죄의 해당자는 선발될 수 없음.
+5. 창원시설공단 도급강사 운영계약 지침 제12조 결격사유에 해당하지 않는 자
+제12조(결격사유) 다음 각 호의 어느 하나에 해당하는 자는 도급강사로 계약할 수 없다.
+1. 피성년후견인
+2. 파산선고를 받은 자로서 복권되지 아니한 자
+3. 금고 이상의 형을 선고받고 그 집행이 끝나거나 집행을 받지 아니하기로 확정된 후 5년이 지나지 아니한 자
+4. 금고 이상의 형을 선고받고 그 집행유예기간이 끝난 날부터 2년이 지나지 아니한 자
+5. 금고 이상의 형의 선고유예를 선고받고 그 선고유예기간 중에 있는 자
+6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 자
+7. 징계로 파면처분을 받은 날부터 5년이 지나지 아니한 자
+8. 징계로 해임처분을 받은 날부터 3년이 지나지 아니한 자
+9. 부패방지 및 국민권익위원회의 설치와 운영에 관한 법률 제82조에 따른 비위면직자 등의 취업제한 적용을 받는 자
+10. 재직기간 중 직무와 관련하여 「형법」 제355조 및 제356조에 규정된 죄를 범한 사람
+으로서 300만원 이상의 벌금형을 선고받고 그 형이 확정된 후 2년이 지나지 아니한 사람
+11. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 규정된 죄를 범한 사람으로서 100만원 이상의
+벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람
+12. 미성년자에 대한 다음 각 목의 어느 하나에 해당하는 죄를 저질러 파면ㆍ해임되거나 형 또는 치료감호를 선고받아
+그 형 또는 치료감호가 확정된 사람(집행유예를 선고받은 후 그 집행유예 기간이 경과한 사람을 포함한다)
+가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>여부</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>TRX 필라테스</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1704&amp;page=1</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>마산합포스포츠센터 생활체육 프로그램 도급강사 공개경쟁모집 공고</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단(마산합포스포츠센터팀)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 1. ~ 12. 31.</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>1. 모집인원: 2개분야 2명
+2. 접수기간: 10. 16.(금) 09:00 ~ 10. 22.(목) 18:00
+3. 접수방법: 방문접수(※ 우편접수 불가, 토ᆞ일요일 및 공휴일 접수 불가)
+4. 접 수 처
+- 마산합포스포츠센 2층 관리사무실
+5. 문 의 처 : [전화번호]
+※ 자세한 내용과 제출서류는 붙임 문서 참고 바랍니다.
+마산합포스포츠센터 공고 제2026 - 12호
+마산합포스포츠센터 생활체육 프로그램 도급강사 공개경쟁모집 공고
+마산합포스포츠센터 프로그램 운영을 위한 우수 강사진을 공개 모집하오니 많은 참여 바랍니다.
+2026년 10월 12일
+창원시설공단 마산합포스포츠센터 팀장Ⅰ
+모집인원: 2명 (배분율 참조)
+생활체육 프로그램: 2명(2개 종목)
+모집분야인원요 일시 간
+배분율(%)
+(공단:강사)
+자격요건합 계2명요가1명
+월ㆍ수ㆍ금
+09:10~10:00
+45:55
+- 해당종목 자격증 소지자 중
+지도경력 6개월 이상자
+10:10~11:00
+11:10~12:00
+바레운동1명토
+08:00~08:50
+50:50
+09:00~09:50Ⅱ
+기본(공통)자격
+가. 해당 관련 자격증 소지자 중 해당 경력 6개월 이상인 자(19세 이상)
+➟ 중복지원 가능 / 중복 지원 시 응시서류는 각각 제출(동일 시간대 불가)
+➟ 응시 자격에 보조강사가 있는 경우 지원강사 본인 외 보조강사 지원 서류 동일 제출
+나. 남성의 경우 병역법상 문제가 없는 자(병역기피 사실이 없는 자)
+다. 아동 청소년의 성보호에 관한 법률 시행령에 의거 성범죄의 해당자는 선발될 수 없음.
+라. 도급강사 운영계약 지침 제12조 결격사유에 해당하지 않는 자
+제12조(결격사유) 다음 각 호의 어느 하나에 해당하는 자는 도급강사로 계약할 수 없다.
+1. 피성년후견인
+2. 파산선고를 받은 자로서 복권되지 아니한 자
+3. 금고 이상의 형을 선고받고 그 집행이 끝나거나 집행을 받지 아니하기로 확정된 후 5년이 지나지 아니한 자
+4. 금고 이상의 형을 선고받고 그 집행유예기간이 끝난 날부터 2년이 지나지 아니한 자
+5. 금고 이상의 형의 선고유예를 선고받고 그 선고유예기간 중에 있는 자
+6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 자
+7. 징계로 파면처분을 받은 날부터 5년이 지나지 아니한 자
+8. 징계로 해임처분을 받은 날부터 3년이 지나지 아니한 자
+9. 부패방지 및 국민권익위원회의 설치와 운영에 관한 법률 제82조에 따른 비위면직자 등의 취업제한 적용을 받는 자
+10. 재직기간 중 직무와 관련하여 「형법」 제355조 및 제356조에 규정된 죄를 범한 사람으로서 300만원 이상의 벌금형을 선고받고 그 형이 확정된 후 2년이 지나지 아니한 사람
+11.「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 규정된 죄를 범한 사람으로서 100만원 이상의 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>합 계</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5006</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>웅남중 학교운동부지도자 채용공고(태권도)</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>웅남중학교</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>2026.12.01.(화)~2027.2.28.(일)</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>웅남중학교 운동부 지도자 채용 공고
 - 채용분야: 운동부지도자
@@ -2252,98 +2683,186 @@
 자세한 사항은 붙임 문서를 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814764</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>2026.10.1.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명
 2. 기간: 2026.10.1.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>김해율하도서관 2027년 율하아카데미 교육강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>김해시</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>경남 김해시</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>2027. 2. ~ 2027. 11.(3학기 기준)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>김해율하도서관 2027년 율하아카데미 교육강사 채용을 위하여 붙임의 고시공고를 홈페이지에 게제하고자 합니다.
+김해시청 제2026-4441호
+김해율하도서관 2027년 율하아카데미 교육강사 채용 공고묶음 개체입니다.
+김해율하도서관 2027년 율하아카데미 교육강사 채용 공고
+김해율하도서관 2027년 율하아카데미 운영을 위하여 다음과 같이 강사를 채용하오니 전문 강사분들의 많은 관심과 참여 부탁드립니다.2026년 10월 8일장 유 도 서 관 장
+김해율하도서관 2027년 율하아카데미 운영을 위하여 다음과 같이 강사를 채용하오니 전문 강사분들의 많은 관심과 참여 부탁드립니다.
+2026년 10월 8일
+장 유 도 서 관 장
+1. 모집 개요
+○ (모집대상) 2027년 김해율하도서관 율하아카데미 교육강사
+○ (모집인원) 32강좌 32명(성인강좌 16, 초등강좌12, 유아강좌 4)
+분야별모집강좌강의요일 및 시간모집인원비 고계32강좌32명성 인미 술(4)화 / 10:00~11:401명목 / 10:00~11:401명수 / 19:00~20:401명야간금 / 19:00~20:401명비대면어 학(4)화 / 10:00~11:401명수 / 10:00~11:401명금 / 19:00~19:401명야간목 / 19:00~20:401명비대면인 문(7)수 / 10:00~11:401명목 / 10:00~11:401명금 / 10:00~11:401명화 / 19:00~20:401명야간목 / 19:00~20:401명화 / 19:00~20:401명비대면수 / 19:00~20:401명디 지 털(1)금 / 10:00~11:401명분야별
+모집강좌
+강의요일 및 시간
+모집인원비 고계
+32강좌32명성 인
+미 술(4)
+화 / 10:00~11:401명
+목 / 10:00~11:401명
+수 / 19:00~20:401명야간
+금 / 19:00~20:401명비대면
+어 학(4)
+화 / 10:00~11:401명
+수 / 10:00~11:401명
+금 / 19:00~19:401명야간
+목 / 19:00~20:401명비대면
+인 문(7)
+수 / 10:00~11:401명
+목 / 10:00~11:401명
+금 / 10:00~11:401명
+화 / 19:00~20:401명야간
+목 / 19:00~20:401명
+화 / 19:00~20:401명비대면
+수 / 19:00~20:401명
+디 지 털(1)
+금 / 10:00~11:401명
+초 등미술·체험·놀이(6)수 / 17:00~17:501명목 / 17:00~17:501명토 / 10:00~10:501명토 / 11:00~11:501명토 / 14:00~14:501명토 / 15:00~15:501명학 습(5)화 / 17:00~17:501명수 / 17:00~17:501명토 / 10:00~10:501명토 / 10:00~10:501명비대면토 / 11:00~11:501명디 지 털(1)금 / 17:00~17:501명유 아미술·체험·놀이(4)금 / 17:00~17:501명토 / 11:00~11:501명토 / 14:00~14:501명토 / 15:00~15:501명초 등
+미술·체험·놀이(6)</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>모집 분야 수업 내용</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>6448</v>
+      </c>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110418&amp;cpage=1&amp;section=05</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>유영초등학교</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~2026.10.30.(19일간)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 초등 결원대체 강사(전일제)
 2. 채용 인원: 1명
@@ -2351,49 +2870,143 @@
 4. 자세한 사항은 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n">
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>안의고등학교 역사, 국어과 결원대체강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>안의고등학교</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>국어-2026.11.23.(월)~2026.11.27.(금) (5일)</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>안의고등학교 결원대체강사 채용 공고
+2026학년도 안의고등학교에 근무할 결원대체강사(전일제/시간제)를 다음과 같이 채용 공고합니다.
+1. 채용내용 및 응모 자격
+채용과목  역사(1), 국어(1)
+채용기간  역사-2026.11.12.(목)~2026.12.2.(수) (15일)
+국어-2026.11.23.(월)~2026.11.27.(금) (5일)
+응모자격
+1순위: 만 69세 미만 동일 자격 소지자
+2순위: 다른 학교급 또는 유사과목 자격 소지자, 명예퇴직자, 정년퇴직자
+(1순위 지원자가 있을 경우 2순위는 심사 대상에서 제외)
+2. 전형방법
+가. 1차 시험 : 서류전형
+나. 2차 시험 : 면접 (서류전형 합격한 자에 한하여 개별 통보)
+3. 제출서류
+가. 응시자 제출서류
+◦ 응시원서 1부. (붙임 서식1, 사진 첨부, 연락 가능한 전화번호 반드시 기재)
+◦ 자기소개서 1부. (붙임 서식2)
+◦ 계약제교원 채용을 위한 개인정보 수집 및 이용 동의서 1부. (붙임 서식3)
+나. 최종합격자 제출서류
+◦ 교사 자격증 사본 또는 자격 인정 조서 1부.
+◦ 졸업증명서 사본 1부. (원본 지참)
+◦ 개인정보 수집 및 활용 동의서 1부. (붙임 서식4)
+◦ 범죄경력조회동의서 1부. (붙임 서식5)
+◦ 행정정보 공동이용 사전동의서 1부. (붙임 서식6)
+◦ 가족 채용 제한 여부 확인서 (붙임 서식7)
+◦ 공무원채용신체검사서 (또는 일반 건강검진 결과서) 1부.
+◦ 잠복결핵감염검진 확인서 1부. (인력풀에 업로드된 경우 생략 가능)
+◦ 마약류 투약 또는 중독 여부 판별 결과 통보서 또는 의사 진단서 1부.
+4. 서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간 : 2026. 11. 12.(월)～ 2026. 11. 16.(금) 16시
+◦ 접수장소 : 안의고등학교 전자우편
+◦ 접수방법 : 전자우편(주소: [이메일], 파일 제출, 면접 시 원본 제출, 2026. 11. 16. 16:00 발송분까지)
+나. 1차 : 서류전형 합격자 발표 (개별 문자/전화 통지) 예정일 : 2026. 11. 19.(월) 10:00이후
+다. 2차 : 면접 (서류심사 합격자에 한함) 예정일 : 2026. 11. 20.(화) 오전 09:30
+◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
+5. 합격자 발표
+◦ 최종합격자 발표 : 2026. 11. 20.(화) 15:00이후
+6. 유의사항
+◦ 신규임용대기자 또는 계약제교원 인력풀 등재자는 우선 임용될 수 있습니다.
+◦ 신규임용대기자 또는 계약제교원 인력풀 등재자는 최종 합격 후 확인이 불가능한 서류만 제출
+◦ 상기 일정은 진행 상황에 따라 변경될 수 있으며, 변경 시 별도 통보합니다.
+◦ 기재 사항이 사실과 다르거나 허위로 작성된 경우는 합격을 취소합니다.
+◦ 제출서류의 기재 착오, 누락, 서류 미제출, 연락 불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>1순위: 만 69세 미만 동일 자격 소지자
+2순위: 다른 학교급 또는 유사과목 자격 소지자, 명예퇴직자, 정년퇴직자
+(1순위 지원자가 있을 경우 2순위는 심사 대상에서 제외)</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814832</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>남지초등학교</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등기간제교원
 나. 채용 기간: 2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)
@@ -2406,49 +3019,49 @@
 ※자세한 사항은 공고문 참고</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n">
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
 1. 채용과목: 영어(1명)
@@ -2456,49 +3069,49 @@
 상세내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n">
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -2553,15 +3166,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H39" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -2571,81 +3184,40 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>남지읍 평생학습센터 강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>창녕군</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>경남 창녕군</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>율하중 계약제교원(체육 시간강사) 채용 계획(3차 공고)</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1)
 2. 서류접수 및 전형방법
@@ -2657,51 +3229,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814756</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>진주중앙고 전일제 강사(체육) 채용 공고</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>진주중앙고등학교</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진주중앙고등학교 전일제 강사를 다음과 같이 채용 공고 합니다.
 1. 채용 과목 및 인원: 체육 1명.
@@ -2710,53 +3282,53 @@
 4. 자세한 사항은 붙임 문서를 참고 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n">
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814791</t>
         </is>
       </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>진해용원고등학교 물리 계약제교원(전일제/시간제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>진해용원고등학교</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진해용원고등학교에 근무할 계약제교원(전일제강사/시간강사)을 다음과 같이 채용 공고 합니다.
 1. 채용과목: 물리
@@ -2777,51 +3349,51 @@
 ◦ 최종합격자 발표: 2026. 10. 14.(수) 10시 이후 합격자에 한해 개별 전화 통지</t>
         </is>
       </c>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814797</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>산양초등학교 돌봄교실 특기적성 프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>산양초등학교</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>본교 돌봄교실 운영과 관련하여 특기적성 프로그램 개인 위탁 강사님을 모시고자 하오니,  관심있으신 분들의 지원을 바랍니다.
 1. 모집분야: 보드게임 1명
@@ -2830,53 +3402,53 @@
 4. 기타 자세한 사항은 첨부파일 공고문을 참고 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n">
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814814</t>
         </is>
       </c>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>교원 장기재직 휴가 대체 시간 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>삼천포여자중학교</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>2026 교원 장기재직 휴가 대체 시간 강사 채용 계획을 붙임과 같이 공고합니다.
 1. 채용내용: 장기재직 휴가 데체 시간 강사(과학)
@@ -2888,51 +3460,113 @@
 마. 최종 합격자 발표: 10. 16.(금) 16:00 이후 개별 통보</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814790</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>어방초 방과후학교 개인위탁 외부강사 모집 재공고(컴퓨터)</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>어방초등학교</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
+1. 모집 분야 및 인원: 컴퓨터 1명
+2.모집 세부 사항
+가. 공고 기간: 2026.10.12.(월)∼2026.10.14.(수) 12:00까지
+나. 접수 장소: 어방초등학교 교무실(1층)
+본인 직접 제출(주말, 공휴일 제외)
+또는 학교 e-mail 접수
+e-mail 주소: [이메일]
+※ 서류 제출 시 봉투 겉면에 프로그램명, 강사명, 연락처를 정확히 기재하여 제출
+(서류는 스템플러가 아닌 집게나 클립 사용)
+※ 공휴일, 토, 일 서류 접수 불가, 평일 16시 30분 이후 접수 불가
+※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814852</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집공고(수학)</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>거제고현중학교</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>★  모집 세부 사항
 가. 공고 기간: 2026.10.7.(수)~2026.10.14.(수)
@@ -2948,51 +3582,147 @@
 다. 방과후학교 개인위탁 외부강사 활동에 제한이 없는 자</t>
         </is>
       </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814746</t>
         </is>
       </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>진주고등학교 계약제교원(시간제강사-일본어) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>진주고등학교</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>1. 채용과목 및 인원
+시간제강사 - 일본어 1명
+2. 응시 자격
+가. 해당 교과 중등 2급 정교사 이상 자격증 소지자
+나. 국가공무원법 제33조에 의한 결격 사유가 없는 자
+다. 직무수행에 결격 사유가 없는 자
+3. 전형방법
+가. 1차전형: 서류전형(응시원서, 자기소개서) 후 개별통보
+나. 2차전형: 면접(일반 및 심청면접), 필요시 수업시연
+4.  전형일정 및 서류접수
+가. 원서접수
+◦ 접수기간: 2026. 10. 8.(목) ~ 2026. 10. 15.(목) 16:00 까지
+◦ 온라인 접수: [이메일] (우편, 방문접수 불가)
+* 제출시간이내(16:00) 도착분에 한하여 접수함.
+나. 1차 전형 합격자 발표일: 2026. 10. 16(금) 14:00 ~ (1차 합격자에게만 개별통지)
+다. 2차 전형일: 2026.10.19.(월)  10:30 ~  진주고 Wee클래스 상담실
+◦ 일시 및 장소는 서류전형 합격자에게만 개별통보
+라. 최종합격자 발표: 2026.10.19.(월) 13:00 이후 (합격자에게만 개별 통지)
+5. 제출 서류
+가. 응시원서 및 자기소개서 1부. (붙임서류 참조)
+※ 응시원서: 경력사항→근무기간(년,월,일 모두 기재) 및 근무형태(기간제교사,시간강사) 정확히 기재 요망.  허위작성시 불합격 처리됨.
+※ 자기소개서 작성
+- 자신의 장단점, 업무능력, 교과․진로 학생 생활지도계획 포함하여 작성
+- 글씨 크기: 13포인트, 자기소개서 A4 1매 이상 자유롭게 기술
+나. 개인정보 수입·이용 동의서 1부.
+※ 최종합격자 추가 제출 서류
+- 자격증 사본 등 자격 증빙서류(해당자에 한함) 각1부.
+6. 최종합격자 제출서류
+가. 교원자격증 사본 1부
+나. 최종학력증명서 사본 1부.
+다. 주민등록 초본 1부
+라. 공무원 채용신체검사서 1부
+마. 초임호봉획정을 위한 경력기간 합산신청서 1부. (기간제교원)
+바. 결격사유조회 및 범죄경력조회동의서 1부.
+사. 범죄경력조회동의서 1부.
+아. 호봉획정을 위한 경력증명서(기간제교원)
+자. 잠복결핵 검진확인서
+차. 마약 등 중독자 결격 사유 검사 확인서
+※ 계약제교원 인력풀 등재 권장
+◎서류는 추가될 수 있음.
+7. 유의사항
+◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 우선 임용될 수 있습니다.
+◦ 상기 일정은 진행 상황에 따라 변경될 수 있으며 별도 통보합니다.
+◦ 제출서류의 기재착오, 누락, 서류 미제출, 연락 불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.
+◦ 최종합격자로 발표된 이후에도 결격사유가 있는 자는 합격을 취소하며, 최종합격자가 임용을 포기 할 경우, 채용 심사 결과 차순위 지원자 순으로 임용할 수 있습니다.
+◦ 명시되지 않은 사항은 경상남도교육청 2026학년도 계약제교원 운영 지침에 따릅니다.
+◦ 기타 자세한 사항은 진주고등학교 교무실(☎[전화번호])로 문의하시기 바랍니다.
+**************** 보다 자세한 사항은 첨부파일을 꼭 확인하여 주시기 바랍니다. ******************</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814820</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -3006,51 +3736,51 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교(직업교육 혁신지구 전공심화연구동아리 멘토 교육(전기제어) 외부강사) 모집 공고</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교 공고 제2026 – 65호
 2026학년도 마산공업고등학교에 근무할 전공심화연구동아리 멘토 교육(전기제어) 외부 강사 모집을 다음과 같이 공고 합니다.
@@ -3076,53 +3806,53 @@
 * 자세한 사항은 붙임 공고문을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n">
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814792</t>
         </is>
       </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -3134,53 +3864,53 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n">
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
         </is>
       </c>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="O50" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 위탁운영 단체(법인) 모집 공고</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>고성군</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>경남 고성군</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 재개장을 앞두고 해당 시설의 운영 및 관리를 위한 위탁운영 단체(법인)을  모집하고자 첨부와 같이 공고합니다.
 고성군 공고 제2026-1750호
@@ -3212,106 +3942,106 @@
 &lt; 청소년단체 &gt;</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -3322,51 +4052,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -3418,47 +4148,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -3470,51 +4200,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -3531,97 +4261,97 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O56" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O57" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>함양제일고등학교</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>10.26.(월)-11.11.(수)/ 총58시간</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
 1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
@@ -3630,96 +4360,96 @@
 -자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>마산고등학교</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>대암초등학교</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -3739,49 +4469,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n">
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="O60" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -3790,225 +4520,225 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
         </is>
       </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
         </is>
       </c>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O54" s="5" t="inlineStr">
+      <c r="O62" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>일운초등학교</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
         </is>
       </c>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="O63" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>함안고등학교</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
 자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
         </is>
       </c>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
+      <c r="O64" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>고성군</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>경남 고성군</t>
         </is>
       </c>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
         </is>
       </c>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>소토초등학교 한국어교육 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>소토초등학교</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4030,96 +4760,96 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="O66" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+      <c r="K67" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
         </is>
       </c>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="O67" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>진영중앙초 2학기 집중돌봄 특기적성 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>진영중앙초등학교</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>월,수/수,금/월,금 선택가능(주2회, 총 4차시)</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>1. 모집 분야 및 인원
 가. 모집분야: 창의놀이(예: 영어놀이, 음악놀이, 미술놀이, 보드게임, 마술 등)
@@ -4130,70 +4860,214 @@
 3. 문의사항: 돌봄교실 [전화번호](11시~18시)</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n">
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="5" t="n"/>
+      <c r="K68" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814812</t>
         </is>
       </c>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="O68" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>돌봄·방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>능포초등학교</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>돌봄·방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814781</t>
         </is>
       </c>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="O69" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>함안군 민방위 교육 강사 위촉대상자 공고</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>함안군</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>경남 함안군</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>2026년 함안군 민방위 교육 강사 위촉대상자를 붙임과 같이 공고합니다.
+함안군 공고 제2026-1233호
+2026년 함안군 민방위 교육 강사 위촉대상자 공고
+2026년도 함안군 민방위 교육 강사 위촉대상자를 다음과 같이 공고합니다.
+2026년 10월 8일
+함안군수
+위촉대상자 명단
+위촉대상자 명단
+분야성명비고기본교육이*호민방위 기본실전훈련남*풍화재예방실전훈련정*영응급처치실전훈련강*훈화생방분야성명비고
+기본교육이*호
+민방위 기본
+실전훈련남*풍
+화재예방
+실전훈련정*영
+응급처치
+실전훈련강*훈화생방
+1. 채용과 관련된 사항은 최종합격자에게 개별 통지할 예정이며,
+2. 기타 문의사항은 안전총괄과 안전관리담당(☎[전화번호])으로 문의하시길바랍니다.</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="n"/>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>[용원국민체육센터]생활체육 도급강사 공개경쟁모집 공고</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단 채용정보</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1705&amp;page=1</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O71" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>전일제강사 채용 공고(보건)</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>김해중학교</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>전일제 강사(5일) 모집합니다.</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814827</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="n"/>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O72" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3198,12 +3198,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>율하중 계약제교원(체육 시간강사) 채용 계획(3차 공고)</t>
+          <t>진주중앙고 전일제 강사(체육) 채용 공고</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>율하중학교</t>
+          <t>진주중앙고등학교</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -3213,67 +3213,11 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E40" s="5" t="n"/>
       <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>1. 채용과목: 체육(1)
-2. 서류접수 및 전형방법
--1차: 서류전형 합격자 발표(개별 통지) 예정일: 2026.10.12. 10:30이후
-*접수기간: 2026.10.6.~2026.10.9. 23:00
--2차: 면접심사
-*면접일시: 2026.10.12. 12:30
-*강사비: 시간당 22,000원
-*자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814756</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>진주중앙고 전일제 강사(체육) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>진주중앙고등학교</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진주중앙고등학교 전일제 강사를 다음과 같이 채용 공고 합니다.
 1. 채용 과목 및 인원: 체육 1명.
@@ -3282,53 +3226,53 @@
 4. 자세한 사항은 붙임 문서를 참고 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n">
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814791</t>
         </is>
       </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>진해용원고등학교 물리 계약제교원(전일제/시간제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>진해용원고등학교</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진해용원고등학교에 근무할 계약제교원(전일제강사/시간강사)을 다음과 같이 채용 공고 합니다.
 1. 채용과목: 물리
@@ -3349,51 +3293,51 @@
 ◦ 최종합격자 발표: 2026. 10. 14.(수) 10시 이후 합격자에 한해 개별 전화 통지</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814797</t>
         </is>
       </c>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>산양초등학교 돌봄교실 특기적성 프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>산양초등학교</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>본교 돌봄교실 운영과 관련하여 특기적성 프로그램 개인 위탁 강사님을 모시고자 하오니,  관심있으신 분들의 지원을 바랍니다.
 1. 모집분야: 보드게임 1명
@@ -3402,53 +3346,53 @@
 4. 기타 자세한 사항은 첨부파일 공고문을 참고 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814814</t>
         </is>
       </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>교원 장기재직 휴가 대체 시간 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>삼천포여자중학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>2026 교원 장기재직 휴가 대체 시간 강사 채용 계획을 붙임과 같이 공고합니다.
 1. 채용내용: 장기재직 휴가 데체 시간 강사(과학)
@@ -3460,51 +3404,51 @@
 마. 최종 합격자 발표: 10. 16.(금) 16:00 이후 개별 통보</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814790</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 재공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -3520,53 +3464,53 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n">
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814852</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집공고(수학)</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>거제고현중학교</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>★  모집 세부 사항
 가. 공고 기간: 2026.10.7.(수)~2026.10.14.(수)
@@ -3582,51 +3526,51 @@
 다. 방과후학교 개인위탁 외부강사 활동에 제한이 없는 자</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814746</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>진주고등학교 계약제교원(시간제강사-일본어) 채용 공고</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>진주고등학교</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목 및 인원
 시간제강사 - 일본어 1명
@@ -3678,51 +3622,51 @@
 **************** 보다 자세한 사항은 첨부파일을 꼭 확인하여 주시기 바랍니다. ******************</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814820</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -3736,51 +3680,51 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교(직업교육 혁신지구 전공심화연구동아리 멘토 교육(전기제어) 외부강사) 모집 공고</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교 공고 제2026 – 65호
 2026학년도 마산공업고등학교에 근무할 전공심화연구동아리 멘토 교육(전기제어) 외부 강사 모집을 다음과 같이 공고 합니다.
@@ -3806,53 +3750,53 @@
 * 자세한 사항은 붙임 공고문을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n">
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814792</t>
         </is>
       </c>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -3864,53 +3808,53 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n">
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
         </is>
       </c>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 위탁운영 단체(법인) 모집 공고</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>고성군</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>경남 고성군</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 재개장을 앞두고 해당 시설의 운영 및 관리를 위한 위탁운영 단체(법인)을  모집하고자 첨부와 같이 공고합니다.
 고성군 공고 제2026-1750호
@@ -3942,11 +3886,70 @@
 &lt; 청소년단체 &gt;</t>
         </is>
       </c>
-      <c r="G51" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>내곡초등학교</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명(전일제 또는 시간제)
+2. 기간: 2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명(전일제 또는 시간제)</t>
+        </is>
+      </c>
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="n"/>
       <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n"/>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
+        </is>
+      </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="5" t="n"/>
       <c r="N51" s="5" t="inlineStr">
@@ -3956,19 +3959,19 @@
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
+          <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>내곡초등학교</t>
+          <t>율하중학교</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3978,70 +3981,11 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n"/>
       <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>아래와 같이 결원대체강사 채용을 공고합니다.
-1. 대상: 초등교사 1명(전일제 또는 시간제)
-2. 기간: 2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>초등교사 1명(전일제 또는 시간제)</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>계약제 교원(시간 강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>율하중학교</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -4052,51 +3996,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -4148,47 +4092,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O54" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -4200,51 +4144,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -4261,13 +4205,59 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
       <c r="G56" s="5" t="n"/>
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="n"/>
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
       <c r="L56" s="5" t="n"/>
@@ -4279,19 +4269,19 @@
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>함양제일고등학교</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -4300,11 +4290,18 @@
         </is>
       </c>
       <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
+        </is>
+      </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
+1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
+2. 과목: 특수
+3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
+-자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
       <c r="G57" s="5" t="n"/>
@@ -4313,7 +4310,7 @@
       <c r="J57" s="5" t="n"/>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
       <c r="L57" s="5" t="n"/>
@@ -4325,19 +4322,19 @@
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>함양제일고등학교</t>
+          <t>마산고등학교</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4346,18 +4343,10 @@
         </is>
       </c>
       <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
-        </is>
-      </c>
+      <c r="E58" s="5" t="n"/>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
-1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
-2. 과목: 특수
-3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
--자세한 내용은 공고문 참조 바랍니다.</t>
+          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
       <c r="G58" s="5" t="n"/>
@@ -4366,7 +4355,7 @@
       <c r="J58" s="5" t="n"/>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
       <c r="L58" s="5" t="n"/>
@@ -4378,19 +4367,19 @@
       </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
+          <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>마산고등학교</t>
+          <t>대암초등학교</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -4399,57 +4388,12 @@
         </is>
       </c>
       <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
+        </is>
+      </c>
       <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O59" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>기초학력전담강사 채용 공고문</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>대암초등학교</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -4469,49 +4413,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n">
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -4520,13 +4464,59 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
       <c r="G61" s="5" t="n"/>
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="n"/>
       <c r="J61" s="5" t="n"/>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
         </is>
       </c>
       <c r="L61" s="5" t="n"/>
@@ -4545,12 +4535,12 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>일운초등학교</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -4562,8 +4552,7 @@
       <c r="E62" s="5" t="n"/>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
       <c r="G62" s="5" t="n"/>
@@ -4572,7 +4561,7 @@
       <c r="J62" s="5" t="n"/>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
         </is>
       </c>
       <c r="L62" s="5" t="n"/>
@@ -4591,12 +4580,12 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>일운초등학교</t>
+          <t>함안고등학교</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -4608,7 +4597,8 @@
       <c r="E63" s="5" t="n"/>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
       <c r="G63" s="5" t="n"/>
@@ -4617,7 +4607,7 @@
       <c r="J63" s="5" t="n"/>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
         </is>
       </c>
       <c r="L63" s="5" t="n"/>
@@ -4636,36 +4626,31 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>함안고등학교</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 고성군</t>
         </is>
       </c>
       <c r="D64" s="5" t="n"/>
       <c r="E64" s="5" t="n"/>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
-자세한 내용은 첨부파일 확인 바랍니다.</t>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
         </is>
       </c>
       <c r="G64" s="5" t="n"/>
       <c r="H64" s="5" t="n"/>
       <c r="I64" s="5" t="n"/>
       <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
-        </is>
-      </c>
+      <c r="K64" s="5" t="n"/>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="5" t="n"/>
       <c r="N64" s="5" t="inlineStr">
@@ -4682,63 +4667,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>소토초등학교</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>경남 고성군</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D65" s="5" t="n"/>
       <c r="E65" s="5" t="n"/>
       <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="n"/>
-      <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
-      <c r="N65" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O65" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교 한국어교육 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4760,13 +4704,58 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>경남혜림학교</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
+        </is>
+      </c>
       <c r="G66" s="5" t="n"/>
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="n"/>
       <c r="J66" s="5" t="n"/>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
         </is>
       </c>
       <c r="L66" s="5" t="n"/>
@@ -4785,12 +4774,12 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
+          <t>진영중앙초 2학기 집중돌봄 특기적성 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>경남혜림학교</t>
+          <t>진영중앙초등학교</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -4799,57 +4788,12 @@
         </is>
       </c>
       <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="n"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>월,수/수,금/월,금 선택가능(주2회, 총 4차시)</t>
+        </is>
+      </c>
       <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="n"/>
-      <c r="M67" s="5" t="n"/>
-      <c r="N67" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O67" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>진영중앙초 2학기 집중돌봄 특기적성 프로그램 개인위탁 외부강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>진영중앙초등학교</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>월,수/수,금/월,금 선택가능(주2회, 총 4차시)</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>1. 모집 분야 및 인원
 가. 모집분야: 창의놀이(예: 영어놀이, 음악놀이, 미술놀이, 보드게임, 마술 등)
@@ -4860,15 +4804,60 @@
 3. 문의사항: 돌봄교실 [전화번호](11시~18시)</t>
         </is>
       </c>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814812</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>돌봄·방과후학교 배드민턴 외부강사 채용공고</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>능포초등학교</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>돌봄·방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+        </is>
+      </c>
       <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="n"/>
       <c r="J68" s="5" t="n"/>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814812</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814781</t>
         </is>
       </c>
       <c r="L68" s="5" t="n"/>
@@ -4880,74 +4869,29 @@
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>돌봄·방과후학교 배드민턴 외부강사 채용공고</t>
+          <t>함안군 민방위 교육 강사 위촉대상자 공고</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>능포초등학교</t>
+          <t>함안군</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 함안군</t>
         </is>
       </c>
       <c r="D69" s="5" t="n"/>
       <c r="E69" s="5" t="n"/>
       <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>돌봄·방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814781</t>
-        </is>
-      </c>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
-      <c r="N69" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O69" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>함안군 민방위 교육 강사 위촉대상자 공고</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>함안군</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>경남 함안군</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>2026년 함안군 민방위 교육 강사 위촉대상자를 붙임과 같이 공고합니다.
 함안군 공고 제2026-1233호
@@ -4969,11 +4913,52 @@
 2. 기타 문의사항은 안전총괄과 안전관리담당(☎[전화번호])으로 문의하시길바랍니다.</t>
         </is>
       </c>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O69" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[용원국민체육센터]생활체육 도급강사 공개경쟁모집 공고</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단 채용정보</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
       <c r="G70" s="5" t="n"/>
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="n"/>
       <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n"/>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1705&amp;page=1</t>
+        </is>
+      </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="5" t="n"/>
       <c r="N70" s="5" t="inlineStr">
@@ -4983,36 +4968,40 @@
       </c>
       <c r="O70" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>[용원국민체육센터]생활체육 도급강사 공개경쟁모집 공고</t>
+          <t>전일제강사 채용 공고(보건)</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>창원시설공단 채용정보</t>
+          <t>김해중학교</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>경남 창원시</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D71" s="5" t="n"/>
       <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>전일제 강사(5일) 모집합니다.</t>
+        </is>
+      </c>
       <c r="G71" s="5" t="n"/>
       <c r="H71" s="5" t="n"/>
       <c r="I71" s="5" t="n"/>
       <c r="J71" s="5" t="n"/>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1705&amp;page=1</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814827</t>
         </is>
       </c>
       <c r="L71" s="5" t="n"/>
@@ -5023,51 +5012,6 @@
         </is>
       </c>
       <c r="O71" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>전일제강사 채용 공고(보건)</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>김해중학교</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>전일제 강사(5일) 모집합니다.</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814827</t>
-        </is>
-      </c>
-      <c r="L72" s="5" t="n"/>
-      <c r="M72" s="5" t="n"/>
-      <c r="N72" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O72" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>성호초등학교 전일제강사 채용 공고</t>
+          <t>통영여자중학교 시간강사(수학) 채용</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>성호초등학교</t>
+          <t>통영여자중학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -640,405 +640,15 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026.10.13.~ 2026.10.21.(9일)</t>
+          <t>2026. 10. 15~2026. 10. 23</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 성호초등학교에 근무할 계약제교원(기간제교사)를 다음과 같이 채용 (재)공고 합니다.
-1. 채용과목 및 인원: 특수교사 1명
-2. 채용기간: 2026.10.13.~ 2026.10.21.(9일)
-3. 접수기간: 2026.10.6.(화) ~ 10.11.(일) 15:00까지
-4. 접수장소 및 방법: 성호초등학교 대표메일([이메일])로 제출
-(현장접수 가능/ 면접 시 원본 제출)
-*자세한 사항은 붙임 참고 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814618</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>창원남산고등학교 계약제교원 채용공고(체육 기간제 또는 강사)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>창원남산고등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.14.(수)~2026.12.4.(금)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>창원남산고등학교 계약제교원 채용공고
-1. 채용인원 : 체육 기간제 교사 또는 강사
-2. 채용과목: 체육
-3. 채용기간: 2026.10.14.(수)~2026.12.4.(금)
-4. 지원자격: 해당교과목 자격증 소지자
-5. 채용일정
-가. 응시원서접수기간: 2026.10.07.(수)~10.11.(일)16:30 까지 도착분에 한함.
-나. 접수방법:  e-mail접수 [이메일]
-다. 서류전형 합격자 발표: 2026.10.12. (월) 11:00 이후 (합격자에 한해 개별통보)
-라. 면접일시: 2026.10.13.(화)11시
-마. 최종합격자 발표: 2026.10.13.(화) 14시 이후
-6. 자세한 사항은 채용공고문을 참고하시기 바랍니다</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>해당교과목 자격증 소지자</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814789</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>웅상고 계약제교원(학교폭력담당자 수업경감 시간강사) 2차 채용 공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>웅상고등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.19. ~ 2026.12.31.</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>웅상고등학교 공고 제2026 – 50호
-웅상고등학교 학교폭력담당자 수업경감 강사 3차 채용 공고
-2026학년도 웅상고등학교에 근무할 기간제교사를 다음과 같이 채용 공고 합니다.
-1. 채용과목 및 응모 자격
-물리(과학), 1명, 시간강사
-2026.10.19. ~ 2026.12.31.
-주당 5시간, 시간당 25,000원.
-물리교사자격증 소지자
-- 공통과학, 지구과학, 생물, 화학 교사자격증 지원가능
-- 정년퇴직자 및 명예퇴직자
-- 만 62세까지 지원가능
-❈ 채용의 1순위: 결원 교원과
-동일한 급별‧과목별
-교원자격증소지자, 만 62세 미만
-동일 자격소지자를 우선 임용.
-2순위: 명예퇴직자, 정년퇴직자,
-다른 학교급·유사과목 자격증 소지자 등, 만 62세 미만.
-2. 전형방법
-가. 1차 시험 : 서류전형
-나. 2차 시험 : 면접
-3. 제출서류
-가. 응시자 제출서류
-◦ 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
-◦ 자기소개서 1부.(붙임서식)
-◦ 개인정보동의서(붙임서식)
-나. 최종합격자 제출서류
-◦ 교사 자격증 사본 또는 자격 인정 조서 1부.
-◦ 졸업증명서 사본 1부.(원본지참)
-◦ 기본증명서 및 병적증명서 또는 주민등록 초본 1부.
-◦ 범죄경력조회동의서 1부.
-◦ 공무원채용신체검사서 1부.
-4. 서류접수 및 전형일정
-가. 원서접수
-◦ 접수기간 : 2026. 10. 7.(수) 9:00 ~ 2026. 10. 11.(일) 21:00까지
-◦ 접수장소 : 웅상고등학교 3층 1교무실
-◦ 접수방법 : 이메일접수 ([이메일](영타), 2026. 10. 11.(일) 21:00까지)
-나. 1차 : 서류전형 합격자 발표(개별 전화 통지) 예정일 : 2026. 10. 12.(월) 15:00 이후
-다. 2차 : 면접예정일 : 2026. 10. 13.(화), 10:00 예정
-* 일시 및 장소는 서류전형 합격자에게만 개별 통보
-5. 합격자 발표
-◦ 최종합격자 발표 : 2026. 10. 13.(화) 17:00 이후 개별통보
-6. 유의사항
-◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 우선 임용될 수 있음
-◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 최종합격 후 확인이 불가능한 서류만 제출
-◦ 상기 일정은 진행상황에 따라 변경될 수 있으며 별도 통보함
-◦ 기재사항이 사실과 다르거나 허위로 작성된 경우는 합격을 취소합니다.
-◦ 제출서류의 기재착오, 누락, 서류 미제출, 연락불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.
-◦ 최종합격자로 발표된 이후에도 결격사유가 있는 자는 합격을 취소합니다.
-◦ 기타 자세한 사항은 웅상고등학교(☎[전화번호])로 문의하시기 바랍니다.
-2026년 10월 7일
-웅상고등학교장</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814610</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>마산가포고등학교 결원대체강사(1순위:지리, 2순위: 일반사회, 윤리) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>마산가포고등학교</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.26.~2026.10.30.(총16시간)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
-1. 채용내용 및 응모자격
-가. 채용과목 및 인원: 지리 1명(1순위: 지리, 2순위: 일반사회, 윤리)
-나. 채용기간: 2026.10.26.~2026.10.30.(총16시간)
-다. 수당: 시간당 35,000원
-라. 응모자격
-1) 1순위: 만 62세 미만의 결원 교원과 동일 학교급 및 과목 자격증 소지자
-2) 2순위: 만 62세 미만의 결원 교원과 다른 학교급 또는 유사 과목* 자격증 소지자, 정년퇴직자 혹은 명예퇴직자
-※ 1차 모집 공고부터 우선순위를 정하여 1순위 지원자가 없을 시 후 순위 지원자 채용 가능
-2. 전형방법
-가. 1차 시험 : 서류전형(채용 예정 인원의 3배수 이내 선발)
-나. 2차 시험 : 면접(1차 서류 전형 합격자에 한하여 실시하며, 대상자에게 개별 통보)
-3. 응시자 제출서류
-가. 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
-나. 자기소개서 1부.(붙임서식)
-다. 계약제교원 채용을 위한 개인정보 수집 이용 동의서 1부.(붙임서식)
-4. 서류접수 및 전형일정
-가. 서류접수
-◦ 접수기간 : 2026. 10. 6.(화) ~ 2026. 10. 11.(일) 24:00까지
-◦ 접수방법 : 온라인접수([이메일] 스캔본 제출, 면접 시 원본제출, 2026. 10. 11.(일) 24:00 발송분까지)
-나. 1차 서류 전형 합격자 발표 : 2026. 10. 12.(월) 14:00 이후(1차 서류 전형 합격자에 한해 개별 통보)
-다. 2차 면접 : 2026. 10. 13.(화) 13:30~
-라. 최종합격자 발표 : 2026. 10. 13.(화) 15:00 이후 개별통보
-5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814575</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>증산중학교 계약제교원(시간강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>증산중학교</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>증산중학교 시간강사 채용
-1. 채용과목: 수학 1명
-2. 채용기간: 2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)
-2. 일정
-가. 원서접수:2026.9.28.(월)∼10.11.(일) 24:00까지 도착분에 한함
-나. 접수방법: 전자우편([이메일])으로 1개의 PDF 파일로 제출
-다. 1차 서류전형 발표일: 2026.10.12.(월) 15:00 이후
-라. 2차 면접일: 2026.10.13.(화) 11:30~
-마. 합격자 발표: 2026.10.13.(화)  16:00 이후 (합격자에 한해 개별 통지)
-* 기타 사항은 첨부파일 참고</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814584</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>증산중학교 시간강사 채용 공고(수학)</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>증산중학교</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>증산중학교 시간강사 채용
-1. 채용과목: 수학 1명
-2. 채용기간: 2026. 10. 26.~2026. 10. 28. (3일, 총12시간, 시간당 24,000원)
-2. 일정
-가. 원서접수:2026.9.28.(월)∼10.11.(일) 24:00까지 도착분에 한함
-나. 접수방법: 전자우편([이메일])으로 1개의 PDF 파일로 제출
-다. 1차 서류전형 발표일: 2026.10.12.(월) 15:00 이후
-라. 2차 면접일: 2026.10.13.(화) 11:30~
-마. 합격자 발표: 2026.10.13.(화)  16:00 이후 (합격자에 한해 개별 통지)
-* 기타 사항은 첨부파일 참고</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814744</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>통영여자중학교 시간강사(수학) 채용</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>통영여자중학교</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 15~2026. 10. 23</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>통영여자중학교에서 근무할 시간강사를 다음과 같이 채용 공고합니다.
 - 채용기간 : 2026. 10. 15~2026. 10. 23
@@ -1048,47 +658,47 @@
 자세한 내용은 첨부파일을 참고해주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814706</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>김해수남고 학교폭력 업무담당자 수업경감 시간강사 채용 재공고8차(일반사회)</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>김해수남고등학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16. ~ 2027. 2. 5. (일반사회-시간강사) 주4시간(금요일), 시간당 25,000원</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>2026학년도 김해수남고등학교에 근무할 시간강사를 다음과 같이 채용 재공고합니다.
 1. 과목: 일반사회(사회계열 모두 가능) 1명
@@ -1100,47 +710,47 @@
 7. 문의전화: 김해수남고 교무센터 ☎724-9350, 기타 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814759</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>동진초등학교 2026.10.12.자 계약제교원(결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>동진초등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 10. 17.(5일)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등교사
 나. 채용 기간: 2026. 10. 12. ~ 2026. 10. 17.(5일)
@@ -1152,49 +762,49 @@
 ※ 국가공무원법 제33조의 규정에 의한 공무원임용 결격사유가 없는 자</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814468</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>증산고등학교 결원대체강사(전일제강사/수학) 채용 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>증산고등학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 15.(목) ~ 2026. 11. 6.(금) 17일, 110,000/일</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>증산고등학교에서 근무할 결원대체강사(전일제강사/수학) 를 다음과 같이 채용하고자 합니다.
 1. 채용과목: 수학
@@ -1211,47 +821,47 @@
 * 자세한 사항은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814809</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 쿠키클레이 재모집 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>중부초등학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 1일∼2027년 2월 28일(4개월)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>가. 모집 분야: 쿠키클레이 1명
 나. 접수 기간: 2026년 10월 8일(목) ∼ 2026년 10월 13일(화) 14:00까지
@@ -1261,49 +871,49 @@
 *자세한 사항 및 필요 제출서류는 첨부파일을 확인하시고 기한내에 제출해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814838</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -1356,49 +966,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -1449,49 +1059,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -1515,47 +1125,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(기술 가정) 채용 공고</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고
 합니다.
@@ -1580,49 +1190,49 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>마산중앙중학교 강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>마산중앙중학교</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2026. 11. 11.(수)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산중앙중학교 강사 채용 공고를 다음과 같이 합니다.
 공고 기간: 2026. 10. 8.(목) ~ 2026. 10. 14.(수) 13:00까지
@@ -1635,49 +1245,49 @@
 * 기타 자세한 사항은 채용공고 첨부파일을 참조 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814851</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>악양초등학교 계약제 교원(결원대체강사)-전일제강사 채용</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>악양초등학교</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2026.10.26 ~ 2026.10.30.(총5일)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>2026학년도 악양초등학교에 근무할 결원 대체 강사를 다음과 같이 채용 공고 안내
 1. 채용과목 : 초등(전일제강사 1명)
@@ -1696,59 +1306,59 @@
 * 자세한 사항은 붙임 공고문을 참조바랍니다.</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>1순위: 만 62세 미만 동일 자격 소지자
 2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
 1순위 지원자 없을 시 2순위자 채용 가능</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재), 자기소개서 1부.(붙임서식), 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814828</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>팔룡중학교 결원대체강사(진로진학상담)채용 공고</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>팔룡중학교</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 3.~2026. 11. 6.(총 13시간)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>[팔룡중학교 공고 제2026 - 39호]
 팔룡중학교 결원대체강사(진로진학상담 시간강사) 채용 공고
@@ -1769,47 +1379,47 @@
 ※기타 자세한 사항은 첨부파일 확인 및 팔룡중학교 교무실 [전화번호] 문의 바랍니다.</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814841</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>전일제강사 채용공고(사회)</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>덕산중학교</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 9.(월) ~2026. 11. 23.(월) (11일)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>2026학년도 덕산중학교에 근무할 전일제 강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 사회
@@ -1819,49 +1429,49 @@
 기타사항은 첨부파일 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814821</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>대방중학교 전일제강사(기술·가정과) 채용 공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>대방중학교</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 9일 ~ 2026년 11월 13일(5일)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>2026학년도 대방중학교 기술·가정과 전일제강사를 다음과 같이 채용 공고(2차)합니다.
 1. 접수기간: 2026년 10월 8일(목) ~ 2026년 10월 14일(수), 09:00까지 도착분에 한함
@@ -1873,47 +1483,47 @@
 기타 자세한 사항은 붙임 문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814661</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>하동고등학교 결원대체강사(국어) 채용 공고</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>하동고등학교</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026.11.09.~2026.11.13.(5일), 2026.12.21.~2026.12.22.(2일)(총 7일)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>2026학년도 하동고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모 자격(결원대체강사;전일제/시간제)
@@ -1936,53 +1546,53 @@
 자세한 내용은 붙임파일을 참고해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>1순위: 채용 과목 중등 자격증 소지자</t>
         </is>
       </c>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814762</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>거창중학교 스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>거창중학교</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 20.(화) ~ 2027. 2. 10.(수)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>거창중학교 학교스포츠클럽 강사 공고
 1. 계약기간 : 2026. 10. 20.(화) ~ 2027. 2. 10.(수)
@@ -1998,47 +1608,47 @@
 자세한 사항은 첨부파일을 참조하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814839</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>사회과(역사 또는 일반사회 또는 지리) 중등수업지원강사 채용 공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>창원상남중학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 12. 31.(2학년 역사수업, 주당 7시간, 월요일 2,3,4교시/목요일 1,2,3,4교시)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원상남중학교에서 근무할 중등수업지원강사를 다음과 같이 채용 공고합니다.
 1. 채용과목(인원): 사회(역사 또는 일반사회 또는 지리)(1명)
@@ -2052,49 +1662,49 @@
 *자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n">
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814787</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>신문초등학교 초등돌봄교실 특기‧적성 프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>신문초등학교</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 6.(금) ~ 2027. 2. 26.(금)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>신문초등학교에서는 2026학년도 초등돌봄교실 운영과 관련하여 아래와 같이 특기‧적성 프로그램 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 선정 인원: 초등돌봄교실 특기·적성 프로그램 외부강사 1명
@@ -2107,47 +1717,47 @@
 ※ 자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814822</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -2198,53 +1808,53 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H20" s="5" t="n">
         <v>8046</v>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>유목초등학교</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>구체적인 내용은 공고문을 참고바랍니다.
 1. 분야: 특수학급 결원대체강사
@@ -2252,49 +1862,49 @@
 3.기간: 2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>유목초 특수학급 결원대체강사 채용 공고</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>유목초등학교</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>구체적인 내용은 공고문을 참고바랍니다.
 1. 분야: 특수학급 결원대체강사
@@ -2302,49 +1912,49 @@
 3.기간: 2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(내서스포츠센터팀)</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 2개분야 3명
 2. 접수기간: 10. 12.(월) 09:00 ~ 10. 19.(월) 18:00
@@ -2410,57 +2020,57 @@
 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>여부</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H23" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>TRX 필라테스</t>
         </is>
       </c>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5003</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>[내서스포츠센터] 프로그램 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>내서스포츠센터팀 공고 제2026-7호
 내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고
@@ -2522,57 +2132,57 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>여부</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>TRX 필라테스</t>
         </is>
       </c>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1704&amp;page=1</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>마산합포스포츠센터 생활체육 프로그램 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(마산합포스포츠센터팀)</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 2개분야 2명
 2. 접수기간: 10. 16.(금) 09:00 ~ 10. 22.(목) 18:00
@@ -2624,53 +2234,53 @@
 11.「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 규정된 죄를 범한 사람으로서 100만원 이상의 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n">
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>합 계</t>
         </is>
       </c>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5006</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>웅남중 학교운동부지도자 채용공고(태권도)</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>웅남중학교</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>2026.12.01.(화)~2027.2.28.(일)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>웅남중학교 운동부 지도자 채용 공고
 - 채용분야: 운동부지도자
@@ -2683,98 +2293,98 @@
 자세한 사항은 붙임 문서를 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814764</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>2026.10.1.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명
 2. 기간: 2026.10.1.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>김해율하도서관 2027년 율하아카데미 교육강사 채용 공고</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>2027. 2. ~ 2027. 11.(3학기 기준)</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>김해율하도서관 2027년 율하아카데미 교육강사 채용을 위하여 붙임의 고시공고를 홈페이지에 게제하고자 합니다.
 김해시청 제2026-4441호
@@ -2816,53 +2426,53 @@
 미술·체험·놀이(6)</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H28" s="5" t="n">
         <v>6448</v>
       </c>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110418&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>유영초등학교</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~2026.10.30.(19일간)</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 초등 결원대체 강사(전일제)
 2. 채용 인원: 1명
@@ -2870,49 +2480,49 @@
 4. 자세한 사항은 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n">
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
         </is>
       </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>안의고등학교 역사, 국어과 결원대체강사 채용 공고</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>안의고등학교</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>국어-2026.11.23.(월)~2026.11.27.(금) (5일)</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>안의고등학교 결원대체강사 채용 공고
 2026학년도 안의고등학교에 근무할 결원대체강사(전일제/시간제)를 다음과 같이 채용 공고합니다.
@@ -2960,53 +2570,53 @@
 ◦ 제출서류의 기재 착오, 누락, 서류 미제출, 연락 불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.</t>
         </is>
       </c>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>1순위: 만 69세 미만 동일 자격 소지자
 2순위: 다른 학교급 또는 유사과목 자격 소지자, 명예퇴직자, 정년퇴직자
 (1순위 지원자가 있을 경우 2순위는 심사 대상에서 제외)</t>
         </is>
       </c>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814832</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>남지초등학교</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등기간제교원
 나. 채용 기간: 2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)
@@ -3019,49 +2629,49 @@
 ※자세한 사항은 공고문 참고</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n">
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
         </is>
       </c>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="n"/>
-      <c r="O37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
 1. 채용과목: 영어(1명)
@@ -3069,49 +2679,49 @@
 상세내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n">
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="n"/>
-      <c r="O38" s="5" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -3166,15 +2776,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H33" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -3184,160 +2794,40 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="n"/>
-      <c r="O39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>진주중앙고 전일제 강사(체육) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>진주중앙고등학교</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>산양초등학교 돌봄교실 특기적성 프로그램 외부강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>산양초등학교</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 진주중앙고등학교 전일제 강사를 다음과 같이 채용 공고 합니다.
-1. 채용 과목 및 인원: 체육 1명.
-2. 접수 기간: 2026. 10. 7.(수) ~ 10. 11.(일) 15시 발송분까지
-3. 접수장소: 진주중앙고등학교 전자우편([이메일])
-4. 자세한 사항은 붙임 문서를 참고 하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814791</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>진해용원고등학교 물리 계약제교원(전일제/시간제강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>진해용원고등학교</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 진해용원고등학교에 근무할 계약제교원(전일제강사/시간강사)을 다음과 같이 채용 공고 합니다.
-1. 채용과목: 물리
-2. 채용예정기간: 2026.10.19.~2026.10.23.
-3. 전형방법
-가. 1차 시험: 서류전형
-나. 2차 시험: 면접(서류전형 합격한 자에 한하여 개별 통보)
-**수업실연(서류전형 합격자에 한하여 필요한 경우 실시)
-4. 서류접수 및 전형일정
-가. 원서접수
-◦ 접수기간: 2026. 10. 8.(목) ~ 2026. 10. 11.(일)
-◦ 접수방법: 온라인(E-mail) 접수 ([이메일]) 2026. 10. 11.(일) 발송분까지
-- 파일명은 교과목-성명으로 첨부(예시: 영어-홍길동)
-※ 개인 서명한 스캔파일(PDF파일), 면접시 원본 제출
-나. 1차: 서류전형 합격자 발표(합격자에 한해 개별 전화 통지) 예정일: 2026. 10. 12.(월) 14시 이후
-다. 2차: 면접 (서류심사 합격자에 한함) 예정일: 2026. 10. 13.(화) 14시 2층 소회의실
-5. 합격자 발표
-◦ 최종합격자 발표: 2026. 10. 14.(수) 10시 이후 합격자에 한해 개별 전화 통지</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814797</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>산양초등학교 돌봄교실 특기적성 프로그램 외부강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>산양초등학교</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>본교 돌봄교실 운영과 관련하여 특기적성 프로그램 개인 위탁 강사님을 모시고자 하오니,  관심있으신 분들의 지원을 바랍니다.
 1. 모집분야: 보드게임 1명
@@ -3346,53 +2836,53 @@
 4. 기타 자세한 사항은 첨부파일 공고문을 참고 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n">
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814814</t>
         </is>
       </c>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>교원 장기재직 휴가 대체 시간 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>삼천포여자중학교</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>2026 교원 장기재직 휴가 대체 시간 강사 채용 계획을 붙임과 같이 공고합니다.
 1. 채용내용: 장기재직 휴가 데체 시간 강사(과학)
@@ -3404,51 +2894,51 @@
 마. 최종 합격자 발표: 10. 16.(금) 16:00 이후 개별 통보</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814790</t>
         </is>
       </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 재공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -3464,53 +2954,53 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n">
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814852</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집공고(수학)</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>거제고현중학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>★  모집 세부 사항
 가. 공고 기간: 2026.10.7.(수)~2026.10.14.(수)
@@ -3526,51 +3016,51 @@
 다. 방과후학교 개인위탁 외부강사 활동에 제한이 없는 자</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814746</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>진주고등학교 계약제교원(시간제강사-일본어) 채용 공고</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>진주고등학교</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목 및 인원
 시간제강사 - 일본어 1명
@@ -3622,51 +3112,51 @@
 **************** 보다 자세한 사항은 첨부파일을 꼭 확인하여 주시기 바랍니다. ******************</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814820</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -3680,51 +3170,51 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교(직업교육 혁신지구 전공심화연구동아리 멘토 교육(전기제어) 외부강사) 모집 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교 공고 제2026 – 65호
 2026학년도 마산공업고등학교에 근무할 전공심화연구동아리 멘토 교육(전기제어) 외부 강사 모집을 다음과 같이 공고 합니다.
@@ -3750,53 +3240,53 @@
 * 자세한 사항은 붙임 공고문을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n">
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814792</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -3808,53 +3298,53 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n">
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
         </is>
       </c>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 위탁운영 단체(법인) 모집 공고</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>고성군</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>경남 고성군</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 재개장을 앞두고 해당 시설의 운영 및 관리를 위한 위탁운영 단체(법인)을  모집하고자 첨부와 같이 공고합니다.
 고성군 공고 제2026-1750호
@@ -3886,106 +3376,106 @@
 &lt; 청소년단체 &gt;</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -3996,51 +3486,51 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -4092,47 +3582,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -4144,51 +3634,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O54" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -4205,97 +3695,97 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
         </is>
       </c>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>함양제일고등학교</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>10.26.(월)-11.11.(수)/ 총58시간</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
 1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
@@ -4304,96 +3794,96 @@
 -자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>마산고등학교</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="O50" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>대암초등학교</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -4413,49 +3903,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n">
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -4464,225 +3954,225 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
         </is>
       </c>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
         </is>
       </c>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>일운초등학교</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="inlineStr">
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
         </is>
       </c>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O62" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>함안고등학교</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
 자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="n"/>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
         </is>
       </c>
-      <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>고성군</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>경남 고성군</t>
         </is>
       </c>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
         </is>
       </c>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="n"/>
-      <c r="L64" s="5" t="n"/>
-      <c r="M64" s="5" t="n"/>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O64" s="5" t="inlineStr">
+      <c r="O56" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>소토초등학교 한국어교육 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>소토초등학교</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4704,96 +4194,96 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O65" s="5" t="inlineStr">
+      <c r="O57" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="inlineStr">
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
         </is>
       </c>
-      <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
-      <c r="N66" s="5" t="inlineStr">
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O66" s="5" t="inlineStr">
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>진영중앙초 2학기 집중돌봄 특기적성 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>진영중앙초등학교</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>월,수/수,금/월,금 선택가능(주2회, 총 4차시)</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>1. 모집 분야 및 인원
 가. 모집분야: 창의놀이(예: 영어놀이, 음악놀이, 미술놀이, 보드게임, 마술 등)
@@ -4804,94 +4294,94 @@
 3. 문의사항: 돌봄교실 [전화번호](11시~18시)</t>
         </is>
       </c>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="n">
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814812</t>
         </is>
       </c>
-      <c r="L67" s="5" t="n"/>
-      <c r="M67" s="5" t="n"/>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O67" s="5" t="inlineStr">
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>돌봄·방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>능포초등학교</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>돌봄·방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="n"/>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="inlineStr">
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814781</t>
         </is>
       </c>
-      <c r="L68" s="5" t="n"/>
-      <c r="M68" s="5" t="n"/>
-      <c r="N68" s="5" t="inlineStr">
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O68" s="5" t="inlineStr">
+      <c r="O60" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>함안군 민방위 교육 강사 위촉대상자 공고</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>함안군</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>경남 함안군</t>
         </is>
       </c>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>2026년 함안군 민방위 교육 강사 위촉대상자를 붙임과 같이 공고합니다.
 함안군 공고 제2026-1233호
@@ -4913,105 +4403,105 @@
 2. 기타 문의사항은 안전총괄과 안전관리담당(☎[전화번호])으로 문의하시길바랍니다.</t>
         </is>
       </c>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="n"/>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O69" s="5" t="inlineStr">
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>[용원국민체육센터]생활체육 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="inlineStr">
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1705&amp;page=1</t>
         </is>
       </c>
-      <c r="L70" s="5" t="n"/>
-      <c r="M70" s="5" t="n"/>
-      <c r="N70" s="5" t="inlineStr">
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O70" s="5" t="inlineStr">
+      <c r="O62" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>전일제강사 채용 공고(보건)</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>김해중학교</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>전일제 강사(5일) 모집합니다.</t>
         </is>
       </c>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814827</t>
         </is>
       </c>
-      <c r="L71" s="5" t="n"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O71" s="5" t="inlineStr">
+      <c r="O63" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>통영여자중학교 시간강사(수학) 채용</t>
+          <t>증산고등학교 결원대체강사(전일제강사/수학) 채용 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>통영여자중학교</t>
+          <t>증산고등학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -640,171 +640,15 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026. 10. 15~2026. 10. 23</t>
+          <t>2026. 10. 15.(목) ~ 2026. 11. 6.(금) 17일, 110,000/일</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>통영여자중학교에서 근무할 시간강사를 다음과 같이 채용 공고합니다.
-- 채용기간 : 2026. 10. 15~2026. 10. 23
-- 접수기간 : 2026. 10. 7～2026. 10. 12. 15:00시까지
-- 접수장소 : 통영여자중학교 전자우편
-- 접수방법 : 전자우편(주소: [이메일], 스캔본 제출, 면접 시 원본 제출, 2026. 10. 12. 15:00시 발송분까지)
-자세한 내용은 첨부파일을 참고해주시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814706</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>김해수남고 학교폭력 업무담당자 수업경감 시간강사 채용 재공고8차(일반사회)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>김해수남고등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 16. ~ 2027. 2. 5. (일반사회-시간강사) 주4시간(금요일), 시간당 25,000원</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 김해수남고등학교에 근무할 시간강사를 다음과 같이 채용 재공고합니다.
-1. 과목: 일반사회(사회계열 모두 가능) 1명
-2. 채용기간: 2026. 10. 16. ~ 2027. 2. 5. (일반사회-시간강사) 주4시간(금요일), 시간당 25,000원
-3. 서류접수 : 2026. 10. 6.(화)～ 2026. 10. 12.(월) 15:00까지, 전자우편 ( [이메일] )
-4. 1차 : 서류전형 합격자 발표(개별 문자 통지): 2026. 10. 13.(화) 17:00~
-5. 2차 : 면접 (서류심사 합격자에 한함) 예정일 : 2026. 10. 14.(수) 13:00~
-6. 최종합격자 발표 : 2026. 10. 14.(수) 17:00~ 합격자 개별 통보
-7. 문의전화: 김해수남고 교무센터 ☎724-9350, 기타 자세한 사항은 첨부파일을 확인하시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814759</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>동진초등학교 2026.10.12.자 계약제교원(결원대체강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>동진초등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 12. ~ 2026. 10. 17.(5일)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>가. 채용 분야: 초등교사
-나. 채용 기간: 2026. 10. 12. ~ 2026. 10. 17.(5일)
-다. 채용 인원: 1명
-라. 응모 자격
-1) 1순위: 결원교원과 동일 학교급 자격증 소지자(만62세 미만)
-2) 2순위: 결원교원과 다른 학교급 또는 유사과목 자격소지자(만62세 미만),
-정년퇴직 혹은 명예퇴직자(만65세 미만)
-※ 국가공무원법 제33조의 규정에 의한 공무원임용 결격사유가 없는 자</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814468</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>증산고등학교 결원대체강사(전일제강사/수학) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>증산고등학교</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2026. 10. 15.(목) ~ 2026. 11. 6.(금) 17일, 110,000/일</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>증산고등학교에서 근무할 결원대체강사(전일제강사/수학) 를 다음과 같이 채용하고자 합니다.
 1. 채용과목: 수학
@@ -821,47 +665,97 @@
 * 자세한 사항은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814809</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>계약제교원(전일제강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>태룡초등학교</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.19.(월)~10.26.(월) (6일간)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 태룡초등학교에 근무할 전일제강사를 다음과 같이 채용 공고합니다.
+1. 채용 구분: 초등교사(1명)
+2.채용 기간: 2026.10.19.(월)~10.26.(월) (6일간)
+3.서류접수기간: 2026.10.12.(월)~10.13.(화) 12:00
+4.서류접수방법: 태룡초 교무실 직접 제출 및 전자우편 (주소: [이메일] ) * 스캔본 제출, 면접 시 원본 제출
+5.기타 문의: 태룡초등학교 교무실([전화번호])</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814876</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 쿠키클레이 재모집 공고</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>중부초등학교</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 1일∼2027년 2월 28일(4개월)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>가. 모집 분야: 쿠키클레이 1명
 나. 접수 기간: 2026년 10월 8일(목) ∼ 2026년 10월 13일(화) 14:00까지
@@ -871,49 +765,49 @@
 *자세한 사항 및 필요 제출서류는 첨부파일을 확인하시고 기한내에 제출해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814838</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -966,49 +860,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -1059,49 +953,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -1125,47 +1019,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(기술 가정) 채용 공고</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고
 합니다.
@@ -1190,49 +1084,49 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>마산중앙중학교 강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>마산중앙중학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2026. 11. 11.(수)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산중앙중학교 강사 채용 공고를 다음과 같이 합니다.
 공고 기간: 2026. 10. 8.(목) ~ 2026. 10. 14.(수) 13:00까지
@@ -1245,49 +1139,49 @@
 * 기타 자세한 사항은 채용공고 첨부파일을 참조 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814851</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>악양초등학교 계약제 교원(결원대체강사)-전일제강사 채용</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>악양초등학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026.10.26 ~ 2026.10.30.(총5일)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>2026학년도 악양초등학교에 근무할 결원 대체 강사를 다음과 같이 채용 공고 안내
 1. 채용과목 : 초등(전일제강사 1명)
@@ -1306,59 +1200,59 @@
 * 자세한 사항은 붙임 공고문을 참조바랍니다.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>1순위: 만 62세 미만 동일 자격 소지자
 2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
 1순위 지원자 없을 시 2순위자 채용 가능</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재), 자기소개서 1부.(붙임서식), 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814828</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>팔룡중학교 결원대체강사(진로진학상담)채용 공고</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>팔룡중학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 3.~2026. 11. 6.(총 13시간)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>[팔룡중학교 공고 제2026 - 39호]
 팔룡중학교 결원대체강사(진로진학상담 시간강사) 채용 공고
@@ -1379,13 +1273,171 @@
 ※기타 자세한 사항은 첨부파일 확인 및 팔룡중학교 교무실 [전화번호] 문의 바랍니다.</t>
         </is>
       </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814841</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>용원초등학교 계약제교원(전일제 강사)채용 공고</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>용원초등학교</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.29.  ~2026.11.25.(20일 간)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>1. 채용과목 및 응모 자격
+-채용 구분: 전일제 강사
+-채용인원: 1명
+-채용 기간:  2026.10.29.  ~2026.11.25.(20일 간)
+-응모자격 :
+.결원교원과 동일 학교급 자격증 소지자(만 62세 미만)
+.결원교원과 다른 학교급 자격증 소지자(만 62세 미만)
+.명예퇴직자,정년퇴직자(동일학교급 자격증소지자)
+2. 전형방법
+가. 1차 시험 : 서류전형
+나. 2차 시험 : 면접(서류전형 합격한 자에 한하여 개별 통보)
+3. 제출서류
+가. 응시자 제출서류
+◦ 응시원서 1부(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
+◦ 자기소개서 1부(붙임서식)
+◦ 개인정보 수집 및 활용 동의서 1부(붙임서식)
+나. 최종합격자 제출서류
+◦ 교사 자격증 사본 또는 자격 인정 조서 1부.
+◦ 최종학력 졸업증명서 1부.
+◦ 공무원채용신체검사서(유효기간 1년 이내)
+◦ 성범죄경력 및 아동학대관련 범죄 전력 조회동의서 1부
+◦ 개인정보 수집 및 활용 동의서 1부
+◦ 초임호봉획정을 위한 경력기간 합산신청서 1부
+◦ 병적증명서 또는 주민등록표 초본 1부
+◦ 가족채용제한여부 확인서 1부
+◦ 마약류 투약 또는 중독 여부 판별 결과 통보서 또는 의사 진단서(유효기간 1년)
+◦ 잠복결핵검사 확인서 1부(신규채용 후 1개월 이내 제출- 검사비 학교 부담)
+4. 서류접수 및 전형일정
+가. 원서접수
+◦ 접수 기간: 2026.10.12.(월)~ 2026.10.14.(수) 16:00
+◦ 접수 방법: 전자우편(주소: 첨부문서 참조)
+나. 1차 서류전형 합격자 발표예정일: 2026.10.15.(목) 11:00 이후(개별통보)
+다. 2차 면접 예정일: 2026.10.16.(금).14:00
+◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
+5. 합격자 발표
+◦ 최종합격자 발표: 2026.10.16.(금).17:00 이후(합격자에게만 개별통보)
+6. 유의사항
+◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 우선 임용될 수 있습니다.
+◦ 신규임용대기자 또는 기간제교원 인력풀 등재자는 최종합격 후 확인이 불가능한 서류만 제출합니다.
+◦ 상기 일정은 진행상황에 따라 변경될 수 있으며, 변경 시 별도 통보합니다.
+◦ 기재사항이 사실과 다르거나 허위로 작성된 경우는 합격을 취소합니다.
+◦ 제출서류의 기재착오, 누락, 서류 미제출, 연락불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.
+◦ 제출한 서류(전자우편 등 온라인으로 제출된 경우 제외)는 「채용절차의 공정화에 관한 법률」제11조에 따라 합격자 발표가 끝난 후 불합격자의 채용서류 반환 청구 희망할 경우만 반환합니다. (채용서류 반환청구서 작성 필수)
+◦ 최종합격자로 발표된 이후에도 결격사유가 있는 자는 합격을 취소합니다.
+◦ 기타 자세한 사항은 용원초등학교(☎ 552-2730)로 문의하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>.결원교원과 동일 학교급 자격증 소지자(만 62세 미만)
+.결원교원과 다른 학교급 자격증 소지자(만 62세 미만)
+.명예퇴직자,정년퇴직자(동일학교급 자격증소지자)</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814872</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>밀양고 전일제강사(수학) 채용공고 3차</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>밀양고등학교</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 19. ~ 2026. 10. 23.(5일, 17시수)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>밀양고등학교 공고 제2026-36호
+2026학년도 밀양고등학교 전일제 강사 채용 공고
+2026학년도 밀양고등학교에 근무할 전일제 강사를 다음과 같이 채용 공고합니다.
+1. 채용내용 및 응모자격
+가. 채용 교과 및 인원
+1) 과목: 수학(미적분1, 기하, 인공지능수학)
+2) 채용인원: 1명
+3) 채용사유: 특별휴가
+4) 채용기간: 2026. 10. 19. ~ 2026. 10. 23.(5일, 17시수)
+5) 비고: 전일제 강사 일 110,000원
+2. 서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간: 2026. 10. 12.(월) ~ 2026. 10. 14.(수) 16:30까지
+◦ 접수방법: 전자우편(주소: [이메일] 스캔본 제출, 면접 시 원본 제출
+자세한 사항은 첨부파일을 참고</t>
+        </is>
+      </c>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
+      <c r="H13" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814841</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814860</t>
         </is>
       </c>
       <c r="L13" s="5" t="n"/>
@@ -1625,30 +1677,337 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>10월 삼룡초등학교 계약제교원(전일제강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>삼룡초등학교</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.19.~2026.11.06.(3주간)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 10월 삼룡초등학교 계약제교원(전일제강사) 채용 공고
+1. 인원: 초등 전일제강사 1명(6학년담임)
+2. 세부내역
+가. 공고기간: 2026. 10. 12.(월) ~ 10. 15.(목) 12:00까지
+나. 채용과목 및 기간: 초등전일제강사 1명(6학년담임)
+2026.10.19.~2026.11.06.(3주간)
+다. 원서접수
+-접수기간: 2026. 10. 12.(월) ~ 10. 15.(목) 12:00까지
+-접수장소: 삼룡초등학교 교무실(온라인접수만 받음)
+-접수방법: 전자우편(주소: [이메일] 스캔본 제출, 면접 시 원본 제출)
+라. 1차: 서류전형 합격자 발표(개별 전화 통지) 예정일 - 2026. 10. 15.(목) 16시 이후
+마. 2차: 면접예정일 - 2026. 10. 16.(금) 14:00이후(1차 합격자에 한함/개별통보)
+바. 2026. 계약제교원 운영지침에 따른 채용 우선 순위 안내
+1) 1순위 : 만 62세 미만, 초등 자격 소지자
+2) 2순위 : 만 62세 미만, 초등 외 다른 학교급 또는 유사 과목 자격 소지자
+정년퇴직자 및 명예퇴직자
+3. 기타 - 기타 세부 사항은 첨부물 참고</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814870</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>마산가포고등학교 지리과 결원대체강사(1순위: 지리, 2순위: 일반사회, 윤리) 채용 3차 공고</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>마산가포고등학교</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.26.~2026.10.30.(총16시간)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
+1. 채용내용 및 응모자격
+가. 채용과목 및 인원: 지리 1명(1순위: 지리, 2순위: 일반사회, 윤리)
+나. 채용기간: 2026.10.26.~2026.10.30.(총16시간)
+다. 수당: 시간당 35,000원
+라. 응모자격
+1) 1순위: 만 62세 미만의 결원 교원과 동일 학교급 및 과목 자격증 소지자
+2) 2순위: 만 62세 미만의 결원 교원과 다른 학교급 또는 유사 과목* 자격증 소지자, 정년퇴직자 혹은 명예퇴직자
+※ 1차 모집 공고부터 우선순위를 정하여 1순위 지원자가 없을 시 후 순위 지원자 채용 가능
+2. 전형방법
+가. 1차 시험 : 서류전형(채용 예정 인원의 3배수 이내 선발)
+나. 2차 시험 : 면접(1차 서류 전형 합격자에 한하여 실시하며, 대상자에게 개별 통보)
+3. 응시자 제출서류
+가. 응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재)
+나. 자기소개서 1부.(붙임서식)
+다. 계약제교원 채용을 위한 개인정보 수집 이용 동의서 1부.(붙임서식)
+4. 서류접수 및 전형일정
+가. 서류접수
+◦ 접수기간 : 2026. 10. 12.(월) ~ 2026. 10. 15.(목) 12:00까지
+◦ 접수방법 : 온라인접수([이메일] 스캔본 제출, 면접 시 원본제출, 2026. 10. 15.(목) 12:00 발송분까지)
+나. 1차 서류 전형 합격자 발표 : 2026. 10. 15.(목) 15:00 이후(1차 서류 전형 합격자에 한해 개별 통보)
+다. 2차 면접 : 2026. 10. 16.(금) 09:00~
+라. 최종합격자 발표 : 2026. 10. 16.(금) 12:00 이후 개별통보
+5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814899</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>은하수초등학교 결원대체강사(전일제 강사_과학전담_초4) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>은하수초등학교</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.19.-202611.6. *조정 가능</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 2학기 은하수초등학교에 근무할 결원대체강사(전일제 강사_과학전담)를 다음과 같이 채용 공고합니다.
+1. 채용기간: 2026.10.19.-202611.6. *조정 가능
+2. 채용 인원: 1명(과학전담_초4_주14시간)
+3. 지원 자격
+가. 초등교사 또는 중등교사 자격증 소지자
+나. 교원 임용에 결격 사유가 없는 자
+4. 서류 접수 및 전형일정
+가. 공고 및 접수기간 : 2026.10.12.(월)~2026.10.15.(목) 12:00
+나. 원서접수 방법 : 교무실 또는 온라인접수 전자우편([이메일]) 접수
+다. 면접 일시 및 장소: 2026. 10. 16.(금) 10:30 예정, 은하수초등학교
+라. 합격자 발표(개별 통지) 예정일 : 2026. 10. 16.(금) 17:00 이후
+5. 제출서류
+1) 응시원서 1부.(사진첨부, 연락 가능한 전화번호 반드시 기재)
+2) 자기소개서 1부
+*기타 자세한 사항은 첨부파일 참고 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814883</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>호암초등학교 계약제교원(특수 전일제강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>호암초등학교</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 23.(월)~2026. 11. 27.(금)(5일)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>호암초등학교에 근무할 특수 전일제강사를 다음과 같이 채용하고자 합니다.
+1. 채용 과목 및 인원: 특수 1명
+2. 접수기간: 2026. 10. 12.(월)~2026. 10. 15.(목) 까지
+3. 계약기간: 2026. 11. 23.(월)~2026. 11. 27.(금)(5일)
+4. 접수처: 호암초등학교 전자우편([이메일])
+5. 자세한 사항은 첨부파일 참고바랍니다.</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814879</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>태봉고등학교 결원대체시간강사(수학) 채용 공고(2차)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>태봉고등학교</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고(2차)입니다.
+1. 채용과목 및 인원, 채용기간
+가. 채용과목: 수학
+나. 채용인원: 1명
+다. 채용기간: 2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)
+라. 수업시수 및 수당: 총 9시간(주당 6시간)/시간당 26,000원
+2. 서류접수 및 전형일정
+가. 원서접수  ◦ 접수기간 : 2026.10.12.(월)~2026.10.16.(금) 14:00까지(시간내 도착분에 한함)
+◦ 접수장소 : 태봉고등학교 전자우편(주소: [이메일], 스캔본 제출, 면접 시 반드시 원본 제출)
+나. 1차 : 서류전형 합격자 발표(개별 전화 통지) 예정일 : 2026. 10. 19.(월) 14:00 이후
+다. 2차 : 면접전형(서류심사 합격자에 한함) 예정일 : 2026. 10. 20.(화) 11:00 예정
+◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
+라. 최종합격자 발표 : 2026. 10. 21.(수) 10:00 이후(합격자 개별 통보)
+바. 비고: 오전수업만 있음
+※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814861</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>사회과(역사 또는 일반사회 또는 지리) 중등수업지원강사 채용 공고</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>창원상남중학교</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 12. 31.(2학년 역사수업, 주당 7시간, 월요일 2,3,4교시/목요일 1,2,3,4교시)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원상남중학교에서 근무할 중등수업지원강사를 다음과 같이 채용 공고합니다.
 1. 채용과목(인원): 사회(역사 또는 일반사회 또는 지리)(1명)
@@ -1662,49 +2021,49 @@
 *자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814787</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>신문초등학교 초등돌봄교실 특기‧적성 프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>신문초등학교</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 6.(금) ~ 2027. 2. 26.(금)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>신문초등학교에서는 2026학년도 초등돌봄교실 운영과 관련하여 아래와 같이 특기‧적성 프로그램 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 선정 인원: 초등돌봄교실 특기·적성 프로그램 외부강사 1명
@@ -1717,47 +2076,47 @@
 ※ 자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814822</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -1808,53 +2167,53 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H25" s="5" t="n">
         <v>8046</v>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>유목초등학교</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>구체적인 내용은 공고문을 참고바랍니다.
 1. 분야: 특수학급 결원대체강사
@@ -1862,49 +2221,49 @@
 3.기간: 2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n">
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>유목초 특수학급 결원대체강사 채용 공고</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>유목초등학교</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>구체적인 내용은 공고문을 참고바랍니다.
 1. 분야: 특수학급 결원대체강사
@@ -1912,49 +2271,106 @@
 3.기간: 2026.10.6.~2026.10.16.</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n">
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>거제 하청초 방과후학교 개인위탁 외부강사 모집-모듬북(풍물)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>하청초등학교</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>2026년 11월 1일∼2026년 12월 18일</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>모집 세부 사항
+가. 공고 기간: 2026년 10월 12일(월) ∼ 2026년 10월 19일(월)
+나. 서류 접수: 2026년 10월 13일(화) ∼ 2026년 10월 19일(월) 14:00까지
+다. 접수 장소: 하청초등학교 교무실로 본인 직접 접수 또는 전자우편 접수
+※ 전자우편 주소: [이메일]
+※ 하청초등학교 메일 계정에 2026년 10월 19일 14:00 도착분에 한하여 인정함
+라. 합격자 통보
+1) 1차 제안서 평가: 2026년 10월 20일
+1차 제안서 평가 통과자에 한하여 개별통보
+2) 2차 프로그램 운영 능력평가: 2026년 10월 21일 오전 10시 30분
+3) 최종 합격자 발표: 2026년 10월 22일
+바. 계약 기간: 2026년 11월 1일∼2026년 12월 18일
+자세한 사항은 첨부파일 참조.</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814887</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(내서스포츠센터팀)</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 2개분야 3명
 2. 접수기간: 10. 12.(월) 09:00 ~ 10. 19.(월) 18:00
@@ -2020,57 +2436,57 @@
 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>여부</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H29" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>TRX 필라테스</t>
         </is>
       </c>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5003</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>[내서스포츠센터] 프로그램 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>내서스포츠센터팀 공고 제2026-7호
 내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고
@@ -2132,57 +2548,57 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>여부</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>TRX 필라테스</t>
         </is>
       </c>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1704&amp;page=1</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>마산합포스포츠센터 생활체육 프로그램 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(마산합포스포츠센터팀)</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 2개분야 2명
 2. 접수기간: 10. 16.(금) 09:00 ~ 10. 22.(목) 18:00
@@ -2234,53 +2650,152 @@
 11.「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 규정된 죄를 범한 사람으로서 100만원 이상의 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n">
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>합 계</t>
         </is>
       </c>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5006</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>[마산합포스포츠센터] 생활체육 프로그램 도급강사 공개경쟁 모집 공고</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단 채용정보</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 1. ~ 12. 31.</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>마산합포스포츠센터 공고 제2026 - 12호
+마산합포스포츠센터 생활체육 프로그램 도급강사 공개경쟁모집 공고
+마산합포스포츠센터 프로그램 운영을 위한 우수 강사진을 공개 모집하오니 많은 참여 바랍니다.
+2026년 10월 12일
+창원시설공단 마산합포스포츠센터 팀장Ⅰ
+모집인원: 2명 (배분율 참조)
+생활체육 프로그램: 2명(2개 종목)
+모집분야인원요 일시 간
+배분율(%)
+(공단:강사)
+자격요건합 계2명요가1명
+월ㆍ수ㆍ금
+09:10~10:00
+45:55
+- 해당종목 자격증 소지자 중
+지도경력 6개월 이상자
+10:10~11:00
+11:10~12:00
+바레운동1명토
+08:00~08:50
+50:50
+09:00~09:50Ⅱ
+기본(공통)자격
+가. 해당 관련 자격증 소지자 중 해당 경력 6개월 이상인 자(19세 이상)
+➟ 중복지원 가능 / 중복 지원 시 응시서류는 각각 제출(동일 시간대 불가)
+➟ 응시 자격에 보조강사가 있는 경우 지원강사 본인 외 보조강사 지원 서류 동일 제출
+나. 남성의 경우 병역법상 문제가 없는 자(병역기피 사실이 없는 자)
+다. 아동 청소년의 성보호에 관한 법률 시행령에 의거 성범죄의 해당자는 선발될 수 없음.
+라. 도급강사 운영계약 지침 제12조 결격사유에 해당하지 않는 자
+제12조(결격사유) 다음 각 호의 어느 하나에 해당하는 자는 도급강사로 계약할 수 없다.
+1. 피성년후견인
+2. 파산선고를 받은 자로서 복권되지 아니한 자
+3. 금고 이상의 형을 선고받고 그 집행이 끝나거나 집행을 받지 아니하기로 확정된 후 5년이 지나지 아니한 자
+4. 금고 이상의 형을 선고받고 그 집행유예기간이 끝난 날부터 2년이 지나지 아니한 자
+5. 금고 이상의 형의 선고유예를 선고받고 그 선고유예기간 중에 있는 자
+6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 자
+7. 징계로 파면처분을 받은 날부터 5년이 지나지 아니한 자
+8. 징계로 해임처분을 받은 날부터 3년이 지나지 아니한 자
+9. 부패방지 및 국민권익위원회의 설치와 운영에 관한 법률 제82조에 따른 비위면직자 등의 취업제한 적용을 받는 자
+10. 재직기간 중 직무와 관련하여 「형법」 제355조 및 제356조에 규정된 죄를 범한 사람으로서 300만원 이상의 벌금형을 선고받고 그 형이 확정된 후 2년이 지나지 아니한 사람
+11.「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 규정된 죄를 범한 사람으로서 100만원 이상의 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람
+12. 미성년자에 대한 다음 각 목의 어느 하나에 해당하는 죄를 저질러 파면ㆍ해임되거나 형 또는 치료감호를 선고받아 그 형 또는 치료감호가 확정된 사람(집행유예를 선고받은 후 그 집행유예기간이 경과한 사람을 포함한다)
+가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄
+나. 「아동ㆍ청소년의 성보호에 관한 법률」 제2조제2호에 따른 아동ㆍ청소년대상 성범죄Ⅲ
+전형일정 및 방법
+가. 전형일정
+▸ 모집공고: 2026. 10. 12. ~ 10. 22.
+▸ 모집절차구분
+접수기간</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>합 계</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1706&amp;page=1</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>웅남중 학교운동부지도자 채용공고(태권도)</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>웅남중학교</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>2026.12.01.(화)~2027.2.28.(일)</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>웅남중학교 운동부 지도자 채용 공고
 - 채용분야: 운동부지도자
@@ -2293,98 +2808,196 @@
 자세한 사항은 붙임 문서를 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814764</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[늘푸른전당] 프로그램 도급강사 공개경쟁 모집 공고</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단 채용정보</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>늘푸른전당 공고 제2026-10호
+늘푸른전당 생활체육 프로그램 도급강사 공개모집 공고
+늘푸른전당 프로그램 운영을 위한 우수 강사진을 공개 모집하오니
+많은 참여 바랍니다.
+2026년 10월 13일
+창원시설공단 늘푸른전당팀장Ⅰ
+모집인원 : 1명
+프로그램 : 기구필라테스종 목모집인원
+강 습 일
+운 영 시 간배분율
+(공단:강사)
+자 격 요 건기 구
+필라테스1명
+월·수금/화·목
+15:00~15:50
+50:50
+‣ 관련종목 자격증 소지자 중 해당 종목지도경력 6개월 이상인자
+16:00~16:50
+※ 자격증은 원수접수 마감일로부터 계약 종료일까지 유효하여야 함.Ⅱ
+기본(공통)자격
+만 18세 이상인 자로서 응시자격을 충족하는 자
+해당 종목 관련 자격증 소지자 중 해당 경력 6개월 이상인 자
+아동·청소년의 성 보호에 관한 법률에 의거 성범죄의 해당자는 선발할 수 없음
+도급강사 운영계약 지침 제12조 결격사유에 해당하지 않는 자
+제12조(결격사유) 다음 각 호의 어느 하나에 해당하는 자는 도급강사로 계약할 수 없다.
+1. 피성년후견인
+2. 파산선고를 받은 자로서 복권되지 아니한 자
+3. 금고 이상의 형을 선고받고 그 집행이 끝나거나 집행을 받지 아니하기로 확정된 후 5년이 지나지
+아니한 자
+4. 금고 이상의 형을 선고받고 그 집행유예기간이 끝난 날부터 2년이 지나지 아니한 자
+5. 금고 이상의 형의 선고유예를 선고받고 그 선고유예기간 중에 있는 자
+6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 자
+7. 징계로 파면처분을 받은 날부터 5년이 지나지 아니한 자
+8. 징계로 해임처분을 받은 날부터 3년이 지나지 아니한 자
+9. 부패방지 및 국민권익위원회의 설치와 운영에 관한 법률 제82조에 따른 비위면직자 등의
+취업제한 적용을 받는 자
+10. 재직기간 중 직무와 관련하여 「형법」 제355조 및 제356조에 규정된 죄를 범한 사람
+으로서 300만원 이상의 벌금형을 선고받고 그 형이 확정된 후 2년이 지나지 아니한 사람
+11. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 규정된 죄를 범한 사람으로서 100만
+원 이상의 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람
+12. 미성년자에 대한 다음 각 목의 어느 하나에 해당하는 죄를 저질러 파면ㆍ해임되거나 형 또는 치료감
+호를 선고받아 그 형 또는 치료감호가 확정된 사람(집행유예를 선고받은 후 그 집행유예기간이 경과한
+사람을 포함한다)
+가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄
+나. 「아동ㆍ청소년의 성보호에 관한 법률」 제2조제2호에 따른 아동ㆍ청소년대상 성범죄Ⅲ
+전형일정 및 방법
+계약기간: 2026. 11. 1. ~ 12. 31.(2개월)
+※ 1. 공사 및 휴장 등으로 인해 프로그램 운영이 어려울 시 계약기간이 변경될 수 있음
+2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가
+적용하는 감면금액 적용 후 부가가치세를 공제한 금액으로 배분하여
+강사의 수입금 중 사업소득세를 공제한 금액을 지급한다.
+전형일정</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1694&amp;page=1</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>2026.10.1.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명
 2. 기간: 2026.10.1.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>김해율하도서관 2027년 율하아카데미 교육강사 채용 공고</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>2027. 2. ~ 2027. 11.(3학기 기준)</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>김해율하도서관 2027년 율하아카데미 교육강사 채용을 위하여 붙임의 고시공고를 홈페이지에 게제하고자 합니다.
 김해시청 제2026-4441호
@@ -2426,53 +3039,154 @@
 미술·체험·놀이(6)</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="H36" s="5" t="n">
         <v>6448</v>
       </c>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110418&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[마산회원체육센터] 기간제(초단시간)근로자 공개경쟁채용 공고(수영강사)</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단 채용정보</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 1. ~ 12. 31.</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>마산회원체육센터팀 공고 제2026-14호
+기간제(초단시간)근로자 공개경쟁 채용공고
+마산회원체육센터 기간제(초단시간)근로자를 다음과 같이 공개 모집 합니다.
+2026년 10월 12일
+창원시설공단 마산회원체육센터팀 팀장Ⅰ
+채용분야 및 인원: 1개분야 1명
+가. 채용분야
+- 기간제(초단시간)근로자: 주 소정근로시간 15시간 미만 / 월 60시간 미만구 분
+채용인원
+근무시간
+근무요일
+담당업무
+단가(시급)
+수영강습1명
+06:00 ~ 08:00
+월 ~ 금
+수영강습
+18,000원
+(1시간)
+※ 보수기준: 2026년 기간제근로자 관리·운영 지침에 의한 임금기준 적용
+나. 분야별 자격요건구 분
+자 격 요 건
+공통자격
+⁍ 성별, 학력 제한 없음
+⁍ 만 18세 이상
+⁍ 남성의 경우 병역법상 문제가 없는 자(병역기피 사실이 없는 자)
+⁍ 공무직 및 기간제 근로자 관리규정 제11조 채용 결격사유에 해당하지 않는 자
+수영강습
+(초단시간)
+⁍ 생활/전문/노인/유소년 스포츠지도사 2급(수영)이상 또는 수상
+안전요원 또는 수상구조사 자격증 소지자
+단, 수상안전요원 또는 수상구조사 자격증 소지 시 강습경력 3개월 이상 필요
+※ 경력인정 범위
+- 공단 수영강사 양성 아카데미 수료자 강습 경력 3개월 인정 ⇒ 수료확인서 제출
+- 대한수영연맹 선수등록 기간 강습 경력 인정 ⇒ 경력증명서 제출
+※ 자격증은 원서접수 마감일로부터 고용계약 종료일까지 유효하여야 함
+다. 근 무 지: 마산회원체육센터 올림픽수영장
+라. 계약기간: 2026. 11. 1. ~ 12. 31.Ⅱ
+기본(공통)자격
+가. 성별 및 학력 제한 없음
+나. 만18세 이상
+다. 남성의 경우 병역법상 문제가 없는 자(병역기피 사실이 없는 자)
+라. 공단 공무직 및 기간제 근로자 관리규정 제11조 채용 결격 사유에 해당하지 않는 자
+마. 공단 인사규정 제14조 채용 결격사유에 해당하지 않는 자
+제14조 (결격사유) 다음 각호의 1에 해당하는 자는 직원이 될 수 없다.
+1. 「지방공무원법」제31조 각 호에 해당하는 사람
+지방공무원법 제31조(결격사유) 다음 각 호의 어느 하나에 해당하는 사람은 공무원이 될 수 없다.
+1. 피성년후견인
+2. 파산선고를 받고 복권되지 아니한 사람
+3. 금고 이상의 실형을 선고받고 그 집행이 끝나거나(집행이 끝난 것으로 보는 경우를 포함한다) 집행이 면제된 날부터 5년이 지나지 아니한 사람
+4. 금고 이상의 형의 집행유예를 선고받고 그 집행유예기간이 끝난 날부터 2년이 지나지 아니한 사람
+5. 금고 이상의 형의 선고유예를 선고받고 그 선고유예기간 중에 있는 사람
+6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 사람
+6의2. 공무원으로 재직기간 중 직무와 관련하여 「형법」 제355조및 제356조에 규정된 죄를 범한 사람으로서 300만원 이상의 벌금형을 선고받고 그 형이 확정된 후 2년이 지나지 아니한 사람
+6의3. 다음 각 목의 어느 하나에 해당하는 죄를 범한 사람으로서 100만원 이상의 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1707&amp;page=1</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>유영초등학교</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~2026.10.30.(19일간)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 초등 결원대체 강사(전일제)
 2. 채용 인원: 1명
@@ -2480,49 +3194,101 @@
 4. 자세한 사항은 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n">
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>전일제 강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>창원천광학교</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>2026. 10. 16.~11. 6.(16일)</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 창원천광학교에서 근무할 중등 전일제 강사를 채용 공고합니다.
+1.채용과목: 중등특수
+2.채용인원: 1명
+3.채용기간: 2026. 10. 16.~11. 6.(16일)
+4.접수방법:전자우편 접수( [이메일] )
+기타 자세한 사항은 첨부파일을 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814884</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>안의고등학교 역사, 국어과 결원대체강사 채용 공고</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>안의고등학교</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>국어-2026.11.23.(월)~2026.11.27.(금) (5일)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>안의고등학교 결원대체강사 채용 공고
 2026학년도 안의고등학교에 근무할 결원대체강사(전일제/시간제)를 다음과 같이 채용 공고합니다.
@@ -2570,53 +3336,53 @@
 ◦ 제출서류의 기재 착오, 누락, 서류 미제출, 연락 불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>1순위: 만 69세 미만 동일 자격 소지자
 2순위: 다른 학교급 또는 유사과목 자격 소지자, 명예퇴직자, 정년퇴직자
 (1순위 지원자가 있을 경우 2순위는 심사 대상에서 제외)</t>
         </is>
       </c>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814832</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>남지초등학교</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등기간제교원
 나. 채용 기간: 2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)
@@ -2629,49 +3395,97 @@
 ※자세한 사항은 공고문 참고</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n">
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교 전일제 강사(과학-생명과학 우대) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>2026.11.2.~2026.11.27.(20일)</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>1.과목 및 인원-과학 (생명과학 우대): 1명
+2.채용기간:2026.11.2.~2026.11.27.(20일)
+*비고:임용일에 따라 채용기간변동
+기타 자세한 사항은 첨부파일을 확인하시고 문의사항은 마산고 교무실([전화번호])으로 연락바랍니다.</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814898</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>칠원고등학교</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
 1. 채용과목: 영어(1명)
@@ -2679,49 +3493,100 @@
 상세내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n">
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>결원대체강사(시간강사) 채용 2차 재공고(영어)</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>칠원고등학교</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>11. 16.~11. 17.(8시간), 11. 23.~12. 11.(주당 15시간)</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 결원대체강사(시간강사) 채용 2차 재공고합니다.
+1. 채용과목: 영어(1명)
+2. 채용기간: 11. 16.~11. 17.(8시간), 11. 23.~12. 11.(주당 15시간)
+상세내용은 첨부파일 참고바랍니다.
+문의 ([전화번호]</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814868</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -2776,15 +3641,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H45" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -2794,40 +3659,93 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>창원여고 전일제강사(보건) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>창원여자고등학교</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 창원여고 전일제강사(보건)를 다음과 같이 채용하고자 합니다.
+1. 채용 인원-보건(1명): 2026. 10.14 ~ 2026.10.19.(전일제강사)4일,일당110,000원
+2.접수기간: 2026. 10. 12(월) ~ 2026. 10.13.(화) 11:00까지
+3. 접수방법: 전자우편(주소: [이메일], 2026. 10.13. 11:00 발송분까지)
+*자세한 내용은 채용공고 참고바랍니다.</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814864</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>산양초등학교 돌봄교실 특기적성 프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>산양초등학교</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>본교 돌봄교실 운영과 관련하여 특기적성 프로그램 개인 위탁 강사님을 모시고자 하오니,  관심있으신 분들의 지원을 바랍니다.
 1. 모집분야: 보드게임 1명
@@ -2836,53 +3754,102 @@
 4. 기타 자세한 사항은 첨부파일 공고문을 참고 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814814</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80004</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>교원 장기재직 휴가 대체 시간 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>삼천포여자중학교</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>2026 교원 장기재직 휴가 대체 시간 강사 채용 계획을 붙임과 같이 공고합니다.
 1. 채용내용: 장기재직 휴가 데체 시간 강사(과학)
@@ -2894,51 +3861,51 @@
 마. 최종 합격자 발표: 10. 16.(금) 16:00 이후 개별 통보</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814790</t>
         </is>
       </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 재공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -2954,53 +3921,109 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n">
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814852</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="O50" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>천성초(영어저학년)방과후학교 개인위탁 외부강사 재모집 공고</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>천성초등학교</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>천성초등학교에서는 방과후학교 프로그램(영어저학년) 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
+&lt;모집분야&gt;  영어저학년(대상학년  : 1~2학년. 요일 : 화, 목)
+1) 접수기간 : 2026.10.12.(월)~2026.10.14.(수) 16:00까지
+2) 접수방법 : 전자우편( chyj1010 @ korea.kr )제출 및 직접제출( 26. 10. 14.(수) 16시 발송분까지)
+2) 서류심사 : 2026.10.15.(목) 1차 제안서 평가 통과자에 한하여 개별 통보
+3) 면접심사 : 2026.10.20.(화) 10:30
+4) 합격자통보 : 2026.10.21.(수) 10:00  이후 (개별통보)
+※ 자세한 사항 및 필요 제출서류는 첨부파일을 확인하시고 기한내에 제출해 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814875</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집공고(수학)</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>거제고현중학교</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>★  모집 세부 사항
 가. 공고 기간: 2026.10.7.(수)~2026.10.14.(수)
@@ -3016,51 +4039,51 @@
 다. 방과후학교 개인위탁 외부강사 활동에 제한이 없는 자</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814746</t>
         </is>
       </c>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>진주고등학교 계약제교원(시간제강사-일본어) 채용 공고</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>진주고등학교</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목 및 인원
 시간제강사 - 일본어 1명
@@ -3112,51 +4135,143 @@
 **************** 보다 자세한 사항은 첨부파일을 꼭 확인하여 주시기 바랍니다. ******************</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814820</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>장애인일자리(복지일자리) 수행기관 모집</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>의령군</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>경남 의령군</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>취업 취약계층인 장애인에게 일자리 제공을 통한 사회참여 확대 및 소득지원을 위하여 장애인일자리사업 수행기관을 공개모집합니다.
+의령군 공고 제2026-1185
+장애인일자리사업(복지일자리) 수행기관 모집 공고
+취업 취약계층인 장애인에게 일자리 제공을 통한 사회참여 확대 및 소득지원을 위하여 장애인일자리사업 수행기관을 다음과 같이 공개모집합니다.
+2026. 10. 12. ~ 10. 15.
+의 령 군 수
+1. 수행사업 : 장애인일자리사업(복지일자리)
+※ 장애인 편의시설 모니터링 사업 포함
+2. 위탁기간 : 2026. 11. 1. ~ 2029. 10. 31. (3년간)
+3. 신청자격 : 의령군에 소재하며 아래 기준을 갖춘 단체 또는 법인
+❍ 「장애인복지법」 제54조에 따른 장애인자립생활지원센터
+❍ 「장애인복지법」 제58조에 따른 장애인복지관
+❍ 「장애인복지법」 제63조에 따른 장애인복지단체
+❍ 「비영리민간단체지원법」에 따른 비영리민간단체 중 장애인 관련 단체
+4. 사업내용
+❍ 장애인일자리(복지일자리) 참여 장애인 모집·선발
+- 심한장애인 맞춤형 직무(11개)를 포함하여 사업 수행이 가능함
+구분심한장애인 맞춤형 직무직무명▶ 문화예술 활동 ▶ 온라인콘텐츠 모니터링 ▶ 장애인전용주차구역 계도 및 홍보 ▶ 정신장애특화 동료지원 활동 ▶ 알기 쉬운 자료 감수▶ 장애인 편의시설 모니터링▶ 인식개선교육 보조강사▶ 사회서비스사업 모니터링▶ 디앤디케어▶ 농-농케어▶ 홍보지원 업무구분
+심한장애인 맞춤형 직무직무명
+▶ 문화예술 활동
+▶ 온라인콘텐츠 모니터링
+▶ 장애인전용주차구역 계도 및 홍보
+▶ 정신장애특화 동료지원 활동
+▶ 알기 쉬운 자료 감수
+▶ 장애인 편의시설 모니터링
+▶ 인식개선교육 보조강사
+▶ 사회서비스사업 모니터링
+▶ 디앤디케어
+▶ 농-농케어
+▶ 홍보지원 업무
+❍ 장애인일자리 참여자 배치·복무 관리(안전교육, 급여 지급 등)
+❍ 사업실적 전산시스템 입력 및 보고
+❍ 일자리 참여자 상담, 고충 처리 및 취업지원 연계 등 사업 일체
+❍ 위탁협약서상의 제반규정 및 위탁기관 지시사항 등
+※ 2027년 장애인일자리(복지일자리) 채용부터 위탁 시행
+[참고] 2027년 장애인일자리사업(복지일자리)
+❍ 참여기간: 2027. 1. ~ 12. (12개월)
+❍ 참여인원: 34명 ※ 복지일자리 33명, 장애인 편의시설 모니터링 1명
+❍ 예산규모: 266,880천원(복지일자리 246,680, 장애인 편의시설 모니터링 20,200)
+❍ 근무시간: 주 14시간 이하(월 56시간이내)
+※ 장애인 편의시설 모니터링 주 25시간 월 100시간
+❍ 보 수: 월 599,200원 ※ 장애인 편의시설 모니터링 1,291,660원
+※ 상기 내용은 향후 변동될 수 있음
+5. 신청접수
+❍ 재공고 및 접수기간: 2026. 10. 12. ~ 10. 15.(3일간)
+❍ 접 수 처: 의령군청 주민생활지원과 장애인복지팀 (☎[전화번호])
+❍ 접수방법: 방문접수(우편 접수 불가)
+※ 평일 근무시간(평일 09:00~18:00) 내 직접 방문 접수</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -3170,51 +4285,137 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>진해신항초등학교 계약제교원(전일제강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>진해신항초등학교</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 진해신항초등학교 계약제교원(전일제강사) 다음과 같이 채용 공고합니다.
+◆ 채용내용
+가. 채용기간 및 채용인원: 1명- 전일제강사: 2026. 10. 26.~ 2027. 11. 13. 1명(5학년)
+◆ 전형방법
+가. 1차 전형: 서류전형(서류전형 합격한 자에 한하여 2차 전형 대상자 개별 통보)
+나. 2차 전형: 면접
+◆ 제출서류
+가. 응시자 제출서류
+◦ 응시원서 1부(붙임 서식, 사진 첨부, 연락 가능한 전화번호 반드시 기재)
+◦ 자기소개서 1부(붙임 서식)
+◦ 개인정보 수집·이용에 대한 동의서(붙임 서식)
+나. 최종합격자 제출서류
+◦ 교사 자격증 사본 또는 자격 인정 조서 1부
+◦ 졸업증명서 사본 1부(원본지참)
+◦ 주민등록 초본 1부
+◦ 공무원채용신체검사서(1년 이내) 1부
+◦ 잠복결핵검사 확인서 1부(최초 검사의 확인서를 계속 사용 가능)
+◦ 마약/대마/향정신성의약품 검사결과통보서(진단서) 1부
+◦ 초임호봉획정을 위한 경력기간 합산신청서 1부
+◦ 범죄경력조회동의서 1부
+◦ 가족 채용 제한 여부 확인서 1부
+◦ 청렴 서약서 1부
+◆ 서류접수 및 전형일정
+가. 원서접수
+◦ 접수기간: 2026. 10. 12.(월)~10. 16.(금) 10:00까지
+◦ 접수방법: 온라인 접수- 메일주소: [이메일] 스캔파일 제출(제출서류 미비시 접수 불가), 면접 시 해당 서류 원본 제출
+나. 1차: 류전형 합격자(만 개별 전화 통지) 발표 예정일 &gt; 2026. 10. 16.(금), 10:00 이후
+다. 2차: 면접(서류심사 합격자에 한함) 예정일 &gt; 2026. 10. 19.(월) 16:00, 교무실
+◦ 일시 및 장소는 서류전형 합격자에게만 개별 통보
+6. 합격자 발표◦ 최종합격자 발표: 2026. 10. 19.(뤟) 18:00 이후 (최종합격자에게만 개별 통지)
+7. 유의사항
+◦ 인력풀 등재자는 우선 임용될 수 있습니다.
+◦ 인력풀 등재자는 최종합격 후 확인이 불가능한 서류만 제출합니다.
+◦ 상기 일정은 진행 상황에 따라 변경될 수 있으며, 변경 시 별도 통보합니다.
+◦ 기재사항이 사실과 다르거나 허위로 작성된 경우는 합격을 취소합니다.
+◦ 제출 서류의 기재착오, 누락, 서류 미제출, 연락 불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.
+◦ 최종합격자로 발표된 이후에도 결격사유가 있는 자는 합격을 취소할 수 있습니다.
+◦ 기타 자세한 사항은 진해신항초등학교(☎551-2018)로 문의하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814873</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교(직업교육 혁신지구 전공심화연구동아리 멘토 교육(전기제어) 외부강사) 모집 공고</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교 공고 제2026 – 65호
 2026학년도 마산공업고등학교에 근무할 전공심화연구동아리 멘토 교육(전기제어) 외부 강사 모집을 다음과 같이 공고 합니다.
@@ -3240,53 +4441,53 @@
 * 자세한 사항은 붙임 공고문을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n">
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814792</t>
         </is>
       </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="O57" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -3298,53 +4499,249 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n">
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
         </is>
       </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>계약제 교원(결원대체강사-전일제강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>대청초등학교</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>계약제 교원(결원대체강사-전일제강사) 담임교사</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814892</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80264</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>김해시도시개발공사 장유스포츠센터팀 배분제 위탁강사(배드민턴) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>김해시도시개발공사</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>경남 김해시</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>1. 배드민턴강습 및 고객 관리</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80275</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 55) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>용원국민체육센터 생활체육 도급강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80216</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 위탁운영 단체(법인) 모집 공고</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>고성군</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>경남 고성군</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 재개장을 앞두고 해당 시설의 운영 및 관리를 위한 위탁운영 단체(법인)을  모집하고자 첨부와 같이 공고합니다.
 고성군 공고 제2026-1750호
@@ -3376,106 +4773,261 @@
 &lt; 청소년단체 &gt;</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="O63" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>마산회원체육센터 기간제(초단시간)근로자 공개경쟁 채용공고</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단(마산회원체육센터팀)</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 1. ~ 12. 31.</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>1. 모집인원: 1개분야 1명
+2. 접수기간: 10. 19.(월) 09:00 ~ 10. 23.(금) 18:00
+3. 접수방법: 방문접수(※ 우편접수 불가, 토ᆞ일요일 및 공휴일 접수 불가)
+4. 접 수 처
+- 올림픽기념관 지하 1층 수영강사실
+5. 문 의 처 : [전화번호]
+※ 자세한 내용과 제출서류는 붙임 문서 참고 바랍니다.
+마산회원체육센터팀 공고 제2026-14호
+기간제(초단시간)근로자 공개경쟁 채용공고
+마산회원체육센터 기간제(초단시간)근로자를 다음과 같이 공개 모집 합니다.
+2026년 10월 12일
+창원시설공단 마산회원체육센터팀 팀장Ⅰ
+채용분야 및 인원: 1개분야 1명
+가. 채용분야
+- 기간제(초단시간)근로자: 주 소정근로시간 15시간 미만 / 월 60시간 미만구 분
+채용인원
+근무시간
+근무요일
+담당업무
+단가(시급)
+수영강습1명
+06:00 ~ 08:00
+월 ~ 금
+수영강습
+18,000원
+(1시간)
+※ 보수기준: 2026년 기간제근로자 관리·운영 지침에 의한 임금기준 적용
+나. 분야별 자격요건구 분
+자 격 요 건
+공통자격
+⁍ 성별, 학력 제한 없음
+⁍ 만 18세 이상
+⁍ 남성의 경우 병역법상 문제가 없는 자(병역기피 사실이 없는 자)
+⁍ 공무직 및 기간제 근로자 관리규정 제11조 채용 결격사유에 해당하지 않는 자
+수영강습
+(초단시간)
+⁍ 생활/전문/노인/유소년 스포츠지도사 2급(수영)이상 또는 수상
+안전요원 또는 수상구조사 자격증 소지자
+단, 수상안전요원 또는 수상구조사 자격증 소지 시 강습경력 3개월 이상 필요
+※ 경력인정 범위
+- 공단 수영강사 양성 아카데미 수료자 강습 경력 3개월 인정 ⇒ 수료확인서 제출
+- 대한수영연맹 선수등록 기간 강습 경력 인정 ⇒ 경력증명서 제출
+※ 자격증은 원서접수 마감일로부터 고용계약 종료일까지 유효하여야 함
+다. 근 무 지: 마산회원체육센터 올림픽수영장
+라. 계약기간: 2026. 11. 1. ~ 12. 31.Ⅱ
+기본(공통)자격
+가. 성별 및 학력 제한 없음
+나. 만18세 이상
+다. 남성의 경우 병역법상 문제가 없는 자(병역기피 사실이 없는 자)
+라. 공단 공무직 및 기간제 근로자 관리규정 제11조 채용 결격 사유에 해당하지 않는 자
+마. 공단 인사규정 제14조 채용 결격사유에 해당하지 않는 자
+제14조 (결격사유) 다음 각호의 1에 해당하는 자는 직원이 될 수 없다.
+1. 「지방공무원법」제31조 각 호에 해당하는 사람
+지방공무원법 제31조(결격사유) 다음 각 호의 어느 하나에 해당하는 사람은 공무원이 될 수 없다.
+1. 피성년후견인
+2. 파산선고를 받고 복권되지 아니한 사람
+3. 금고 이상의 실형을 선고받고 그 집행이 끝나거나(집행이 끝난 것으로 보는 경우를 포함한다) 집행이 면제된 날부터 5년이 지나지 아니한 사람
+4. 금고 이상의 형의 집행유예를 선고받고 그 집행유예기간이 끝난 날부터 2년이 지나지 아니한 사람
+5. 금고 이상의 형의 선고유예를 선고받고 그 선고유예기간 중에 있는 사람
+6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 사람</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5007</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
         </is>
       </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>창녕군장애인체육회 장애인생활체육지도자 채용 공고</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>창녕군</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>경남 창녕군</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>율하중학교</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -3486,51 +5038,151 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+      <c r="K67" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O67" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>의령군 청년 일경험(인턴) 지원사업 참여기업 모집</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>의령군</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>경남 의령군</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>최소 3개월 이상 / 주 5일, 일 8시간 근무 원칙(주 40시간, 조정 가능)</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>2026년 의령군 청년 일경험(인턴) 지원사업 참여기업 모집 재공고를 [홈페이지]에 게재하고자 합니다.
+1. 사 업 명: 2026년 의령군 청년 일경험(인턴) 지원사업
+2. 모집기간: 2026. 10. 13.(화) ~ 11. 16.(월)
+3. 모집대상: 관내 청년을 신규 채용할 의사가 있는 의령군 소재 기업
+4. 모집개소: 2개소(실 사업량: 청년 2명)
+5. 지원내용: 청년 일경험 기회 제공 사업장에 지원
+- 일경험수당: 월 150만원/인×3개월
+- 멘토수당: 월 5만원/인×3개월
+붙임  2026년 의령군 청년 일경험(인턴) 지원사업 참여기업 모집
+의령군 공고 제2026-1186호
+2026년 의령군『청년 일경험(인턴)지원사업』참여기업 모집 재공고
+미취업 청년들의 실무경험을 통한 취업역량 강화를 위해「2026년 의령군
+청년 일경험(인턴) 지원사업」참여기업을 다음과 같이 모집 재공고합니다.
+2026. 10. 12.
+의 령 군 수
+모집개요
+가. 사 업 명: 2026년 의령군 청년 일경험(인턴) 지원사업
+나. 모집기간: 2026. 10. 13.(화) ~ 11. 16.(월)
+다. 모집대상: 의령군 소재 기업
+라. 모집개소: 2개소 ※실 사업량: 청년 2명
+- 선정된 기업이 자격요건에 해당하는 청년을 직접 채용
+마. 지원내용: 청년 일경험 기회 제공 사업장에 지원
+- 일경험 수당: 월 150만원/인 ✕ 3개월
+- 멘 토 수 당: 월 5만원/인 ✕ 3개월
+신청자격
+가. 신청대상
+(기 업) 관내 청년을 신규 채용할 의사가 있는 의령군 소재 기업
+- 소 재 지: 사업자등록증 소재지 기준
+- 구인활동: 공고일 이후, 워크넷을 통한 구인 등록 1회 이상 (15일이상) 필수 이행
+- 상시근로자: 3인 이상 기업(고용보험 피보험자 수 기준)
+(청 년) 18세 이상 39세 이하이며 해당 사업 참여일 기준 의령군에 주민등록이 되어 있는 미취업 청년
+※ 사업 참여기간 동안 의령군에 주민등록 유지, 타 지역에 주소를 둔 경우
+사업 참여 1개월 이내 전입 시 가능(1개월 이내 미전입 시 참여배제 및 수당 미지급)
+※ 해당 기업 선정 후 채용된 청년
+나. 청년 직무내용 및 근로조건
+- 직무내용: IT, 사무경영 등 직무보조 수준이 아닌 취업에 연계 가능한 실제 직무
+- 채용기간: 최소 3개월 이상
+- 인턴급여: 최저임금 이상 지급(월급제 기준 최소 2,156,880원)
+- 근무시간: 주 5일, 일 8시간 근무 원칙(주 40시간, 조정 가능)
+- 4대 사회보험 의무 가입, 근로기준법 및 노동관계법 등 준수
+다. 지원제외
+- 참여 제한 업종 및 직무에 해당하는 경우(붙임 1)
+- 국가 또는 다른 지방자치단체로부터 동일·유사 사업 등에 의한인건비를 지원받는 청년
+신청방법 및 제출서류
+가. 신청기간: 2026. 10. 13.(화) ~ 11. 16.(월)
+나. 신청방법: 의령군 경제기업과 일자리팀 방문 및 등기우편 접수
+(문의 ☎[전화번호])
+다. 제출서류(1~7번 필수, 8~9번 선택)</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n"/>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>발급 및 작성요령, 비고, 1, 사업 참여 신청서, 사업자등록증 첨부, (고유번호증), 서식 1호, 2</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
+          <t>강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -3582,47 +5234,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O69" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -3634,51 +5286,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="n"/>
+      <c r="K70" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O70" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F71" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -3695,97 +5347,97 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O71" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="n"/>
+      <c r="N72" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O72" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>함양제일고등학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>10.26.(월)-11.11.(수)/ 총58시간</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
 1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
@@ -3794,96 +5446,96 @@
 -자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="5" t="n"/>
+      <c r="K73" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="L73" s="5" t="n"/>
+      <c r="M73" s="5" t="n"/>
+      <c r="N73" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O73" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>마산고등학교</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="5" t="n"/>
+      <c r="K74" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
+      <c r="N74" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O74" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>대암초등학교</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -3903,49 +5555,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n">
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="5" t="n"/>
+      <c r="K75" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="L75" s="5" t="n"/>
+      <c r="M75" s="5" t="n"/>
+      <c r="N75" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="O75" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -3954,225 +5606,225 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="5" t="n"/>
+      <c r="I76" s="5" t="n"/>
+      <c r="J76" s="5" t="n"/>
+      <c r="K76" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
         </is>
       </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="L76" s="5" t="n"/>
+      <c r="M76" s="5" t="n"/>
+      <c r="N76" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="O76" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="5" t="n"/>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="n"/>
+      <c r="K77" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
         </is>
       </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="L77" s="5" t="n"/>
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O77" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>일운초등학교</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="n"/>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
         </is>
       </c>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="L78" s="5" t="n"/>
+      <c r="M78" s="5" t="n"/>
+      <c r="N78" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O54" s="5" t="inlineStr">
+      <c r="O78" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>함안고등학교</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
 자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="5" t="n"/>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="5" t="n"/>
+      <c r="K79" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
         </is>
       </c>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="L79" s="5" t="n"/>
+      <c r="M79" s="5" t="n"/>
+      <c r="N79" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="O79" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>고성군</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>경남 고성군</t>
         </is>
       </c>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="inlineStr">
         <is>
           <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
         </is>
       </c>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="5" t="n"/>
+      <c r="L80" s="5" t="n"/>
+      <c r="M80" s="5" t="n"/>
+      <c r="N80" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
+      <c r="O80" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>소토초등학교 한국어교육 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>소토초등학교</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -4194,96 +5846,96 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="5" t="n"/>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="5" t="n"/>
+      <c r="K81" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="L81" s="5" t="n"/>
+      <c r="M81" s="5" t="n"/>
+      <c r="N81" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="O81" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="5" t="n"/>
+      <c r="I82" s="5" t="n"/>
+      <c r="J82" s="5" t="n"/>
+      <c r="K82" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
         </is>
       </c>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="L82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
+      <c r="N82" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="O82" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>진영중앙초 2학기 집중돌봄 특기적성 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>진영중앙초등학교</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>월,수/수,금/월,금 선택가능(주2회, 총 4차시)</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr">
         <is>
           <t>1. 모집 분야 및 인원
 가. 모집분야: 창의놀이(예: 영어놀이, 음악놀이, 미술놀이, 보드게임, 마술 등)
@@ -4294,216 +5946,321 @@
 3. 문의사항: 돌봄교실 [전화번호](11시~18시)</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n">
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="5" t="n"/>
+      <c r="K83" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814812</t>
         </is>
       </c>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="O83" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>돌봄·방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>능포초등학교</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>돌봄·방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="5" t="n"/>
+      <c r="I84" s="5" t="n"/>
+      <c r="J84" s="5" t="n"/>
+      <c r="K84" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814781</t>
         </is>
       </c>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="L84" s="5" t="n"/>
+      <c r="M84" s="5" t="n"/>
+      <c r="N84" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="O84" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>함안군 민방위 교육 강사 위촉대상자 공고</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>함안군</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>경남 함안군</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>2026년 함안군 민방위 교육 강사 위촉대상자를 붙임과 같이 공고합니다.
-함안군 공고 제2026-1233호
-2026년 함안군 민방위 교육 강사 위촉대상자 공고
-2026년도 함안군 민방위 교육 강사 위촉대상자를 다음과 같이 공고합니다.
-2026년 10월 8일
-함안군수
-위촉대상자 명단
-위촉대상자 명단
-분야성명비고기본교육이*호민방위 기본실전훈련남*풍화재예방실전훈련정*영응급처치실전훈련강*훈화생방분야성명비고
-기본교육이*호
-민방위 기본
-실전훈련남*풍
-화재예방
-실전훈련정*영
-응급처치
-실전훈련강*훈화생방
-1. 채용과 관련된 사항은 최종합격자에게 개별 통지할 예정이며,
-2. 기타 문의사항은 안전총괄과 안전관리담당(☎[전화번호])으로 문의하시길바랍니다.</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="n"/>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
-      <c r="N61" s="5" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>[용원국민체육센터]생활체육 도급강사 공개경쟁모집 공고</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단 채용정보</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="5" t="n"/>
+      <c r="I85" s="5" t="n"/>
+      <c r="J85" s="5" t="n"/>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1705&amp;page=1</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="n"/>
+      <c r="M85" s="5" t="n"/>
+      <c r="N85" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="O85" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>전일제강사 채용 공고(보건)</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>김해중학교</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>전일제 강사(5일) 모집합니다.</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="5" t="n"/>
+      <c r="I86" s="5" t="n"/>
+      <c r="J86" s="5" t="n"/>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814827</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O86" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>[용원국민체육센터]생활체육 도급강사 공개경쟁모집 공고</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>창원시설공단 채용정보</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>경남 창원시</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1705&amp;page=1</t>
-        </is>
-      </c>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
-      <c r="N62" s="5" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>결원대체강사(전일제강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>이북초등학교</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>2학년 담임교사
+전화 먼저 주셔요   [전화번호]</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="5" t="n"/>
+      <c r="I87" s="5" t="n"/>
+      <c r="J87" s="5" t="n"/>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814885</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="n"/>
+      <c r="M87" s="5" t="n"/>
+      <c r="N87" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O62" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>전일제강사 채용 공고(보건)</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>김해중학교</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="O87" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 수시채용 공고</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>전일제 강사(5일) 모집합니다.</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="n"/>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814827</t>
-        </is>
-      </c>
-      <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>2026. 학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고
+자세한 내용은 첨부파일을 참고하시기바랍니다.</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="5" t="n"/>
+      <c r="I88" s="5" t="n"/>
+      <c r="J88" s="5" t="n"/>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814877</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="O88" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>창덕중학교 전일제강사 또는 시간강사(과학) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>창덕중학교</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.19.(월)~10.21.(수) / 08:30~16:30</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>■ 채용과목: 과학(전일제강사 또는 시간강사 중 택일가능)
+■ 채용기간: 2026.10.19.(월)~10.21.(수)
+- 전일제강사 1일 단가(110,000원)
+- 시간강사 1시간당(29,000원)
+■ 수업시수(교과 시간표 변경은 안됨)
+- 10.19(월): 1, 3, 4, 6교시(4)
+- 10.20(화): 1, 4, 6, 7교시(4)
+- 10.21(수): 2, 3, 5, 6교시(4)
+■ 근무시간: 08:30~16:30
+■ 담임 및 업무: 없음
+■ 채용연령: 만 62세까지
+■ 선착순 전화 상담후 채용
+※ 채용을 희망하시는 선생님께서는 교무실 [전화번호]로 연락주세요.
+감사합니다.
+[일과운영 시간]
+- 1교시: 8:50~9:35(45')
+- 2교시: 9:45~10:30(45')
+- 3교시: 10:40~11:25(45')
+- 4교시: 11:35~12:20(45')
+&lt;점심&gt; 12:20~13:20(60')
+- 5교시: 13:20~14:05(45')
+- 6교시: 14:15~15:00(45')
+- 7교시: 15:10~15:55(45')</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="5" t="n"/>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814900</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O89" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6264,6 +6264,52 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>함안고 계약제교원 전일제강사 채용 공고(영양)</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>함안고등학교</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>계약제교원 전일제강사 채용 공고(영양)입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="5" t="n"/>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814905</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="n"/>
+      <c r="M90" s="5" t="n"/>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O90" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4794,30 +4794,79 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
+          <t>마산합포스포츠센터 생활체육 프로그램 도급강사 공개경쟁모집 공고</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80365</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
           <t>마산회원체육센터 기간제(초단시간)근로자 공개경쟁 채용공고</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(마산회원체육센터팀)</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1개분야 1명
 2. 접수기간: 10. 19.(월) 09:00 ~ 10. 23.(금) 18:00
@@ -4881,117 +4930,76 @@
 6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 사람</t>
         </is>
       </c>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n">
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5007</t>
         </is>
       </c>
-      <c r="L64" s="5" t="n"/>
-      <c r="M64" s="5" t="n"/>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O64" s="5" t="inlineStr">
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명(전일제 또는 시간제)
 2. 기간: 2026.10.6.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명(전일제 또는 시간제)</t>
         </is>
       </c>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
-      <c r="N65" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O65" s="5" t="inlineStr">
-        <is>
-          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>창녕군장애인체육회 장애인생활체육지도자 채용 공고</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>창녕군</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>경남 창녕군</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="n"/>
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="n"/>
       <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="n"/>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
+        </is>
+      </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="5" t="n"/>
       <c r="N66" s="5" t="inlineStr">
@@ -5001,33 +5009,123 @@
       </c>
       <c r="O66" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>계약제 교원(시간 강사) 채용 공고</t>
+          <t>늘푸른전당 생활체육 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>율하중학교</t>
+          <t>창원시설공단</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 창원시</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E67" s="5" t="n"/>
       <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80367</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>창녕군장애인체육회 장애인생활체육지도자 채용 공고</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>창녕군</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>경남 창녕군</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n"/>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="5" t="n"/>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>계약제 교원(시간 강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>율하중학교</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -5038,55 +5136,55 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L67" s="5" t="n"/>
-      <c r="M67" s="5" t="n"/>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O67" s="5" t="inlineStr">
+      <c r="O69" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>의령군 청년 일경험(인턴) 지원사업 참여기업 모집</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>의령군</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>경남 의령군</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>최소 3개월 이상 / 주 5일, 일 8시간 근무 원칙(주 40시간, 조정 가능)</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>2026년 의령군 청년 일경험(인턴) 지원사업 참여기업 모집 재공고를 [홈페이지]에 게재하고자 합니다.
 1. 사 업 명: 2026년 의령군 청년 일경험(인턴) 지원사업
@@ -5138,51 +5236,51 @@
 다. 제출서류(1~7번 필수, 8~9번 선택)</t>
         </is>
       </c>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="n"/>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="5" t="inlineStr">
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>발급 및 작성요령, 비고, 1, 사업 참여 신청서, 사업자등록증 첨부, (고유번호증), 서식 1호, 2</t>
         </is>
       </c>
-      <c r="K68" s="5" t="n"/>
-      <c r="L68" s="5" t="n"/>
-      <c r="M68" s="5" t="n"/>
-      <c r="N68" s="5" t="inlineStr">
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O68" s="5" t="inlineStr">
+      <c r="O70" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -5234,47 +5332,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="inlineStr">
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O69" s="5" t="inlineStr">
+      <c r="O71" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -5286,51 +5384,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="inlineStr">
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L70" s="5" t="n"/>
-      <c r="M70" s="5" t="n"/>
-      <c r="N70" s="5" t="inlineStr">
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="n"/>
+      <c r="N72" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O70" s="5" t="inlineStr">
+      <c r="O72" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -5347,97 +5445,97 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="5" t="n"/>
+      <c r="K73" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
         </is>
       </c>
-      <c r="L71" s="5" t="n"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="L73" s="5" t="n"/>
+      <c r="M73" s="5" t="n"/>
+      <c r="N73" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O71" s="5" t="inlineStr">
+      <c r="O73" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
 자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="inlineStr">
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="5" t="n"/>
+      <c r="K74" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
         </is>
       </c>
-      <c r="L72" s="5" t="n"/>
-      <c r="M72" s="5" t="n"/>
-      <c r="N72" s="5" t="inlineStr">
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
+      <c r="N74" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O72" s="5" t="inlineStr">
+      <c r="O74" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>함양제일고등학교</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>10.26.(월)-11.11.(수)/ 총58시간</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
 1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
@@ -5446,96 +5544,96 @@
 -자세한 내용은 공고문 참조 바랍니다.</t>
         </is>
       </c>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="5" t="n"/>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="5" t="n"/>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="5" t="n"/>
+      <c r="K75" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
         </is>
       </c>
-      <c r="L73" s="5" t="n"/>
-      <c r="M73" s="5" t="n"/>
-      <c r="N73" s="5" t="inlineStr">
+      <c r="L75" s="5" t="n"/>
+      <c r="M75" s="5" t="n"/>
+      <c r="N75" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O73" s="5" t="inlineStr">
+      <c r="O75" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>마산고등학교</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
         </is>
       </c>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="5" t="n"/>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="inlineStr">
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="5" t="n"/>
+      <c r="I76" s="5" t="n"/>
+      <c r="J76" s="5" t="n"/>
+      <c r="K76" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
-      <c r="L74" s="5" t="n"/>
-      <c r="M74" s="5" t="n"/>
-      <c r="N74" s="5" t="inlineStr">
+      <c r="L76" s="5" t="n"/>
+      <c r="M76" s="5" t="n"/>
+      <c r="N76" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O74" s="5" t="inlineStr">
+      <c r="O76" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>대암초등학교</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -5555,49 +5653,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="n">
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="n"/>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="n"/>
+      <c r="K77" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L75" s="5" t="n"/>
-      <c r="M75" s="5" t="n"/>
-      <c r="N75" s="5" t="inlineStr">
+      <c r="L77" s="5" t="n"/>
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O75" s="5" t="inlineStr">
+      <c r="O77" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -5606,104 +5704,13 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
-      <c r="G76" s="5" t="n"/>
-      <c r="H76" s="5" t="n"/>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="5" t="n"/>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
-        </is>
-      </c>
-      <c r="L76" s="5" t="n"/>
-      <c r="M76" s="5" t="n"/>
-      <c r="N76" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O76" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="n"/>
-      <c r="M77" s="5" t="n"/>
-      <c r="N77" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O77" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 배드민턴 외부강사 채용공고</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>일운초등학교</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="n"/>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
-        </is>
-      </c>
       <c r="G78" s="5" t="n"/>
       <c r="H78" s="5" t="n"/>
       <c r="I78" s="5" t="n"/>
       <c r="J78" s="5" t="n"/>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
         </is>
       </c>
       <c r="L78" s="5" t="n"/>
@@ -5722,12 +5729,12 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>함안고등학교</t>
+          <t>김해생명과학고등학교</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -5739,8 +5746,8 @@
       <c r="E79" s="5" t="n"/>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
-자세한 내용은 첨부파일 확인 바랍니다.</t>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
       <c r="G79" s="5" t="n"/>
@@ -5749,7 +5756,7 @@
       <c r="J79" s="5" t="n"/>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
         </is>
       </c>
       <c r="L79" s="5" t="n"/>
@@ -5768,31 +5775,35 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>일운초등학교</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>경남 고성군</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D80" s="5" t="n"/>
       <c r="E80" s="5" t="n"/>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
       <c r="G80" s="5" t="n"/>
       <c r="H80" s="5" t="n"/>
       <c r="I80" s="5" t="n"/>
       <c r="J80" s="5" t="n"/>
-      <c r="K80" s="5" t="n"/>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
+        </is>
+      </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="5" t="n"/>
       <c r="N80" s="5" t="inlineStr">
@@ -5809,12 +5820,12 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>소토초등학교 한국어교육 강사 채용 공고</t>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>소토초등학교</t>
+          <t>함안고등학교</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -5825,6 +5836,93 @@
       <c r="D81" s="5" t="n"/>
       <c r="E81" s="5" t="n"/>
       <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="5" t="n"/>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="5" t="n"/>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="n"/>
+      <c r="M81" s="5" t="n"/>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O81" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>고성군</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>경남 고성군</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="5" t="n"/>
+      <c r="I82" s="5" t="n"/>
+      <c r="J82" s="5" t="n"/>
+      <c r="K82" s="5" t="n"/>
+      <c r="L82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O82" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>소토초등학교</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -5846,96 +5944,96 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="5" t="n"/>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="5" t="n"/>
-      <c r="K81" s="5" t="inlineStr">
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="5" t="n"/>
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="5" t="n"/>
+      <c r="K83" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L81" s="5" t="n"/>
-      <c r="M81" s="5" t="n"/>
-      <c r="N81" s="5" t="inlineStr">
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O81" s="5" t="inlineStr">
+      <c r="O83" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G82" s="5" t="n"/>
-      <c r="H82" s="5" t="n"/>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="5" t="n"/>
-      <c r="K82" s="5" t="inlineStr">
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="5" t="n"/>
+      <c r="I84" s="5" t="n"/>
+      <c r="J84" s="5" t="n"/>
+      <c r="K84" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
         </is>
       </c>
-      <c r="L82" s="5" t="n"/>
-      <c r="M82" s="5" t="n"/>
-      <c r="N82" s="5" t="inlineStr">
+      <c r="L84" s="5" t="n"/>
+      <c r="M84" s="5" t="n"/>
+      <c r="N84" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O82" s="5" t="inlineStr">
+      <c r="O84" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>진영중앙초 2학기 집중돌봄 특기적성 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>진영중앙초등학교</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D83" s="5" t="n"/>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="inlineStr">
         <is>
           <t>월,수/수,금/월,금 선택가능(주2회, 총 4차시)</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F85" s="5" t="inlineStr">
         <is>
           <t>1. 모집 분야 및 인원
 가. 모집분야: 창의놀이(예: 영어놀이, 음악놀이, 미술놀이, 보드게임, 마술 등)
@@ -5946,101 +6044,15 @@
 3. 문의사항: 돌봄교실 [전화번호](11시~18시)</t>
         </is>
       </c>
-      <c r="G83" s="5" t="n"/>
-      <c r="H83" s="5" t="n">
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="5" t="n"/>
-      <c r="K83" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814812</t>
-        </is>
-      </c>
-      <c r="L83" s="5" t="n"/>
-      <c r="M83" s="5" t="n"/>
-      <c r="N83" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O83" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>돌봄·방과후학교 배드민턴 외부강사 채용공고</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>능포초등학교</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>돌봄·방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="5" t="n"/>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="n"/>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814781</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="n"/>
-      <c r="M84" s="5" t="n"/>
-      <c r="N84" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O84" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>[용원국민체육센터]생활체육 도급강사 공개경쟁모집 공고</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>창원시설공단 채용정보</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>경남 창원시</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="n"/>
-      <c r="E85" s="5" t="n"/>
-      <c r="F85" s="5" t="n"/>
-      <c r="G85" s="5" t="n"/>
-      <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="n"/>
       <c r="J85" s="5" t="n"/>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1705&amp;page=1</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814812</t>
         </is>
       </c>
       <c r="L85" s="5" t="n"/>
@@ -6052,19 +6064,19 @@
       </c>
       <c r="O85" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일, 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>전일제강사 채용 공고(보건)</t>
+          <t>돌봄·방과후학교 배드민턴 외부강사 채용공고</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>김해중학교</t>
+          <t>능포초등학교</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -6076,7 +6088,7 @@
       <c r="E86" s="5" t="n"/>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>전일제 강사(5일) 모집합니다.</t>
+          <t>돌봄·방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
         </is>
       </c>
       <c r="G86" s="5" t="n"/>
@@ -6085,7 +6097,7 @@
       <c r="J86" s="5" t="n"/>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814827</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814781</t>
         </is>
       </c>
       <c r="L86" s="5" t="n"/>
@@ -6104,34 +6116,29 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>결원대체강사(전일제강사) 채용 공고</t>
+          <t>[용원국민체육센터]생활체육 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>이북초등학교</t>
+          <t>창원시설공단 채용정보</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 창원시</t>
         </is>
       </c>
       <c r="D87" s="5" t="n"/>
       <c r="E87" s="5" t="n"/>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>2학년 담임교사
-전화 먼저 주셔요   [전화번호]</t>
-        </is>
-      </c>
+      <c r="F87" s="5" t="n"/>
       <c r="G87" s="5" t="n"/>
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="n"/>
       <c r="J87" s="5" t="n"/>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814885</t>
+          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1705&amp;page=1</t>
         </is>
       </c>
       <c r="L87" s="5" t="n"/>
@@ -6143,19 +6150,19 @@
       </c>
       <c r="O87" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 수시채용 공고</t>
+          <t>전일제강사 채용 공고(보건)</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>마산고등학교</t>
+          <t>김해중학교</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -6167,8 +6174,7 @@
       <c r="E88" s="5" t="n"/>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>2026. 학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고
-자세한 내용은 첨부파일을 참고하시기바랍니다.</t>
+          <t>전일제 강사(5일) 모집합니다.</t>
         </is>
       </c>
       <c r="G88" s="5" t="n"/>
@@ -6177,7 +6183,7 @@
       <c r="J88" s="5" t="n"/>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814877</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814827</t>
         </is>
       </c>
       <c r="L88" s="5" t="n"/>
@@ -6196,26 +6202,118 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
+          <t>결원대체강사(전일제강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>이북초등학교</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>2학년 담임교사
+전화 먼저 주셔요   [전화번호]</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="5" t="n"/>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814885</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O89" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 수시채용 공고</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>2026. 학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고
+자세한 내용은 첨부파일을 참고하시기바랍니다.</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="5" t="n"/>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814877</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="n"/>
+      <c r="M90" s="5" t="n"/>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O90" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
           <t>창덕중학교 전일제강사 또는 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>창덕중학교</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D89" s="5" t="n"/>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="5" t="inlineStr">
         <is>
           <t>2026.10.19.(월)~10.21.(수) / 08:30~16:30</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F91" s="5" t="inlineStr">
         <is>
           <t>■ 채용과목: 과학(전일제강사 또는 시간강사 중 택일가능)
 ■ 채용기간: 2026.10.19.(월)~10.21.(수)
@@ -6242,69 +6340,69 @@
 - 7교시: 15:10~15:55(45')</t>
         </is>
       </c>
-      <c r="G89" s="5" t="n"/>
-      <c r="H89" s="5" t="n"/>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="5" t="n"/>
-      <c r="K89" s="5" t="inlineStr">
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="5" t="n"/>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="5" t="n"/>
+      <c r="K91" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814900</t>
         </is>
       </c>
-      <c r="L89" s="5" t="n"/>
-      <c r="M89" s="5" t="n"/>
-      <c r="N89" s="5" t="inlineStr">
+      <c r="L91" s="5" t="n"/>
+      <c r="M91" s="5" t="n"/>
+      <c r="N91" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O89" s="5" t="inlineStr">
+      <c r="O91" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>함안고 계약제교원 전일제강사 채용 공고(영양)</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>함안고등학교</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D90" s="5" t="n"/>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>계약제교원 전일제강사 채용 공고(영양)입니다.
 자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="5" t="n"/>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n"/>
-      <c r="K90" s="5" t="inlineStr">
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="5" t="n"/>
+      <c r="K92" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814905</t>
         </is>
       </c>
-      <c r="L90" s="5" t="n"/>
-      <c r="M90" s="5" t="n"/>
-      <c r="N90" s="5" t="inlineStr">
+      <c r="L92" s="5" t="n"/>
+      <c r="M92" s="5" t="n"/>
+      <c r="N92" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O90" s="5" t="inlineStr">
+      <c r="O92" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>증산고등학교 결원대체강사(전일제강사/수학) 채용 공고</t>
+          <t>방과후학교 개인위탁 외부강사 쿠키클레이 재모집 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>증산고등학교</t>
+          <t>중부초등학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -645,117 +645,10 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026. 10. 15.(목) ~ 2026. 11. 6.(금) 17일, 110,000/일</t>
+          <t>2026년 11월 1일∼2027년 2월 28일(4개월)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>증산고등학교에서 근무할 결원대체강사(전일제강사/수학) 를 다음과 같이 채용하고자 합니다.
-1. 채용과목: 수학
-2. 채용기간: 2026. 10. 15.(목) ~ 2026. 11. 6.(금) 17일, 110,000/일
-3. 서류접수 및 전형일정
-가. 서류접수
-- 접수기간: 2026년10월7일(수) ∼ 2026년10월13일(화) 12:00 까지
-- 접수방법: 채용 담당자 이메일([이메일])로 온라인 접수
-나. 1차 서류전형 합격자 발표(개별 통지): 2026년10월13일(화) 15:00이후
-다. 2차 면접 및 수업시연(서류심사 합격자에 한함)
-- 면접 일시 및 장소: 2026년10월14일(수)10:00~ (1층 교무실)
-- 일시 및 장소는 서류전형 합격자에게 개별 통보
-4. 최종합격자발표 : 2026년10월14일(수)12:00 이후(합격자 개별 통보)
-* 자세한 사항은 첨부파일 확인 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814809</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>계약제교원(전일제강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>태룡초등학교</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.19.(월)~10.26.(월) (6일간)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 태룡초등학교에 근무할 전일제강사를 다음과 같이 채용 공고합니다.
-1. 채용 구분: 초등교사(1명)
-2.채용 기간: 2026.10.19.(월)~10.26.(월) (6일간)
-3.서류접수기간: 2026.10.12.(월)~10.13.(화) 12:00
-4.서류접수방법: 태룡초 교무실 직접 제출 및 전자우편 (주소: [이메일] ) * 스캔본 제출, 면접 시 원본 제출
-5.기타 문의: 태룡초등학교 교무실([전화번호])</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814876</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 개인위탁 외부강사 쿠키클레이 재모집 공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>중부초등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026년 11월 1일∼2027년 2월 28일(4개월)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>가. 모집 분야: 쿠키클레이 1명
 나. 접수 기간: 2026년 10월 8일(목) ∼ 2026년 10월 13일(화) 14:00까지
@@ -765,49 +658,49 @@
 *자세한 사항 및 필요 제출서류는 첨부파일을 확인하시고 기한내에 제출해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814838</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(시민생활체육관팀)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1명
 2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
@@ -860,49 +753,49 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 공고 제2026-18호
 시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
@@ -953,49 +846,49 @@
 2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>경남 거제시</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -1019,47 +912,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(기술 가정) 채용 공고</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고
 합니다.
@@ -1084,49 +977,49 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>마산중앙중학교 강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>마산중앙중학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2026. 11. 11.(수)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산중앙중학교 강사 채용 공고를 다음과 같이 합니다.
 공고 기간: 2026. 10. 8.(목) ~ 2026. 10. 14.(수) 13:00까지
@@ -1139,49 +1032,49 @@
 * 기타 자세한 사항은 채용공고 첨부파일을 참조 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814851</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>악양초등학교 계약제 교원(결원대체강사)-전일제강사 채용</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>악양초등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026.10.26 ~ 2026.10.30.(총5일)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2026학년도 악양초등학교에 근무할 결원 대체 강사를 다음과 같이 채용 공고 안내
 1. 채용과목 : 초등(전일제강사 1명)
@@ -1200,59 +1093,59 @@
 * 자세한 사항은 붙임 공고문을 참조바랍니다.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>1순위: 만 62세 미만 동일 자격 소지자
 2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
 1순위 지원자 없을 시 2순위자 채용 가능</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재), 자기소개서 1부.(붙임서식), 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814828</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>팔룡중학교 결원대체강사(진로진학상담)채용 공고</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>팔룡중학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 3.~2026. 11. 6.(총 13시간)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>[팔룡중학교 공고 제2026 - 39호]
 팔룡중학교 결원대체강사(진로진학상담 시간강사) 채용 공고
@@ -1273,47 +1166,47 @@
 ※기타 자세한 사항은 첨부파일 확인 및 팔룡중학교 교무실 [전화번호] 문의 바랍니다.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814841</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>용원초등학교 계약제교원(전일제 강사)채용 공고</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>용원초등학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026.10.29.  ~2026.11.25.(20일 간)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목 및 응모 자격
 -채용 구분: 전일제 강사
@@ -1362,55 +1255,55 @@
 ◦ 기타 자세한 사항은 용원초등학교(☎ 552-2730)로 문의하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>.결원교원과 동일 학교급 자격증 소지자(만 62세 미만)
 .결원교원과 다른 학교급 자격증 소지자(만 62세 미만)
 .명예퇴직자,정년퇴직자(동일학교급 자격증소지자)</t>
         </is>
       </c>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814872</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>밀양고 전일제강사(수학) 채용공고 3차</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>밀양고등학교</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 19. ~ 2026. 10. 23.(5일, 17시수)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>밀양고등학교 공고 제2026-36호
 2026학년도 밀양고등학교 전일제 강사 채용 공고
@@ -1429,49 +1322,49 @@
 자세한 사항은 첨부파일을 참고</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814860</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>전일제강사 채용공고(사회)</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>덕산중학교</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 9.(월) ~2026. 11. 23.(월) (11일)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>2026학년도 덕산중학교에 근무할 전일제 강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 사회
@@ -1481,49 +1374,49 @@
 기타사항은 첨부파일 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814821</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>대방중학교 전일제강사(기술·가정과) 채용 공고</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>대방중학교</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026년 11월 9일 ~ 2026년 11월 13일(5일)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>2026학년도 대방중학교 기술·가정과 전일제강사를 다음과 같이 채용 공고(2차)합니다.
 1. 접수기간: 2026년 10월 8일(목) ~ 2026년 10월 14일(수), 09:00까지 도착분에 한함
@@ -1535,47 +1428,47 @@
 기타 자세한 사항은 붙임 문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814661</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>하동고등학교 결원대체강사(국어) 채용 공고</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>하동고등학교</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026.11.09.~2026.11.13.(5일), 2026.12.21.~2026.12.22.(2일)(총 7일)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>2026학년도 하동고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모 자격(결원대체강사;전일제/시간제)
@@ -1598,53 +1491,53 @@
 자세한 내용은 붙임파일을 참고해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>1순위: 채용 과목 중등 자격증 소지자</t>
         </is>
       </c>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814762</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>거창중학교 스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>거창중학교</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 20.(화) ~ 2027. 2. 10.(수)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>거창중학교 학교스포츠클럽 강사 공고
 1. 계약기간 : 2026. 10. 20.(화) ~ 2027. 2. 10.(수)
@@ -1660,47 +1553,47 @@
 자세한 사항은 첨부파일을 참조하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814839</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>10월 삼룡초등학교 계약제교원(전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>삼룡초등학교</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026.10.19.~2026.11.06.(3주간)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>2026학년도 10월 삼룡초등학교 계약제교원(전일제강사) 채용 공고
 1. 인원: 초등 전일제강사 1명(6학년담임)
@@ -1721,49 +1614,49 @@
 3. 기타 - 기타 세부 사항은 첨부물 참고</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814870</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교 지리과 결원대체강사(1순위: 지리, 2순위: 일반사회, 윤리) 채용 3차 공고</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>마산가포고등학교</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>2026.10.26.~2026.10.30.(총16시간)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산가포고등학교에 근무할 결원대체강사를 다음과 같이 채용 공고합니다.
 1. 채용내용 및 응모자격
@@ -1791,49 +1684,49 @@
 5. 자세한 내용은 붙임파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n">
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814899</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>은하수초등학교 결원대체강사(전일제 강사_과학전담_초4) 모집 공고</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>은하수초등학교</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>2026.10.19.-202611.6. *조정 가능</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>2026학년도 2학기 은하수초등학교에 근무할 결원대체강사(전일제 강사_과학전담)를 다음과 같이 채용 공고합니다.
 1. 채용기간: 2026.10.19.-202611.6. *조정 가능
@@ -1852,49 +1745,49 @@
 *기타 자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n">
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814883</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>호암초등학교 계약제교원(특수 전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>호암초등학교</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 23.(월)~2026. 11. 27.(금)(5일)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>호암초등학교에 근무할 특수 전일제강사를 다음과 같이 채용하고자 합니다.
 1. 채용 과목 및 인원: 특수 1명
@@ -1904,49 +1797,49 @@
 5. 자세한 사항은 첨부파일 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n">
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814879</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교 결원대체시간강사(수학) 채용 공고(2차)</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>태봉고등학교</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>2026.11.9.(월)~2026.11.17.(화)(7일간, 주말 제외)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>2026학년도 태봉고등학교 결원대체시간강사(수학) 채용 공고(2차)입니다.
 1. 채용과목 및 인원, 채용기간
@@ -1965,49 +1858,49 @@
 ※ 기타 자세한 내용은 첨부파일을 확인하시거나 태봉고등학교 교무실([전화번호])로 문의바랍니다.</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814861</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>사회과(역사 또는 일반사회 또는 지리) 중등수업지원강사 채용 공고</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>창원상남중학교</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 16.~2026. 12. 31.(2학년 역사수업, 주당 7시간, 월요일 2,3,4교시/목요일 1,2,3,4교시)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원상남중학교에서 근무할 중등수업지원강사를 다음과 같이 채용 공고합니다.
 1. 채용과목(인원): 사회(역사 또는 일반사회 또는 지리)(1명)
@@ -2021,49 +1914,49 @@
 *자세한 사항은 첨부파일을 확인해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814787</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>신문초등학교 초등돌봄교실 특기‧적성 프로그램 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>신문초등학교</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 6.(금) ~ 2027. 2. 26.(금)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>신문초등학교에서는 2026학년도 초등돌봄교실 운영과 관련하여 아래와 같이 특기‧적성 프로그램 외부강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 선정 인원: 초등돌봄교실 특기·적성 프로그램 외부강사 1명
@@ -2076,47 +1969,47 @@
 ※ 자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814822</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2027. 1. ~ 2027. 12.</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>「장유도서관 2027년 평생학습강좌 교육강사 채용」공고를 붙임과 같이 홈페이지에 게시하고자 합니다.
 김해시 제2026-4325호
@@ -2167,19 +2060,119 @@
 미 술(1)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
+      <c r="H23" s="5" t="n">
+        <v>8046</v>
+      </c>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>유목초 특수학급 결원대체강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>유목초등학교</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>구체적인 내용은 공고문을 참고바랍니다.
+1. 분야: 특수학급 결원대체강사
+2. 채용인원: 1명
+3.기간: 2026.10.6.~2026.10.16.</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>8046</v>
+        <v>1</v>
       </c>
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110243&amp;cpage=1&amp;section=05</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
         </is>
       </c>
       <c r="L25" s="5" t="n"/>
@@ -2190,12 +2183,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>유목초 계약제교원(특수학급 결원대체강사) 채용 공고</t>
+          <t>거제 하청초 방과후학교 개인위탁 외부강사 모집-모듬북(풍물)</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>유목초등학교</t>
+          <t>하청초등학교</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2205,115 +2198,15 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2026.10.6.~2026.10.16.</t>
+          <t>2026년 11월 1일∼2026년 12월 18일</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>구체적인 내용은 공고문을 참고바랍니다.
-1. 분야: 특수학급 결원대체강사
-2. 채용인원: 1명
-3.기간: 2026.10.6.~2026.10.16.</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814507</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>유목초 특수학급 결원대체강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>유목초등학교</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.6.~2026.10.16.</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>구체적인 내용은 공고문을 참고바랍니다.
-1. 분야: 특수학급 결원대체강사
-2. 채용인원: 1명
-3.기간: 2026.10.6.~2026.10.16.</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814550</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>거제 하청초 방과후학교 개인위탁 외부강사 모집-모듬북(풍물)</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>하청초등학교</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>2026년 11월 1일∼2026년 12월 18일</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>모집 세부 사항
 가. 공고 기간: 2026년 10월 12일(월) ∼ 2026년 10월 19일(월)
@@ -2330,47 +2223,47 @@
 자세한 사항은 첨부파일 참조.</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814887</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(내서스포츠센터팀)</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 2개분야 3명
 2. 접수기간: 10. 12.(월) 09:00 ~ 10. 19.(월) 18:00
@@ -2436,57 +2329,57 @@
 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>여부</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H27" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>TRX 필라테스</t>
         </is>
       </c>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5003</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>[내서스포츠센터] 프로그램 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>내서스포츠센터팀 공고 제2026-7호
 내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고
@@ -2548,57 +2441,57 @@
 가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>여부</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H28" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>TRX 필라테스</t>
         </is>
       </c>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1704&amp;page=1</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>마산합포스포츠센터 생활체육 프로그램 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(마산합포스포츠센터팀)</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 2개분야 2명
 2. 접수기간: 10. 16.(금) 09:00 ~ 10. 22.(목) 18:00
@@ -2650,53 +2543,53 @@
 11.「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 규정된 죄를 범한 사람으로서 100만원 이상의 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n">
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>합 계</t>
         </is>
       </c>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5006</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>[마산합포스포츠센터] 생활체육 프로그램 도급강사 공개경쟁 모집 공고</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>마산합포스포츠센터 공고 제2026 - 12호
 마산합포스포츠센터 생활체육 프로그램 도급강사 공개경쟁모집 공고
@@ -2749,53 +2642,53 @@
 접수기간</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n">
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>합 계</t>
         </is>
       </c>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1706&amp;page=1</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>웅남중 학교운동부지도자 채용공고(태권도)</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>웅남중학교</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>2026.12.01.(화)~2027.2.28.(일)</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>웅남중학교 운동부 지도자 채용 공고
 - 채용분야: 운동부지도자
@@ -2808,47 +2701,47 @@
 자세한 사항은 붙임 문서를 참고하여 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814764</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>[늘푸른전당] 프로그램 도급강사 공개경쟁 모집 공고</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>늘푸른전당 공고 제2026-10호
 늘푸른전당 생활체육 프로그램 도급강사 공개모집 공고
@@ -2904,100 +2797,100 @@
 전형일정</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n">
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1694&amp;page=1</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>거제 내곡초등학교 결원대체강사(초등 교원) 채용</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>내곡초등학교</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>2026.10.1.~2026.10.23.</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>아래와 같이 결원대체강사 채용을 공고합니다.
 1. 대상: 초등교사 1명
 2. 기간: 2026.10.1.~2026.10.23.</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>초등교사 1명</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814470</t>
         </is>
       </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>김해율하도서관 2027년 율하아카데미 교육강사 채용 공고</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>2027. 2. ~ 2027. 11.(3학기 기준)</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>김해율하도서관 2027년 율하아카데미 교육강사 채용을 위하여 붙임의 고시공고를 홈페이지에 게제하고자 합니다.
 김해시청 제2026-4441호
@@ -3039,53 +2932,53 @@
 미술·체험·놀이(6)</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>모집 분야 수업 내용</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="H34" s="5" t="n">
         <v>6448</v>
       </c>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110418&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>[마산회원체육센터] 기간제(초단시간)근로자 공개경쟁채용 공고(수영강사)</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>창원시설공단 채용정보</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>마산회원체육센터팀 공고 제2026-14호
 기간제(초단시간)근로자 공개경쟁 채용공고
@@ -3144,49 +3037,49 @@
 6의3. 다음 각 목의 어느 하나에 해당하는 죄를 범한 사람으로서 100만원 이상의 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n">
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1707&amp;page=1</t>
         </is>
       </c>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="n"/>
-      <c r="O37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>유영초등학교 결원대체강사 채용 공고(3차)</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>유영초등학교</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~2026.10.30.(19일간)</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 초등 결원대체 강사(전일제)
 2. 채용 인원: 1명
@@ -3194,49 +3087,49 @@
 4. 자세한 사항은 첨부파일 참조</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n">
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814512</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="n"/>
-      <c r="O38" s="5" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>전일제 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>창원천광학교</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.~11. 6.(16일)</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>2026학년도 창원천광학교에서 근무할 중등 전일제 강사를 채용 공고합니다.
 1.채용과목: 중등특수
@@ -3246,49 +3139,49 @@
 기타 자세한 사항은 첨부파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n">
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814884</t>
         </is>
       </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="n"/>
-      <c r="O39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>안의고등학교 역사, 국어과 결원대체강사 채용 공고</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>안의고등학교</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>국어-2026.11.23.(월)~2026.11.27.(금) (5일)</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>안의고등학교 결원대체강사 채용 공고
 2026학년도 안의고등학교에 근무할 결원대체강사(전일제/시간제)를 다음과 같이 채용 공고합니다.
@@ -3336,53 +3229,53 @@
 ◦ 제출서류의 기재 착오, 누락, 서류 미제출, 연락 불능 등으로 인한 불이익은 모두 응시자 책임으로 합니다.</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>1순위: 만 69세 미만 동일 자격 소지자
 2순위: 다른 학교급 또는 유사과목 자격 소지자, 명예퇴직자, 정년퇴직자
 (1순위 지원자가 있을 경우 2순위는 심사 대상에서 제외)</t>
         </is>
       </c>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814832</t>
         </is>
       </c>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="n"/>
-      <c r="O40" s="5" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>남지초등학교 기간제 교원(강사제외) 채용(2차) 공고</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>남지초등학교</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>가. 채용 분야: 초등기간제교원
 나. 채용 기간: 2026. 10. 12. ~ 2026. 11. 23.(기간 연장될 수 있음)
@@ -3395,6 +3288,104 @@
 ※자세한 사항은 공고문 참고</t>
         </is>
       </c>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교 전일제 강사(과학-생명과학 우대) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>2026.11.2.~2026.11.27.(20일)</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>1.과목 및 인원-과학 (생명과학 우대): 1명
+2.채용기간:2026.11.2.~2026.11.27.(20일)
+*비고:임용일에 따라 채용기간변동
+기타 자세한 사항은 첨부파일을 확인하시고 문의사항은 마산고 교무실([전화번호])으로 연락바랍니다.</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814898</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>칠원고등학교</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
+1. 채용과목: 영어(1명)
+2. 채용기간: 2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)
+상세내용은 첨부파일 확인 바랍니다.</t>
+        </is>
+      </c>
       <c r="G41" s="5" t="n"/>
       <c r="H41" s="5" t="n">
         <v>1</v>
@@ -3403,7 +3394,7 @@
       <c r="J41" s="5" t="n"/>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814696</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
         </is>
       </c>
       <c r="L41" s="5" t="n"/>
@@ -3414,12 +3405,12 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>마산고등학교 전일제 강사(과학-생명과학 우대) 채용 공고</t>
+          <t>결원대체강사(시간강사) 채용 2차 재공고(영어)</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>마산고등학교</t>
+          <t>칠원고등학교</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -3429,113 +3420,15 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>2026.11.2.~2026.11.27.(20일)</t>
+          <t>11. 16.~11. 17.(8시간), 11. 23.~12. 11.(주당 15시간)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>1.과목 및 인원-과학 (생명과학 우대): 1명
-2.채용기간:2026.11.2.~2026.11.27.(20일)
-*비고:임용일에 따라 채용기간변동
-기타 자세한 사항은 첨부파일을 확인하시고 문의사항은 마산고 교무실([전화번호])으로 연락바랍니다.</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814898</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="n"/>
-      <c r="O42" s="5" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>칠원고등학교 결원대체강사(시간제:영어) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>칠원고등학교</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 칠원고등학교 결원대체강사(시간제:영어) 채용 공고
-1. 채용과목: 영어(1명)
-2. 채용기간: 2026. 11. 16.~2026. 11. 17.(8시간), 2026. 11.23.~2026. 12. 11.(주당 15시간)
-상세내용은 첨부파일 확인 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814546</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="n"/>
-      <c r="O43" s="5" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>결원대체강사(시간강사) 채용 2차 재공고(영어)</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>칠원고등학교</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>11. 16.~11. 17.(8시간), 11. 23.~12. 11.(주당 15시간)</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>2026학년도 결원대체강사(시간강사) 채용 2차 재공고합니다.
 1. 채용과목: 영어(1명)
@@ -3544,49 +3437,49 @@
 문의 ([전화번호]</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814868</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="n"/>
-      <c r="O44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 평생학습강좌 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>김해시</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>경남 김해시</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>2027. 01. ~ 12. (1년)</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>진영한빛도서관 2027년도 평생학습강좌 강사를 다음과 같이 모집합니다.
 - 모집대상 : 21개 강좌 18명
@@ -3641,15 +3534,15 @@
 수 09:30~11:1014</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>분야</t>
         </is>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="H43" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>공고일 기준 만 20세 이상 (’06. 9. 18. 이전 출생자)
 성별·주소지 제한 없음
@@ -3659,93 +3552,40 @@
 해당 분야 관련 자격증 소지자</t>
         </is>
       </c>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://www.gimhae.go.kr/03360/00023/00031.web?amode=view&amp;not_ancmt_mgt_no=110069&amp;cpage=1&amp;section=05</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="n"/>
-      <c r="O45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>창원여고 전일제강사(보건) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>창원여자고등학교</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>산양초등학교 돌봄교실 특기적성 프로그램 외부강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>산양초등학교</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>2026학년도 창원여고 전일제강사(보건)를 다음과 같이 채용하고자 합니다.
-1. 채용 인원-보건(1명): 2026. 10.14 ~ 2026.10.19.(전일제강사)4일,일당110,000원
-2.접수기간: 2026. 10. 12(월) ~ 2026. 10.13.(화) 11:00까지
-3. 접수방법: 전자우편(주소: [이메일], 2026. 10.13. 11:00 발송분까지)
-*자세한 내용은 채용공고 참고바랍니다.</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814864</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>산양초등학교 돌봄교실 특기적성 프로그램 외부강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>산양초등학교</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>본교 돌봄교실 운영과 관련하여 특기적성 프로그램 개인 위탁 강사님을 모시고자 하오니,  관심있으신 분들의 지원을 바랍니다.
 1. 모집분야: 보드게임 1명
@@ -3754,102 +3594,102 @@
 4. 기타 자세한 사항은 첨부파일 공고문을 참고 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n">
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814814</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>창원시설공단</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80004</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>교원 장기재직 휴가 대체 시간 강사 채용 공고</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>삼천포여자중학교</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>2026 교원 장기재직 휴가 대체 시간 강사 채용 계획을 붙임과 같이 공고합니다.
 1. 채용내용: 장기재직 휴가 데체 시간 강사(과학)
@@ -3861,51 +3701,51 @@
 마. 최종 합격자 발표: 10. 16.(금) 16:00 이후 개별 통보</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814790</t>
         </is>
       </c>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>어방초 방과후학교 개인위탁 외부강사 모집 재공고(컴퓨터)</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>어방초등학교</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>어방초등학교에서는 방과후학교 운영과 관련하여 아래와 같이 방과후학교 프로그램 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 1. 모집 분야 및 인원: 컴퓨터 1명
@@ -3921,53 +3761,53 @@
 ※ 자세한 사항은 붙임 파일을 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n">
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814852</t>
         </is>
       </c>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>천성초(영어저학년)방과후학교 개인위탁 외부강사 재모집 공고</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>천성초등학교</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>천성초등학교에서는 방과후학교 프로그램(영어저학년) 위탁강사를 모집하오니, 관심 있는 분들의 많은 지원 바랍니다.
 &lt;모집분야&gt;  영어저학년(대상학년  : 1~2학년. 요일 : 화, 목)
@@ -3979,51 +3819,51 @@
 ※ 자세한 사항 및 필요 제출서류는 첨부파일을 확인하시고 기한내에 제출해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814875</t>
         </is>
       </c>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>방과후학교 개인위탁 외부강사 모집공고(수학)</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>거제고현중학교</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>★  모집 세부 사항
 가. 공고 기간: 2026.10.7.(수)~2026.10.14.(수)
@@ -4039,51 +3879,51 @@
 다. 방과후학교 개인위탁 외부강사 활동에 제한이 없는 자</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814746</t>
         </is>
       </c>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>진주고등학교 계약제교원(시간제강사-일본어) 채용 공고</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>진주고등학교</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목 및 인원
 시간제강사 - 일본어 1명
@@ -4135,51 +3975,51 @@
 **************** 보다 자세한 사항은 첨부파일을 꼭 확인하여 주시기 바랍니다. ******************</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814820</t>
         </is>
       </c>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O50" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>장애인일자리(복지일자리) 수행기관 모집</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>의령군</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>경남 의령군</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>취업 취약계층인 장애인에게 일자리 제공을 통한 사회참여 확대 및 소득지원을 위하여 장애인일자리사업 수행기관을 공개모집합니다.
 의령군 공고 제2026-1185
@@ -4231,47 +4071,47 @@
 ※ 평일 근무시간(평일 09:00~18:00) 내 직접 방문 접수</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O54" s="5" t="inlineStr">
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>동원고등학교 결원대체강사 채용공고(수학)</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>동원고등학교</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>2026. 동원고등학교 결원대체강사 채용 공고(수학)
 1. 원서접수
@@ -4285,51 +4125,51 @@
 ***자세한 사항은 첨부파일을 확인해 주시기 바랍니다.***</t>
         </is>
       </c>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814733</t>
         </is>
       </c>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>진해신항초등학교 계약제교원(전일제강사) 채용 공고</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>진해신항초등학교</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>2026학년도 진해신항초등학교 계약제교원(전일제강사) 다음과 같이 채용 공고합니다.
 ◆ 채용내용
@@ -4371,51 +4211,51 @@
 ◦ 기타 자세한 사항은 진해신항초등학교(☎551-2018)로 문의하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814873</t>
         </is>
       </c>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교(직업교육 혁신지구 전공심화연구동아리 멘토 교육(전기제어) 외부강사) 모집 공고</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>마산공업고등학교 공고 제2026 – 65호
 2026학년도 마산공업고등학교에 근무할 전공심화연구동아리 멘토 교육(전기제어) 외부 강사 모집을 다음과 같이 공고 합니다.
@@ -4441,53 +4281,53 @@
 * 자세한 사항은 붙임 공고문을 참고바랍니다.</t>
         </is>
       </c>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n">
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814792</t>
         </is>
       </c>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>감계중학교 결원대체강사(시간강사) 채용 공고(과학)</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>감계중학교</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>2026학년도 감계중학교에 근무할 결원대체강사(시간강사)를 다음과 같이 채용 공고합니다.
 1. 채용 인원: 과학 1명
@@ -4499,15 +4339,162 @@
 ※ 그 외 제반 서류는 최종합격 후 제출함.자세한 사항은 첨부파일 참고 바랍니다.</t>
         </is>
       </c>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>계약제 교원(결원대체강사-전일제강사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>대청초등학교</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>계약제 교원(결원대체강사-전일제강사) 담임교사</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814892</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80264</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>김해시도시개발공사 장유스포츠센터팀 배분제 위탁강사(배드민턴) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>김해시도시개발공사</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>경남 김해시</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>1. 배드민턴강습 및 고객 관리</t>
+        </is>
+      </c>
       <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="n"/>
       <c r="J58" s="5" t="n"/>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814663</t>
+          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80275</t>
         </is>
       </c>
       <c r="L58" s="5" t="n"/>
@@ -4519,35 +4506,35 @@
       </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 55) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>계약제 교원(결원대체강사-전일제강사) 채용 공고</t>
+          <t>용원국민체육센터 생활체육 도급강사 모집 공고</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>대청초등학교</t>
+          <t>창원시설공단</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 창원시</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E59" s="5" t="n"/>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>계약제 교원(결원대체강사-전일제강사) 담임교사</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G59" s="5" t="n"/>
@@ -4556,7 +4543,7 @@
       <c r="J59" s="5" t="n"/>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814892</t>
+          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80216</t>
         </is>
       </c>
       <c r="L59" s="5" t="n"/>
@@ -4575,173 +4562,26 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>내서스포츠센터 프로그램 도급강사 공개경쟁모집 공고</t>
+          <t>경상남도 청소년수련원 위탁운영 단체(법인) 모집 공고</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>창원시설공단</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>경남 창원시</t>
+          <t>경남 고성군</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E60" s="5" t="n"/>
       <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80264</t>
-        </is>
-      </c>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>김해시도시개발공사 장유스포츠센터팀 배분제 위탁강사(배드민턴) 모집 공고</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>김해시도시개발공사</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>경남 김해시</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>1. 배드민턴강습 및 고객 관리</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80275</t>
-        </is>
-      </c>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
-      <c r="N61" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O61" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 55) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>용원국민체육센터 생활체육 도급강사 모집 공고</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>창원시설공단</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>경남 창원시</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80216</t>
-        </is>
-      </c>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
-      <c r="N62" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O62" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>경상남도 청소년수련원 위탁운영 단체(법인) 모집 공고</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>고성군</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>경남 고성군</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>경상남도 청소년수련원 재개장을 앞두고 해당 시설의 운영 및 관리를 위한 위탁운영 단체(법인)을  모집하고자 첨부와 같이 공고합니다.
 고성군 공고 제2026-1750호
@@ -4773,100 +4613,100 @@
 &lt; 청소년단체 &gt;</t>
         </is>
       </c>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="n"/>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="n"/>
-      <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="O60" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 · 강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>마산합포스포츠센터 생활체육 프로그램 도급강사 공개경쟁모집 공고</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>창원시설공단</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80365</t>
         </is>
       </c>
-      <c r="L64" s="5" t="n"/>
-      <c r="M64" s="5" t="n"/>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O64" s="5" t="inlineStr">
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>마산회원체육센터 기간제(초단시간)근로자 공개경쟁 채용공고</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>창원시설공단(마산회원체육센터팀)</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>경남 창원시</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 1. ~ 12. 31.</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>1. 모집인원: 1개분야 1명
 2. 접수기간: 10. 19.(월) 09:00 ~ 10. 23.(금) 18:00
@@ -4930,17 +4770,166 @@
 6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 사람</t>
         </is>
       </c>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5007</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>내곡초등학교</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>아래와 같이 결원대체강사 채용을 공고합니다.
+1. 대상: 초등교사 1명(전일제 또는 시간제)
+2. 기간: 2026.10.6.~2026.10.23.</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>초등교사 1명(전일제 또는 시간제)</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
+          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>늘푸른전당 생활체육 프로그램 도급강사 공개모집 공고</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80367</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>창녕군장애인체육회 장애인생활체육지도자 채용 공고</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>창녕군</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>경남 창녕군</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
       <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="H65" s="5" t="n"/>
       <c r="I65" s="5" t="n"/>
       <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=5007</t>
-        </is>
-      </c>
+      <c r="K65" s="5" t="n"/>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="5" t="n"/>
       <c r="N65" s="5" t="inlineStr">
@@ -4950,19 +4939,19 @@
       </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
-          <t>강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>거제 내곡초등학교 결원대체강사(전일제 또는 시간제) 변경 공고</t>
+          <t>계약제 교원(시간 강사) 채용 공고</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>내곡초등학교</t>
+          <t>율하중학교</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -4972,160 +4961,11 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n"/>
       <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>아래와 같이 결원대체강사 채용을 공고합니다.
-1. 대상: 초등교사 1명(전일제 또는 시간제)
-2. 기간: 2026.10.6.~2026.10.23.</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>초등교사 1명(전일제 또는 시간제)</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814602</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
-      <c r="N66" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O66" s="5" t="inlineStr">
-        <is>
-          <t>강사 공고인지 판별 유보(점수 50) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>늘푸른전당 생활체육 프로그램 도급강사 공개모집 공고</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>창원시설공단</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>경남 창원시</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>https://job.cleaneye.go.kr/user/ypCareersData.do?idx=80367</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="n"/>
-      <c r="M67" s="5" t="n"/>
-      <c r="N67" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O67" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>창녕군장애인체육회 장애인생활체육지도자 채용 공고</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>창녕군</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>경남 창녕군</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="n"/>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="n"/>
-      <c r="L68" s="5" t="n"/>
-      <c r="M68" s="5" t="n"/>
-      <c r="N68" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O68" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>계약제 교원(시간 강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>율하중학교</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목: 체육(1), 영어(1)
 2. 서류접수 및 전형방법
@@ -5136,55 +4976,55 @@
 *자세한 내용은 첨부파일 참조(문의사항: [전화번호])</t>
         </is>
       </c>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="inlineStr">
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814488</t>
         </is>
       </c>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O69" s="5" t="inlineStr">
+      <c r="O66" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>의령군 청년 일경험(인턴) 지원사업 참여기업 모집</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>의령군</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>경남 의령군</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>최소 3개월 이상 / 주 5일, 일 8시간 근무 원칙(주 40시간, 조정 가능)</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>2026년 의령군 청년 일경험(인턴) 지원사업 참여기업 모집 재공고를 [홈페이지]에 게재하고자 합니다.
 1. 사 업 명: 2026년 의령군 청년 일경험(인턴) 지원사업
@@ -5236,51 +5076,51 @@
 다. 제출서류(1~7번 필수, 8~9번 선택)</t>
         </is>
       </c>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>발급 및 작성요령, 비고, 1, 사업 참여 신청서, 사업자등록증 첨부, (고유번호증), 서식 1호, 2</t>
         </is>
       </c>
-      <c r="K70" s="5" t="n"/>
-      <c r="L70" s="5" t="n"/>
-      <c r="M70" s="5" t="n"/>
-      <c r="N70" s="5" t="inlineStr">
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O70" s="5" t="inlineStr">
+      <c r="O67" s="5" t="inlineStr">
         <is>
           <t>강사 공고인지 판별 유보(점수 60) — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>웅상고 계약제교원(결원대체 시간강사)3차 수시 채용 공고-물리(과학)</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>웅상고등학교 공고 제2026 – 47 호
 계약제교원(결원대체 시간강사) 3차 수시 채용 공고
@@ -5332,47 +5172,47 @@
 웅상고등학교장</t>
         </is>
       </c>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n"/>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="5" t="n"/>
+      <c r="K68" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814490</t>
         </is>
       </c>
-      <c r="L71" s="5" t="n"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O71" s="5" t="inlineStr">
+      <c r="O68" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>통영시민오케스트라 교육강사(플루트) 모집 공고</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>경남 통영시</t>
         </is>
       </c>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>2026 통영시민오케스트라
 교육강사(플루트)
@@ -5384,51 +5224,51 @@
 재단법인 통영국제음악재단 이사장</t>
         </is>
       </c>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="inlineStr">
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>https://timf.org/kr/sub/timf/notice.asp?mode=view&amp;bid=1&amp;s_type=&amp;s_keyword=&amp;s_cate=&amp;idx=3824&amp;page=1</t>
         </is>
       </c>
-      <c r="L72" s="5" t="n"/>
-      <c r="M72" s="5" t="n"/>
-      <c r="N72" s="5" t="inlineStr">
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O72" s="5" t="inlineStr">
+      <c r="O69" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교 기초학력전담강사 채용 공고</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>주촌초등학교</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>2026.10.12.~ 2026.12.(주당 15시간 미만) 방학제외</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>2026학년도 주촌초등학교에 근무할 기초학력전담강사를 다음과 같이 채용 공고합니다.
 □ 채용 구분 및 인원: 기초학력 전담강사 1명
@@ -5445,13 +5285,157 @@
 □ 전형일정 및 제출서류 : 첨부파일 참고</t>
         </is>
       </c>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="n"/>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O71" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고등학교</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
+1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
+2. 과목: 특수
+3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
+-자세한 내용은 공고문 참조 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="n"/>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O72" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
+        </is>
+      </c>
       <c r="G73" s="5" t="n"/>
       <c r="H73" s="5" t="n"/>
       <c r="I73" s="5" t="n"/>
       <c r="J73" s="5" t="n"/>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814528</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
         </is>
       </c>
       <c r="L73" s="5" t="n"/>
@@ -5463,19 +5447,19 @@
       </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 전일제(보건)강사 채용 공고</t>
+          <t>기초학력전담강사 채용 공고문</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>대암초등학교</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -5484,156 +5468,12 @@
         </is>
       </c>
       <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
+        </is>
+      </c>
       <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건) 채용공고 입니다.
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="5" t="n"/>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814648</t>
-        </is>
-      </c>
-      <c r="L74" s="5" t="n"/>
-      <c r="M74" s="5" t="n"/>
-      <c r="N74" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O74" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>함양제일고 결원대체 시간강사(특수) 채용 2차 공고</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>함양제일고등학교</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>10.26.(월)-11.11.(수)/ 총58시간</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>함양제일고에서 결원대체 시간강사를 채용 공고합니다. 관심있는 분들의 많은 지원 부탁드립니다.
-1. 기간: 10.26.(월)-11.11.(수)/ 총58시간
-2. 과목: 특수
-3. 2차 공고 후에도 지원자 없을 경우 원서접수 마감 기간을 연장합니다.
--자세한 내용은 공고문 참조 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="n"/>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814689</t>
-        </is>
-      </c>
-      <c r="L75" s="5" t="n"/>
-      <c r="M75" s="5" t="n"/>
-      <c r="N75" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O75" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교에서 성실히 학생들을 지도하실 운동부 지도자(야구부 코치) 출산 및 육아휴직 대체자 하실분을 모십니다.</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="n"/>
-      <c r="H76" s="5" t="n"/>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="5" t="n"/>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814734</t>
-        </is>
-      </c>
-      <c r="L76" s="5" t="n"/>
-      <c r="M76" s="5" t="n"/>
-      <c r="N76" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O76" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>기초학력전담강사 채용 공고문</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>대암초등학교</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>2026년 10월 13일~ 2027년 1월(14주 내외, 주당 14시간 이내 근무)</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
         <is>
           <t>2026년 대암초등학교 기초학력 전담강사 채용 공고문
 □ 모집 인원 : 1명
@@ -5653,49 +5493,49 @@
 * 자세한 사항은 붙임문서를 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="5" t="n">
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="5" t="inlineStr">
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="5" t="n"/>
+      <c r="K74" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814613</t>
         </is>
       </c>
-      <c r="L77" s="5" t="n"/>
-      <c r="M77" s="5" t="n"/>
-      <c r="N77" s="5" t="inlineStr">
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
+      <c r="N74" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O77" s="5" t="inlineStr">
+      <c r="O74" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교 학교스포츠강사 채용 공고</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>진주여자중학교</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D78" s="5" t="n"/>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>1. 종목: 축구 1명
 2. 심사일정 및 시험장소
@@ -5704,13 +5544,150 @@
 3. 최종합격자 발표 및 장소 : 2026.10.6.(화) 14:00 이후, 최종합격자에 한해 개별 통보함</t>
         </is>
       </c>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="5" t="n"/>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="5" t="n"/>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="n"/>
+      <c r="M75" s="5" t="n"/>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O75" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
+자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="5" t="n"/>
+      <c r="I76" s="5" t="n"/>
+      <c r="J76" s="5" t="n"/>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="n"/>
+      <c r="M76" s="5" t="n"/>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O76" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>일운초등학교</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="5" t="n"/>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="n"/>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="n"/>
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O77" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>함안고등학교</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
+자세한 내용은 첨부파일 확인 바랍니다.</t>
+        </is>
+      </c>
       <c r="G78" s="5" t="n"/>
       <c r="H78" s="5" t="n"/>
       <c r="I78" s="5" t="n"/>
       <c r="J78" s="5" t="n"/>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814694</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
         </is>
       </c>
       <c r="L78" s="5" t="n"/>
@@ -5729,36 +5706,31 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사-보건)교원 채용 공고</t>
+          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 고성군</t>
         </is>
       </c>
       <c r="D79" s="5" t="n"/>
       <c r="E79" s="5" t="n"/>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>김해생명과학고등학교 계약직(전일제강사)교원 채용 공고
-자세한 내용은 첨부파일을 참고하여 주시기 바랍니다.</t>
+          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
         </is>
       </c>
       <c r="G79" s="5" t="n"/>
       <c r="H79" s="5" t="n"/>
       <c r="I79" s="5" t="n"/>
       <c r="J79" s="5" t="n"/>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814714</t>
-        </is>
-      </c>
+      <c r="K79" s="5" t="n"/>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="5" t="n"/>
       <c r="N79" s="5" t="inlineStr">
@@ -5775,12 +5747,12 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 배드민턴 외부강사 채용공고</t>
+          <t>소토초등학교 한국어교육 강사 채용 공고</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>일운초등학교</t>
+          <t>소토초등학교</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -5791,138 +5763,6 @@
       <c r="D80" s="5" t="n"/>
       <c r="E80" s="5" t="n"/>
       <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="n"/>
-      <c r="H80" s="5" t="n"/>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="5" t="n"/>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814645</t>
-        </is>
-      </c>
-      <c r="L80" s="5" t="n"/>
-      <c r="M80" s="5" t="n"/>
-      <c r="N80" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O80" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>함안고등학교</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="n"/>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>함안고 계약제교원 시간강사(생물) 채용 3차 공고입니다.
-자세한 내용은 첨부파일 확인 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="5" t="n"/>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="5" t="n"/>
-      <c r="K81" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814502</t>
-        </is>
-      </c>
-      <c r="L81" s="5" t="n"/>
-      <c r="M81" s="5" t="n"/>
-      <c r="N81" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O81" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>고성군 역량강화사업 완료지구 활성화 프로그램(3차) 운영강사 ...</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>고성군</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>경남 고성군</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>2026년도 일반농산어촌개발사업 완료지구 활성화 프로그램 운영 강사를 다음과 같이 모집하오니 많은 응시 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="n"/>
-      <c r="H82" s="5" t="n"/>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="5" t="n"/>
-      <c r="K82" s="5" t="n"/>
-      <c r="L82" s="5" t="n"/>
-      <c r="M82" s="5" t="n"/>
-      <c r="N82" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O82" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교 한국어교육 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>소토초등학교</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="n"/>
-      <c r="E83" s="5" t="n"/>
-      <c r="F83" s="5" t="inlineStr">
         <is>
           <t>1. 채용 구분
 1) 구분 및 인원: 한국어 교육 강사 1명
@@ -5944,96 +5784,96 @@
 3. 기타 자세한 사항은 첨부된 공고문 참고</t>
         </is>
       </c>
-      <c r="G83" s="5" t="n"/>
-      <c r="H83" s="5" t="n"/>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="5" t="n"/>
-      <c r="K83" s="5" t="inlineStr">
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814643</t>
         </is>
       </c>
-      <c r="L83" s="5" t="n"/>
-      <c r="M83" s="5" t="n"/>
-      <c r="N83" s="5" t="inlineStr">
+      <c r="L80" s="5" t="n"/>
+      <c r="M80" s="5" t="n"/>
+      <c r="N80" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O83" s="5" t="inlineStr">
+      <c r="O80" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교 방과후 교내강좌(맞춤형4) 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="inlineStr">
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="inlineStr">
         <is>
           <t>경남혜림학교(공립특수학교)에서는 2026학년도 방과후 교내강좌 운영과 관련하여 붙임과 같이 프로그램 개인위탁 외부강사를 모집하오니, 관심 있는 분들의 지원 바랍니다.</t>
         </is>
       </c>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="5" t="n"/>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="n"/>
-      <c r="K84" s="5" t="inlineStr">
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="5" t="n"/>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="5" t="n"/>
+      <c r="K81" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814767</t>
         </is>
       </c>
-      <c r="L84" s="5" t="n"/>
-      <c r="M84" s="5" t="n"/>
-      <c r="N84" s="5" t="inlineStr">
+      <c r="L81" s="5" t="n"/>
+      <c r="M81" s="5" t="n"/>
+      <c r="N81" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O84" s="5" t="inlineStr">
+      <c r="O81" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>진영중앙초 2학기 집중돌봄 특기적성 프로그램 개인위탁 외부강사 모집 공고</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>진영중앙초등학교</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D85" s="5" t="n"/>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>월,수/수,금/월,금 선택가능(주2회, 총 4차시)</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
         <is>
           <t>1. 모집 분야 및 인원
 가. 모집분야: 창의놀이(예: 영어놀이, 음악놀이, 미술놀이, 보드게임, 마술 등)
@@ -6044,15 +5884,146 @@
 3. 문의사항: 돌봄교실 [전화번호](11시~18시)</t>
         </is>
       </c>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I82" s="5" t="n"/>
+      <c r="J82" s="5" t="n"/>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814812</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O82" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>돌봄·방과후학교 배드민턴 외부강사 채용공고</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>능포초등학교</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>돌봄·방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="5" t="n"/>
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="5" t="n"/>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814781</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O83" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>[용원국민체육센터]생활체육 도급강사 공개경쟁모집 공고</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>창원시설공단 채용정보</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="5" t="n"/>
+      <c r="I84" s="5" t="n"/>
+      <c r="J84" s="5" t="n"/>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1705&amp;page=1</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="n"/>
+      <c r="M84" s="5" t="n"/>
+      <c r="N84" s="5" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="O84" s="5" t="inlineStr">
+        <is>
+          <t>빈 필수 칸: 마감일, 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>전일제강사 채용 공고(보건)</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>김해중학교</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>전일제 강사(5일) 모집합니다.</t>
+        </is>
+      </c>
       <c r="G85" s="5" t="n"/>
-      <c r="H85" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="n"/>
       <c r="J85" s="5" t="n"/>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814812</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814827</t>
         </is>
       </c>
       <c r="L85" s="5" t="n"/>
@@ -6064,19 +6035,19 @@
       </c>
       <c r="O85" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>돌봄·방과후학교 배드민턴 외부강사 채용공고</t>
+          <t>결원대체강사(전일제강사) 채용 공고</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>능포초등학교</t>
+          <t>이북초등학교</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -6088,7 +6059,8 @@
       <c r="E86" s="5" t="n"/>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>돌봄·방과후학교 배드민턴 외부강사 모집합니다. 붙임 참조하여 많은 지원 바랍니다.</t>
+          <t>2학년 담임교사
+전화 먼저 주셔요   [전화번호]</t>
         </is>
       </c>
       <c r="G86" s="5" t="n"/>
@@ -6097,7 +6069,7 @@
       <c r="J86" s="5" t="n"/>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814781</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814885</t>
         </is>
       </c>
       <c r="L86" s="5" t="n"/>
@@ -6116,29 +6088,34 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>[용원국민체육센터]생활체육 도급강사 공개경쟁모집 공고</t>
+          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 수시채용 공고</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>창원시설공단 채용정보</t>
+          <t>마산고등학교</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>경남 창원시</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D87" s="5" t="n"/>
       <c r="E87" s="5" t="n"/>
-      <c r="F87" s="5" t="n"/>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>2026. 학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고
+자세한 내용은 첨부파일을 참고하시기바랍니다.</t>
+        </is>
+      </c>
       <c r="G87" s="5" t="n"/>
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="n"/>
       <c r="J87" s="5" t="n"/>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1705&amp;page=1</t>
+          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814877</t>
         </is>
       </c>
       <c r="L87" s="5" t="n"/>
@@ -6150,19 +6127,19 @@
       </c>
       <c r="O87" s="5" t="inlineStr">
         <is>
-          <t>빈 필수 칸: 마감일, 수업 일정, 상세 내용 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
+          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>전일제강사 채용 공고(보건)</t>
+          <t>창덕중학교 전일제강사 또는 시간강사(과학) 채용 공고</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>김해중학교</t>
+          <t>창덕중학교</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -6171,149 +6148,12 @@
         </is>
       </c>
       <c r="D88" s="5" t="n"/>
-      <c r="E88" s="5" t="n"/>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>2026.10.19.(월)~10.21.(수) / 08:30~16:30</t>
+        </is>
+      </c>
       <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>전일제 강사(5일) 모집합니다.</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="n"/>
-      <c r="H88" s="5" t="n"/>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="5" t="n"/>
-      <c r="K88" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814827</t>
-        </is>
-      </c>
-      <c r="L88" s="5" t="n"/>
-      <c r="M88" s="5" t="n"/>
-      <c r="N88" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O88" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>결원대체강사(전일제강사) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>이북초등학교</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="n"/>
-      <c r="E89" s="5" t="n"/>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>2학년 담임교사
-전화 먼저 주셔요   [전화번호]</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="n"/>
-      <c r="H89" s="5" t="n"/>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="5" t="n"/>
-      <c r="K89" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814885</t>
-        </is>
-      </c>
-      <c r="L89" s="5" t="n"/>
-      <c r="M89" s="5" t="n"/>
-      <c r="N89" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O89" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 수시채용 공고</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>마산고등학교</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="n"/>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>2026. 학교운동부 야구부 지도자-코치(출산휴가 및 육아휴직 대체자) 모집공고
-자세한 내용은 첨부파일을 참고하시기바랍니다.</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="5" t="n"/>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n"/>
-      <c r="K90" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814877</t>
-        </is>
-      </c>
-      <c r="L90" s="5" t="n"/>
-      <c r="M90" s="5" t="n"/>
-      <c r="N90" s="5" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="O90" s="5" t="inlineStr">
-        <is>
-          <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>창덕중학교 전일제강사 또는 시간강사(과학) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>창덕중학교</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="n"/>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>2026.10.19.(월)~10.21.(수) / 08:30~16:30</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
         <is>
           <t>■ 채용과목: 과학(전일제강사 또는 시간강사 중 택일가능)
 ■ 채용기간: 2026.10.19.(월)~10.21.(수)
@@ -6340,69 +6180,69 @@
 - 7교시: 15:10~15:55(45')</t>
         </is>
       </c>
-      <c r="G91" s="5" t="n"/>
-      <c r="H91" s="5" t="n"/>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="5" t="n"/>
-      <c r="K91" s="5" t="inlineStr">
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="5" t="n"/>
+      <c r="I88" s="5" t="n"/>
+      <c r="J88" s="5" t="n"/>
+      <c r="K88" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814900</t>
         </is>
       </c>
-      <c r="L91" s="5" t="n"/>
-      <c r="M91" s="5" t="n"/>
-      <c r="N91" s="5" t="inlineStr">
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O91" s="5" t="inlineStr">
+      <c r="O88" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>함안고 계약제교원 전일제강사 채용 공고(영양)</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>함안고등학교</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D92" s="5" t="n"/>
-      <c r="E92" s="5" t="n"/>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="inlineStr">
         <is>
           <t>계약제교원 전일제강사 채용 공고(영양)입니다.
 자세한 내용은 첨부파일 확인 바랍니다.</t>
         </is>
       </c>
-      <c r="G92" s="5" t="n"/>
-      <c r="H92" s="5" t="n"/>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="5" t="n"/>
-      <c r="K92" s="5" t="inlineStr">
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="5" t="n"/>
+      <c r="K89" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814905</t>
         </is>
       </c>
-      <c r="L92" s="5" t="n"/>
-      <c r="M92" s="5" t="n"/>
-      <c r="N92" s="5" t="inlineStr">
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="O92" s="5" t="inlineStr">
+      <c r="O89" s="5" t="inlineStr">
         <is>
           <t>빈 필수 칸: 마감일, 수업 일정 — 원문을 확인해 채운 뒤 '보류'를 지우세요</t>
         </is>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -625,270 +625,30 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>방과후학교 개인위탁 외부강사 쿠키클레이 재모집 공고</t>
+          <t>지세포중학교 시간강사(과학) 채용 공고</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>중부초등학교</t>
+          <t>지세포중학교</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경남 거제시</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2026년 11월 1일∼2027년 2월 28일(4개월)</t>
+          <t>2026. 11. 02.~2026. 11. 27.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>가. 모집 분야: 쿠키클레이 1명
-나. 접수 기간: 2026년 10월 8일(목) ∼ 2026년 10월 13일(화) 14:00까지
-다. 1차 제안서 평가: 1차 제안서 평가 통과자에 한하여 개별 통보
-라. 2차 프로그램 운영 능력평가: 2026년 10월 15일 16:00, 2층 회의실
-마. 계약 기간: 2026년 11월 1일∼2027년 2월 28일(4개월)
-*자세한 사항 및 필요 제출서류는 첨부파일을 확인하시고 기한내에 제출해 주시기 바랍니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814838</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>시민생활체육관 탁구 프로그램 도급강사 공개모집 공고</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>창원시설공단(시민생활체육관팀)</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>경남 창원시</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>1. 모집인원: 1명
-2. 접수기간: 10. 6.(화) 09:00 ~ 10. 13.(화) 18:00
-3. 접수방법: 방문접수(※ 우편접수 불가, 토ᆞ일요일 및 공휴일 접수 불가)
-4. 접 수 처
-- 시민생활체육관 1층 사무실(종합안내실 옆)
-5. 문 의 처 : [전화번호]
-※ 자세한 내용과 제출서류는 붙임 문서 참고 바랍니다.
-시민생활체육관 공고 제2026-18호
-시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
-시민생활체육관 프로그램 운영을 위한 우수 강사진을 공개 모집하오니
-많은 참여 바랍니다.
-2026년 9월 30일
-창원시설공단 시민생활체육관팀장Ⅰ
-모집인원 : 1명
-프로그램 : 탁구종 목모집인원
-강 습 일
-운 영 시 간배분율
-(공단:강사)
-자 격 요 건탁 구1명월~일
-09:00~22:00
-20 : 80
-‣ 전문·생활스포츠(탁구 2급)이상 소지자 또는 전국대회이상 3위 이상 입상자(해당 종목 지도 경력 6개월 이상인 자
-※ 탁구: 보조강사 1명 이상 필수 / 보조강사 자격증 필수
-※ 탁구 강습반: 월·수·금 11개반, 화·목 11개반, 토(월 4회) 2개반Ⅱ
-기본(공통)자격
-만 18세 이상인 자로서 응시자격을 충족하는 자
-해당 종목 관련 자격증 소지자 중 해당 경력 6개월 이상인 자
-아동·청소년의 성 보호에 관한 법률에 의거 성범죄의 해당자는 선발할 수 없음
-도급강사 운영계약 지침 제12조 결격사유에 해당하지 않는 자
-제12조(결격사유) 다음 각 호의 어느 하나에 해당하는 자는 도급강사로 계약할 수 없다.
-1. 피성년후견인
-2. 파산선고를 받은 자로서 복권되지 아니한 자
-3. 금고 이상의 형을 선고받고 그 집행이 끝나거나 집행을 받지 아니하기로 확정된 후 5년이 지나지
-아니한 자
-4. 금고 이상의 형을 선고받고 그 집행유예기간이 끝난 날부터 2년이 지나지 아니한 자
-5. 금고 이상의 형의 선고유예를 선고받고 그 선고유예기간 중에 있는 자
-6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 자
-7. 징계로 파면처분을 받은 날부터 5년이 지나지 아니한 자
-8. 징계로 해임처분을 받은 날부터 3년이 지나지 아니한 자
-9. 부패방지 및 국민권익위원회의 설치와 운영에 관한 법률 제82조에 따른 비위면직자 등의
-취업제한 적용을 받는 자
-10. 재직기간 중 직무와 관련하여 「형법」 제355조 및 제356조에 규정된 죄를 범한 사람
-으로서 300만원 이상의 벌금형을 선고받고 그 형이 확정된 후 2년이 지나지 아니한 사람
-11. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 규정된 죄를 범한 사람으로서 100만
-원 이상의 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람
-12. 미성년자에 대한 다음 각 목의 어느 하나에 해당하는 죄를 저질러 파면ㆍ해임되거나 형 또는 치료감
-호를 선고받아 그 형 또는 치료감호가 확정된 사람(집행유예를 선고받은 후 그 집행유예기간이 경과한
-사람을 포함한다)
-가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10440.web?amode=view&amp;idx=4987</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>(시민생활체육관) 탁구 도급강사 모집공고</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>창원시설공단 채용정보</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>경남 창원시</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026. 11. 1. ~ 12. 31.(2개월)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>시민생활체육관 공고 제2026-18호
-시민생활체육관 탁구 프로그램 도급강사 공개모집 공고
-시민생활체육관 프로그램 운영을 위한 우수 강사진을 공개 모집하오니
-많은 참여 바랍니다.
-2026년 9월 30일
-창원시설공단 시민생활체육관팀장Ⅰ
-모집인원 : 1명
-프로그램 : 탁구종 목모집인원
-강 습 일
-운 영 시 간배분율
-(공단:강사)
-자 격 요 건탁 구1명월~일
-09:00~22:00
-20 : 80
-‣ 전문·생활스포츠(탁구 2급)이상 소지자 또는 전국대회이상 3위 이상 입상자(해당 종목 지도 경력 6개월 이상인 자
-※ 탁구: 보조강사 1명 이상 필수 / 보조강사 자격증 필수
-※ 탁구 강습반: 월·수·금 11개반, 화·목 11개반, 토(월 4회) 2개반Ⅱ
-기본(공통)자격
-만 18세 이상인 자로서 응시자격을 충족하는 자
-해당 종목 관련 자격증 소지자 중 해당 경력 6개월 이상인 자
-아동·청소년의 성 보호에 관한 법률에 의거 성범죄의 해당자는 선발할 수 없음
-도급강사 운영계약 지침 제12조 결격사유에 해당하지 않는 자
-제12조(결격사유) 다음 각 호의 어느 하나에 해당하는 자는 도급강사로 계약할 수 없다.
-1. 피성년후견인
-2. 파산선고를 받은 자로서 복권되지 아니한 자
-3. 금고 이상의 형을 선고받고 그 집행이 끝나거나 집행을 받지 아니하기로 확정된 후 5년이 지나지
-아니한 자
-4. 금고 이상의 형을 선고받고 그 집행유예기간이 끝난 날부터 2년이 지나지 아니한 자
-5. 금고 이상의 형의 선고유예를 선고받고 그 선고유예기간 중에 있는 자
-6. 법원의 판결 또는 다른 법률에 따라 자격이 상실되거나 정지된 자
-7. 징계로 파면처분을 받은 날부터 5년이 지나지 아니한 자
-8. 징계로 해임처분을 받은 날부터 3년이 지나지 아니한 자
-9. 부패방지 및 국민권익위원회의 설치와 운영에 관한 법률 제82조에 따른 비위면직자 등의
-취업제한 적용을 받는 자
-10. 재직기간 중 직무와 관련하여 「형법」 제355조 및 제356조에 규정된 죄를 범한 사람
-으로서 300만원 이상의 벌금형을 선고받고 그 형이 확정된 후 2년이 지나지 아니한 사람
-11. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 규정된 죄를 범한 사람으로서 100만
-원 이상의 벌금형을 선고받고 그 형이 확정된 후 3년이 지나지 아니한 사람
-12. 미성년자에 대한 다음 각 목의 어느 하나에 해당하는 죄를 저질러 파면ㆍ해임되거나 형 또는 치료감
-호를 선고받아 그 형 또는 치료감호가 확정된 사람(집행유예를 선고받은 후 그 집행유예기간이 경과한
-사람을 포함한다)
-가. 「성폭력범죄의 처벌 등에 관한 특례법」 제2조에 따른 성폭력범죄
-나. 「아동ㆍ청소년의 성보호에 관한 법률」 제2조제2호에 따른 아동ㆍ청소년대상 성범죄Ⅲ
-전형일정 및 방법
-계약기간: 2026. 11. 1. ~ 12. 31.(2개월)
-※ 1. 공사 및 휴장 등으로 인해 프로그램 운영이 어려울 시 계약기간이 변경될 수 있음
-2. 강사료 지급: 매월 등록한 자의 총 강습료 수입금 중 환불금을 제외하고 창원시가</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.cwsisul.or.kr/bbs/board.php?bo_table=sub06_04_04&amp;wr_id=1689&amp;page=1</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>지세포중학교 시간강사(과학) 채용 공고</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>지세포중학교</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>경남 거제시</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2026. 11. 02.~2026. 11. 27.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고합니다.
 1. 채용과목: 과학(1)
@@ -912,47 +672,47 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814597</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>지세포중학교 시간강사(기술 가정) 채용 공고</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>지세포중학교</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2026.11.27.(금)~2026.12.24.(목) (수업일 기준 20일간)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>2026학년도 지세포중학교에 근무할 시간강사를 다음과 같이 채용 공고
 합니다.
@@ -977,49 +737,49 @@
 ◦ 최종합격자 발표 : 2026.10.16.(금)  16:00 이후, 개별통보(전화)</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814641</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>마산중앙중학교 강사(과학) 채용 공고</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>마산중앙중학교</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 16.(금) ~ 2026. 11. 11.(수)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026학년도 마산중앙중학교 강사 채용 공고를 다음과 같이 합니다.
 공고 기간: 2026. 10. 8.(목) ~ 2026. 10. 14.(수) 13:00까지
@@ -1032,49 +792,49 @@
 * 기타 자세한 사항은 채용공고 첨부파일을 참조 하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814851</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>악양초등학교 계약제 교원(결원대체강사)-전일제강사 채용</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>악양초등학교</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026.10.26 ~ 2026.10.30.(총5일)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026학년도 악양초등학교에 근무할 결원 대체 강사를 다음과 같이 채용 공고 안내
 1. 채용과목 : 초등(전일제강사 1명)
@@ -1093,59 +853,59 @@
 * 자세한 사항은 붙임 공고문을 참조바랍니다.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>1순위: 만 62세 미만 동일 자격 소지자
 2순위: 만62세의 미만의 다른 학교급 또는 유사과목 자격 소지자, 정년·명예퇴직자
 1순위 지원자 없을 시 2순위자 채용 가능</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>응시원서 1부.(붙임서식, 사진첨부, 연락 가능한 전화번호 반드시 기재), 자기소개서 1부.(붙임서식), 계약제교원 채용을 위한 개인정보 수집ㆍ이용 동의서 1부(붙임 서식)</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814828</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>팔룡중학교 결원대체강사(진로진학상담)채용 공고</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>팔룡중학교</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 3.~2026. 11. 6.(총 13시간)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>[팔룡중학교 공고 제2026 - 39호]
 팔룡중학교 결원대체강사(진로진학상담 시간강사) 채용 공고
@@ -1166,47 +926,47 @@
 ※기타 자세한 사항은 첨부파일 확인 및 팔룡중학교 교무실 [전화번호] 문의 바랍니다.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814841</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>용원초등학교 계약제교원(전일제 강사)채용 공고</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>용원초등학교</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026.10.29.  ~2026.11.25.(20일 간)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. 채용과목 및 응모 자격
 -채용 구분: 전일제 강사
@@ -1255,55 +1015,55 @@
 ◦ 기타 자세한 사항은 용원초등학교(☎ 552-2730)로 문의하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>.결원교원과 동일 학교급 자격증 소지자(만 62세 미만)
 .결원교원과 다른 학교급 자격증 소지자(만 62세 미만)
 .명예퇴직자,정년퇴직자(동일학교급 자격증소지자)</t>
         </is>
       </c>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814872</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>밀양고 전일제강사(수학) 채용공고 3차</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>밀양고등학교</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026. 10. 19. ~ 2026. 10. 23.(5일, 17시수)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>밀양고등학교 공고 제2026-36호
 2026학년도 밀양고등학교 전일제 강사 채용 공고
@@ -1322,49 +1082,49 @@
 자세한 사항은 첨부파일을 참고</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.gne.go.kr/works/user/recruitment/BD_recruitmentDetail.do?regSn=1814860</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>전일제강사 채용공고(사회)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>덕산중학교</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>경남</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026. 11. 9.(월) ~2026. 11. 23.(월) (11일)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineSt